--- a/data/Table-Data-Base.xlsx
+++ b/data/Table-Data-Base.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inaki\Downloads\Pleistocene_Human_Use_Of_Caves-master\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7528D02E-3B84-46AB-9BF9-7DD79731FE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63D0BAE-EB41-400D-B058-4D6840BC5C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{493D11CC-922E-4265-992F-96F2D38DEEBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Caves" sheetId="2" r:id="rId1"/>
-    <sheet name="Datings" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="Datings" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Caves!$A$1:$Y$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datings!$A$1:$K$1035</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Caves!$A$1:$Y$503</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Datings!$A$1:$K$1035</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17385" uniqueCount="3781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17424" uniqueCount="3796">
   <si>
     <t>San Antonio</t>
   </si>
@@ -13137,6 +13138,51 @@
   </si>
   <si>
     <t>Sala del Fascio</t>
+  </si>
+  <si>
+    <t>Simanya</t>
+  </si>
+  <si>
+    <t>IMG</t>
+  </si>
+  <si>
+    <t>wkt_geom</t>
+  </si>
+  <si>
+    <t>fid</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Point</t>
+  </si>
+  <si>
+    <t>2.00913030110195123</t>
+  </si>
+  <si>
+    <t>41.67416292120139332</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>C14 AMS; Lithic Typology</t>
+  </si>
+  <si>
+    <t>Morales et al., 2023</t>
+  </si>
+  <si>
+    <t>M. Salas-Altès (pers. Comm.)</t>
+  </si>
+  <si>
+    <t>West Gallery</t>
+  </si>
+  <si>
+    <t>VIII-IX ?</t>
+  </si>
+  <si>
+    <t>Salas-Altès et al., 2024</t>
   </si>
 </sst>
 </file>
@@ -13305,7 +13351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13463,6 +13509,19 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13797,7 +13856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CDA5EAF-A655-4519-9C43-6E6BE0DBE4DA}">
-  <dimension ref="A1:Y501"/>
+  <dimension ref="A1:Y503"/>
   <sheetFormatPr defaultColWidth="35.77734375" defaultRowHeight="17.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45" style="4" bestFit="1" customWidth="1"/>
@@ -40866,7 +40925,9 @@
       <c r="D430" s="6" t="s">
         <v>3778</v>
       </c>
-      <c r="E430" s="6"/>
+      <c r="E430" s="6" t="s">
+        <v>3789</v>
+      </c>
       <c r="F430" s="7" t="s">
         <v>725</v>
       </c>
@@ -42709,148 +42770,150 @@
       <c r="X459" s="3"/>
       <c r="Y459" s="3"/>
     </row>
-    <row r="460" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B460" s="12" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C460" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D460" s="11" t="s">
-        <v>430</v>
-      </c>
-      <c r="E460" s="8">
-        <v>795</v>
-      </c>
-      <c r="F460" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="G460" s="8" t="s">
+    <row r="460" spans="1:25" s="56" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A460" s="53" t="s">
+        <v>3781</v>
+      </c>
+      <c r="B460" s="53" t="s">
+        <v>3782</v>
+      </c>
+      <c r="C460" s="53" t="s">
+        <v>3787</v>
+      </c>
+      <c r="D460" s="53" t="s">
+        <v>3788</v>
+      </c>
+      <c r="E460" s="53">
+        <v>885</v>
+      </c>
+      <c r="F460" s="53" t="s">
+        <v>651</v>
+      </c>
+      <c r="G460" s="53" t="s">
         <v>663</v>
       </c>
-      <c r="H460" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="I460" s="8" t="s">
-        <v>1319</v>
-      </c>
-      <c r="J460" s="12" t="s">
-        <v>1191</v>
-      </c>
-      <c r="K460" s="8">
-        <v>60</v>
-      </c>
-      <c r="L460" s="8" t="s">
+      <c r="H460" s="54" t="s">
+        <v>3790</v>
+      </c>
+      <c r="I460" s="54" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J460" s="54" t="s">
+        <v>3791</v>
+      </c>
+      <c r="K460" s="53">
+        <v>70</v>
+      </c>
+      <c r="L460" s="53" t="s">
         <v>1377</v>
       </c>
-      <c r="M460" s="8" t="s">
+      <c r="M460" s="53" t="s">
+        <v>1238</v>
+      </c>
+      <c r="N460" s="55" t="s">
+        <v>1252</v>
+      </c>
+      <c r="O460" s="54" t="s">
+        <v>3792</v>
+      </c>
+      <c r="P460" s="53"/>
+      <c r="Q460" s="53"/>
+      <c r="R460" s="53"/>
+      <c r="S460" s="53" t="s">
+        <v>675</v>
+      </c>
+      <c r="T460" s="53" t="s">
+        <v>675</v>
+      </c>
+      <c r="U460" s="53"/>
+      <c r="V460" s="53" t="s">
+        <v>675</v>
+      </c>
+      <c r="W460" s="53"/>
+      <c r="X460" s="53" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y460" s="53" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="461" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A461" s="3" t="s">
+        <v>3781</v>
+      </c>
+      <c r="B461" s="3" t="s">
+        <v>3793</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>3787</v>
+      </c>
+      <c r="D461" s="3" t="s">
+        <v>3788</v>
+      </c>
+      <c r="E461" s="3">
+        <v>885</v>
+      </c>
+      <c r="F461" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="G461" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="H461" s="8" t="s">
+        <v>3790</v>
+      </c>
+      <c r="I461" s="8" t="s">
+        <v>3794</v>
+      </c>
+      <c r="J461" s="8" t="s">
+        <v>3795</v>
+      </c>
+      <c r="K461" s="3">
+        <v>20</v>
+      </c>
+      <c r="L461" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M461" s="3" t="s">
         <v>1236</v>
       </c>
-      <c r="N460" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O460" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P460" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q460" s="8"/>
-      <c r="R460" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="S460" s="8"/>
-      <c r="T460" s="8"/>
-      <c r="U460" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="V460" s="8"/>
-      <c r="W460" s="8"/>
-      <c r="X460" s="8"/>
-      <c r="Y460" s="8"/>
-    </row>
-    <row r="461" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A461" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B461" s="12" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C461" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="D461" s="8" t="s">
-        <v>549</v>
-      </c>
-      <c r="E461" s="8">
-        <v>185</v>
-      </c>
-      <c r="F461" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="G461" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="H461" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="I461" s="8" t="s">
-        <v>1314</v>
-      </c>
-      <c r="J461" s="8" t="s">
-        <v>1192</v>
-      </c>
-      <c r="K461" s="8">
-        <v>40</v>
-      </c>
-      <c r="L461" s="8" t="s">
-        <v>1376</v>
-      </c>
-      <c r="M461" s="8" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N461" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O461" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P461" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q461" s="8"/>
-      <c r="R461" s="8"/>
-      <c r="S461" s="8"/>
-      <c r="T461" s="8"/>
-      <c r="U461" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="V461" s="8"/>
-      <c r="W461" s="8"/>
-      <c r="X461" s="8"/>
-      <c r="Y461" s="8"/>
+      <c r="N461" s="29" t="s">
+        <v>727</v>
+      </c>
+      <c r="O461" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P461" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="Q461" s="3"/>
+      <c r="R461" s="3"/>
+      <c r="S461" s="3"/>
+      <c r="T461" s="3"/>
+      <c r="U461" s="3"/>
+      <c r="V461" s="3"/>
+      <c r="W461" s="3"/>
+      <c r="X461" s="3"/>
+      <c r="Y461" s="3"/>
     </row>
     <row r="462" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="8" t="s">
-        <v>1539</v>
-      </c>
-      <c r="B462" s="8" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C462" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D462" s="8" t="s">
-        <v>552</v>
+        <v>22</v>
+      </c>
+      <c r="B462" s="12" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C462" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D462" s="11" t="s">
+        <v>430</v>
       </c>
       <c r="E462" s="8">
-        <v>209</v>
+        <v>795</v>
       </c>
       <c r="F462" s="8" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G462" s="8" t="s">
         <v>663</v>
@@ -42859,13 +42922,13 @@
         <v>853</v>
       </c>
       <c r="I462" s="8" t="s">
-        <v>1522</v>
-      </c>
-      <c r="J462" s="8" t="s">
-        <v>1154</v>
+        <v>1319</v>
+      </c>
+      <c r="J462" s="12" t="s">
+        <v>1191</v>
       </c>
       <c r="K462" s="8">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L462" s="8" t="s">
         <v>1377</v>
@@ -42876,96 +42939,102 @@
       <c r="N462" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="O462" s="25" t="s">
+      <c r="O462" s="12" t="s">
         <v>727</v>
       </c>
       <c r="P462" s="8" t="s">
         <v>675</v>
       </c>
       <c r="Q462" s="8"/>
-      <c r="R462" s="8"/>
+      <c r="R462" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="S462" s="8"/>
       <c r="T462" s="8"/>
-      <c r="U462" s="8"/>
+      <c r="U462" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="V462" s="8"/>
       <c r="W462" s="8"/>
       <c r="X462" s="8"/>
       <c r="Y462" s="8"/>
     </row>
     <row r="463" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A463" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B463" s="14" t="s">
+      <c r="A463" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B463" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="C463" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D463" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="E463" s="10">
-        <v>219</v>
-      </c>
-      <c r="F463" s="10" t="s">
+      <c r="C463" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D463" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="E463" s="8">
+        <v>185</v>
+      </c>
+      <c r="F463" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="G463" s="10" t="s">
+      <c r="G463" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="H463" s="10" t="s">
-        <v>878</v>
-      </c>
-      <c r="I463" s="10" t="s">
-        <v>1472</v>
-      </c>
-      <c r="J463" s="10" t="s">
-        <v>1154</v>
-      </c>
-      <c r="K463" s="10">
-        <v>130</v>
-      </c>
-      <c r="L463" s="10" t="s">
-        <v>1379</v>
-      </c>
-      <c r="M463" s="10" t="s">
-        <v>1238</v>
-      </c>
-      <c r="N463" s="27" t="s">
-        <v>1537</v>
-      </c>
-      <c r="O463" s="27" t="s">
-        <v>727</v>
-      </c>
-      <c r="P463" s="10" t="s">
-        <v>676</v>
-      </c>
-      <c r="Q463" s="10"/>
-      <c r="R463" s="10"/>
-      <c r="S463" s="10"/>
-      <c r="T463" s="10"/>
-      <c r="U463" s="10"/>
-      <c r="V463" s="10"/>
-      <c r="W463" s="10"/>
-      <c r="X463" s="10"/>
-      <c r="Y463" s="10"/>
+      <c r="H463" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="I463" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J463" s="8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="K463" s="8">
+        <v>40</v>
+      </c>
+      <c r="L463" s="8" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M463" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N463" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O463" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P463" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q463" s="8"/>
+      <c r="R463" s="8"/>
+      <c r="S463" s="8"/>
+      <c r="T463" s="8"/>
+      <c r="U463" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="V463" s="8"/>
+      <c r="W463" s="8"/>
+      <c r="X463" s="8"/>
+      <c r="Y463" s="8"/>
     </row>
     <row r="464" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B464" s="12" t="s">
-        <v>1357</v>
+        <v>1539</v>
+      </c>
+      <c r="B464" s="8" t="s">
+        <v>1346</v>
       </c>
       <c r="C464" s="8" t="s">
-        <v>161</v>
+        <v>300</v>
       </c>
       <c r="D464" s="8" t="s">
-        <v>413</v>
+        <v>552</v>
       </c>
       <c r="E464" s="8">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F464" s="8" t="s">
         <v>651</v>
@@ -42974,25 +43043,25 @@
         <v>663</v>
       </c>
       <c r="H464" s="8" t="s">
-        <v>878</v>
+        <v>853</v>
       </c>
       <c r="I464" s="8" t="s">
-        <v>3313</v>
+        <v>1522</v>
       </c>
       <c r="J464" s="8" t="s">
         <v>1154</v>
       </c>
       <c r="K464" s="8">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L464" s="8" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="M464" s="8" t="s">
         <v>1236</v>
       </c>
       <c r="N464" s="25" t="s">
-        <v>1537</v>
+        <v>727</v>
       </c>
       <c r="O464" s="25" t="s">
         <v>727</v>
@@ -43007,59 +43076,57 @@
       <c r="U464" s="8"/>
       <c r="V464" s="8"/>
       <c r="W464" s="8"/>
-      <c r="X464" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="X464" s="8"/>
       <c r="Y464" s="8"/>
     </row>
     <row r="465" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="10" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="B465" s="14" t="s">
         <v>1357</v>
       </c>
       <c r="C465" s="10" t="s">
-        <v>326</v>
+        <v>161</v>
       </c>
       <c r="D465" s="10" t="s">
-        <v>578</v>
+        <v>413</v>
       </c>
       <c r="E465" s="10">
-        <v>126</v>
+        <v>219</v>
       </c>
       <c r="F465" s="10" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G465" s="10" t="s">
         <v>663</v>
       </c>
       <c r="H465" s="10" t="s">
-        <v>853</v>
+        <v>878</v>
       </c>
       <c r="I465" s="10" t="s">
-        <v>1314</v>
+        <v>1472</v>
       </c>
       <c r="J465" s="10" t="s">
-        <v>1050</v>
+        <v>1154</v>
       </c>
       <c r="K465" s="10">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="L465" s="10" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="M465" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N465" s="26" t="s">
-        <v>1367</v>
-      </c>
-      <c r="O465" s="26" t="s">
+      <c r="N465" s="27" t="s">
+        <v>1537</v>
+      </c>
+      <c r="O465" s="27" t="s">
         <v>727</v>
       </c>
       <c r="P465" s="10" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Q465" s="10"/>
       <c r="R465" s="10"/>
@@ -43069,25 +43136,23 @@
       <c r="V465" s="10"/>
       <c r="W465" s="10"/>
       <c r="X465" s="10"/>
-      <c r="Y465" s="10" t="s">
-        <v>675</v>
-      </c>
+      <c r="Y465" s="10"/>
     </row>
     <row r="466" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B466" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B466" s="12" t="s">
         <v>1357</v>
       </c>
       <c r="C466" s="8" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D466" s="8" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="E466" s="8">
-        <v>70</v>
+        <v>219</v>
       </c>
       <c r="F466" s="8" t="s">
         <v>651</v>
@@ -43096,143 +43161,135 @@
         <v>663</v>
       </c>
       <c r="H466" s="8" t="s">
-        <v>1193</v>
+        <v>878</v>
       </c>
       <c r="I466" s="8" t="s">
-        <v>1318</v>
+        <v>3313</v>
       </c>
       <c r="J466" s="8" t="s">
-        <v>1194</v>
+        <v>1154</v>
       </c>
       <c r="K466" s="8">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="L466" s="8" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="M466" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="N466" s="24" t="s">
-        <v>1195</v>
-      </c>
-      <c r="O466" s="24" t="s">
+      <c r="N466" s="25" t="s">
+        <v>1537</v>
+      </c>
+      <c r="O466" s="25" t="s">
         <v>727</v>
       </c>
       <c r="P466" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="Q466" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="Q466" s="8"/>
       <c r="R466" s="8"/>
-      <c r="S466" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="T466" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="U466" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="S466" s="8"/>
+      <c r="T466" s="8"/>
+      <c r="U466" s="8"/>
       <c r="V466" s="8"/>
       <c r="W466" s="8"/>
-      <c r="X466" s="8"/>
+      <c r="X466" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="Y466" s="8"/>
     </row>
     <row r="467" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A467" s="8" t="s">
-        <v>3723</v>
-      </c>
-      <c r="B467" s="8" t="s">
-        <v>3724</v>
-      </c>
-      <c r="C467" s="11" t="s">
-        <v>3725</v>
-      </c>
-      <c r="D467" s="11" t="s">
-        <v>3726</v>
-      </c>
-      <c r="E467" s="8">
-        <v>10</v>
-      </c>
-      <c r="F467" s="8" t="s">
-        <v>3614</v>
-      </c>
-      <c r="G467" s="8" t="s">
-        <v>3615</v>
-      </c>
-      <c r="H467" s="8" t="s">
-        <v>3727</v>
-      </c>
-      <c r="I467" s="8" t="s">
-        <v>3313</v>
-      </c>
-      <c r="J467" s="8" t="s">
-        <v>3718</v>
-      </c>
-      <c r="K467" s="8">
-        <v>130</v>
-      </c>
-      <c r="L467" s="8" t="s">
+      <c r="A467" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B467" s="14" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C467" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D467" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="E467" s="10">
+        <v>126</v>
+      </c>
+      <c r="F467" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="G467" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="H467" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="I467" s="10" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J467" s="10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K467" s="10">
+        <v>20</v>
+      </c>
+      <c r="L467" s="10" t="s">
         <v>1377</v>
       </c>
-      <c r="M467" s="8" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N467" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O467" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="P467" s="8"/>
-      <c r="Q467" s="8"/>
-      <c r="R467" s="8"/>
-      <c r="S467" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="T467" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="U467" s="8"/>
-      <c r="V467" s="8"/>
-      <c r="W467" s="8"/>
-      <c r="X467" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y467" s="8"/>
+      <c r="M467" s="10" t="s">
+        <v>1238</v>
+      </c>
+      <c r="N467" s="26" t="s">
+        <v>1367</v>
+      </c>
+      <c r="O467" s="26" t="s">
+        <v>727</v>
+      </c>
+      <c r="P467" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q467" s="10"/>
+      <c r="R467" s="10"/>
+      <c r="S467" s="10"/>
+      <c r="T467" s="10"/>
+      <c r="U467" s="10"/>
+      <c r="V467" s="10"/>
+      <c r="W467" s="10"/>
+      <c r="X467" s="10"/>
+      <c r="Y467" s="10" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="468" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="8" t="s">
-        <v>1341</v>
+        <v>5</v>
       </c>
       <c r="B468" s="8" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C468" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D468" s="11" t="s">
-        <v>431</v>
+        <v>1357</v>
+      </c>
+      <c r="C468" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D468" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="E468" s="8">
-        <v>512</v>
+        <v>70</v>
       </c>
       <c r="F468" s="8" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G468" s="8" t="s">
         <v>663</v>
       </c>
       <c r="H468" s="8" t="s">
-        <v>801</v>
+        <v>1193</v>
       </c>
       <c r="I468" s="8" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="J468" s="8" t="s">
-        <v>1142</v>
+        <v>1194</v>
       </c>
       <c r="K468" s="8">
         <v>20</v>
@@ -43244,15 +43301,17 @@
         <v>1236</v>
       </c>
       <c r="N468" s="24" t="s">
-        <v>1538</v>
+        <v>1195</v>
       </c>
       <c r="O468" s="24" t="s">
-        <v>1342</v>
+        <v>727</v>
       </c>
       <c r="P468" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="Q468" s="8"/>
+        <v>675</v>
+      </c>
+      <c r="Q468" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="R468" s="8"/>
       <c r="S468" s="8" t="s">
         <v>675</v>
@@ -43260,47 +43319,47 @@
       <c r="T468" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="U468" s="8"/>
+      <c r="U468" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="V468" s="8"/>
       <c r="W468" s="8"/>
       <c r="X468" s="8"/>
-      <c r="Y468" s="8" t="s">
-        <v>676</v>
-      </c>
+      <c r="Y468" s="8"/>
     </row>
     <row r="469" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="8" t="s">
-        <v>1341</v>
+        <v>3723</v>
       </c>
       <c r="B469" s="8" t="s">
-        <v>1346</v>
+        <v>3724</v>
       </c>
       <c r="C469" s="11" t="s">
-        <v>179</v>
+        <v>3725</v>
       </c>
       <c r="D469" s="11" t="s">
-        <v>431</v>
+        <v>3726</v>
       </c>
       <c r="E469" s="8">
-        <v>512</v>
+        <v>10</v>
       </c>
       <c r="F469" s="8" t="s">
-        <v>655</v>
+        <v>3614</v>
       </c>
       <c r="G469" s="8" t="s">
-        <v>663</v>
+        <v>3615</v>
       </c>
       <c r="H469" s="8" t="s">
-        <v>853</v>
+        <v>3727</v>
       </c>
       <c r="I469" s="8" t="s">
-        <v>1319</v>
+        <v>3313</v>
       </c>
       <c r="J469" s="8" t="s">
-        <v>1343</v>
+        <v>3718</v>
       </c>
       <c r="K469" s="8">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="L469" s="8" t="s">
         <v>1377</v>
@@ -43311,12 +43370,10 @@
       <c r="N469" s="24" t="s">
         <v>727</v>
       </c>
-      <c r="O469" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P469" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="O469" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="P469" s="8"/>
       <c r="Q469" s="8"/>
       <c r="R469" s="8"/>
       <c r="S469" s="8" t="s">
@@ -43328,88 +43385,94 @@
       <c r="U469" s="8"/>
       <c r="V469" s="8"/>
       <c r="W469" s="8"/>
-      <c r="X469" s="8"/>
-      <c r="Y469" s="8" t="s">
+      <c r="X469" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y469" s="8"/>
+    </row>
+    <row r="470" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A470" s="8" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B470" s="8" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C470" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D470" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="E470" s="8">
+        <v>512</v>
+      </c>
+      <c r="F470" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="G470" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H470" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="I470" s="8" t="s">
+        <v>1313</v>
+      </c>
+      <c r="J470" s="8" t="s">
+        <v>1142</v>
+      </c>
+      <c r="K470" s="8">
+        <v>20</v>
+      </c>
+      <c r="L470" s="8" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M470" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N470" s="24" t="s">
+        <v>1538</v>
+      </c>
+      <c r="O470" s="24" t="s">
+        <v>1342</v>
+      </c>
+      <c r="P470" s="8" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="470" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A470" s="12" t="s">
-        <v>687</v>
-      </c>
-      <c r="B470" s="12" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C470" s="13" t="s">
-        <v>688</v>
-      </c>
-      <c r="D470" s="13" t="s">
-        <v>689</v>
-      </c>
-      <c r="E470" s="12">
-        <v>49</v>
-      </c>
-      <c r="F470" s="12" t="s">
-        <v>651</v>
-      </c>
-      <c r="G470" s="12" t="s">
-        <v>663</v>
-      </c>
-      <c r="H470" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="I470" s="12" t="s">
-        <v>1536</v>
-      </c>
-      <c r="J470" s="12" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K470" s="12">
-        <v>70</v>
-      </c>
-      <c r="L470" s="12" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M470" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N470" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O470" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P470" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q470" s="12"/>
-      <c r="R470" s="12"/>
-      <c r="S470" s="12"/>
-      <c r="T470" s="12"/>
-      <c r="U470" s="12"/>
-      <c r="V470" s="12"/>
-      <c r="W470" s="12"/>
-      <c r="X470" s="12"/>
-      <c r="Y470" s="12"/>
+      <c r="Q470" s="8"/>
+      <c r="R470" s="8"/>
+      <c r="S470" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="T470" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U470" s="8"/>
+      <c r="V470" s="8"/>
+      <c r="W470" s="8"/>
+      <c r="X470" s="8"/>
+      <c r="Y470" s="8" t="s">
+        <v>676</v>
+      </c>
     </row>
     <row r="471" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="8" t="s">
-        <v>139</v>
+        <v>1341</v>
       </c>
       <c r="B471" s="8" t="s">
-        <v>1541</v>
+        <v>1346</v>
       </c>
       <c r="C471" s="11" t="s">
-        <v>390</v>
+        <v>179</v>
       </c>
       <c r="D471" s="11" t="s">
-        <v>642</v>
+        <v>431</v>
       </c>
       <c r="E471" s="8">
-        <v>47</v>
+        <v>512</v>
       </c>
       <c r="F471" s="8" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G471" s="8" t="s">
         <v>663</v>
@@ -43417,23 +43480,23 @@
       <c r="H471" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="I471" s="12" t="s">
-        <v>1536</v>
+      <c r="I471" s="8" t="s">
+        <v>1319</v>
       </c>
       <c r="J471" s="8" t="s">
-        <v>1188</v>
+        <v>1343</v>
       </c>
       <c r="K471" s="8">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="L471" s="8" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="M471" s="8" t="s">
         <v>1236</v>
       </c>
       <c r="N471" s="24" t="s">
-        <v>1196</v>
+        <v>727</v>
       </c>
       <c r="O471" s="8" t="s">
         <v>727</v>
@@ -43443,216 +43506,218 @@
       </c>
       <c r="Q471" s="8"/>
       <c r="R471" s="8"/>
-      <c r="S471" s="8"/>
+      <c r="S471" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="T471" s="8" t="s">
         <v>675</v>
       </c>
       <c r="U471" s="8"/>
       <c r="V471" s="8"/>
-      <c r="W471" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="X471" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y471" s="8"/>
+      <c r="W471" s="8"/>
+      <c r="X471" s="8"/>
+      <c r="Y471" s="8" t="s">
+        <v>676</v>
+      </c>
     </row>
     <row r="472" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="10" t="s">
+      <c r="A472" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="B472" s="12" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C472" s="13" t="s">
+        <v>688</v>
+      </c>
+      <c r="D472" s="13" t="s">
+        <v>689</v>
+      </c>
+      <c r="E472" s="12">
+        <v>49</v>
+      </c>
+      <c r="F472" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="G472" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="H472" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="I472" s="12" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J472" s="12" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K472" s="12">
+        <v>70</v>
+      </c>
+      <c r="L472" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M472" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N472" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O472" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P472" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q472" s="12"/>
+      <c r="R472" s="12"/>
+      <c r="S472" s="12"/>
+      <c r="T472" s="12"/>
+      <c r="U472" s="12"/>
+      <c r="V472" s="12"/>
+      <c r="W472" s="12"/>
+      <c r="X472" s="12"/>
+      <c r="Y472" s="12"/>
+    </row>
+    <row r="473" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A473" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B473" s="8" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C473" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="D473" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="E473" s="8">
+        <v>47</v>
+      </c>
+      <c r="F473" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="G473" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H473" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="I473" s="12" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J473" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="K473" s="8">
+        <v>120</v>
+      </c>
+      <c r="L473" s="8" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M473" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N473" s="24" t="s">
+        <v>1196</v>
+      </c>
+      <c r="O473" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P473" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q473" s="8"/>
+      <c r="R473" s="8"/>
+      <c r="S473" s="8"/>
+      <c r="T473" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U473" s="8"/>
+      <c r="V473" s="8"/>
+      <c r="W473" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="X473" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y473" s="8"/>
+    </row>
+    <row r="474" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A474" s="10" t="s">
         <v>1456</v>
       </c>
-      <c r="B472" s="10" t="s">
+      <c r="B474" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="C472" s="9" t="s">
+      <c r="C474" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D472" s="9" t="s">
+      <c r="D474" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="E472" s="10">
+      <c r="E474" s="10">
         <v>320</v>
       </c>
-      <c r="F472" s="10" t="s">
+      <c r="F474" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="G472" s="10" t="s">
+      <c r="G474" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H472" s="10" t="s">
+      <c r="H474" s="10" t="s">
         <v>1082</v>
       </c>
-      <c r="I472" s="10" t="s">
+      <c r="I474" s="10" t="s">
         <v>1439</v>
       </c>
-      <c r="J472" s="10" t="s">
+      <c r="J474" s="10" t="s">
         <v>1083</v>
       </c>
-      <c r="K472" s="10">
+      <c r="K474" s="10">
         <v>20</v>
       </c>
-      <c r="L472" s="10" t="s">
+      <c r="L474" s="10" t="s">
         <v>1377</v>
       </c>
-      <c r="M472" s="10" t="s">
+      <c r="M474" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N472" s="26" t="s">
+      <c r="N474" s="26" t="s">
         <v>1084</v>
       </c>
-      <c r="O472" s="10" t="s">
+      <c r="O474" s="10" t="s">
         <v>1085</v>
       </c>
-      <c r="P472" s="10" t="s">
+      <c r="P474" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="Q472" s="10"/>
-      <c r="R472" s="10"/>
-      <c r="S472" s="10"/>
-      <c r="T472" s="10"/>
-      <c r="U472" s="10"/>
-      <c r="V472" s="10"/>
-      <c r="W472" s="10"/>
-      <c r="X472" s="10"/>
-      <c r="Y472" s="10"/>
-    </row>
-    <row r="473" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A473" s="12" t="s">
-        <v>704</v>
-      </c>
-      <c r="B473" s="12" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C473" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="D473" s="13" t="s">
-        <v>601</v>
-      </c>
-      <c r="E473" s="12">
-        <v>165</v>
-      </c>
-      <c r="F473" s="12" t="s">
-        <v>655</v>
-      </c>
-      <c r="G473" s="12" t="s">
-        <v>663</v>
-      </c>
-      <c r="H473" s="12" t="s">
-        <v>878</v>
-      </c>
-      <c r="I473" s="12" t="s">
-        <v>1323</v>
-      </c>
-      <c r="J473" s="12" t="s">
-        <v>1003</v>
-      </c>
-      <c r="K473" s="12">
-        <v>30</v>
-      </c>
-      <c r="L473" s="12" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M473" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N473" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O473" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P473" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q473" s="12"/>
-      <c r="R473" s="12"/>
-      <c r="S473" s="12"/>
-      <c r="T473" s="12"/>
-      <c r="U473" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="V473" s="12"/>
-      <c r="W473" s="12"/>
-      <c r="X473" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y473" s="12"/>
-    </row>
-    <row r="474" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A474" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B474" s="12" t="s">
-        <v>1542</v>
-      </c>
-      <c r="C474" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D474" s="12" t="s">
-        <v>434</v>
-      </c>
-      <c r="E474" s="12">
-        <v>530</v>
-      </c>
-      <c r="F474" s="12" t="s">
-        <v>655</v>
-      </c>
-      <c r="G474" s="12" t="s">
-        <v>663</v>
-      </c>
-      <c r="H474" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="I474" s="12" t="s">
-        <v>1322</v>
-      </c>
-      <c r="J474" s="12" t="s">
-        <v>1018</v>
-      </c>
-      <c r="K474" s="12">
-        <v>120</v>
-      </c>
-      <c r="L474" s="12" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M474" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N474" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O474" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P474" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q474" s="12"/>
-      <c r="R474" s="12"/>
-      <c r="S474" s="12"/>
-      <c r="T474" s="12"/>
-      <c r="U474" s="12"/>
-      <c r="V474" s="12"/>
-      <c r="W474" s="12"/>
-      <c r="X474" s="12"/>
-      <c r="Y474" s="12"/>
+      <c r="Q474" s="10"/>
+      <c r="R474" s="10"/>
+      <c r="S474" s="10"/>
+      <c r="T474" s="10"/>
+      <c r="U474" s="10"/>
+      <c r="V474" s="10"/>
+      <c r="W474" s="10"/>
+      <c r="X474" s="10"/>
+      <c r="Y474" s="10"/>
     </row>
     <row r="475" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="12" t="s">
-        <v>24</v>
+        <v>704</v>
       </c>
       <c r="B475" s="12" t="s">
-        <v>1543</v>
-      </c>
-      <c r="C475" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D475" s="12" t="s">
-        <v>434</v>
+        <v>1357</v>
+      </c>
+      <c r="C475" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="D475" s="13" t="s">
+        <v>601</v>
       </c>
       <c r="E475" s="12">
-        <v>530</v>
+        <v>165</v>
       </c>
       <c r="F475" s="12" t="s">
         <v>655</v>
@@ -43661,16 +43726,16 @@
         <v>663</v>
       </c>
       <c r="H475" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="I475" s="8" t="s">
-        <v>1319</v>
+        <v>878</v>
+      </c>
+      <c r="I475" s="12" t="s">
+        <v>1323</v>
       </c>
       <c r="J475" s="12" t="s">
-        <v>1018</v>
+        <v>1003</v>
       </c>
       <c r="K475" s="12">
-        <v>170</v>
+        <v>30</v>
       </c>
       <c r="L475" s="12" t="s">
         <v>1377</v>
@@ -43691,42 +43756,46 @@
       <c r="R475" s="12"/>
       <c r="S475" s="12"/>
       <c r="T475" s="12"/>
-      <c r="U475" s="12"/>
+      <c r="U475" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="V475" s="12"/>
       <c r="W475" s="12"/>
-      <c r="X475" s="12"/>
+      <c r="X475" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="Y475" s="12"/>
     </row>
     <row r="476" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="12" t="s">
-        <v>3258</v>
+        <v>24</v>
       </c>
       <c r="B476" s="12" t="s">
-        <v>1545</v>
-      </c>
-      <c r="C476" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D476" s="13" t="s">
-        <v>395</v>
+        <v>1542</v>
+      </c>
+      <c r="C476" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D476" s="12" t="s">
+        <v>434</v>
       </c>
       <c r="E476" s="12">
-        <v>45</v>
+        <v>530</v>
       </c>
       <c r="F476" s="12" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G476" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H476" s="8" t="s">
-        <v>1132</v>
+      <c r="H476" s="12" t="s">
+        <v>853</v>
       </c>
       <c r="I476" s="12" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="J476" s="12" t="s">
-        <v>1197</v>
+        <v>1018</v>
       </c>
       <c r="K476" s="12">
         <v>120</v>
@@ -43740,70 +43809,58 @@
       <c r="N476" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="O476" s="25" t="s">
+      <c r="O476" s="12" t="s">
         <v>727</v>
       </c>
       <c r="P476" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="Q476" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="R476" s="12" t="s">
-        <v>676</v>
-      </c>
-      <c r="S476" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="T476" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="U476" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="Q476" s="12"/>
+      <c r="R476" s="12"/>
+      <c r="S476" s="12"/>
+      <c r="T476" s="12"/>
+      <c r="U476" s="12"/>
       <c r="V476" s="12"/>
       <c r="W476" s="12"/>
-      <c r="X476" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="X476" s="12"/>
       <c r="Y476" s="12"/>
     </row>
     <row r="477" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="12" t="s">
-        <v>3258</v>
+        <v>24</v>
       </c>
       <c r="B477" s="12" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C477" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D477" s="13" t="s">
-        <v>395</v>
+        <v>1543</v>
+      </c>
+      <c r="C477" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D477" s="12" t="s">
+        <v>434</v>
       </c>
       <c r="E477" s="12">
-        <v>45</v>
+        <v>530</v>
       </c>
       <c r="F477" s="12" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G477" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H477" s="8" t="s">
+      <c r="H477" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="I477" s="12" t="s">
-        <v>1374</v>
+      <c r="I477" s="8" t="s">
+        <v>1319</v>
       </c>
       <c r="J477" s="12" t="s">
-        <v>1197</v>
+        <v>1018</v>
       </c>
       <c r="K477" s="12">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="L477" s="12" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="M477" s="12" t="s">
         <v>1236</v>
@@ -43811,24 +43868,20 @@
       <c r="N477" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="O477" s="25" t="s">
+      <c r="O477" s="12" t="s">
         <v>727</v>
       </c>
       <c r="P477" s="12" t="s">
         <v>675</v>
       </c>
       <c r="Q477" s="12"/>
-      <c r="R477" s="12" t="s">
-        <v>676</v>
-      </c>
+      <c r="R477" s="12"/>
       <c r="S477" s="12"/>
       <c r="T477" s="12"/>
       <c r="U477" s="12"/>
       <c r="V477" s="12"/>
       <c r="W477" s="12"/>
-      <c r="X477" s="12" t="s">
-        <v>676</v>
-      </c>
+      <c r="X477" s="12"/>
       <c r="Y477" s="12"/>
     </row>
     <row r="478" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -43836,7 +43889,7 @@
         <v>3258</v>
       </c>
       <c r="B478" s="12" t="s">
-        <v>1347</v>
+        <v>1545</v>
       </c>
       <c r="C478" s="13" t="s">
         <v>143</v>
@@ -43854,19 +43907,19 @@
         <v>663</v>
       </c>
       <c r="H478" s="8" t="s">
-        <v>878</v>
+        <v>1132</v>
       </c>
       <c r="I478" s="12" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="J478" s="12" t="s">
         <v>1197</v>
       </c>
       <c r="K478" s="12">
-        <v>540</v>
+        <v>120</v>
       </c>
       <c r="L478" s="12" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="M478" s="12" t="s">
         <v>1236</v>
@@ -43880,23 +43933,25 @@
       <c r="P478" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="Q478" s="12"/>
+      <c r="Q478" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="R478" s="12" t="s">
         <v>676</v>
       </c>
       <c r="S478" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="T478" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="U478" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="V478" s="12"/>
       <c r="W478" s="12"/>
       <c r="X478" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="Y478" s="12"/>
     </row>
@@ -43923,16 +43978,16 @@
         <v>663</v>
       </c>
       <c r="H479" s="8" t="s">
-        <v>1132</v>
+        <v>853</v>
       </c>
       <c r="I479" s="12" t="s">
-        <v>1319</v>
+        <v>1374</v>
       </c>
       <c r="J479" s="12" t="s">
         <v>1197</v>
       </c>
       <c r="K479" s="12">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="L479" s="12" t="s">
         <v>1376</v>
@@ -43943,31 +43998,23 @@
       <c r="N479" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="O479" s="12" t="s">
+      <c r="O479" s="25" t="s">
         <v>727</v>
       </c>
       <c r="P479" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="Q479" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="Q479" s="12"/>
       <c r="R479" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="S479" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="T479" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="U479" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="S479" s="12"/>
+      <c r="T479" s="12"/>
+      <c r="U479" s="12"/>
       <c r="V479" s="12"/>
       <c r="W479" s="12"/>
       <c r="X479" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Y479" s="12"/>
     </row>
@@ -43976,7 +44023,7 @@
         <v>3258</v>
       </c>
       <c r="B480" s="12" t="s">
-        <v>1544</v>
+        <v>1347</v>
       </c>
       <c r="C480" s="13" t="s">
         <v>143</v>
@@ -43993,20 +44040,20 @@
       <c r="G480" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H480" s="12" t="s">
-        <v>934</v>
+      <c r="H480" s="8" t="s">
+        <v>878</v>
       </c>
       <c r="I480" s="12" t="s">
-        <v>1228</v>
+        <v>1313</v>
       </c>
       <c r="J480" s="12" t="s">
-        <v>855</v>
+        <v>1197</v>
       </c>
       <c r="K480" s="12">
         <v>540</v>
       </c>
       <c r="L480" s="12" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="M480" s="12" t="s">
         <v>1236</v>
@@ -44014,7 +44061,7 @@
       <c r="N480" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="O480" s="12" t="s">
+      <c r="O480" s="25" t="s">
         <v>727</v>
       </c>
       <c r="P480" s="12" t="s">
@@ -44024,14 +44071,20 @@
       <c r="R480" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="S480" s="12"/>
+      <c r="S480" s="12" t="s">
+        <v>676</v>
+      </c>
       <c r="T480" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="U480" s="12"/>
+        <v>676</v>
+      </c>
+      <c r="U480" s="12" t="s">
+        <v>676</v>
+      </c>
       <c r="V480" s="12"/>
       <c r="W480" s="12"/>
-      <c r="X480" s="12"/>
+      <c r="X480" s="12" t="s">
+        <v>676</v>
+      </c>
       <c r="Y480" s="12"/>
     </row>
     <row r="481" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -44039,7 +44092,7 @@
         <v>3258</v>
       </c>
       <c r="B481" s="12" t="s">
-        <v>3482</v>
+        <v>1347</v>
       </c>
       <c r="C481" s="13" t="s">
         <v>143</v>
@@ -44056,20 +44109,20 @@
       <c r="G481" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H481" s="12" t="s">
-        <v>1500</v>
+      <c r="H481" s="8" t="s">
+        <v>1132</v>
       </c>
       <c r="I481" s="12" t="s">
-        <v>3313</v>
+        <v>1319</v>
       </c>
       <c r="J481" s="12" t="s">
-        <v>3483</v>
+        <v>1197</v>
       </c>
       <c r="K481" s="12">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="L481" s="12" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="M481" s="12" t="s">
         <v>1236</v>
@@ -44083,94 +44136,106 @@
       <c r="P481" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="Q481" s="12"/>
-      <c r="R481" s="12"/>
-      <c r="S481" s="12"/>
-      <c r="T481" s="12"/>
+      <c r="Q481" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="R481" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="S481" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="T481" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="U481" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="V481" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="V481" s="12"/>
       <c r="W481" s="12"/>
-      <c r="X481" s="12"/>
+      <c r="X481" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="Y481" s="12"/>
     </row>
     <row r="482" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A482" s="14" t="s">
+      <c r="A482" s="12" t="s">
         <v>3258</v>
       </c>
-      <c r="B482" s="14" t="s">
-        <v>3494</v>
-      </c>
-      <c r="C482" s="15" t="s">
+      <c r="B482" s="12" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C482" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D482" s="15" t="s">
+      <c r="D482" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="E482" s="14">
+      <c r="E482" s="12">
         <v>45</v>
       </c>
-      <c r="F482" s="14" t="s">
+      <c r="F482" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="G482" s="14" t="s">
+      <c r="G482" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H482" s="14" t="s">
-        <v>805</v>
-      </c>
-      <c r="I482" s="14" t="s">
-        <v>3338</v>
-      </c>
-      <c r="J482" s="14" t="s">
-        <v>3483</v>
-      </c>
-      <c r="K482" s="14">
-        <v>120</v>
-      </c>
-      <c r="L482" s="14" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M482" s="14" t="s">
-        <v>1238</v>
-      </c>
-      <c r="N482" s="27" t="s">
-        <v>1265</v>
-      </c>
-      <c r="O482" s="14" t="s">
-        <v>3483</v>
-      </c>
-      <c r="P482" s="14" t="s">
+      <c r="H482" s="12" t="s">
+        <v>934</v>
+      </c>
+      <c r="I482" s="12" t="s">
+        <v>1228</v>
+      </c>
+      <c r="J482" s="12" t="s">
+        <v>855</v>
+      </c>
+      <c r="K482" s="12">
+        <v>540</v>
+      </c>
+      <c r="L482" s="12" t="s">
+        <v>1378</v>
+      </c>
+      <c r="M482" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N482" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O482" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P482" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q482" s="12"/>
+      <c r="R482" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="Q482" s="14"/>
-      <c r="R482" s="14"/>
-      <c r="S482" s="14"/>
-      <c r="T482" s="14"/>
-      <c r="U482" s="14"/>
-      <c r="V482" s="14"/>
-      <c r="W482" s="14"/>
-      <c r="X482" s="14"/>
-      <c r="Y482" s="14"/>
+      <c r="S482" s="12"/>
+      <c r="T482" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="U482" s="12"/>
+      <c r="V482" s="12"/>
+      <c r="W482" s="12"/>
+      <c r="X482" s="12"/>
+      <c r="Y482" s="12"/>
     </row>
     <row r="483" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="12" t="s">
-        <v>1458</v>
+        <v>3258</v>
       </c>
       <c r="B483" s="12" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C483" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="D483" s="12" t="s">
-        <v>468</v>
+        <v>3482</v>
+      </c>
+      <c r="C483" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D483" s="13" t="s">
+        <v>395</v>
       </c>
       <c r="E483" s="12">
-        <v>500</v>
+        <v>45</v>
       </c>
       <c r="F483" s="12" t="s">
         <v>651</v>
@@ -44179,16 +44244,16 @@
         <v>663</v>
       </c>
       <c r="H483" s="12" t="s">
-        <v>853</v>
+        <v>1500</v>
       </c>
       <c r="I483" s="12" t="s">
-        <v>1374</v>
+        <v>3313</v>
       </c>
       <c r="J483" s="12" t="s">
-        <v>945</v>
-      </c>
-      <c r="K483" s="12" t="s">
-        <v>944</v>
+        <v>3483</v>
+      </c>
+      <c r="K483" s="12">
+        <v>120</v>
       </c>
       <c r="L483" s="12" t="s">
         <v>1377</v>
@@ -44209,88 +44274,90 @@
       <c r="R483" s="12"/>
       <c r="S483" s="12"/>
       <c r="T483" s="12"/>
-      <c r="U483" s="12"/>
-      <c r="V483" s="12"/>
+      <c r="U483" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="V483" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="W483" s="12"/>
       <c r="X483" s="12"/>
       <c r="Y483" s="12"/>
     </row>
     <row r="484" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A484" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B484" s="12" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C484" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="D484" s="13" t="s">
-        <v>592</v>
-      </c>
-      <c r="E484" s="12">
-        <v>255</v>
-      </c>
-      <c r="F484" s="12" t="s">
-        <v>655</v>
-      </c>
-      <c r="G484" s="12" t="s">
+      <c r="A484" s="14" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B484" s="14" t="s">
+        <v>3494</v>
+      </c>
+      <c r="C484" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D484" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="E484" s="14">
+        <v>45</v>
+      </c>
+      <c r="F484" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="G484" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="H484" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="I484" s="12" t="s">
-        <v>1374</v>
-      </c>
-      <c r="J484" s="12" t="s">
-        <v>1019</v>
-      </c>
-      <c r="K484" s="12">
-        <v>90</v>
-      </c>
-      <c r="L484" s="12" t="s">
-        <v>1376</v>
-      </c>
-      <c r="M484" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N484" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O484" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P484" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q484" s="12"/>
-      <c r="R484" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="S484" s="12"/>
-      <c r="T484" s="12"/>
-      <c r="U484" s="12"/>
-      <c r="V484" s="12"/>
-      <c r="W484" s="12"/>
-      <c r="X484" s="12"/>
-      <c r="Y484" s="12"/>
+      <c r="H484" s="14" t="s">
+        <v>805</v>
+      </c>
+      <c r="I484" s="14" t="s">
+        <v>3338</v>
+      </c>
+      <c r="J484" s="14" t="s">
+        <v>3483</v>
+      </c>
+      <c r="K484" s="14">
+        <v>120</v>
+      </c>
+      <c r="L484" s="14" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M484" s="14" t="s">
+        <v>1238</v>
+      </c>
+      <c r="N484" s="27" t="s">
+        <v>1265</v>
+      </c>
+      <c r="O484" s="14" t="s">
+        <v>3483</v>
+      </c>
+      <c r="P484" s="14" t="s">
+        <v>676</v>
+      </c>
+      <c r="Q484" s="14"/>
+      <c r="R484" s="14"/>
+      <c r="S484" s="14"/>
+      <c r="T484" s="14"/>
+      <c r="U484" s="14"/>
+      <c r="V484" s="14"/>
+      <c r="W484" s="14"/>
+      <c r="X484" s="14"/>
+      <c r="Y484" s="14"/>
     </row>
     <row r="485" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="12" t="s">
-        <v>76</v>
+        <v>1458</v>
       </c>
       <c r="B485" s="12" t="s">
-        <v>1357</v>
+        <v>1346</v>
       </c>
       <c r="C485" s="12" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="D485" s="12" t="s">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="E485" s="12">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F485" s="12" t="s">
         <v>651</v>
@@ -44302,16 +44369,16 @@
         <v>853</v>
       </c>
       <c r="I485" s="12" t="s">
-        <v>1384</v>
+        <v>1374</v>
       </c>
       <c r="J485" s="12" t="s">
-        <v>1020</v>
-      </c>
-      <c r="K485" s="12">
-        <v>18</v>
+        <v>945</v>
+      </c>
+      <c r="K485" s="12" t="s">
+        <v>944</v>
       </c>
       <c r="L485" s="12" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="M485" s="12" t="s">
         <v>1236</v>
@@ -44336,235 +44403,219 @@
       <c r="Y485" s="12"/>
     </row>
     <row r="486" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A486" s="10" t="s">
+      <c r="A486" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B486" s="12" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C486" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="D486" s="13" t="s">
+        <v>592</v>
+      </c>
+      <c r="E486" s="12">
+        <v>255</v>
+      </c>
+      <c r="F486" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="G486" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="H486" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="I486" s="12" t="s">
+        <v>1374</v>
+      </c>
+      <c r="J486" s="12" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K486" s="12">
+        <v>90</v>
+      </c>
+      <c r="L486" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M486" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N486" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O486" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P486" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q486" s="12"/>
+      <c r="R486" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="S486" s="12"/>
+      <c r="T486" s="12"/>
+      <c r="U486" s="12"/>
+      <c r="V486" s="12"/>
+      <c r="W486" s="12"/>
+      <c r="X486" s="12"/>
+      <c r="Y486" s="12"/>
+    </row>
+    <row r="487" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A487" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B487" s="12" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C487" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D487" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="E487" s="12">
+        <v>50</v>
+      </c>
+      <c r="F487" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="G487" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="H487" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="I487" s="12" t="s">
+        <v>1384</v>
+      </c>
+      <c r="J487" s="12" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K487" s="12">
+        <v>18</v>
+      </c>
+      <c r="L487" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M487" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N487" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O487" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P487" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q487" s="12"/>
+      <c r="R487" s="12"/>
+      <c r="S487" s="12"/>
+      <c r="T487" s="12"/>
+      <c r="U487" s="12"/>
+      <c r="V487" s="12"/>
+      <c r="W487" s="12"/>
+      <c r="X487" s="12"/>
+      <c r="Y487" s="12"/>
+    </row>
+    <row r="488" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A488" s="10" t="s">
         <v>1224</v>
       </c>
-      <c r="B486" s="10" t="s">
+      <c r="B488" s="10" t="s">
         <v>1223</v>
       </c>
-      <c r="C486" s="9" t="s">
+      <c r="C488" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D486" s="9" t="s">
+      <c r="D488" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="E486" s="9" t="s">
+      <c r="E488" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="F486" s="10" t="s">
+      <c r="F488" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="G486" s="10" t="s">
+      <c r="G488" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H486" s="10" t="s">
+      <c r="H488" s="10" t="s">
         <v>798</v>
       </c>
-      <c r="I486" s="10" t="s">
+      <c r="I488" s="10" t="s">
         <v>1227</v>
       </c>
-      <c r="J486" s="10" t="s">
+      <c r="J488" s="10" t="s">
         <v>845</v>
       </c>
-      <c r="K486" s="10">
+      <c r="K488" s="10">
         <v>410</v>
       </c>
-      <c r="L486" s="10" t="s">
+      <c r="L488" s="10" t="s">
         <v>1379</v>
       </c>
-      <c r="M486" s="10" t="s">
+      <c r="M488" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N486" s="28" t="s">
+      <c r="N488" s="28" t="s">
         <v>1263</v>
       </c>
-      <c r="O486" s="10" t="s">
+      <c r="O488" s="10" t="s">
         <v>845</v>
       </c>
-      <c r="P486" s="10"/>
-      <c r="Q486" s="10"/>
-      <c r="R486" s="10"/>
-      <c r="S486" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="T486" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="U486" s="10"/>
-      <c r="V486" s="10"/>
-      <c r="W486" s="10"/>
-      <c r="X486" s="10"/>
-      <c r="Y486" s="10"/>
-    </row>
-    <row r="487" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A487" s="8" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B487" s="8" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C487" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D487" s="11" t="s">
-        <v>436</v>
-      </c>
-      <c r="E487" s="11" t="s">
-        <v>869</v>
-      </c>
-      <c r="F487" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="G487" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="H487" s="8" t="s">
-        <v>801</v>
-      </c>
-      <c r="I487" s="8" t="s">
-        <v>1228</v>
-      </c>
-      <c r="J487" s="8" t="s">
-        <v>845</v>
-      </c>
-      <c r="K487" s="8">
-        <v>410</v>
-      </c>
-      <c r="L487" s="8" t="s">
-        <v>1376</v>
-      </c>
-      <c r="M487" s="8" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N487" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O487" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P487" s="8"/>
-      <c r="Q487" s="8"/>
-      <c r="R487" s="8"/>
-      <c r="S487" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="T487" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="U487" s="8"/>
-      <c r="V487" s="8"/>
-      <c r="W487" s="8"/>
-      <c r="X487" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="Y487" s="8"/>
-    </row>
-    <row r="488" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A488" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B488" s="8" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C488" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D488" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="E488" s="8">
-        <v>450</v>
-      </c>
-      <c r="F488" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="G488" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="H488" s="8" t="s">
-        <v>1132</v>
-      </c>
-      <c r="I488" s="8" t="s">
-        <v>1319</v>
-      </c>
-      <c r="J488" s="8" t="s">
-        <v>845</v>
-      </c>
-      <c r="K488" s="8">
-        <v>650</v>
-      </c>
-      <c r="L488" s="8" t="s">
-        <v>1378</v>
-      </c>
-      <c r="M488" s="8" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N488" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O488" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P488" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q488" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="R488" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="S488" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="T488" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="U488" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="V488" s="8"/>
-      <c r="W488" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="X488" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y488" s="8"/>
+      <c r="P488" s="10"/>
+      <c r="Q488" s="10"/>
+      <c r="R488" s="10"/>
+      <c r="S488" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="T488" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="U488" s="10"/>
+      <c r="V488" s="10"/>
+      <c r="W488" s="10"/>
+      <c r="X488" s="10"/>
+      <c r="Y488" s="10"/>
     </row>
     <row r="489" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="8" t="s">
-        <v>677</v>
+        <v>1224</v>
       </c>
       <c r="B489" s="8" t="s">
-        <v>1357</v>
+        <v>1344</v>
       </c>
       <c r="C489" s="11" t="s">
-        <v>678</v>
+        <v>184</v>
       </c>
       <c r="D489" s="11" t="s">
-        <v>679</v>
-      </c>
-      <c r="E489" s="8">
-        <v>1070</v>
+        <v>436</v>
+      </c>
+      <c r="E489" s="11" t="s">
+        <v>869</v>
       </c>
       <c r="F489" s="8" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G489" s="8" t="s">
         <v>663</v>
       </c>
       <c r="H489" s="8" t="s">
-        <v>853</v>
+        <v>801</v>
       </c>
       <c r="I489" s="8" t="s">
-        <v>1364</v>
+        <v>1228</v>
       </c>
       <c r="J489" s="8" t="s">
-        <v>942</v>
+        <v>845</v>
       </c>
       <c r="K489" s="8">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="L489" s="8" t="s">
         <v>1376</v>
@@ -44578,55 +44629,59 @@
       <c r="O489" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="P489" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="P489" s="8"/>
       <c r="Q489" s="8"/>
       <c r="R489" s="8"/>
-      <c r="S489" s="8"/>
-      <c r="T489" s="8"/>
+      <c r="S489" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="T489" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="U489" s="8"/>
       <c r="V489" s="8"/>
       <c r="W489" s="8"/>
-      <c r="X489" s="8"/>
+      <c r="X489" s="8" t="s">
+        <v>676</v>
+      </c>
       <c r="Y489" s="8"/>
     </row>
     <row r="490" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="8" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B490" s="8" t="s">
         <v>1357</v>
       </c>
-      <c r="C490" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="D490" s="11" t="s">
-        <v>415</v>
+      <c r="C490" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D490" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="E490" s="8">
-        <v>25</v>
+        <v>450</v>
       </c>
       <c r="F490" s="8" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G490" s="8" t="s">
         <v>663</v>
       </c>
       <c r="H490" s="8" t="s">
-        <v>878</v>
+        <v>1132</v>
       </c>
       <c r="I490" s="8" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="J490" s="8" t="s">
-        <v>1198</v>
+        <v>845</v>
       </c>
       <c r="K490" s="8">
-        <v>40</v>
+        <v>650</v>
       </c>
       <c r="L490" s="8" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="M490" s="8" t="s">
         <v>1236</v>
@@ -44640,470 +44695,482 @@
       <c r="P490" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="Q490" s="8"/>
-      <c r="R490" s="8"/>
-      <c r="S490" s="8"/>
-      <c r="T490" s="8"/>
-      <c r="U490" s="8"/>
+      <c r="Q490" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="R490" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="S490" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="T490" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U490" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="V490" s="8"/>
-      <c r="W490" s="8"/>
-      <c r="X490" s="8"/>
+      <c r="W490" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="X490" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="Y490" s="8"/>
     </row>
     <row r="491" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A491" s="10" t="s">
+      <c r="A491" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B491" s="8" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C491" s="11" t="s">
+        <v>678</v>
+      </c>
+      <c r="D491" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="E491" s="8">
+        <v>1070</v>
+      </c>
+      <c r="F491" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="G491" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H491" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="I491" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="J491" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="K491" s="8">
+        <v>80</v>
+      </c>
+      <c r="L491" s="8" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M491" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N491" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O491" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P491" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q491" s="8"/>
+      <c r="R491" s="8"/>
+      <c r="S491" s="8"/>
+      <c r="T491" s="8"/>
+      <c r="U491" s="8"/>
+      <c r="V491" s="8"/>
+      <c r="W491" s="8"/>
+      <c r="X491" s="8"/>
+      <c r="Y491" s="8"/>
+    </row>
+    <row r="492" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A492" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B492" s="8" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C492" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D492" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="E492" s="8">
+        <v>25</v>
+      </c>
+      <c r="F492" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="G492" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H492" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="I492" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J492" s="8" t="s">
+        <v>1198</v>
+      </c>
+      <c r="K492" s="8">
+        <v>40</v>
+      </c>
+      <c r="L492" s="8" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M492" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N492" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O492" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P492" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q492" s="8"/>
+      <c r="R492" s="8"/>
+      <c r="S492" s="8"/>
+      <c r="T492" s="8"/>
+      <c r="U492" s="8"/>
+      <c r="V492" s="8"/>
+      <c r="W492" s="8"/>
+      <c r="X492" s="8"/>
+      <c r="Y492" s="8"/>
+    </row>
+    <row r="493" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A493" s="10" t="s">
         <v>1485</v>
       </c>
-      <c r="B491" s="10" t="s">
+      <c r="B493" s="10" t="s">
         <v>1486</v>
       </c>
-      <c r="C491" s="9" t="s">
+      <c r="C493" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="D491" s="9" t="s">
+      <c r="D493" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="E491" s="10">
+      <c r="E493" s="10">
         <v>595</v>
       </c>
-      <c r="F491" s="10" t="s">
+      <c r="F493" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="G491" s="10" t="s">
+      <c r="G493" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H491" s="10" t="s">
+      <c r="H493" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="I491" s="14" t="s">
+      <c r="I493" s="14" t="s">
         <v>1434</v>
       </c>
-      <c r="J491" s="10" t="s">
+      <c r="J493" s="10" t="s">
         <v>1118</v>
       </c>
-      <c r="K491" s="10">
+      <c r="K493" s="10">
         <v>80</v>
       </c>
-      <c r="L491" s="10" t="s">
+      <c r="L493" s="10" t="s">
         <v>1380</v>
       </c>
-      <c r="M491" s="10" t="s">
+      <c r="M493" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N491" s="27" t="s">
+      <c r="N493" s="27" t="s">
         <v>1265</v>
       </c>
-      <c r="O491" s="10" t="s">
-        <v>727</v>
-      </c>
-      <c r="P491" s="10" t="s">
+      <c r="O493" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="P493" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="Q491" s="10"/>
-      <c r="R491" s="10"/>
-      <c r="S491" s="10"/>
-      <c r="T491" s="10"/>
-      <c r="U491" s="10"/>
-      <c r="V491" s="10"/>
-      <c r="W491" s="10"/>
-      <c r="X491" s="10"/>
-      <c r="Y491" s="10"/>
-    </row>
-    <row r="492" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A492" s="14" t="s">
+      <c r="Q493" s="10"/>
+      <c r="R493" s="10"/>
+      <c r="S493" s="10"/>
+      <c r="T493" s="10"/>
+      <c r="U493" s="10"/>
+      <c r="V493" s="10"/>
+      <c r="W493" s="10"/>
+      <c r="X493" s="10"/>
+      <c r="Y493" s="10"/>
+    </row>
+    <row r="494" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A494" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B492" s="14" t="s">
+      <c r="B494" s="14" t="s">
         <v>1546</v>
       </c>
-      <c r="C492" s="15" t="s">
+      <c r="C494" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="D492" s="15" t="s">
+      <c r="D494" s="15" t="s">
         <v>604</v>
       </c>
-      <c r="E492" s="14">
+      <c r="E494" s="14">
         <v>220</v>
       </c>
-      <c r="F492" s="14" t="s">
+      <c r="F494" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="G492" s="14" t="s">
+      <c r="G494" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="H492" s="14" t="s">
+      <c r="H494" s="14" t="s">
         <v>853</v>
       </c>
-      <c r="I492" s="14" t="s">
+      <c r="I494" s="14" t="s">
         <v>1547</v>
       </c>
-      <c r="J492" s="14" t="s">
+      <c r="J494" s="14" t="s">
         <v>1021</v>
       </c>
-      <c r="K492" s="14">
+      <c r="K494" s="14">
         <v>60</v>
       </c>
-      <c r="L492" s="14" t="s">
+      <c r="L494" s="14" t="s">
         <v>1378</v>
       </c>
-      <c r="M492" s="14" t="s">
+      <c r="M494" s="14" t="s">
         <v>1238</v>
       </c>
-      <c r="N492" s="27" t="s">
+      <c r="N494" s="27" t="s">
         <v>1023</v>
       </c>
-      <c r="O492" s="14" t="s">
+      <c r="O494" s="14" t="s">
         <v>1022</v>
       </c>
-      <c r="P492" s="14" t="s">
+      <c r="P494" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="Q492" s="14"/>
-      <c r="R492" s="14"/>
-      <c r="S492" s="14"/>
-      <c r="T492" s="14"/>
-      <c r="U492" s="14"/>
-      <c r="V492" s="14"/>
-      <c r="W492" s="14"/>
-      <c r="X492" s="14"/>
-      <c r="Y492" s="14"/>
-    </row>
-    <row r="493" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A493" s="8" t="s">
+      <c r="Q494" s="14"/>
+      <c r="R494" s="14"/>
+      <c r="S494" s="14"/>
+      <c r="T494" s="14"/>
+      <c r="U494" s="14"/>
+      <c r="V494" s="14"/>
+      <c r="W494" s="14"/>
+      <c r="X494" s="14"/>
+      <c r="Y494" s="14"/>
+    </row>
+    <row r="495" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A495" s="8" t="s">
         <v>1299</v>
       </c>
-      <c r="B493" s="8" t="s">
+      <c r="B495" s="8" t="s">
         <v>1357</v>
       </c>
-      <c r="C493" s="8" t="s">
+      <c r="C495" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="D493" s="8" t="s">
+      <c r="D495" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="E493" s="8">
+      <c r="E495" s="8">
         <v>144</v>
       </c>
-      <c r="F493" s="8" t="s">
+      <c r="F495" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="G493" s="8" t="s">
+      <c r="G495" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="H493" s="8" t="s">
+      <c r="H495" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="I493" s="8" t="s">
+      <c r="I495" s="8" t="s">
         <v>1364</v>
       </c>
-      <c r="J493" s="8" t="s">
+      <c r="J495" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="K493" s="8">
+      <c r="K495" s="8">
         <v>12</v>
       </c>
-      <c r="L493" s="8" t="s">
+      <c r="L495" s="8" t="s">
         <v>1376</v>
       </c>
-      <c r="M493" s="8" t="s">
+      <c r="M495" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="N493" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O493" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P493" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q493" s="8"/>
-      <c r="R493" s="8"/>
-      <c r="S493" s="8"/>
-      <c r="T493" s="8"/>
-      <c r="U493" s="8"/>
-      <c r="V493" s="8"/>
-      <c r="W493" s="8"/>
-      <c r="X493" s="8"/>
-      <c r="Y493" s="8"/>
-    </row>
-    <row r="494" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A494" s="7" t="s">
+      <c r="N495" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O495" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P495" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q495" s="8"/>
+      <c r="R495" s="8"/>
+      <c r="S495" s="8"/>
+      <c r="T495" s="8"/>
+      <c r="U495" s="8"/>
+      <c r="V495" s="8"/>
+      <c r="W495" s="8"/>
+      <c r="X495" s="8"/>
+      <c r="Y495" s="8"/>
+    </row>
+    <row r="496" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A496" s="7" t="s">
         <v>756</v>
       </c>
-      <c r="B494" s="7" t="s">
+      <c r="B496" s="7" t="s">
         <v>1230</v>
       </c>
-      <c r="C494" s="6" t="s">
+      <c r="C496" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="D494" s="6" t="s">
+      <c r="D496" s="6" t="s">
         <v>782</v>
       </c>
-      <c r="E494" s="6" t="s">
+      <c r="E496" s="6" t="s">
         <v>836</v>
       </c>
-      <c r="F494" s="7" t="s">
+      <c r="F496" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="G494" s="7" t="s">
+      <c r="G496" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="H494" s="7" t="s">
+      <c r="H496" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="I494" s="7" t="s">
+      <c r="I496" s="7" t="s">
         <v>1227</v>
       </c>
-      <c r="J494" s="7" t="s">
+      <c r="J496" s="7" t="s">
         <v>837</v>
       </c>
-      <c r="K494" s="7">
+      <c r="K496" s="7">
         <v>15</v>
       </c>
-      <c r="L494" s="7" t="s">
+      <c r="L496" s="7" t="s">
         <v>1377</v>
       </c>
-      <c r="M494" s="7" t="s">
+      <c r="M496" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="N494" s="28" t="s">
+      <c r="N496" s="28" t="s">
         <v>1367</v>
       </c>
-      <c r="O494" s="7" t="s">
+      <c r="O496" s="7" t="s">
         <v>837</v>
       </c>
-      <c r="P494" s="7"/>
-      <c r="Q494" s="7"/>
-      <c r="R494" s="7"/>
-      <c r="S494" s="7"/>
-      <c r="T494" s="7"/>
-      <c r="U494" s="7"/>
-      <c r="V494" s="7"/>
-      <c r="W494" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="X494" s="7"/>
-      <c r="Y494" s="7"/>
-    </row>
-    <row r="495" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A495" s="14" t="s">
+      <c r="P496" s="7"/>
+      <c r="Q496" s="7"/>
+      <c r="R496" s="7"/>
+      <c r="S496" s="7"/>
+      <c r="T496" s="7"/>
+      <c r="U496" s="7"/>
+      <c r="V496" s="7"/>
+      <c r="W496" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="X496" s="7"/>
+      <c r="Y496" s="7"/>
+    </row>
+    <row r="497" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A497" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B495" s="14" t="s">
+      <c r="B497" s="14" t="s">
         <v>1421</v>
       </c>
-      <c r="C495" s="15" t="s">
+      <c r="C497" s="15" t="s">
         <v>668</v>
       </c>
-      <c r="D495" s="15" t="s">
+      <c r="D497" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="E495" s="14">
+      <c r="E497" s="14">
         <v>74</v>
       </c>
-      <c r="F495" s="14" t="s">
+      <c r="F497" s="14" t="s">
         <v>651</v>
       </c>
-      <c r="G495" s="14" t="s">
+      <c r="G497" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="H495" s="10" t="s">
+      <c r="H497" s="10" t="s">
         <v>1548</v>
       </c>
-      <c r="I495" s="14" t="s">
+      <c r="I497" s="14" t="s">
         <v>1318</v>
       </c>
-      <c r="J495" s="14" t="s">
+      <c r="J497" s="14" t="s">
         <v>1068</v>
       </c>
-      <c r="K495" s="14">
+      <c r="K497" s="14">
         <v>40</v>
       </c>
-      <c r="L495" s="14" t="s">
+      <c r="L497" s="14" t="s">
         <v>1376</v>
       </c>
-      <c r="M495" s="14" t="s">
+      <c r="M497" s="14" t="s">
         <v>1238</v>
       </c>
-      <c r="N495" s="27" t="s">
+      <c r="N497" s="27" t="s">
         <v>1367</v>
       </c>
-      <c r="O495" s="14" t="s">
-        <v>727</v>
-      </c>
-      <c r="P495" s="14"/>
-      <c r="Q495" s="14"/>
-      <c r="R495" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="S495" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="T495" s="14"/>
-      <c r="U495" s="14"/>
-      <c r="V495" s="14"/>
-      <c r="W495" s="14"/>
-      <c r="X495" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y495" s="14" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="496" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A496" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B496" s="12" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C496" s="13" t="s">
-        <v>668</v>
-      </c>
-      <c r="D496" s="13" t="s">
-        <v>669</v>
-      </c>
-      <c r="E496" s="12">
-        <v>74</v>
-      </c>
-      <c r="F496" s="12" t="s">
-        <v>651</v>
-      </c>
-      <c r="G496" s="12" t="s">
-        <v>663</v>
-      </c>
-      <c r="H496" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="I496" s="12" t="s">
-        <v>1374</v>
-      </c>
-      <c r="J496" s="12" t="s">
-        <v>1068</v>
-      </c>
-      <c r="K496" s="12">
-        <v>100</v>
-      </c>
-      <c r="L496" s="12" t="s">
-        <v>1376</v>
-      </c>
-      <c r="M496" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N496" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O496" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P496" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q496" s="12"/>
-      <c r="R496" s="12"/>
-      <c r="S496" s="12"/>
-      <c r="T496" s="12"/>
-      <c r="U496" s="12"/>
-      <c r="V496" s="12"/>
-      <c r="W496" s="12"/>
-      <c r="X496" s="12"/>
-      <c r="Y496" s="12"/>
-    </row>
-    <row r="497" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A497" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B497" s="10" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C497" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="D497" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="E497" s="10">
-        <v>112</v>
-      </c>
-      <c r="F497" s="10" t="s">
-        <v>655</v>
-      </c>
-      <c r="G497" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="H497" s="10" t="s">
-        <v>853</v>
-      </c>
-      <c r="I497" s="10" t="s">
-        <v>1318</v>
-      </c>
-      <c r="J497" s="10" t="s">
-        <v>1050</v>
-      </c>
-      <c r="K497" s="10">
-        <v>15</v>
-      </c>
-      <c r="L497" s="10" t="s">
-        <v>1376</v>
-      </c>
-      <c r="M497" s="10" t="s">
-        <v>1238</v>
-      </c>
-      <c r="N497" s="26" t="s">
-        <v>1070</v>
-      </c>
-      <c r="O497" s="10" t="s">
-        <v>1050</v>
-      </c>
-      <c r="P497" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q497" s="10"/>
-      <c r="R497" s="10"/>
-      <c r="S497" s="10"/>
-      <c r="T497" s="10"/>
-      <c r="U497" s="10"/>
-      <c r="V497" s="10"/>
-      <c r="W497" s="10"/>
-      <c r="X497" s="10"/>
-      <c r="Y497" s="10" t="s">
-        <v>676</v>
+      <c r="O497" s="14" t="s">
+        <v>727</v>
+      </c>
+      <c r="P497" s="14"/>
+      <c r="Q497" s="14"/>
+      <c r="R497" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="S497" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="T497" s="14"/>
+      <c r="U497" s="14"/>
+      <c r="V497" s="14"/>
+      <c r="W497" s="14"/>
+      <c r="X497" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y497" s="14" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="498" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="12" t="s">
-        <v>1345</v>
+        <v>49</v>
       </c>
       <c r="B498" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="C498" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D498" s="12" t="s">
-        <v>507</v>
+      <c r="C498" s="13" t="s">
+        <v>668</v>
+      </c>
+      <c r="D498" s="13" t="s">
+        <v>669</v>
       </c>
       <c r="E498" s="12">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="F498" s="12" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G498" s="12" t="s">
         <v>663</v>
       </c>
       <c r="H498" s="12" t="s">
-        <v>878</v>
+        <v>853</v>
       </c>
       <c r="I498" s="12" t="s">
-        <v>1322</v>
+        <v>1374</v>
       </c>
       <c r="J498" s="12" t="s">
-        <v>1024</v>
+        <v>1068</v>
       </c>
       <c r="K498" s="12">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L498" s="12" t="s">
         <v>1376</v>
@@ -45111,10 +45178,10 @@
       <c r="M498" s="12" t="s">
         <v>1236</v>
       </c>
-      <c r="N498" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O498" s="24" t="s">
+      <c r="N498" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O498" s="12" t="s">
         <v>727</v>
       </c>
       <c r="P498" s="12" t="s">
@@ -45125,224 +45192,344 @@
       <c r="S498" s="12"/>
       <c r="T498" s="12"/>
       <c r="U498" s="12"/>
-      <c r="V498" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="V498" s="12"/>
       <c r="W498" s="12"/>
       <c r="X498" s="12"/>
       <c r="Y498" s="12"/>
     </row>
     <row r="499" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A499" s="8" t="s">
+      <c r="A499" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B499" s="10" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C499" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="D499" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="E499" s="10">
+        <v>112</v>
+      </c>
+      <c r="F499" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="G499" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="H499" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="I499" s="10" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J499" s="10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K499" s="10">
+        <v>15</v>
+      </c>
+      <c r="L499" s="10" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M499" s="10" t="s">
+        <v>1238</v>
+      </c>
+      <c r="N499" s="26" t="s">
+        <v>1070</v>
+      </c>
+      <c r="O499" s="10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="P499" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q499" s="10"/>
+      <c r="R499" s="10"/>
+      <c r="S499" s="10"/>
+      <c r="T499" s="10"/>
+      <c r="U499" s="10"/>
+      <c r="V499" s="10"/>
+      <c r="W499" s="10"/>
+      <c r="X499" s="10"/>
+      <c r="Y499" s="10" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="500" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A500" s="12" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B500" s="12" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C500" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D500" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="E500" s="12">
+        <v>123</v>
+      </c>
+      <c r="F500" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="G500" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="H500" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="I500" s="12" t="s">
+        <v>1322</v>
+      </c>
+      <c r="J500" s="12" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K500" s="12">
+        <v>60</v>
+      </c>
+      <c r="L500" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M500" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N500" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O500" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="P500" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q500" s="12"/>
+      <c r="R500" s="12"/>
+      <c r="S500" s="12"/>
+      <c r="T500" s="12"/>
+      <c r="U500" s="12"/>
+      <c r="V500" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="W500" s="12"/>
+      <c r="X500" s="12"/>
+      <c r="Y500" s="12"/>
+    </row>
+    <row r="501" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A501" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B499" s="8" t="s">
+      <c r="B501" s="8" t="s">
         <v>1357</v>
       </c>
-      <c r="C499" s="8" t="s">
+      <c r="C501" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="D499" s="8" t="s">
+      <c r="D501" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="E499" s="8">
+      <c r="E501" s="8">
         <v>171</v>
       </c>
-      <c r="F499" s="8" t="s">
+      <c r="F501" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="G499" s="8" t="s">
+      <c r="G501" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="H499" s="8" t="s">
+      <c r="H501" s="8" t="s">
         <v>878</v>
       </c>
-      <c r="I499" s="8" t="s">
+      <c r="I501" s="8" t="s">
         <v>1323</v>
       </c>
-      <c r="J499" s="8" t="s">
+      <c r="J501" s="8" t="s">
         <v>1071</v>
       </c>
-      <c r="K499" s="8">
+      <c r="K501" s="8">
         <v>125</v>
       </c>
-      <c r="L499" s="8" t="s">
+      <c r="L501" s="8" t="s">
         <v>1376</v>
       </c>
-      <c r="M499" s="8" t="s">
+      <c r="M501" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="N499" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O499" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="P499" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q499" s="8"/>
-      <c r="R499" s="8" t="s">
+      <c r="N501" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O501" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="P501" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q501" s="8"/>
+      <c r="R501" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="S499" s="8" t="s">
+      <c r="S501" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="T499" s="8" t="s">
+      <c r="T501" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="U499" s="8" t="s">
+      <c r="U501" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="V499" s="8"/>
-      <c r="W499" s="8"/>
-      <c r="X499" s="8" t="s">
+      <c r="V501" s="8"/>
+      <c r="W501" s="8"/>
+      <c r="X501" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="Y499" s="8"/>
-    </row>
-    <row r="500" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A500" s="8" t="s">
+      <c r="Y501" s="8"/>
+    </row>
+    <row r="502" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A502" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B500" s="8" t="s">
+      <c r="B502" s="8" t="s">
         <v>1357</v>
       </c>
-      <c r="C500" s="8" t="s">
+      <c r="C502" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="D500" s="8" t="s">
+      <c r="D502" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="E500" s="8">
+      <c r="E502" s="8">
         <v>171</v>
       </c>
-      <c r="F500" s="8" t="s">
+      <c r="F502" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="G500" s="8" t="s">
+      <c r="G502" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="H500" s="8" t="s">
+      <c r="H502" s="8" t="s">
         <v>878</v>
       </c>
-      <c r="I500" s="8" t="s">
+      <c r="I502" s="8" t="s">
         <v>1314</v>
       </c>
-      <c r="J500" s="8" t="s">
+      <c r="J502" s="8" t="s">
         <v>1071</v>
       </c>
-      <c r="K500" s="8">
+      <c r="K502" s="8">
         <v>125</v>
       </c>
-      <c r="L500" s="8" t="s">
+      <c r="L502" s="8" t="s">
         <v>1376</v>
       </c>
-      <c r="M500" s="8" t="s">
+      <c r="M502" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="N500" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O500" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="P500" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q500" s="8"/>
-      <c r="R500" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="S500" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="T500" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="U500" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="V500" s="8"/>
-      <c r="W500" s="8"/>
-      <c r="X500" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y500" s="8"/>
-    </row>
-    <row r="501" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A501" s="7" t="s">
+      <c r="N502" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O502" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="P502" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q502" s="8"/>
+      <c r="R502" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="S502" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="T502" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U502" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="V502" s="8"/>
+      <c r="W502" s="8"/>
+      <c r="X502" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y502" s="8"/>
+    </row>
+    <row r="503" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A503" s="7" t="s">
         <v>1232</v>
       </c>
-      <c r="B501" s="7" t="s">
+      <c r="B503" s="7" t="s">
         <v>1231</v>
       </c>
-      <c r="C501" s="6" t="s">
+      <c r="C503" s="6" t="s">
         <v>1176</v>
       </c>
-      <c r="D501" s="6" t="s">
+      <c r="D503" s="6" t="s">
         <v>1178</v>
       </c>
-      <c r="E501" s="6" t="s">
+      <c r="E503" s="6" t="s">
         <v>1180</v>
       </c>
-      <c r="F501" s="7" t="s">
+      <c r="F503" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="G501" s="7" t="s">
+      <c r="G503" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="H501" s="7" t="s">
+      <c r="H503" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="I501" s="7">
+      <c r="I503" s="7">
         <v>0</v>
       </c>
-      <c r="J501" s="7" t="s">
+      <c r="J503" s="7" t="s">
         <v>1173</v>
       </c>
-      <c r="K501" s="7">
+      <c r="K503" s="7">
         <v>140</v>
       </c>
-      <c r="L501" s="7" t="s">
+      <c r="L503" s="7" t="s">
         <v>1377</v>
       </c>
-      <c r="M501" s="7" t="s">
+      <c r="M503" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="N501" s="28" t="s">
+      <c r="N503" s="28" t="s">
         <v>1481</v>
       </c>
-      <c r="O501" s="7" t="s">
+      <c r="O503" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="P501" s="7"/>
-      <c r="Q501" s="7" t="s">
+      <c r="P503" s="7"/>
+      <c r="Q503" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="R501" s="7"/>
-      <c r="S501" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="T501" s="7"/>
-      <c r="U501" s="7"/>
-      <c r="V501" s="7"/>
-      <c r="W501" s="7"/>
-      <c r="X501" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y501" s="7" t="s">
+      <c r="R503" s="7"/>
+      <c r="S503" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="T503" s="7"/>
+      <c r="U503" s="7"/>
+      <c r="V503" s="7"/>
+      <c r="W503" s="7"/>
+      <c r="X503" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y503" s="7" t="s">
         <v>675</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y501" xr:uid="{8CDA5EAF-A655-4519-9C43-6E6BE0DBE4DA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y501">
-      <sortCondition ref="A1:A501"/>
+  <autoFilter ref="A1:Y503" xr:uid="{8CDA5EAF-A655-4519-9C43-6E6BE0DBE4DA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y503">
+      <sortCondition ref="A1:A503"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y501">
-    <sortCondition ref="A93:A501"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y503">
+    <sortCondition ref="A93:A503"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -45350,6 +45537,41 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F25AE6-2372-4014-8F2D-0F2F560D2ECA}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>3783</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3784</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3786</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>3787</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>3788</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15FA49C-AA6C-4C9D-BD3F-DDB2E499D207}">
   <dimension ref="A1:AK1190"/>
   <sheetFormatPr defaultColWidth="63.33203125" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/data/Table-Data-Base.xlsx
+++ b/data/Table-Data-Base.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inaki\Downloads\Pleistocene_Human_Use_Of_Caves-master\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63D0BAE-EB41-400D-B058-4D6840BC5C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938053EC-5EA4-4209-9BB7-30324AB23131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{493D11CC-922E-4265-992F-96F2D38DEEBB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{493D11CC-922E-4265-992F-96F2D38DEEBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Caves" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
-    <sheet name="Datings" sheetId="4" r:id="rId3"/>
+    <sheet name="Datings" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Caves!$A$1:$Y$503</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Datings!$A$1:$K$1035</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datings!$A$1:$K$1035</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17424" uniqueCount="3796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17418" uniqueCount="3792">
   <si>
     <t>San Antonio</t>
   </si>
@@ -13144,18 +13143,6 @@
   </si>
   <si>
     <t>IMG</t>
-  </si>
-  <si>
-    <t>wkt_geom</t>
-  </si>
-  <si>
-    <t>fid</t>
-  </si>
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>Point</t>
   </si>
   <si>
     <t>2.00913030110195123</t>
@@ -13351,7 +13338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13509,19 +13496,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -40926,7 +40900,7 @@
         <v>3778</v>
       </c>
       <c r="E430" s="6" t="s">
-        <v>3789</v>
+        <v>3785</v>
       </c>
       <c r="F430" s="7" t="s">
         <v>725</v>
@@ -42770,70 +42744,70 @@
       <c r="X459" s="3"/>
       <c r="Y459" s="3"/>
     </row>
-    <row r="460" spans="1:25" s="56" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="53" t="s">
+    <row r="460" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A460" s="7" t="s">
         <v>3781</v>
       </c>
-      <c r="B460" s="53" t="s">
+      <c r="B460" s="7" t="s">
         <v>3782</v>
       </c>
-      <c r="C460" s="53" t="s">
+      <c r="C460" s="7" t="s">
+        <v>3783</v>
+      </c>
+      <c r="D460" s="7" t="s">
+        <v>3784</v>
+      </c>
+      <c r="E460" s="7">
+        <v>885</v>
+      </c>
+      <c r="F460" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="G460" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="H460" s="10" t="s">
+        <v>3786</v>
+      </c>
+      <c r="I460" s="10" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J460" s="10" t="s">
         <v>3787</v>
       </c>
-      <c r="D460" s="53" t="s">
+      <c r="K460" s="7">
+        <v>70</v>
+      </c>
+      <c r="L460" s="7" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M460" s="7" t="s">
+        <v>1238</v>
+      </c>
+      <c r="N460" s="28" t="s">
+        <v>1252</v>
+      </c>
+      <c r="O460" s="10" t="s">
         <v>3788</v>
       </c>
-      <c r="E460" s="53">
-        <v>885</v>
-      </c>
-      <c r="F460" s="53" t="s">
-        <v>651</v>
-      </c>
-      <c r="G460" s="53" t="s">
-        <v>663</v>
-      </c>
-      <c r="H460" s="54" t="s">
-        <v>3790</v>
-      </c>
-      <c r="I460" s="54" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J460" s="54" t="s">
-        <v>3791</v>
-      </c>
-      <c r="K460" s="53">
-        <v>70</v>
-      </c>
-      <c r="L460" s="53" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M460" s="53" t="s">
-        <v>1238</v>
-      </c>
-      <c r="N460" s="55" t="s">
-        <v>1252</v>
-      </c>
-      <c r="O460" s="54" t="s">
-        <v>3792</v>
-      </c>
-      <c r="P460" s="53"/>
-      <c r="Q460" s="53"/>
-      <c r="R460" s="53"/>
-      <c r="S460" s="53" t="s">
-        <v>675</v>
-      </c>
-      <c r="T460" s="53" t="s">
-        <v>675</v>
-      </c>
-      <c r="U460" s="53"/>
-      <c r="V460" s="53" t="s">
-        <v>675</v>
-      </c>
-      <c r="W460" s="53"/>
-      <c r="X460" s="53" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y460" s="53" t="s">
+      <c r="P460" s="7"/>
+      <c r="Q460" s="7"/>
+      <c r="R460" s="7"/>
+      <c r="S460" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="T460" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="U460" s="7"/>
+      <c r="V460" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="W460" s="7"/>
+      <c r="X460" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y460" s="7" t="s">
         <v>675</v>
       </c>
     </row>
@@ -42842,13 +42816,13 @@
         <v>3781</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>3793</v>
+        <v>3789</v>
       </c>
       <c r="C461" s="3" t="s">
-        <v>3787</v>
+        <v>3783</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>3788</v>
+        <v>3784</v>
       </c>
       <c r="E461" s="3">
         <v>885</v>
@@ -42860,13 +42834,13 @@
         <v>663</v>
       </c>
       <c r="H461" s="8" t="s">
+        <v>3786</v>
+      </c>
+      <c r="I461" s="8" t="s">
         <v>3790</v>
       </c>
-      <c r="I461" s="8" t="s">
-        <v>3794</v>
-      </c>
       <c r="J461" s="8" t="s">
-        <v>3795</v>
+        <v>3791</v>
       </c>
       <c r="K461" s="3">
         <v>20</v>
@@ -45537,41 +45511,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F25AE6-2372-4014-8F2D-0F2F560D2ECA}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>3783</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3784</v>
-      </c>
-      <c r="C1" s="57" t="s">
-        <v>3785</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3786</v>
-      </c>
-      <c r="B2" s="57" t="s">
-        <v>3787</v>
-      </c>
-      <c r="C2" s="57" t="s">
-        <v>3788</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15FA49C-AA6C-4C9D-BD3F-DDB2E499D207}">
   <dimension ref="A1:AK1190"/>
   <sheetFormatPr defaultColWidth="63.33203125" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/data/Table-Data-Base.xlsx
+++ b/data/Table-Data-Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inaki\Downloads\Pleistocene_Human_Use_Of_Caves-master\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938053EC-5EA4-4209-9BB7-30324AB23131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55321804-3624-45E1-8EE2-5811ADDC3C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{493D11CC-922E-4265-992F-96F2D38DEEBB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{493D11CC-922E-4265-992F-96F2D38DEEBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Caves" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Caves!$A$1:$Y$503</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datings!$A$1:$K$1035</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datings!$A$1:$K$1036</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17418" uniqueCount="3792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17429" uniqueCount="3796">
   <si>
     <t>San Antonio</t>
   </si>
@@ -13170,6 +13170,18 @@
   </si>
   <si>
     <t>Salas-Altès et al., 2024</t>
+  </si>
+  <si>
+    <t>Galerie Casteret-Godin</t>
+  </si>
+  <si>
+    <t>10855 - 9700 cal BP</t>
+  </si>
+  <si>
+    <t>Rougier, 2015, p. 19</t>
+  </si>
+  <si>
+    <t>Taçon et al., 2012, p. 139</t>
   </si>
 </sst>
 </file>
@@ -20626,8 +20638,8 @@
       <c r="I108" s="10" t="s">
         <v>1437</v>
       </c>
-      <c r="J108" s="14" t="s">
-        <v>968</v>
+      <c r="J108" s="4" t="s">
+        <v>3795</v>
       </c>
       <c r="K108" s="14">
         <v>15</v>
@@ -20642,7 +20654,7 @@
         <v>1367</v>
       </c>
       <c r="O108" s="14" t="s">
-        <v>727</v>
+        <v>968</v>
       </c>
       <c r="P108" s="14"/>
       <c r="Q108" s="14"/>
@@ -45512,7 +45524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15FA49C-AA6C-4C9D-BD3F-DDB2E499D207}">
-  <dimension ref="A1:AK1190"/>
+  <dimension ref="A1:AK1191"/>
   <sheetFormatPr defaultColWidth="63.33203125" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.77734375" style="32" bestFit="1" customWidth="1"/>
@@ -71629,13 +71641,13 @@
     </row>
     <row r="738" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A738" s="33" t="s">
-        <v>1333</v>
+        <v>1266</v>
       </c>
       <c r="B738" s="33" t="s">
-        <v>2864</v>
+        <v>3792</v>
       </c>
       <c r="C738" s="33" t="s">
-        <v>2882</v>
+        <v>1566</v>
       </c>
       <c r="D738" s="33" t="s">
         <v>805</v>
@@ -71644,22 +71656,22 @@
         <v>1567</v>
       </c>
       <c r="F738" s="33" t="s">
-        <v>2883</v>
+        <v>676</v>
       </c>
       <c r="G738" s="33" t="s">
-        <v>2884</v>
-      </c>
-      <c r="H738" s="33">
-        <v>25150</v>
-      </c>
-      <c r="I738" s="33">
-        <v>110</v>
+        <v>676</v>
+      </c>
+      <c r="H738" s="33" t="s">
+        <v>3793</v>
+      </c>
+      <c r="I738" s="33" t="s">
+        <v>727</v>
       </c>
       <c r="J738" s="33" t="s">
-        <v>2885</v>
+        <v>3794</v>
       </c>
       <c r="K738" s="33" t="s">
-        <v>1525</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="739" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -71670,7 +71682,7 @@
         <v>2864</v>
       </c>
       <c r="C739" s="33" t="s">
-        <v>2771</v>
+        <v>2882</v>
       </c>
       <c r="D739" s="33" t="s">
         <v>805</v>
@@ -71679,22 +71691,22 @@
         <v>1567</v>
       </c>
       <c r="F739" s="33" t="s">
-        <v>2865</v>
+        <v>2883</v>
       </c>
       <c r="G739" s="33" t="s">
-        <v>2866</v>
+        <v>2884</v>
       </c>
       <c r="H739" s="33">
-        <v>12420</v>
+        <v>25150</v>
       </c>
       <c r="I739" s="33">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="J739" s="33" t="s">
-        <v>2867</v>
+        <v>2885</v>
       </c>
       <c r="K739" s="33" t="s">
-        <v>1318</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="740" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -71702,10 +71714,10 @@
         <v>1333</v>
       </c>
       <c r="B740" s="33" t="s">
-        <v>2868</v>
+        <v>2864</v>
       </c>
       <c r="C740" s="33" t="s">
-        <v>1570</v>
+        <v>2771</v>
       </c>
       <c r="D740" s="33" t="s">
         <v>805</v>
@@ -71714,19 +71726,19 @@
         <v>1567</v>
       </c>
       <c r="F740" s="33" t="s">
-        <v>2869</v>
+        <v>2865</v>
       </c>
       <c r="G740" s="33" t="s">
-        <v>2870</v>
+        <v>2866</v>
       </c>
       <c r="H740" s="33">
-        <v>12510</v>
+        <v>12420</v>
       </c>
       <c r="I740" s="33">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J740" s="33" t="s">
-        <v>2871</v>
+        <v>2867</v>
       </c>
       <c r="K740" s="33" t="s">
         <v>1318</v>
@@ -71737,10 +71749,10 @@
         <v>1333</v>
       </c>
       <c r="B741" s="33" t="s">
-        <v>2877</v>
+        <v>2868</v>
       </c>
       <c r="C741" s="33" t="s">
-        <v>2878</v>
+        <v>1570</v>
       </c>
       <c r="D741" s="33" t="s">
         <v>805</v>
@@ -71749,22 +71761,22 @@
         <v>1567</v>
       </c>
       <c r="F741" s="33" t="s">
-        <v>2879</v>
+        <v>2869</v>
       </c>
       <c r="G741" s="33" t="s">
-        <v>2880</v>
+        <v>2870</v>
       </c>
       <c r="H741" s="33">
-        <v>16820</v>
+        <v>12510</v>
       </c>
       <c r="I741" s="33">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J741" s="33" t="s">
-        <v>2881</v>
+        <v>2871</v>
       </c>
       <c r="K741" s="33" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="742" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -71772,10 +71784,10 @@
         <v>1333</v>
       </c>
       <c r="B742" s="33" t="s">
-        <v>2872</v>
+        <v>2877</v>
       </c>
       <c r="C742" s="33" t="s">
-        <v>2873</v>
+        <v>2878</v>
       </c>
       <c r="D742" s="33" t="s">
         <v>805</v>
@@ -71784,33 +71796,33 @@
         <v>1567</v>
       </c>
       <c r="F742" s="33" t="s">
-        <v>2874</v>
+        <v>2879</v>
       </c>
       <c r="G742" s="33" t="s">
-        <v>2875</v>
+        <v>2880</v>
       </c>
       <c r="H742" s="33">
-        <v>13840</v>
+        <v>16820</v>
       </c>
       <c r="I742" s="33">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J742" s="33" t="s">
-        <v>2876</v>
+        <v>2881</v>
       </c>
       <c r="K742" s="33" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="743" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A743" s="33" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B743" s="33" t="s">
-        <v>2886</v>
+        <v>2872</v>
       </c>
       <c r="C743" s="33" t="s">
-        <v>1570</v>
+        <v>2873</v>
       </c>
       <c r="D743" s="33" t="s">
         <v>805</v>
@@ -71819,33 +71831,33 @@
         <v>1567</v>
       </c>
       <c r="F743" s="33" t="s">
-        <v>2887</v>
+        <v>2874</v>
       </c>
       <c r="G743" s="33" t="s">
-        <v>2888</v>
+        <v>2875</v>
       </c>
       <c r="H743" s="33">
-        <v>12980</v>
+        <v>13840</v>
       </c>
       <c r="I743" s="33">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J743" s="33" t="s">
-        <v>1148</v>
+        <v>2876</v>
       </c>
       <c r="K743" s="33" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="744" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A744" s="33" t="s">
-        <v>65</v>
+        <v>1334</v>
       </c>
       <c r="B744" s="33" t="s">
-        <v>2889</v>
+        <v>2886</v>
       </c>
       <c r="C744" s="33" t="s">
-        <v>2890</v>
+        <v>1570</v>
       </c>
       <c r="D744" s="33" t="s">
         <v>805</v>
@@ -71854,33 +71866,33 @@
         <v>1567</v>
       </c>
       <c r="F744" s="33" t="s">
-        <v>2891</v>
+        <v>2887</v>
       </c>
       <c r="G744" s="33" t="s">
-        <v>2892</v>
+        <v>2888</v>
       </c>
       <c r="H744" s="33">
-        <v>26770</v>
+        <v>12980</v>
       </c>
       <c r="I744" s="33">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="J744" s="33" t="s">
-        <v>2893</v>
+        <v>1148</v>
       </c>
       <c r="K744" s="33" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="745" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A745" s="33" t="s">
-        <v>3743</v>
+        <v>65</v>
       </c>
       <c r="B745" s="33" t="s">
-        <v>3753</v>
+        <v>2889</v>
       </c>
       <c r="C745" s="33" t="s">
-        <v>1566</v>
+        <v>2890</v>
       </c>
       <c r="D745" s="33" t="s">
         <v>805</v>
@@ -71889,22 +71901,22 @@
         <v>1567</v>
       </c>
       <c r="F745" s="33" t="s">
-        <v>727</v>
+        <v>2891</v>
       </c>
       <c r="G745" s="33" t="s">
-        <v>3762</v>
+        <v>2892</v>
       </c>
       <c r="H745" s="33">
-        <v>9646</v>
+        <v>26770</v>
       </c>
       <c r="I745" s="33">
-        <v>45</v>
+        <v>380</v>
       </c>
       <c r="J745" s="33" t="s">
-        <v>3748</v>
+        <v>2893</v>
       </c>
       <c r="K745" s="33" t="s">
-        <v>675</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="746" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -71912,10 +71924,10 @@
         <v>3743</v>
       </c>
       <c r="B746" s="33" t="s">
-        <v>3750</v>
+        <v>3753</v>
       </c>
       <c r="C746" s="33" t="s">
-        <v>3751</v>
+        <v>1566</v>
       </c>
       <c r="D746" s="33" t="s">
         <v>805</v>
@@ -71927,19 +71939,19 @@
         <v>727</v>
       </c>
       <c r="G746" s="33" t="s">
-        <v>3754</v>
+        <v>3762</v>
       </c>
       <c r="H746" s="33">
-        <v>8605</v>
+        <v>9646</v>
       </c>
       <c r="I746" s="33">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J746" s="33" t="s">
         <v>3748</v>
       </c>
       <c r="K746" s="33" t="s">
-        <v>3313</v>
+        <v>675</v>
       </c>
     </row>
     <row r="747" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -71947,7 +71959,7 @@
         <v>3743</v>
       </c>
       <c r="B747" s="33" t="s">
-        <v>3752</v>
+        <v>3750</v>
       </c>
       <c r="C747" s="33" t="s">
         <v>3751</v>
@@ -71962,13 +71974,13 @@
         <v>727</v>
       </c>
       <c r="G747" s="33" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="H747" s="33">
-        <v>8749</v>
+        <v>8605</v>
       </c>
       <c r="I747" s="33">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="J747" s="33" t="s">
         <v>3748</v>
@@ -71982,10 +71994,10 @@
         <v>3743</v>
       </c>
       <c r="B748" s="33" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="C748" s="33" t="s">
-        <v>1566</v>
+        <v>3751</v>
       </c>
       <c r="D748" s="33" t="s">
         <v>805</v>
@@ -71997,13 +72009,13 @@
         <v>727</v>
       </c>
       <c r="G748" s="33" t="s">
-        <v>3759</v>
+        <v>3755</v>
       </c>
       <c r="H748" s="33">
-        <v>8890</v>
+        <v>8749</v>
       </c>
       <c r="I748" s="33">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="J748" s="33" t="s">
         <v>3748</v>
@@ -72017,7 +72029,7 @@
         <v>3743</v>
       </c>
       <c r="B749" s="33" t="s">
-        <v>3750</v>
+        <v>3753</v>
       </c>
       <c r="C749" s="33" t="s">
         <v>1566</v>
@@ -72032,13 +72044,13 @@
         <v>727</v>
       </c>
       <c r="G749" s="33" t="s">
-        <v>3756</v>
+        <v>3759</v>
       </c>
       <c r="H749" s="33">
-        <v>9301</v>
+        <v>8890</v>
       </c>
       <c r="I749" s="33">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J749" s="33" t="s">
         <v>3748</v>
@@ -72067,13 +72079,13 @@
         <v>727</v>
       </c>
       <c r="G750" s="33" t="s">
-        <v>3757</v>
+        <v>3756</v>
       </c>
       <c r="H750" s="33">
-        <v>9375</v>
+        <v>9301</v>
       </c>
       <c r="I750" s="33">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J750" s="33" t="s">
         <v>3748</v>
@@ -72102,13 +72114,13 @@
         <v>727</v>
       </c>
       <c r="G751" s="33" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="H751" s="33">
-        <v>9430</v>
+        <v>9375</v>
       </c>
       <c r="I751" s="33">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J751" s="33" t="s">
         <v>3748</v>
@@ -72122,7 +72134,7 @@
         <v>3743</v>
       </c>
       <c r="B752" s="33" t="s">
-        <v>3753</v>
+        <v>3750</v>
       </c>
       <c r="C752" s="33" t="s">
         <v>1566</v>
@@ -72137,13 +72149,13 @@
         <v>727</v>
       </c>
       <c r="G752" s="33" t="s">
-        <v>3761</v>
+        <v>3758</v>
       </c>
       <c r="H752" s="33">
-        <v>9588</v>
+        <v>9430</v>
       </c>
       <c r="I752" s="33">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="J752" s="33" t="s">
         <v>3748</v>
@@ -72172,13 +72184,13 @@
         <v>727</v>
       </c>
       <c r="G753" s="33" t="s">
-        <v>3760</v>
+        <v>3761</v>
       </c>
       <c r="H753" s="33">
-        <v>9589</v>
+        <v>9588</v>
       </c>
       <c r="I753" s="33">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="J753" s="33" t="s">
         <v>3748</v>
@@ -72189,13 +72201,13 @@
     </row>
     <row r="754" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A754" s="33" t="s">
-        <v>3728</v>
+        <v>3743</v>
       </c>
       <c r="B754" s="33" t="s">
-        <v>3729</v>
+        <v>3753</v>
       </c>
       <c r="C754" s="33" t="s">
-        <v>3361</v>
+        <v>1566</v>
       </c>
       <c r="D754" s="33" t="s">
         <v>805</v>
@@ -72207,54 +72219,54 @@
         <v>727</v>
       </c>
       <c r="G754" s="33" t="s">
-        <v>3733</v>
+        <v>3760</v>
       </c>
       <c r="H754" s="33">
-        <v>11670</v>
+        <v>9589</v>
       </c>
       <c r="I754" s="33">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J754" s="33" t="s">
-        <v>3718</v>
+        <v>3748</v>
       </c>
       <c r="K754" s="33" t="s">
-        <v>675</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="755" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A755" s="33" t="s">
-        <v>50</v>
+        <v>3728</v>
       </c>
       <c r="B755" s="33" t="s">
-        <v>3013</v>
+        <v>3729</v>
       </c>
       <c r="C755" s="33" t="s">
-        <v>2932</v>
+        <v>3361</v>
       </c>
       <c r="D755" s="33" t="s">
-        <v>744</v>
+        <v>805</v>
       </c>
       <c r="E755" s="33" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F755" s="33" t="s">
-        <v>3019</v>
+        <v>727</v>
       </c>
       <c r="G755" s="33" t="s">
-        <v>3020</v>
+        <v>3733</v>
       </c>
       <c r="H755" s="33">
-        <v>18766</v>
+        <v>11670</v>
       </c>
       <c r="I755" s="33">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="J755" s="33" t="s">
-        <v>1103</v>
+        <v>3718</v>
       </c>
       <c r="K755" s="33" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="756" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -72265,25 +72277,25 @@
         <v>3013</v>
       </c>
       <c r="C756" s="33" t="s">
-        <v>3014</v>
+        <v>2932</v>
       </c>
       <c r="D756" s="33" t="s">
-        <v>805</v>
+        <v>744</v>
       </c>
       <c r="E756" s="33" t="s">
-        <v>1600</v>
+        <v>1612</v>
       </c>
       <c r="F756" s="33" t="s">
-        <v>3016</v>
+        <v>3019</v>
       </c>
       <c r="G756" s="33" t="s">
-        <v>3018</v>
+        <v>3020</v>
       </c>
       <c r="H756" s="33">
-        <v>53100</v>
+        <v>18766</v>
       </c>
       <c r="I756" s="33">
-        <v>3500</v>
+        <v>127</v>
       </c>
       <c r="J756" s="33" t="s">
         <v>1103</v>
@@ -72297,40 +72309,34 @@
         <v>50</v>
       </c>
       <c r="B757" s="33" t="s">
-        <v>2924</v>
+        <v>3013</v>
       </c>
       <c r="C757" s="33" t="s">
-        <v>2927</v>
+        <v>3014</v>
       </c>
       <c r="D757" s="33" t="s">
-        <v>744</v>
+        <v>805</v>
       </c>
       <c r="E757" s="33" t="s">
         <v>1600</v>
       </c>
       <c r="F757" s="33" t="s">
-        <v>2928</v>
+        <v>3016</v>
       </c>
       <c r="G757" s="33" t="s">
-        <v>2928</v>
-      </c>
-      <c r="H757" s="34">
-        <v>86940</v>
+        <v>3018</v>
+      </c>
+      <c r="H757" s="33">
+        <v>53100</v>
       </c>
       <c r="I757" s="33">
-        <v>1040</v>
+        <v>3500</v>
       </c>
       <c r="J757" s="33" t="s">
-        <v>2929</v>
+        <v>1103</v>
       </c>
       <c r="K757" s="33" t="s">
         <v>676</v>
-      </c>
-      <c r="O757" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="P757" s="2" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="758" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -72341,25 +72347,25 @@
         <v>2924</v>
       </c>
       <c r="C758" s="33" t="s">
-        <v>2932</v>
+        <v>2927</v>
       </c>
       <c r="D758" s="33" t="s">
         <v>744</v>
       </c>
       <c r="E758" s="33" t="s">
-        <v>1612</v>
+        <v>1600</v>
       </c>
       <c r="F758" s="33" t="s">
-        <v>2933</v>
+        <v>2928</v>
       </c>
       <c r="G758" s="33" t="s">
-        <v>2933</v>
+        <v>2928</v>
       </c>
       <c r="H758" s="34">
-        <v>118880</v>
+        <v>86940</v>
       </c>
       <c r="I758" s="33">
-        <v>1930</v>
+        <v>1040</v>
       </c>
       <c r="J758" s="33" t="s">
         <v>2929</v>
@@ -72379,34 +72385,40 @@
         <v>50</v>
       </c>
       <c r="B759" s="33" t="s">
-        <v>3013</v>
+        <v>2924</v>
       </c>
       <c r="C759" s="33" t="s">
-        <v>3014</v>
+        <v>2932</v>
       </c>
       <c r="D759" s="33" t="s">
         <v>744</v>
       </c>
       <c r="E759" s="33" t="s">
-        <v>1600</v>
+        <v>1612</v>
       </c>
       <c r="F759" s="33" t="s">
-        <v>3015</v>
+        <v>2933</v>
       </c>
       <c r="G759" s="33" t="s">
-        <v>3016</v>
-      </c>
-      <c r="H759" s="33" t="s">
-        <v>3017</v>
-      </c>
-      <c r="I759" s="33" t="s">
-        <v>727</v>
+        <v>2933</v>
+      </c>
+      <c r="H759" s="34">
+        <v>118880</v>
+      </c>
+      <c r="I759" s="33">
+        <v>1930</v>
       </c>
       <c r="J759" s="33" t="s">
-        <v>1103</v>
+        <v>2929</v>
       </c>
       <c r="K759" s="33" t="s">
         <v>676</v>
+      </c>
+      <c r="O759" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="P759" s="2" t="s">
+        <v>1680</v>
       </c>
     </row>
     <row r="760" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -72414,34 +72426,34 @@
         <v>50</v>
       </c>
       <c r="B760" s="33" t="s">
-        <v>1335</v>
+        <v>3013</v>
       </c>
       <c r="C760" s="33" t="s">
-        <v>676</v>
+        <v>3014</v>
       </c>
       <c r="D760" s="33" t="s">
-        <v>805</v>
+        <v>744</v>
       </c>
       <c r="E760" s="33" t="s">
         <v>1600</v>
       </c>
       <c r="F760" s="33" t="s">
-        <v>3011</v>
+        <v>3015</v>
       </c>
       <c r="G760" s="33" t="s">
-        <v>3012</v>
+        <v>3016</v>
       </c>
       <c r="H760" s="33" t="s">
-        <v>3269</v>
+        <v>3017</v>
       </c>
       <c r="I760" s="33" t="s">
         <v>727</v>
       </c>
       <c r="J760" s="33" t="s">
-        <v>2897</v>
+        <v>1103</v>
       </c>
       <c r="K760" s="33" t="s">
-        <v>3577</v>
+        <v>676</v>
       </c>
     </row>
     <row r="761" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -72449,7 +72461,7 @@
         <v>50</v>
       </c>
       <c r="B761" s="33" t="s">
-        <v>2936</v>
+        <v>1335</v>
       </c>
       <c r="C761" s="33" t="s">
         <v>676</v>
@@ -72458,31 +72470,25 @@
         <v>805</v>
       </c>
       <c r="E761" s="33" t="s">
-        <v>1567</v>
+        <v>1600</v>
       </c>
       <c r="F761" s="33" t="s">
-        <v>3009</v>
+        <v>3011</v>
       </c>
       <c r="G761" s="33" t="s">
-        <v>3010</v>
-      </c>
-      <c r="H761" s="34">
-        <v>42490</v>
-      </c>
-      <c r="I761" s="33">
-        <v>630</v>
+        <v>3012</v>
+      </c>
+      <c r="H761" s="33" t="s">
+        <v>3269</v>
+      </c>
+      <c r="I761" s="33" t="s">
+        <v>727</v>
       </c>
       <c r="J761" s="33" t="s">
         <v>2897</v>
       </c>
       <c r="K761" s="33" t="s">
-        <v>3576</v>
-      </c>
-      <c r="O761" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="P761" s="2" t="s">
-        <v>1680</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="762" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -72490,10 +72496,10 @@
         <v>50</v>
       </c>
       <c r="B762" s="33" t="s">
-        <v>2894</v>
+        <v>2936</v>
       </c>
       <c r="C762" s="33" t="s">
-        <v>2905</v>
+        <v>676</v>
       </c>
       <c r="D762" s="33" t="s">
         <v>805</v>
@@ -72502,22 +72508,22 @@
         <v>1567</v>
       </c>
       <c r="F762" s="33" t="s">
-        <v>3004</v>
+        <v>3009</v>
       </c>
       <c r="G762" s="33" t="s">
-        <v>3005</v>
+        <v>3010</v>
       </c>
       <c r="H762" s="34">
-        <v>29650</v>
+        <v>42490</v>
       </c>
       <c r="I762" s="33">
-        <v>160</v>
+        <v>630</v>
       </c>
       <c r="J762" s="33" t="s">
-        <v>2900</v>
+        <v>2897</v>
       </c>
       <c r="K762" s="33" t="s">
-        <v>1228</v>
+        <v>3576</v>
       </c>
       <c r="O762" s="2" t="s">
         <v>1680</v>
@@ -72531,10 +72537,10 @@
         <v>50</v>
       </c>
       <c r="B763" s="33" t="s">
-        <v>3006</v>
+        <v>2894</v>
       </c>
       <c r="C763" s="33" t="s">
-        <v>1566</v>
+        <v>2905</v>
       </c>
       <c r="D763" s="33" t="s">
         <v>805</v>
@@ -72543,22 +72549,28 @@
         <v>1567</v>
       </c>
       <c r="F763" s="33" t="s">
-        <v>3007</v>
+        <v>3004</v>
       </c>
       <c r="G763" s="33" t="s">
-        <v>3008</v>
+        <v>3005</v>
       </c>
       <c r="H763" s="34">
-        <v>35320</v>
+        <v>29650</v>
       </c>
       <c r="I763" s="33">
-        <v>360</v>
+        <v>160</v>
       </c>
       <c r="J763" s="33" t="s">
-        <v>1514</v>
+        <v>2900</v>
       </c>
       <c r="K763" s="33" t="s">
         <v>1228</v>
+      </c>
+      <c r="O763" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="P763" s="2" t="s">
+        <v>1680</v>
       </c>
     </row>
     <row r="764" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -72566,10 +72578,10 @@
         <v>50</v>
       </c>
       <c r="B764" s="33" t="s">
-        <v>2894</v>
+        <v>3006</v>
       </c>
       <c r="C764" s="33" t="s">
-        <v>1917</v>
+        <v>1566</v>
       </c>
       <c r="D764" s="33" t="s">
         <v>805</v>
@@ -72578,22 +72590,22 @@
         <v>1567</v>
       </c>
       <c r="F764" s="33" t="s">
-        <v>2984</v>
+        <v>3007</v>
       </c>
       <c r="G764" s="33" t="s">
-        <v>2985</v>
+        <v>3008</v>
       </c>
       <c r="H764" s="34">
-        <v>23350</v>
+        <v>35320</v>
       </c>
       <c r="I764" s="33">
-        <v>190</v>
+        <v>360</v>
       </c>
       <c r="J764" s="33" t="s">
-        <v>2897</v>
+        <v>1514</v>
       </c>
       <c r="K764" s="33" t="s">
-        <v>1322</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="765" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -72601,7 +72613,7 @@
         <v>50</v>
       </c>
       <c r="B765" s="33" t="s">
-        <v>2986</v>
+        <v>2894</v>
       </c>
       <c r="C765" s="33" t="s">
         <v>1917</v>
@@ -72613,19 +72625,19 @@
         <v>1567</v>
       </c>
       <c r="F765" s="33" t="s">
-        <v>2987</v>
+        <v>2984</v>
       </c>
       <c r="G765" s="33" t="s">
-        <v>2988</v>
+        <v>2985</v>
       </c>
       <c r="H765" s="34">
-        <v>23800</v>
+        <v>23350</v>
       </c>
       <c r="I765" s="33">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="J765" s="33" t="s">
-        <v>1514</v>
+        <v>2897</v>
       </c>
       <c r="K765" s="33" t="s">
         <v>1322</v>
@@ -72636,10 +72648,10 @@
         <v>50</v>
       </c>
       <c r="B766" s="33" t="s">
-        <v>2894</v>
+        <v>2986</v>
       </c>
       <c r="C766" s="33" t="s">
-        <v>2905</v>
+        <v>1917</v>
       </c>
       <c r="D766" s="33" t="s">
         <v>805</v>
@@ -72648,19 +72660,19 @@
         <v>1567</v>
       </c>
       <c r="F766" s="33" t="s">
-        <v>2989</v>
+        <v>2987</v>
       </c>
       <c r="G766" s="33" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="H766" s="34">
-        <v>23880</v>
+        <v>23800</v>
       </c>
       <c r="I766" s="33">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="J766" s="33" t="s">
-        <v>2900</v>
+        <v>1514</v>
       </c>
       <c r="K766" s="33" t="s">
         <v>1322</v>
@@ -72674,7 +72686,7 @@
         <v>2894</v>
       </c>
       <c r="C767" s="33" t="s">
-        <v>1566</v>
+        <v>2905</v>
       </c>
       <c r="D767" s="33" t="s">
         <v>805</v>
@@ -72683,19 +72695,19 @@
         <v>1567</v>
       </c>
       <c r="F767" s="33" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
       <c r="G767" s="33" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
       <c r="H767" s="34">
-        <v>24090</v>
+        <v>23880</v>
       </c>
       <c r="I767" s="33">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="J767" s="33" t="s">
-        <v>2897</v>
+        <v>2900</v>
       </c>
       <c r="K767" s="33" t="s">
         <v>1322</v>
@@ -72706,7 +72718,7 @@
         <v>50</v>
       </c>
       <c r="B768" s="33" t="s">
-        <v>2993</v>
+        <v>2894</v>
       </c>
       <c r="C768" s="33" t="s">
         <v>1566</v>
@@ -72718,19 +72730,19 @@
         <v>1567</v>
       </c>
       <c r="F768" s="33" t="s">
-        <v>2994</v>
+        <v>2991</v>
       </c>
       <c r="G768" s="33" t="s">
-        <v>2995</v>
+        <v>2992</v>
       </c>
       <c r="H768" s="34">
-        <v>24130</v>
+        <v>24090</v>
       </c>
       <c r="I768" s="33">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="J768" s="33" t="s">
-        <v>1514</v>
+        <v>2897</v>
       </c>
       <c r="K768" s="33" t="s">
         <v>1322</v>
@@ -72741,7 +72753,7 @@
         <v>50</v>
       </c>
       <c r="B769" s="33" t="s">
-        <v>2894</v>
+        <v>2993</v>
       </c>
       <c r="C769" s="33" t="s">
         <v>1566</v>
@@ -72753,19 +72765,19 @@
         <v>1567</v>
       </c>
       <c r="F769" s="33" t="s">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="G769" s="33" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="H769" s="34">
-        <v>24220</v>
+        <v>24130</v>
       </c>
       <c r="I769" s="33">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="J769" s="33" t="s">
-        <v>2897</v>
+        <v>1514</v>
       </c>
       <c r="K769" s="33" t="s">
         <v>1322</v>
@@ -72788,16 +72800,16 @@
         <v>1567</v>
       </c>
       <c r="F770" s="33" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
       <c r="G770" s="33" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="H770" s="34">
-        <v>24370</v>
+        <v>24220</v>
       </c>
       <c r="I770" s="33">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="J770" s="33" t="s">
         <v>2897</v>
@@ -72823,16 +72835,16 @@
         <v>1567</v>
       </c>
       <c r="F771" s="33" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
       <c r="G771" s="33" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="H771" s="34">
-        <v>24430</v>
+        <v>24370</v>
       </c>
       <c r="I771" s="33">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="J771" s="33" t="s">
         <v>2897</v>
@@ -72858,16 +72870,16 @@
         <v>1567</v>
       </c>
       <c r="F772" s="33" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="G772" s="33" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="H772" s="34">
-        <v>25140</v>
+        <v>24430</v>
       </c>
       <c r="I772" s="33">
-        <v>780</v>
+        <v>180</v>
       </c>
       <c r="J772" s="33" t="s">
         <v>2897</v>
@@ -72884,7 +72896,7 @@
         <v>2894</v>
       </c>
       <c r="C773" s="33" t="s">
-        <v>1917</v>
+        <v>1566</v>
       </c>
       <c r="D773" s="33" t="s">
         <v>805</v>
@@ -72893,22 +72905,22 @@
         <v>1567</v>
       </c>
       <c r="F773" s="33" t="s">
-        <v>2895</v>
+        <v>3002</v>
       </c>
       <c r="G773" s="33" t="s">
-        <v>2896</v>
+        <v>3003</v>
       </c>
       <c r="H773" s="34">
-        <v>12880</v>
+        <v>25140</v>
       </c>
       <c r="I773" s="33">
-        <v>60</v>
+        <v>780</v>
       </c>
       <c r="J773" s="33" t="s">
         <v>2897</v>
       </c>
       <c r="K773" s="33" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="774" spans="1:34" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -72919,7 +72931,7 @@
         <v>2894</v>
       </c>
       <c r="C774" s="33" t="s">
-        <v>1566</v>
+        <v>1917</v>
       </c>
       <c r="D774" s="33" t="s">
         <v>805</v>
@@ -72928,19 +72940,19 @@
         <v>1567</v>
       </c>
       <c r="F774" s="33" t="s">
-        <v>2898</v>
+        <v>2895</v>
       </c>
       <c r="G774" s="33" t="s">
-        <v>2899</v>
+        <v>2896</v>
       </c>
       <c r="H774" s="34">
-        <v>12890</v>
+        <v>12880</v>
       </c>
       <c r="I774" s="33">
         <v>60</v>
       </c>
       <c r="J774" s="33" t="s">
-        <v>2900</v>
+        <v>2897</v>
       </c>
       <c r="K774" s="33" t="s">
         <v>1318</v>
@@ -72951,10 +72963,10 @@
         <v>50</v>
       </c>
       <c r="B775" s="33" t="s">
-        <v>2955</v>
+        <v>2894</v>
       </c>
       <c r="C775" s="33" t="s">
-        <v>1917</v>
+        <v>1566</v>
       </c>
       <c r="D775" s="33" t="s">
         <v>805</v>
@@ -72963,49 +72975,22 @@
         <v>1567</v>
       </c>
       <c r="F775" s="33" t="s">
-        <v>2956</v>
+        <v>2898</v>
       </c>
       <c r="G775" s="33" t="s">
-        <v>2957</v>
+        <v>2899</v>
       </c>
       <c r="H775" s="34">
-        <v>18540</v>
+        <v>12890</v>
       </c>
       <c r="I775" s="33">
         <v>60</v>
       </c>
       <c r="J775" s="33" t="s">
-        <v>2897</v>
+        <v>2900</v>
       </c>
       <c r="K775" s="33" t="s">
-        <v>1323</v>
-      </c>
-      <c r="O775" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="P775" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="U775" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="V775" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AA775" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AB775" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AE775" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AG775" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AH775" s="2" t="s">
-        <v>1680</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="776" spans="1:34" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -73013,10 +72998,10 @@
         <v>50</v>
       </c>
       <c r="B776" s="33" t="s">
-        <v>2916</v>
+        <v>2955</v>
       </c>
       <c r="C776" s="33" t="s">
-        <v>1566</v>
+        <v>1917</v>
       </c>
       <c r="D776" s="33" t="s">
         <v>805</v>
@@ -73025,22 +73010,49 @@
         <v>1567</v>
       </c>
       <c r="F776" s="33" t="s">
-        <v>2958</v>
+        <v>2956</v>
       </c>
       <c r="G776" s="33" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
       <c r="H776" s="34">
-        <v>19390</v>
+        <v>18540</v>
       </c>
       <c r="I776" s="33">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J776" s="33" t="s">
         <v>2897</v>
       </c>
       <c r="K776" s="33" t="s">
         <v>1323</v>
+      </c>
+      <c r="O776" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="P776" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="U776" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="V776" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AA776" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AB776" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AE776" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AG776" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AH776" s="2" t="s">
+        <v>1680</v>
       </c>
     </row>
     <row r="777" spans="1:34" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -73048,10 +73060,10 @@
         <v>50</v>
       </c>
       <c r="B777" s="33" t="s">
-        <v>1335</v>
+        <v>2916</v>
       </c>
       <c r="C777" s="33" t="s">
-        <v>1629</v>
+        <v>1566</v>
       </c>
       <c r="D777" s="33" t="s">
         <v>805</v>
@@ -73060,16 +73072,16 @@
         <v>1567</v>
       </c>
       <c r="F777" s="33" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="G777" s="33" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="H777" s="34">
-        <v>19440</v>
+        <v>19390</v>
       </c>
       <c r="I777" s="33">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="J777" s="33" t="s">
         <v>2897</v>
@@ -73086,7 +73098,7 @@
         <v>1335</v>
       </c>
       <c r="C778" s="33" t="s">
-        <v>1748</v>
+        <v>1629</v>
       </c>
       <c r="D778" s="33" t="s">
         <v>805</v>
@@ -73095,16 +73107,16 @@
         <v>1567</v>
       </c>
       <c r="F778" s="33" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="G778" s="33" t="s">
-        <v>2963</v>
+        <v>2961</v>
       </c>
       <c r="H778" s="34">
-        <v>19620</v>
+        <v>19440</v>
       </c>
       <c r="I778" s="33">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="J778" s="33" t="s">
         <v>2897</v>
@@ -73118,10 +73130,10 @@
         <v>50</v>
       </c>
       <c r="B779" s="33" t="s">
-        <v>2952</v>
+        <v>1335</v>
       </c>
       <c r="C779" s="33" t="s">
-        <v>1566</v>
+        <v>1748</v>
       </c>
       <c r="D779" s="33" t="s">
         <v>805</v>
@@ -73130,25 +73142,22 @@
         <v>1567</v>
       </c>
       <c r="F779" s="33" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="G779" s="33" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
       <c r="H779" s="34">
-        <v>19700</v>
+        <v>19620</v>
       </c>
       <c r="I779" s="33">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J779" s="33" t="s">
         <v>2897</v>
       </c>
       <c r="K779" s="33" t="s">
         <v>1323</v>
-      </c>
-      <c r="O779" s="2" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="780" spans="1:34" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -73156,7 +73165,7 @@
         <v>50</v>
       </c>
       <c r="B780" s="33" t="s">
-        <v>2955</v>
+        <v>2952</v>
       </c>
       <c r="C780" s="33" t="s">
         <v>1566</v>
@@ -73168,19 +73177,19 @@
         <v>1567</v>
       </c>
       <c r="F780" s="33" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
       <c r="G780" s="33" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="H780" s="34">
-        <v>19900</v>
+        <v>19700</v>
       </c>
       <c r="I780" s="33">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="J780" s="33" t="s">
-        <v>2968</v>
+        <v>2897</v>
       </c>
       <c r="K780" s="33" t="s">
         <v>1323</v>
@@ -73194,10 +73203,10 @@
         <v>50</v>
       </c>
       <c r="B781" s="33" t="s">
-        <v>2936</v>
+        <v>2955</v>
       </c>
       <c r="C781" s="33" t="s">
-        <v>1917</v>
+        <v>1566</v>
       </c>
       <c r="D781" s="33" t="s">
         <v>805</v>
@@ -73206,22 +73215,25 @@
         <v>1567</v>
       </c>
       <c r="F781" s="33" t="s">
-        <v>2969</v>
+        <v>2966</v>
       </c>
       <c r="G781" s="33" t="s">
-        <v>2970</v>
+        <v>2967</v>
       </c>
       <c r="H781" s="34">
-        <v>20050</v>
+        <v>19900</v>
       </c>
       <c r="I781" s="33">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="J781" s="33" t="s">
-        <v>2897</v>
+        <v>2968</v>
       </c>
       <c r="K781" s="33" t="s">
         <v>1323</v>
+      </c>
+      <c r="O781" s="2" t="s">
+        <v>1680</v>
       </c>
     </row>
     <row r="782" spans="1:34" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -73232,7 +73244,7 @@
         <v>2936</v>
       </c>
       <c r="C782" s="33" t="s">
-        <v>1748</v>
+        <v>1917</v>
       </c>
       <c r="D782" s="33" t="s">
         <v>805</v>
@@ -73241,16 +73253,16 @@
         <v>1567</v>
       </c>
       <c r="F782" s="33" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="G782" s="33" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="H782" s="34">
-        <v>20430</v>
+        <v>20050</v>
       </c>
       <c r="I782" s="33">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J782" s="33" t="s">
         <v>2897</v>
@@ -73264,10 +73276,10 @@
         <v>50</v>
       </c>
       <c r="B783" s="33" t="s">
-        <v>2952</v>
+        <v>2936</v>
       </c>
       <c r="C783" s="33" t="s">
-        <v>1917</v>
+        <v>1748</v>
       </c>
       <c r="D783" s="33" t="s">
         <v>805</v>
@@ -73276,13 +73288,13 @@
         <v>1567</v>
       </c>
       <c r="F783" s="33" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
       <c r="G783" s="33" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="H783" s="34">
-        <v>20720</v>
+        <v>20430</v>
       </c>
       <c r="I783" s="33">
         <v>70</v>
@@ -73299,10 +73311,10 @@
         <v>50</v>
       </c>
       <c r="B784" s="33" t="s">
-        <v>2975</v>
+        <v>2952</v>
       </c>
       <c r="C784" s="33" t="s">
-        <v>1566</v>
+        <v>1917</v>
       </c>
       <c r="D784" s="33" t="s">
         <v>805</v>
@@ -73311,19 +73323,19 @@
         <v>1567</v>
       </c>
       <c r="F784" s="33" t="s">
-        <v>2976</v>
+        <v>2973</v>
       </c>
       <c r="G784" s="33" t="s">
-        <v>2977</v>
+        <v>2974</v>
       </c>
       <c r="H784" s="34">
-        <v>20980</v>
+        <v>20720</v>
       </c>
       <c r="I784" s="33">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J784" s="33" t="s">
-        <v>1514</v>
+        <v>2897</v>
       </c>
       <c r="K784" s="33" t="s">
         <v>1323</v>
@@ -73334,7 +73346,7 @@
         <v>50</v>
       </c>
       <c r="B785" s="33" t="s">
-        <v>2894</v>
+        <v>2975</v>
       </c>
       <c r="C785" s="33" t="s">
         <v>1566</v>
@@ -73346,19 +73358,19 @@
         <v>1567</v>
       </c>
       <c r="F785" s="33" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
       <c r="G785" s="33" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
       <c r="H785" s="34">
-        <v>21370</v>
+        <v>20980</v>
       </c>
       <c r="I785" s="33">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J785" s="33" t="s">
-        <v>2897</v>
+        <v>1514</v>
       </c>
       <c r="K785" s="33" t="s">
         <v>1323</v>
@@ -73369,10 +73381,10 @@
         <v>50</v>
       </c>
       <c r="B786" s="33" t="s">
-        <v>1335</v>
+        <v>2894</v>
       </c>
       <c r="C786" s="33" t="s">
-        <v>1748</v>
+        <v>1566</v>
       </c>
       <c r="D786" s="33" t="s">
         <v>805</v>
@@ -73381,16 +73393,16 @@
         <v>1567</v>
       </c>
       <c r="F786" s="33" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
       <c r="G786" s="33" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
       <c r="H786" s="34">
-        <v>21580</v>
+        <v>21370</v>
       </c>
       <c r="I786" s="33">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="J786" s="33" t="s">
         <v>2897</v>
@@ -73404,10 +73416,10 @@
         <v>50</v>
       </c>
       <c r="B787" s="33" t="s">
-        <v>2894</v>
+        <v>1335</v>
       </c>
       <c r="C787" s="33" t="s">
-        <v>1917</v>
+        <v>1748</v>
       </c>
       <c r="D787" s="33" t="s">
         <v>805</v>
@@ -73416,19 +73428,19 @@
         <v>1567</v>
       </c>
       <c r="F787" s="33" t="s">
-        <v>2982</v>
+        <v>2980</v>
       </c>
       <c r="G787" s="33" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="H787" s="34">
-        <v>21900</v>
+        <v>21580</v>
       </c>
       <c r="I787" s="33">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="J787" s="33" t="s">
-        <v>2900</v>
+        <v>2897</v>
       </c>
       <c r="K787" s="33" t="s">
         <v>1323</v>
@@ -73439,10 +73451,10 @@
         <v>50</v>
       </c>
       <c r="B788" s="33" t="s">
-        <v>2936</v>
+        <v>2894</v>
       </c>
       <c r="C788" s="33" t="s">
-        <v>1566</v>
+        <v>1917</v>
       </c>
       <c r="D788" s="33" t="s">
         <v>805</v>
@@ -73451,22 +73463,22 @@
         <v>1567</v>
       </c>
       <c r="F788" s="33" t="s">
-        <v>2937</v>
+        <v>2982</v>
       </c>
       <c r="G788" s="33" t="s">
-        <v>2938</v>
+        <v>2983</v>
       </c>
       <c r="H788" s="34">
-        <v>16160</v>
+        <v>21900</v>
       </c>
       <c r="I788" s="33">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="J788" s="33" t="s">
-        <v>2897</v>
+        <v>2900</v>
       </c>
       <c r="K788" s="33" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="789" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -73474,7 +73486,7 @@
         <v>50</v>
       </c>
       <c r="B789" s="33" t="s">
-        <v>2916</v>
+        <v>2936</v>
       </c>
       <c r="C789" s="33" t="s">
         <v>1566</v>
@@ -73486,16 +73498,16 @@
         <v>1567</v>
       </c>
       <c r="F789" s="33" t="s">
-        <v>2939</v>
+        <v>2937</v>
       </c>
       <c r="G789" s="33" t="s">
-        <v>2940</v>
+        <v>2938</v>
       </c>
       <c r="H789" s="34">
-        <v>16270</v>
+        <v>16160</v>
       </c>
       <c r="I789" s="33">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J789" s="33" t="s">
         <v>2897</v>
@@ -73509,10 +73521,10 @@
         <v>50</v>
       </c>
       <c r="B790" s="33" t="s">
-        <v>1335</v>
+        <v>2916</v>
       </c>
       <c r="C790" s="33" t="s">
-        <v>1629</v>
+        <v>1566</v>
       </c>
       <c r="D790" s="33" t="s">
         <v>805</v>
@@ -73521,16 +73533,16 @@
         <v>1567</v>
       </c>
       <c r="F790" s="33" t="s">
-        <v>2941</v>
+        <v>2939</v>
       </c>
       <c r="G790" s="33" t="s">
-        <v>2942</v>
+        <v>2940</v>
       </c>
       <c r="H790" s="34">
-        <v>16840</v>
+        <v>16270</v>
       </c>
       <c r="I790" s="33">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="J790" s="33" t="s">
         <v>2897</v>
@@ -73556,16 +73568,16 @@
         <v>1567</v>
       </c>
       <c r="F791" s="33" t="s">
-        <v>2943</v>
+        <v>2941</v>
       </c>
       <c r="G791" s="33" t="s">
-        <v>2944</v>
+        <v>2942</v>
       </c>
       <c r="H791" s="34">
-        <v>17310</v>
+        <v>16840</v>
       </c>
       <c r="I791" s="33">
-        <v>380</v>
+        <v>110</v>
       </c>
       <c r="J791" s="33" t="s">
         <v>2897</v>
@@ -73582,7 +73594,7 @@
         <v>1335</v>
       </c>
       <c r="C792" s="33" t="s">
-        <v>2945</v>
+        <v>1629</v>
       </c>
       <c r="D792" s="33" t="s">
         <v>805</v>
@@ -73591,16 +73603,16 @@
         <v>1567</v>
       </c>
       <c r="F792" s="33" t="s">
-        <v>2946</v>
+        <v>2943</v>
       </c>
       <c r="G792" s="33" t="s">
-        <v>2947</v>
+        <v>2944</v>
       </c>
       <c r="H792" s="34">
-        <v>17680</v>
+        <v>17310</v>
       </c>
       <c r="I792" s="33">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="J792" s="33" t="s">
         <v>2897</v>
@@ -73614,10 +73626,10 @@
         <v>50</v>
       </c>
       <c r="B793" s="33" t="s">
-        <v>2936</v>
+        <v>1335</v>
       </c>
       <c r="C793" s="33" t="s">
-        <v>1917</v>
+        <v>2945</v>
       </c>
       <c r="D793" s="33" t="s">
         <v>805</v>
@@ -73626,16 +73638,16 @@
         <v>1567</v>
       </c>
       <c r="F793" s="33" t="s">
-        <v>2948</v>
+        <v>2946</v>
       </c>
       <c r="G793" s="33" t="s">
-        <v>2949</v>
+        <v>2947</v>
       </c>
       <c r="H793" s="34">
-        <v>17720</v>
+        <v>17680</v>
       </c>
       <c r="I793" s="33">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J793" s="33" t="s">
         <v>2897</v>
@@ -73661,16 +73673,16 @@
         <v>1567</v>
       </c>
       <c r="F794" s="33" t="s">
-        <v>2950</v>
+        <v>2948</v>
       </c>
       <c r="G794" s="33" t="s">
-        <v>2951</v>
+        <v>2949</v>
       </c>
       <c r="H794" s="34">
-        <v>17900</v>
+        <v>17720</v>
       </c>
       <c r="I794" s="33">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J794" s="33" t="s">
         <v>2897</v>
@@ -73684,7 +73696,7 @@
         <v>50</v>
       </c>
       <c r="B795" s="33" t="s">
-        <v>2952</v>
+        <v>2936</v>
       </c>
       <c r="C795" s="33" t="s">
         <v>1917</v>
@@ -73696,16 +73708,16 @@
         <v>1567</v>
       </c>
       <c r="F795" s="33" t="s">
-        <v>2953</v>
+        <v>2950</v>
       </c>
       <c r="G795" s="33" t="s">
-        <v>2954</v>
+        <v>2951</v>
       </c>
       <c r="H795" s="34">
-        <v>18350</v>
+        <v>17900</v>
       </c>
       <c r="I795" s="33">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="J795" s="33" t="s">
         <v>2897</v>
@@ -73719,10 +73731,10 @@
         <v>50</v>
       </c>
       <c r="B796" s="33" t="s">
-        <v>2894</v>
+        <v>2952</v>
       </c>
       <c r="C796" s="33" t="s">
-        <v>1566</v>
+        <v>1917</v>
       </c>
       <c r="D796" s="33" t="s">
         <v>805</v>
@@ -73731,22 +73743,22 @@
         <v>1567</v>
       </c>
       <c r="F796" s="33" t="s">
-        <v>2918</v>
+        <v>2953</v>
       </c>
       <c r="G796" s="33" t="s">
-        <v>2919</v>
+        <v>2954</v>
       </c>
       <c r="H796" s="34">
-        <v>15290</v>
+        <v>18350</v>
       </c>
       <c r="I796" s="33">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J796" s="33" t="s">
         <v>2897</v>
       </c>
       <c r="K796" s="33" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="797" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -73754,10 +73766,10 @@
         <v>50</v>
       </c>
       <c r="B797" s="33" t="s">
-        <v>2920</v>
+        <v>2894</v>
       </c>
       <c r="C797" s="33" t="s">
-        <v>1748</v>
+        <v>1566</v>
       </c>
       <c r="D797" s="33" t="s">
         <v>805</v>
@@ -73766,19 +73778,19 @@
         <v>1567</v>
       </c>
       <c r="F797" s="33" t="s">
-        <v>2921</v>
+        <v>2918</v>
       </c>
       <c r="G797" s="33" t="s">
-        <v>2922</v>
+        <v>2919</v>
       </c>
       <c r="H797" s="34">
-        <v>15650</v>
+        <v>15290</v>
       </c>
       <c r="I797" s="33">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="J797" s="33" t="s">
-        <v>2923</v>
+        <v>2897</v>
       </c>
       <c r="K797" s="33" t="s">
         <v>1313</v>
@@ -73789,34 +73801,34 @@
         <v>50</v>
       </c>
       <c r="B798" s="33" t="s">
-        <v>2924</v>
+        <v>2920</v>
       </c>
       <c r="C798" s="33" t="s">
-        <v>2932</v>
+        <v>1748</v>
       </c>
       <c r="D798" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E798" s="33" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F798" s="33" t="s">
-        <v>2934</v>
+        <v>2921</v>
       </c>
       <c r="G798" s="33" t="s">
-        <v>2935</v>
+        <v>2922</v>
       </c>
       <c r="H798" s="34">
-        <v>12150</v>
+        <v>15650</v>
       </c>
       <c r="I798" s="33">
-        <v>45</v>
+        <v>300</v>
       </c>
       <c r="J798" s="33" t="s">
         <v>2923</v>
       </c>
       <c r="K798" s="33" t="s">
-        <v>1591</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="799" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -73827,25 +73839,25 @@
         <v>2924</v>
       </c>
       <c r="C799" s="33" t="s">
-        <v>2905</v>
+        <v>2932</v>
       </c>
       <c r="D799" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E799" s="33" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F799" s="33" t="s">
-        <v>2925</v>
+        <v>2934</v>
       </c>
       <c r="G799" s="33" t="s">
-        <v>2926</v>
+        <v>2935</v>
       </c>
       <c r="H799" s="34">
-        <v>15790</v>
+        <v>12150</v>
       </c>
       <c r="I799" s="33">
-        <v>460</v>
+        <v>45</v>
       </c>
       <c r="J799" s="33" t="s">
         <v>2923</v>
@@ -73862,25 +73874,25 @@
         <v>2924</v>
       </c>
       <c r="C800" s="33" t="s">
-        <v>2927</v>
+        <v>2905</v>
       </c>
       <c r="D800" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E800" s="33" t="s">
-        <v>1600</v>
+        <v>1567</v>
       </c>
       <c r="F800" s="33" t="s">
-        <v>2930</v>
+        <v>2925</v>
       </c>
       <c r="G800" s="33" t="s">
-        <v>2931</v>
+        <v>2926</v>
       </c>
       <c r="H800" s="34">
-        <v>20790</v>
+        <v>15790</v>
       </c>
       <c r="I800" s="33">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="J800" s="33" t="s">
         <v>2923</v>
@@ -73894,34 +73906,34 @@
         <v>50</v>
       </c>
       <c r="B801" s="33" t="s">
-        <v>2894</v>
+        <v>2924</v>
       </c>
       <c r="C801" s="33" t="s">
-        <v>1566</v>
+        <v>2927</v>
       </c>
       <c r="D801" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E801" s="33" t="s">
-        <v>1567</v>
+        <v>1600</v>
       </c>
       <c r="F801" s="33" t="s">
-        <v>2901</v>
+        <v>2930</v>
       </c>
       <c r="G801" s="33" t="s">
-        <v>2902</v>
+        <v>2931</v>
       </c>
       <c r="H801" s="34">
-        <v>13120</v>
+        <v>20790</v>
       </c>
       <c r="I801" s="33">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="J801" s="33" t="s">
-        <v>2897</v>
+        <v>2923</v>
       </c>
       <c r="K801" s="33" t="s">
-        <v>1319</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="802" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -73932,7 +73944,7 @@
         <v>2894</v>
       </c>
       <c r="C802" s="33" t="s">
-        <v>1917</v>
+        <v>1566</v>
       </c>
       <c r="D802" s="33" t="s">
         <v>805</v>
@@ -73941,16 +73953,16 @@
         <v>1567</v>
       </c>
       <c r="F802" s="33" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
       <c r="G802" s="33" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
       <c r="H802" s="34">
-        <v>13270</v>
+        <v>13120</v>
       </c>
       <c r="I802" s="33">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="J802" s="33" t="s">
         <v>2897</v>
@@ -73967,7 +73979,7 @@
         <v>2894</v>
       </c>
       <c r="C803" s="33" t="s">
-        <v>2905</v>
+        <v>1917</v>
       </c>
       <c r="D803" s="33" t="s">
         <v>805</v>
@@ -73976,19 +73988,19 @@
         <v>1567</v>
       </c>
       <c r="F803" s="33" t="s">
-        <v>2906</v>
+        <v>2903</v>
       </c>
       <c r="G803" s="33" t="s">
-        <v>2907</v>
+        <v>2904</v>
       </c>
       <c r="H803" s="34">
-        <v>13380</v>
+        <v>13270</v>
       </c>
       <c r="I803" s="33">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J803" s="33" t="s">
-        <v>2900</v>
+        <v>2897</v>
       </c>
       <c r="K803" s="33" t="s">
         <v>1319</v>
@@ -74002,7 +74014,7 @@
         <v>2894</v>
       </c>
       <c r="C804" s="33" t="s">
-        <v>1566</v>
+        <v>2905</v>
       </c>
       <c r="D804" s="33" t="s">
         <v>805</v>
@@ -74011,16 +74023,16 @@
         <v>1567</v>
       </c>
       <c r="F804" s="33" t="s">
-        <v>2908</v>
+        <v>2906</v>
       </c>
       <c r="G804" s="33" t="s">
-        <v>2909</v>
+        <v>2907</v>
       </c>
       <c r="H804" s="34">
-        <v>13490</v>
+        <v>13380</v>
       </c>
       <c r="I804" s="33">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J804" s="33" t="s">
         <v>2900</v>
@@ -74046,16 +74058,16 @@
         <v>1567</v>
       </c>
       <c r="F805" s="33" t="s">
-        <v>2910</v>
+        <v>2908</v>
       </c>
       <c r="G805" s="33" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="H805" s="34">
-        <v>13920</v>
+        <v>13490</v>
       </c>
       <c r="I805" s="33">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J805" s="33" t="s">
         <v>2900</v>
@@ -74081,19 +74093,19 @@
         <v>1567</v>
       </c>
       <c r="F806" s="33" t="s">
-        <v>2912</v>
+        <v>2910</v>
       </c>
       <c r="G806" s="33" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="H806" s="34">
-        <v>14110</v>
+        <v>13920</v>
       </c>
       <c r="I806" s="33">
         <v>60</v>
       </c>
       <c r="J806" s="33" t="s">
-        <v>2897</v>
+        <v>2900</v>
       </c>
       <c r="K806" s="33" t="s">
         <v>1319</v>
@@ -74116,13 +74128,13 @@
         <v>1567</v>
       </c>
       <c r="F807" s="33" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="G807" s="33" t="s">
-        <v>2915</v>
+        <v>2913</v>
       </c>
       <c r="H807" s="34">
-        <v>14320</v>
+        <v>14110</v>
       </c>
       <c r="I807" s="33">
         <v>60</v>
@@ -74139,7 +74151,7 @@
         <v>50</v>
       </c>
       <c r="B808" s="33" t="s">
-        <v>2916</v>
+        <v>2894</v>
       </c>
       <c r="C808" s="33" t="s">
         <v>1566</v>
@@ -74150,20 +74162,20 @@
       <c r="E808" s="33" t="s">
         <v>1567</v>
       </c>
-      <c r="F808" s="33">
-        <v>40</v>
+      <c r="F808" s="33" t="s">
+        <v>2914</v>
       </c>
       <c r="G808" s="33" t="s">
-        <v>2917</v>
+        <v>2915</v>
       </c>
       <c r="H808" s="34">
         <v>14320</v>
       </c>
       <c r="I808" s="33">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J808" s="33" t="s">
-        <v>1514</v>
+        <v>2897</v>
       </c>
       <c r="K808" s="33" t="s">
         <v>1319</v>
@@ -74174,34 +74186,34 @@
         <v>50</v>
       </c>
       <c r="B809" s="33" t="s">
-        <v>3013</v>
+        <v>2916</v>
       </c>
       <c r="C809" s="33" t="s">
-        <v>2932</v>
+        <v>1566</v>
       </c>
       <c r="D809" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E809" s="33" t="s">
-        <v>1612</v>
-      </c>
-      <c r="F809" s="33" t="s">
-        <v>3020</v>
+        <v>1567</v>
+      </c>
+      <c r="F809" s="33">
+        <v>40</v>
       </c>
       <c r="G809" s="33" t="s">
-        <v>3021</v>
-      </c>
-      <c r="H809" s="33">
-        <v>10705</v>
+        <v>2917</v>
+      </c>
+      <c r="H809" s="34">
+        <v>14320</v>
       </c>
       <c r="I809" s="33">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J809" s="33" t="s">
-        <v>1103</v>
+        <v>1514</v>
       </c>
       <c r="K809" s="33" t="s">
-        <v>1689</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="810" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -74209,34 +74221,34 @@
         <v>50</v>
       </c>
       <c r="B810" s="33" t="s">
-        <v>2955</v>
+        <v>3013</v>
       </c>
       <c r="C810" s="33" t="s">
-        <v>676</v>
+        <v>2932</v>
       </c>
       <c r="D810" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E810" s="33" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F810" s="33" t="s">
-        <v>3571</v>
+        <v>3020</v>
       </c>
       <c r="G810" s="33" t="s">
-        <v>3569</v>
+        <v>3021</v>
       </c>
       <c r="H810" s="33">
-        <v>8530</v>
+        <v>10705</v>
       </c>
       <c r="I810" s="33">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J810" s="33" t="s">
         <v>1103</v>
       </c>
       <c r="K810" s="33" t="s">
-        <v>3573</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="811" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -74244,7 +74256,7 @@
         <v>50</v>
       </c>
       <c r="B811" s="33" t="s">
-        <v>2936</v>
+        <v>2955</v>
       </c>
       <c r="C811" s="33" t="s">
         <v>676</v>
@@ -74256,16 +74268,16 @@
         <v>1567</v>
       </c>
       <c r="F811" s="33" t="s">
-        <v>2895</v>
+        <v>3571</v>
       </c>
       <c r="G811" s="33" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="H811" s="33">
-        <v>9660</v>
+        <v>8530</v>
       </c>
       <c r="I811" s="33">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J811" s="33" t="s">
         <v>1103</v>
@@ -74276,37 +74288,37 @@
     </row>
     <row r="812" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A812" s="33" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B812" s="33" t="s">
-        <v>3022</v>
+        <v>2936</v>
       </c>
       <c r="C812" s="33" t="s">
-        <v>1629</v>
+        <v>676</v>
       </c>
       <c r="D812" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E812" s="33" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F812" s="33" t="s">
-        <v>727</v>
+        <v>2895</v>
       </c>
       <c r="G812" s="33" t="s">
-        <v>3023</v>
+        <v>3570</v>
       </c>
       <c r="H812" s="33">
-        <v>12440</v>
+        <v>9660</v>
       </c>
       <c r="I812" s="33">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="J812" s="33" t="s">
-        <v>1316</v>
+        <v>1103</v>
       </c>
       <c r="K812" s="33" t="s">
-        <v>1318</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="813" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -74317,25 +74329,25 @@
         <v>3022</v>
       </c>
       <c r="C813" s="33" t="s">
-        <v>1566</v>
+        <v>1629</v>
       </c>
       <c r="D813" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E813" s="33" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F813" s="33" t="s">
         <v>727</v>
       </c>
       <c r="G813" s="33" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="H813" s="33">
-        <v>12890</v>
+        <v>12440</v>
       </c>
       <c r="I813" s="33">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="J813" s="33" t="s">
         <v>1316</v>
@@ -74349,10 +74361,10 @@
         <v>29</v>
       </c>
       <c r="B814" s="33" t="s">
-        <v>3027</v>
+        <v>3022</v>
       </c>
       <c r="C814" s="33" t="s">
-        <v>3028</v>
+        <v>1566</v>
       </c>
       <c r="D814" s="33" t="s">
         <v>805</v>
@@ -74364,19 +74376,19 @@
         <v>727</v>
       </c>
       <c r="G814" s="33" t="s">
-        <v>3029</v>
+        <v>3024</v>
       </c>
       <c r="H814" s="33">
-        <v>13520</v>
+        <v>12890</v>
       </c>
       <c r="I814" s="33">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="J814" s="33" t="s">
-        <v>3030</v>
+        <v>1316</v>
       </c>
       <c r="K814" s="33" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="815" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -74384,10 +74396,10 @@
         <v>29</v>
       </c>
       <c r="B815" s="33" t="s">
-        <v>3031</v>
+        <v>3027</v>
       </c>
       <c r="C815" s="33" t="s">
-        <v>3032</v>
+        <v>3028</v>
       </c>
       <c r="D815" s="33" t="s">
         <v>805</v>
@@ -74396,13 +74408,13 @@
         <v>1567</v>
       </c>
       <c r="F815" s="33" t="s">
-        <v>3033</v>
+        <v>727</v>
       </c>
       <c r="G815" s="33" t="s">
-        <v>3034</v>
+        <v>3029</v>
       </c>
       <c r="H815" s="33">
-        <v>13570</v>
+        <v>13520</v>
       </c>
       <c r="I815" s="33">
         <v>40</v>
@@ -74419,10 +74431,10 @@
         <v>29</v>
       </c>
       <c r="B816" s="33" t="s">
-        <v>3035</v>
+        <v>3031</v>
       </c>
       <c r="C816" s="33" t="s">
-        <v>3036</v>
+        <v>3032</v>
       </c>
       <c r="D816" s="33" t="s">
         <v>805</v>
@@ -74431,13 +74443,13 @@
         <v>1567</v>
       </c>
       <c r="F816" s="33" t="s">
-        <v>727</v>
+        <v>3033</v>
       </c>
       <c r="G816" s="33" t="s">
-        <v>3037</v>
+        <v>3034</v>
       </c>
       <c r="H816" s="33">
-        <v>13580</v>
+        <v>13570</v>
       </c>
       <c r="I816" s="33">
         <v>40</v>
@@ -74454,31 +74466,31 @@
         <v>29</v>
       </c>
       <c r="B817" s="33" t="s">
-        <v>3038</v>
+        <v>3035</v>
       </c>
       <c r="C817" s="33" t="s">
-        <v>1629</v>
+        <v>3036</v>
       </c>
       <c r="D817" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E817" s="33" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F817" s="33" t="s">
         <v>727</v>
       </c>
       <c r="G817" s="33" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="H817" s="33">
-        <v>13740</v>
+        <v>13580</v>
       </c>
       <c r="I817" s="33">
-        <v>190</v>
+        <v>40</v>
       </c>
       <c r="J817" s="33" t="s">
-        <v>2259</v>
+        <v>3030</v>
       </c>
       <c r="K817" s="33" t="s">
         <v>1319</v>
@@ -74492,25 +74504,25 @@
         <v>3038</v>
       </c>
       <c r="C818" s="33" t="s">
-        <v>1566</v>
+        <v>1629</v>
       </c>
       <c r="D818" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E818" s="33" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F818" s="33" t="s">
         <v>727</v>
       </c>
       <c r="G818" s="33" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="H818" s="33">
-        <v>13850</v>
+        <v>13740</v>
       </c>
       <c r="I818" s="33">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="J818" s="33" t="s">
         <v>2259</v>
@@ -74524,7 +74536,7 @@
         <v>29</v>
       </c>
       <c r="B819" s="33" t="s">
-        <v>3025</v>
+        <v>3038</v>
       </c>
       <c r="C819" s="33" t="s">
         <v>1566</v>
@@ -74539,19 +74551,19 @@
         <v>727</v>
       </c>
       <c r="G819" s="33" t="s">
-        <v>3026</v>
+        <v>3040</v>
       </c>
       <c r="H819" s="33">
-        <v>13060</v>
+        <v>13850</v>
       </c>
       <c r="I819" s="33">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="J819" s="33" t="s">
         <v>2259</v>
       </c>
       <c r="K819" s="33" t="s">
-        <v>1722</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="820" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -74559,10 +74571,10 @@
         <v>29</v>
       </c>
       <c r="B820" s="33" t="s">
-        <v>3398</v>
+        <v>3025</v>
       </c>
       <c r="C820" s="33" t="s">
-        <v>3399</v>
+        <v>1566</v>
       </c>
       <c r="D820" s="33" t="s">
         <v>805</v>
@@ -74574,19 +74586,19 @@
         <v>727</v>
       </c>
       <c r="G820" s="33" t="s">
-        <v>3404</v>
+        <v>3026</v>
       </c>
       <c r="H820" s="33">
-        <v>10100</v>
+        <v>13060</v>
       </c>
       <c r="I820" s="33">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="J820" s="33" t="s">
-        <v>3397</v>
+        <v>2259</v>
       </c>
       <c r="K820" s="33" t="s">
-        <v>675</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="821" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -74609,13 +74621,13 @@
         <v>727</v>
       </c>
       <c r="G821" s="33" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="H821" s="33">
-        <v>10150</v>
+        <v>10100</v>
       </c>
       <c r="I821" s="33">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="J821" s="33" t="s">
         <v>3397</v>
@@ -74629,7 +74641,7 @@
         <v>29</v>
       </c>
       <c r="B822" s="33" t="s">
-        <v>3401</v>
+        <v>3398</v>
       </c>
       <c r="C822" s="33" t="s">
         <v>3399</v>
@@ -74640,23 +74652,23 @@
       <c r="E822" s="33" t="s">
         <v>1567</v>
       </c>
-      <c r="F822" s="33">
-        <v>44</v>
+      <c r="F822" s="33" t="s">
+        <v>727</v>
       </c>
       <c r="G822" s="33" t="s">
-        <v>3402</v>
+        <v>3405</v>
       </c>
       <c r="H822" s="33">
-        <v>9500</v>
+        <v>10150</v>
       </c>
       <c r="I822" s="33">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="J822" s="33" t="s">
         <v>3397</v>
       </c>
       <c r="K822" s="33" t="s">
-        <v>3313</v>
+        <v>675</v>
       </c>
     </row>
     <row r="823" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -74664,7 +74676,7 @@
         <v>29</v>
       </c>
       <c r="B823" s="33" t="s">
-        <v>3398</v>
+        <v>3401</v>
       </c>
       <c r="C823" s="33" t="s">
         <v>3399</v>
@@ -74675,17 +74687,17 @@
       <c r="E823" s="33" t="s">
         <v>1567</v>
       </c>
-      <c r="F823" s="33" t="s">
-        <v>727</v>
+      <c r="F823" s="33">
+        <v>44</v>
       </c>
       <c r="G823" s="33" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="H823" s="33">
-        <v>9850</v>
+        <v>9500</v>
       </c>
       <c r="I823" s="33">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="J823" s="33" t="s">
         <v>3397</v>
@@ -74710,34 +74722,34 @@
       <c r="E824" s="33" t="s">
         <v>1567</v>
       </c>
-      <c r="F824" s="33">
-        <v>73</v>
+      <c r="F824" s="33" t="s">
+        <v>727</v>
       </c>
       <c r="G824" s="33" t="s">
-        <v>3400</v>
+        <v>3403</v>
       </c>
       <c r="H824" s="33">
-        <v>7470</v>
+        <v>9850</v>
       </c>
       <c r="I824" s="33">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="J824" s="33" t="s">
         <v>3397</v>
       </c>
       <c r="K824" s="33" t="s">
-        <v>3338</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="825" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A825" s="33" t="s">
-        <v>700</v>
+        <v>29</v>
       </c>
       <c r="B825" s="33" t="s">
-        <v>3041</v>
+        <v>3398</v>
       </c>
       <c r="C825" s="33" t="s">
-        <v>3042</v>
+        <v>3399</v>
       </c>
       <c r="D825" s="33" t="s">
         <v>805</v>
@@ -74745,50 +74757,23 @@
       <c r="E825" s="33" t="s">
         <v>1567</v>
       </c>
-      <c r="F825" s="33" t="s">
-        <v>3043</v>
+      <c r="F825" s="33">
+        <v>73</v>
       </c>
       <c r="G825" s="33" t="s">
-        <v>3044</v>
+        <v>3400</v>
       </c>
       <c r="H825" s="33">
-        <v>21252</v>
+        <v>7470</v>
       </c>
       <c r="I825" s="33">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J825" s="33" t="s">
-        <v>3045</v>
+        <v>3397</v>
       </c>
       <c r="K825" s="33" t="s">
-        <v>1323</v>
-      </c>
-      <c r="N825" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="O825" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="T825" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="U825" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="Z825" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AA825" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AD825" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AF825" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AG825" s="2" t="s">
-        <v>1680</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="826" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -74799,7 +74784,7 @@
         <v>3041</v>
       </c>
       <c r="C826" s="33" t="s">
-        <v>2364</v>
+        <v>3042</v>
       </c>
       <c r="D826" s="33" t="s">
         <v>805</v>
@@ -74808,22 +74793,49 @@
         <v>1567</v>
       </c>
       <c r="F826" s="33" t="s">
-        <v>3046</v>
+        <v>3043</v>
       </c>
       <c r="G826" s="33" t="s">
-        <v>3047</v>
+        <v>3044</v>
       </c>
       <c r="H826" s="33">
-        <v>21290</v>
+        <v>21252</v>
       </c>
       <c r="I826" s="33">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J826" s="33" t="s">
         <v>3045</v>
       </c>
       <c r="K826" s="33" t="s">
         <v>1323</v>
+      </c>
+      <c r="N826" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="O826" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="T826" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="U826" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="Z826" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AA826" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AD826" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AF826" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AG826" s="2" t="s">
+        <v>1680</v>
       </c>
     </row>
     <row r="827" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -74834,7 +74846,7 @@
         <v>3041</v>
       </c>
       <c r="C827" s="33" t="s">
-        <v>3048</v>
+        <v>2364</v>
       </c>
       <c r="D827" s="33" t="s">
         <v>805</v>
@@ -74843,16 +74855,16 @@
         <v>1567</v>
       </c>
       <c r="F827" s="33" t="s">
-        <v>3049</v>
+        <v>3046</v>
       </c>
       <c r="G827" s="33" t="s">
-        <v>3050</v>
+        <v>3047</v>
       </c>
       <c r="H827" s="33">
-        <v>21870</v>
+        <v>21290</v>
       </c>
       <c r="I827" s="33">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J827" s="33" t="s">
         <v>3045</v>
@@ -74863,13 +74875,13 @@
     </row>
     <row r="828" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A828" s="33" t="s">
-        <v>3734</v>
+        <v>700</v>
       </c>
       <c r="B828" s="33" t="s">
-        <v>3736</v>
+        <v>3041</v>
       </c>
       <c r="C828" s="33" t="s">
-        <v>1566</v>
+        <v>3048</v>
       </c>
       <c r="D828" s="33" t="s">
         <v>805</v>
@@ -74878,22 +74890,22 @@
         <v>1567</v>
       </c>
       <c r="F828" s="33" t="s">
-        <v>727</v>
+        <v>3049</v>
       </c>
       <c r="G828" s="33" t="s">
-        <v>3740</v>
+        <v>3050</v>
       </c>
       <c r="H828" s="33">
-        <v>7740</v>
+        <v>21870</v>
       </c>
       <c r="I828" s="33">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="J828" s="33" t="s">
-        <v>3718</v>
+        <v>3045</v>
       </c>
       <c r="K828" s="33" t="s">
-        <v>3313</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="829" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -74904,7 +74916,7 @@
         <v>3736</v>
       </c>
       <c r="C829" s="33" t="s">
-        <v>3732</v>
+        <v>1566</v>
       </c>
       <c r="D829" s="33" t="s">
         <v>805</v>
@@ -74916,13 +74928,13 @@
         <v>727</v>
       </c>
       <c r="G829" s="33" t="s">
-        <v>3738</v>
+        <v>3740</v>
       </c>
       <c r="H829" s="33">
-        <v>8050</v>
+        <v>7740</v>
       </c>
       <c r="I829" s="33">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="J829" s="33" t="s">
         <v>3718</v>
@@ -74936,10 +74948,10 @@
         <v>3734</v>
       </c>
       <c r="B830" s="33" t="s">
-        <v>3749</v>
+        <v>3736</v>
       </c>
       <c r="C830" s="33" t="s">
-        <v>1566</v>
+        <v>3732</v>
       </c>
       <c r="D830" s="33" t="s">
         <v>805</v>
@@ -74951,16 +74963,16 @@
         <v>727</v>
       </c>
       <c r="G830" s="33" t="s">
-        <v>3763</v>
+        <v>3738</v>
       </c>
       <c r="H830" s="33">
-        <v>8737</v>
+        <v>8050</v>
       </c>
       <c r="I830" s="33">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="J830" s="33" t="s">
-        <v>3748</v>
+        <v>3718</v>
       </c>
       <c r="K830" s="33" t="s">
         <v>3313</v>
@@ -74986,10 +74998,10 @@
         <v>727</v>
       </c>
       <c r="G831" s="33" t="s">
-        <v>3766</v>
+        <v>3763</v>
       </c>
       <c r="H831" s="33">
-        <v>8824</v>
+        <v>8737</v>
       </c>
       <c r="I831" s="33">
         <v>30</v>
@@ -75021,10 +75033,10 @@
         <v>727</v>
       </c>
       <c r="G832" s="33" t="s">
-        <v>3764</v>
+        <v>3766</v>
       </c>
       <c r="H832" s="33">
-        <v>8836</v>
+        <v>8824</v>
       </c>
       <c r="I832" s="33">
         <v>30</v>
@@ -75056,13 +75068,13 @@
         <v>727</v>
       </c>
       <c r="G833" s="33" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="H833" s="33">
-        <v>8854</v>
+        <v>8836</v>
       </c>
       <c r="I833" s="33">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="J833" s="33" t="s">
         <v>3748</v>
@@ -75091,13 +75103,13 @@
         <v>727</v>
       </c>
       <c r="G834" s="33" t="s">
-        <v>3768</v>
+        <v>3765</v>
       </c>
       <c r="H834" s="33">
-        <v>8908</v>
+        <v>8854</v>
       </c>
       <c r="I834" s="33">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="J834" s="33" t="s">
         <v>3748</v>
@@ -75111,7 +75123,7 @@
         <v>3734</v>
       </c>
       <c r="B835" s="33" t="s">
-        <v>3736</v>
+        <v>3749</v>
       </c>
       <c r="C835" s="33" t="s">
         <v>1566</v>
@@ -75126,16 +75138,16 @@
         <v>727</v>
       </c>
       <c r="G835" s="33" t="s">
-        <v>3739</v>
+        <v>3768</v>
       </c>
       <c r="H835" s="33">
-        <v>8941</v>
+        <v>8908</v>
       </c>
       <c r="I835" s="33">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J835" s="33" t="s">
-        <v>3718</v>
+        <v>3748</v>
       </c>
       <c r="K835" s="33" t="s">
         <v>3313</v>
@@ -75146,7 +75158,7 @@
         <v>3734</v>
       </c>
       <c r="B836" s="33" t="s">
-        <v>3749</v>
+        <v>3736</v>
       </c>
       <c r="C836" s="33" t="s">
         <v>1566</v>
@@ -75161,16 +75173,16 @@
         <v>727</v>
       </c>
       <c r="G836" s="33" t="s">
-        <v>3767</v>
+        <v>3739</v>
       </c>
       <c r="H836" s="33">
-        <v>8963</v>
+        <v>8941</v>
       </c>
       <c r="I836" s="33">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J836" s="33" t="s">
-        <v>3748</v>
+        <v>3718</v>
       </c>
       <c r="K836" s="33" t="s">
         <v>3313</v>
@@ -75178,10 +75190,10 @@
     </row>
     <row r="837" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A837" s="33" t="s">
-        <v>1336</v>
+        <v>3734</v>
       </c>
       <c r="B837" s="33" t="s">
-        <v>1337</v>
+        <v>3749</v>
       </c>
       <c r="C837" s="33" t="s">
         <v>1566</v>
@@ -75193,22 +75205,22 @@
         <v>1567</v>
       </c>
       <c r="F837" s="33" t="s">
-        <v>3061</v>
+        <v>727</v>
       </c>
       <c r="G837" s="33" t="s">
-        <v>3062</v>
+        <v>3767</v>
       </c>
       <c r="H837" s="33">
-        <v>15600</v>
+        <v>8963</v>
       </c>
       <c r="I837" s="33">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="J837" s="33" t="s">
-        <v>3063</v>
+        <v>3748</v>
       </c>
       <c r="K837" s="33" t="s">
-        <v>1313</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="838" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -75216,7 +75228,7 @@
         <v>1336</v>
       </c>
       <c r="B838" s="33" t="s">
-        <v>3051</v>
+        <v>1337</v>
       </c>
       <c r="C838" s="33" t="s">
         <v>1566</v>
@@ -75227,53 +75239,52 @@
       <c r="E838" s="33" t="s">
         <v>1567</v>
       </c>
-      <c r="F838" s="33">
-        <v>5</v>
+      <c r="F838" s="33" t="s">
+        <v>3061</v>
       </c>
       <c r="G838" s="33" t="s">
-        <v>3769</v>
+        <v>3062</v>
       </c>
       <c r="H838" s="33">
-        <v>10950</v>
+        <v>15600</v>
       </c>
       <c r="I838" s="33">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="J838" s="33" t="s">
-        <v>3052</v>
+        <v>3063</v>
       </c>
       <c r="K838" s="33" t="s">
-        <v>675</v>
-      </c>
-      <c r="AJ838" s="41"/>
+        <v>1313</v>
+      </c>
     </row>
     <row r="839" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A839" s="33" t="s">
         <v>1336</v>
       </c>
       <c r="B839" s="33" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="C839" s="33" t="s">
-        <v>1629</v>
+        <v>1566</v>
       </c>
       <c r="D839" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E839" s="33" t="s">
-        <v>1612</v>
-      </c>
-      <c r="F839" s="33" t="s">
-        <v>3054</v>
+        <v>1567</v>
+      </c>
+      <c r="F839" s="33">
+        <v>5</v>
       </c>
       <c r="G839" s="33" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="H839" s="33">
-        <v>10980</v>
+        <v>10950</v>
       </c>
       <c r="I839" s="33">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="J839" s="33" t="s">
         <v>3052</v>
@@ -75281,37 +75292,38 @@
       <c r="K839" s="33" t="s">
         <v>675</v>
       </c>
+      <c r="AJ839" s="41"/>
     </row>
     <row r="840" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A840" s="33" t="s">
         <v>1336</v>
       </c>
       <c r="B840" s="33" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="C840" s="33" t="s">
-        <v>1566</v>
+        <v>1629</v>
       </c>
       <c r="D840" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E840" s="33" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F840" s="33" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="G840" s="33" t="s">
-        <v>3057</v>
+        <v>3770</v>
       </c>
       <c r="H840" s="33">
-        <v>10995</v>
+        <v>10980</v>
       </c>
       <c r="I840" s="33">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="J840" s="33" t="s">
-        <v>3058</v>
+        <v>3052</v>
       </c>
       <c r="K840" s="33" t="s">
         <v>675</v>
@@ -75322,7 +75334,7 @@
         <v>1336</v>
       </c>
       <c r="B841" s="33" t="s">
-        <v>3293</v>
+        <v>3055</v>
       </c>
       <c r="C841" s="33" t="s">
         <v>1566</v>
@@ -75334,19 +75346,19 @@
         <v>1567</v>
       </c>
       <c r="F841" s="33" t="s">
-        <v>3295</v>
-      </c>
-      <c r="G841" s="36" t="s">
-        <v>3297</v>
+        <v>3056</v>
+      </c>
+      <c r="G841" s="33" t="s">
+        <v>3057</v>
       </c>
       <c r="H841" s="33">
-        <v>11040</v>
+        <v>10995</v>
       </c>
       <c r="I841" s="33">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="J841" s="33" t="s">
-        <v>3298</v>
+        <v>3058</v>
       </c>
       <c r="K841" s="33" t="s">
         <v>675</v>
@@ -75357,7 +75369,7 @@
         <v>1336</v>
       </c>
       <c r="B842" s="33" t="s">
-        <v>3053</v>
+        <v>3293</v>
       </c>
       <c r="C842" s="33" t="s">
         <v>1566</v>
@@ -75368,20 +75380,20 @@
       <c r="E842" s="33" t="s">
         <v>1567</v>
       </c>
-      <c r="F842" s="33">
-        <v>4</v>
-      </c>
-      <c r="G842" s="33" t="s">
-        <v>3771</v>
+      <c r="F842" s="33" t="s">
+        <v>3295</v>
+      </c>
+      <c r="G842" s="36" t="s">
+        <v>3297</v>
       </c>
       <c r="H842" s="33">
-        <v>11130</v>
+        <v>11040</v>
       </c>
       <c r="I842" s="33">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J842" s="33" t="s">
-        <v>3052</v>
+        <v>3298</v>
       </c>
       <c r="K842" s="33" t="s">
         <v>675</v>
@@ -75392,7 +75404,7 @@
         <v>1336</v>
       </c>
       <c r="B843" s="33" t="s">
-        <v>3059</v>
+        <v>3053</v>
       </c>
       <c r="C843" s="33" t="s">
         <v>1566</v>
@@ -75404,16 +75416,16 @@
         <v>1567</v>
       </c>
       <c r="F843" s="33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G843" s="33" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
       <c r="H843" s="33">
-        <v>11470</v>
+        <v>11130</v>
       </c>
       <c r="I843" s="33">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J843" s="33" t="s">
         <v>3052</v>
@@ -75427,7 +75439,7 @@
         <v>1336</v>
       </c>
       <c r="B844" s="33" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C844" s="33" t="s">
         <v>1566</v>
@@ -75439,16 +75451,16 @@
         <v>1567</v>
       </c>
       <c r="F844" s="33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G844" s="33" t="s">
-        <v>3773</v>
-      </c>
-      <c r="H844" s="32">
-        <v>11540</v>
+        <v>3772</v>
+      </c>
+      <c r="H844" s="33">
+        <v>11470</v>
       </c>
       <c r="I844" s="33">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J844" s="33" t="s">
         <v>3052</v>
@@ -75462,7 +75474,7 @@
         <v>1336</v>
       </c>
       <c r="B845" s="33" t="s">
-        <v>3292</v>
+        <v>3060</v>
       </c>
       <c r="C845" s="33" t="s">
         <v>1566</v>
@@ -75473,20 +75485,20 @@
       <c r="E845" s="33" t="s">
         <v>1567</v>
       </c>
-      <c r="F845" s="33" t="s">
-        <v>3294</v>
+      <c r="F845" s="33">
+        <v>3</v>
       </c>
       <c r="G845" s="33" t="s">
-        <v>3296</v>
-      </c>
-      <c r="H845" s="33">
-        <v>11746</v>
+        <v>3773</v>
+      </c>
+      <c r="H845" s="32">
+        <v>11540</v>
       </c>
       <c r="I845" s="33">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="J845" s="33" t="s">
-        <v>3298</v>
+        <v>3052</v>
       </c>
       <c r="K845" s="33" t="s">
         <v>675</v>
@@ -75494,10 +75506,10 @@
     </row>
     <row r="846" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A846" s="33" t="s">
-        <v>1293</v>
+        <v>1336</v>
       </c>
       <c r="B846" s="33" t="s">
-        <v>3064</v>
+        <v>3292</v>
       </c>
       <c r="C846" s="33" t="s">
         <v>1566</v>
@@ -75509,22 +75521,22 @@
         <v>1567</v>
       </c>
       <c r="F846" s="33" t="s">
-        <v>676</v>
+        <v>3294</v>
       </c>
       <c r="G846" s="33" t="s">
-        <v>3066</v>
+        <v>3296</v>
       </c>
       <c r="H846" s="33">
-        <v>12460</v>
+        <v>11746</v>
       </c>
       <c r="I846" s="33">
-        <v>160</v>
+        <v>33</v>
       </c>
       <c r="J846" s="33" t="s">
-        <v>1753</v>
+        <v>3298</v>
       </c>
       <c r="K846" s="33" t="s">
-        <v>1318</v>
+        <v>675</v>
       </c>
     </row>
     <row r="847" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -75532,10 +75544,10 @@
         <v>1293</v>
       </c>
       <c r="B847" s="33" t="s">
-        <v>3070</v>
+        <v>3064</v>
       </c>
       <c r="C847" s="33" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
       <c r="D847" s="33" t="s">
         <v>805</v>
@@ -75544,22 +75556,22 @@
         <v>1567</v>
       </c>
       <c r="F847" s="33" t="s">
-        <v>3071</v>
+        <v>676</v>
       </c>
       <c r="G847" s="33" t="s">
-        <v>3072</v>
+        <v>3066</v>
       </c>
       <c r="H847" s="33">
-        <v>14700</v>
+        <v>12460</v>
       </c>
       <c r="I847" s="33">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="J847" s="33" t="s">
-        <v>1105</v>
+        <v>1753</v>
       </c>
       <c r="K847" s="33" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="848" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -75567,10 +75579,10 @@
         <v>1293</v>
       </c>
       <c r="B848" s="33" t="s">
-        <v>3067</v>
+        <v>3070</v>
       </c>
       <c r="C848" s="33" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="D848" s="33" t="s">
         <v>805</v>
@@ -75579,22 +75591,22 @@
         <v>1567</v>
       </c>
       <c r="F848" s="33" t="s">
-        <v>676</v>
+        <v>3071</v>
       </c>
       <c r="G848" s="33" t="s">
-        <v>3068</v>
+        <v>3072</v>
       </c>
       <c r="H848" s="33">
-        <v>13730</v>
+        <v>14700</v>
       </c>
       <c r="I848" s="33">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="J848" s="33" t="s">
-        <v>1753</v>
+        <v>1105</v>
       </c>
       <c r="K848" s="33" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="849" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -75605,25 +75617,25 @@
         <v>3067</v>
       </c>
       <c r="C849" s="33" t="s">
-        <v>1629</v>
+        <v>1566</v>
       </c>
       <c r="D849" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E849" s="33" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F849" s="33" t="s">
         <v>676</v>
       </c>
       <c r="G849" s="33" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="H849" s="33">
-        <v>13890</v>
+        <v>13730</v>
       </c>
       <c r="I849" s="33">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="J849" s="33" t="s">
         <v>1753</v>
@@ -75637,42 +75649,42 @@
         <v>1293</v>
       </c>
       <c r="B850" s="33" t="s">
-        <v>3064</v>
+        <v>3067</v>
       </c>
       <c r="C850" s="33" t="s">
-        <v>1566</v>
+        <v>1629</v>
       </c>
       <c r="D850" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E850" s="33" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F850" s="33" t="s">
         <v>676</v>
       </c>
       <c r="G850" s="33" t="s">
-        <v>3065</v>
+        <v>3069</v>
       </c>
       <c r="H850" s="33">
-        <v>11990</v>
+        <v>13890</v>
       </c>
       <c r="I850" s="33">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="J850" s="33" t="s">
         <v>1753</v>
       </c>
       <c r="K850" s="33" t="s">
-        <v>1439</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="851" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A851" s="33" t="s">
-        <v>1338</v>
+        <v>1293</v>
       </c>
       <c r="B851" s="33" t="s">
-        <v>3077</v>
+        <v>3064</v>
       </c>
       <c r="C851" s="33" t="s">
         <v>1566</v>
@@ -75684,22 +75696,22 @@
         <v>1567</v>
       </c>
       <c r="F851" s="33" t="s">
-        <v>3078</v>
+        <v>676</v>
       </c>
       <c r="G851" s="33" t="s">
-        <v>3079</v>
+        <v>3065</v>
       </c>
       <c r="H851" s="33">
-        <v>24640</v>
+        <v>11990</v>
       </c>
       <c r="I851" s="33">
-        <v>390</v>
+        <v>170</v>
       </c>
       <c r="J851" s="33" t="s">
-        <v>3080</v>
+        <v>1753</v>
       </c>
       <c r="K851" s="33" t="s">
-        <v>1322</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="852" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -75707,10 +75719,10 @@
         <v>1338</v>
       </c>
       <c r="B852" s="33" t="s">
-        <v>3073</v>
+        <v>3077</v>
       </c>
       <c r="C852" s="33" t="s">
-        <v>2364</v>
+        <v>1566</v>
       </c>
       <c r="D852" s="33" t="s">
         <v>805</v>
@@ -75719,22 +75731,22 @@
         <v>1567</v>
       </c>
       <c r="F852" s="33" t="s">
-        <v>676</v>
+        <v>3078</v>
       </c>
       <c r="G852" s="33" t="s">
-        <v>727</v>
+        <v>3079</v>
       </c>
       <c r="H852" s="33">
-        <v>18400</v>
+        <v>24640</v>
       </c>
       <c r="I852" s="33">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="J852" s="33" t="s">
-        <v>3076</v>
+        <v>3080</v>
       </c>
       <c r="K852" s="33" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="853" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -75745,31 +75757,31 @@
         <v>3073</v>
       </c>
       <c r="C853" s="33" t="s">
-        <v>1566</v>
+        <v>2364</v>
       </c>
       <c r="D853" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E853" s="33" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F853" s="33" t="s">
         <v>676</v>
       </c>
       <c r="G853" s="33" t="s">
-        <v>3075</v>
+        <v>727</v>
       </c>
       <c r="H853" s="33">
-        <v>11380</v>
+        <v>18400</v>
       </c>
       <c r="I853" s="33">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="J853" s="33" t="s">
-        <v>875</v>
+        <v>3076</v>
       </c>
       <c r="K853" s="33" t="s">
-        <v>675</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="854" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -75792,19 +75804,19 @@
         <v>676</v>
       </c>
       <c r="G854" s="33" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="H854" s="33">
-        <v>11200</v>
+        <v>11380</v>
       </c>
       <c r="I854" s="33">
-        <v>800</v>
+        <v>390</v>
       </c>
       <c r="J854" s="33" t="s">
         <v>875</v>
       </c>
       <c r="K854" s="33" t="s">
-        <v>1689</v>
+        <v>675</v>
       </c>
     </row>
     <row r="855" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -75812,7 +75824,7 @@
         <v>1338</v>
       </c>
       <c r="B855" s="33" t="s">
-        <v>3448</v>
+        <v>3073</v>
       </c>
       <c r="C855" s="33" t="s">
         <v>1566</v>
@@ -75821,25 +75833,25 @@
         <v>805</v>
       </c>
       <c r="E855" s="33" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F855" s="33" t="s">
-        <v>3449</v>
+        <v>676</v>
       </c>
       <c r="G855" s="33" t="s">
-        <v>3451</v>
+        <v>3074</v>
       </c>
       <c r="H855" s="33">
-        <v>8900</v>
+        <v>11200</v>
       </c>
       <c r="I855" s="33">
-        <v>160</v>
+        <v>800</v>
       </c>
       <c r="J855" s="33" t="s">
         <v>875</v>
       </c>
       <c r="K855" s="33" t="s">
-        <v>3313</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="856" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -75862,13 +75874,13 @@
         <v>3449</v>
       </c>
       <c r="G856" s="33" t="s">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="H856" s="33">
-        <v>9070</v>
+        <v>8900</v>
       </c>
       <c r="I856" s="33">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="J856" s="33" t="s">
         <v>875</v>
@@ -75879,10 +75891,10 @@
     </row>
     <row r="857" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A857" s="33" t="s">
-        <v>37</v>
+        <v>1338</v>
       </c>
       <c r="B857" s="33" t="s">
-        <v>1339</v>
+        <v>3448</v>
       </c>
       <c r="C857" s="33" t="s">
         <v>1566</v>
@@ -75894,30 +75906,30 @@
         <v>1567</v>
       </c>
       <c r="F857" s="33" t="s">
-        <v>676</v>
+        <v>3449</v>
       </c>
       <c r="G857" s="33" t="s">
-        <v>3081</v>
-      </c>
-      <c r="H857" s="34">
-        <v>32850</v>
+        <v>3450</v>
+      </c>
+      <c r="H857" s="33">
+        <v>9070</v>
       </c>
       <c r="I857" s="33">
-        <v>520</v>
+        <v>130</v>
       </c>
       <c r="J857" s="33" t="s">
-        <v>1162</v>
+        <v>875</v>
       </c>
       <c r="K857" s="33" t="s">
-        <v>1228</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="858" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A858" s="33" t="s">
-        <v>1340</v>
+        <v>37</v>
       </c>
       <c r="B858" s="33" t="s">
-        <v>3082</v>
+        <v>1339</v>
       </c>
       <c r="C858" s="33" t="s">
         <v>1566</v>
@@ -75929,22 +75941,22 @@
         <v>1567</v>
       </c>
       <c r="F858" s="33" t="s">
-        <v>3083</v>
+        <v>676</v>
       </c>
       <c r="G858" s="33" t="s">
-        <v>3084</v>
-      </c>
-      <c r="H858" s="33">
-        <v>20130</v>
+        <v>3081</v>
+      </c>
+      <c r="H858" s="34">
+        <v>32850</v>
       </c>
       <c r="I858" s="33">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c r="J858" s="33" t="s">
-        <v>2968</v>
+        <v>1162</v>
       </c>
       <c r="K858" s="33" t="s">
-        <v>1323</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="859" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -75952,7 +75964,7 @@
         <v>1340</v>
       </c>
       <c r="B859" s="33" t="s">
-        <v>3473</v>
+        <v>3082</v>
       </c>
       <c r="C859" s="33" t="s">
         <v>1566</v>
@@ -75964,57 +75976,57 @@
         <v>1567</v>
       </c>
       <c r="F859" s="33" t="s">
-        <v>3474</v>
+        <v>3083</v>
       </c>
       <c r="G859" s="33" t="s">
-        <v>3475</v>
+        <v>3084</v>
       </c>
       <c r="H859" s="33">
-        <v>8760</v>
+        <v>20130</v>
       </c>
       <c r="I859" s="33">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="J859" s="33" t="s">
         <v>2968</v>
       </c>
       <c r="K859" s="33" t="s">
-        <v>3476</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="860" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A860" s="33" t="s">
-        <v>3085</v>
+        <v>1340</v>
       </c>
       <c r="B860" s="33" t="s">
-        <v>3086</v>
+        <v>3473</v>
       </c>
       <c r="C860" s="33" t="s">
-        <v>1629</v>
+        <v>1566</v>
       </c>
       <c r="D860" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E860" s="33" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F860" s="33" t="s">
-        <v>3087</v>
+        <v>3474</v>
       </c>
       <c r="G860" s="33" t="s">
-        <v>3088</v>
+        <v>3475</v>
       </c>
       <c r="H860" s="33">
-        <v>10040</v>
+        <v>8760</v>
       </c>
       <c r="I860" s="33">
         <v>100</v>
       </c>
       <c r="J860" s="33" t="s">
-        <v>2756</v>
+        <v>2968</v>
       </c>
       <c r="K860" s="33" t="s">
-        <v>1439</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="861" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -76025,25 +76037,25 @@
         <v>3086</v>
       </c>
       <c r="C861" s="33" t="s">
-        <v>1566</v>
+        <v>1629</v>
       </c>
       <c r="D861" s="33" t="s">
         <v>805</v>
       </c>
       <c r="E861" s="33" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F861" s="33" t="s">
         <v>3087</v>
       </c>
       <c r="G861" s="33" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="H861" s="33">
-        <v>10240</v>
+        <v>10040</v>
       </c>
       <c r="I861" s="33">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J861" s="33" t="s">
         <v>2756</v>
@@ -76054,37 +76066,37 @@
     </row>
     <row r="862" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A862" s="33" t="s">
-        <v>87</v>
+        <v>3085</v>
       </c>
       <c r="B862" s="33" t="s">
-        <v>3096</v>
+        <v>3086</v>
       </c>
       <c r="C862" s="33" t="s">
-        <v>3091</v>
+        <v>1566</v>
       </c>
       <c r="D862" s="33" t="s">
-        <v>1587</v>
+        <v>805</v>
       </c>
       <c r="E862" s="33" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F862" s="33" t="s">
-        <v>676</v>
+        <v>3087</v>
       </c>
       <c r="G862" s="33" t="s">
-        <v>3097</v>
+        <v>3089</v>
       </c>
       <c r="H862" s="33">
-        <v>22595</v>
+        <v>10240</v>
       </c>
       <c r="I862" s="33">
-        <v>2338</v>
+        <v>90</v>
       </c>
       <c r="J862" s="33" t="s">
-        <v>3093</v>
+        <v>2756</v>
       </c>
       <c r="K862" s="33" t="s">
-        <v>1525</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="863" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -76092,7 +76104,7 @@
         <v>87</v>
       </c>
       <c r="B863" s="33" t="s">
-        <v>3090</v>
+        <v>3096</v>
       </c>
       <c r="C863" s="33" t="s">
         <v>3091</v>
@@ -76107,13 +76119,13 @@
         <v>676</v>
       </c>
       <c r="G863" s="33" t="s">
-        <v>3092</v>
+        <v>3097</v>
       </c>
       <c r="H863" s="33">
-        <v>26972</v>
+        <v>22595</v>
       </c>
       <c r="I863" s="33">
-        <v>2747</v>
+        <v>2338</v>
       </c>
       <c r="J863" s="33" t="s">
         <v>3093</v>
@@ -76130,25 +76142,25 @@
         <v>3090</v>
       </c>
       <c r="C864" s="33" t="s">
-        <v>3094</v>
+        <v>3091</v>
       </c>
       <c r="D864" s="33" t="s">
         <v>1587</v>
       </c>
       <c r="E864" s="33" t="s">
-        <v>1600</v>
+        <v>1612</v>
       </c>
       <c r="F864" s="33" t="s">
         <v>676</v>
       </c>
       <c r="G864" s="33" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
       <c r="H864" s="33">
-        <v>32946</v>
+        <v>26972</v>
       </c>
       <c r="I864" s="33">
-        <v>3340</v>
+        <v>2747</v>
       </c>
       <c r="J864" s="33" t="s">
         <v>3093</v>
@@ -76162,10 +76174,10 @@
         <v>87</v>
       </c>
       <c r="B865" s="33" t="s">
-        <v>3096</v>
+        <v>3090</v>
       </c>
       <c r="C865" s="33" t="s">
-        <v>3091</v>
+        <v>3094</v>
       </c>
       <c r="D865" s="33" t="s">
         <v>1587</v>
@@ -76177,13 +76189,13 @@
         <v>676</v>
       </c>
       <c r="G865" s="33" t="s">
-        <v>3098</v>
+        <v>3095</v>
       </c>
       <c r="H865" s="33">
-        <v>35750</v>
+        <v>32946</v>
       </c>
       <c r="I865" s="33">
-        <v>4730</v>
+        <v>3340</v>
       </c>
       <c r="J865" s="33" t="s">
         <v>3093</v>
@@ -76191,77 +76203,77 @@
       <c r="K865" s="33" t="s">
         <v>1525</v>
       </c>
-      <c r="L865" s="32"/>
-      <c r="M865" s="32"/>
-      <c r="N865" s="32"/>
-      <c r="O865" s="32"/>
-      <c r="P865" s="32"/>
-      <c r="Q865" s="32"/>
-      <c r="R865" s="32"/>
-      <c r="S865" s="32"/>
-      <c r="T865" s="32"/>
-      <c r="U865" s="32"/>
-      <c r="V865" s="32"/>
-      <c r="W865" s="32"/>
-      <c r="X865" s="32"/>
-      <c r="Y865" s="32"/>
-      <c r="Z865" s="32"/>
-      <c r="AA865" s="32"/>
-      <c r="AB865" s="32"/>
-      <c r="AC865" s="32"/>
-      <c r="AD865" s="32"/>
-      <c r="AE865" s="32"/>
-      <c r="AF865" s="32"/>
-      <c r="AG865" s="32"/>
-      <c r="AH865" s="32"/>
-      <c r="AI865" s="32"/>
-      <c r="AJ865" s="32"/>
-      <c r="AK865" s="32"/>
-    </row>
-    <row r="866" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A866" s="7" t="s">
-        <v>1553</v>
-      </c>
-      <c r="B866" s="7" t="s">
-        <v>3110</v>
-      </c>
-      <c r="C866" s="7" t="s">
-        <v>3111</v>
-      </c>
-      <c r="D866" s="7" t="s">
-        <v>805</v>
-      </c>
-      <c r="E866" s="7" t="s">
-        <v>1567</v>
-      </c>
-      <c r="F866" s="7" t="s">
-        <v>3112</v>
-      </c>
-      <c r="G866" s="7" t="s">
-        <v>3112</v>
-      </c>
-      <c r="H866" s="7">
-        <v>19619</v>
-      </c>
-      <c r="I866" s="7">
-        <v>72</v>
-      </c>
-      <c r="J866" s="7" t="s">
-        <v>1556</v>
-      </c>
-      <c r="K866" s="7" t="s">
-        <v>1323</v>
-      </c>
+    </row>
+    <row r="866" spans="1:37" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A866" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B866" s="33" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C866" s="33" t="s">
+        <v>3091</v>
+      </c>
+      <c r="D866" s="33" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E866" s="33" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F866" s="33" t="s">
+        <v>676</v>
+      </c>
+      <c r="G866" s="33" t="s">
+        <v>3098</v>
+      </c>
+      <c r="H866" s="33">
+        <v>35750</v>
+      </c>
+      <c r="I866" s="33">
+        <v>4730</v>
+      </c>
+      <c r="J866" s="33" t="s">
+        <v>3093</v>
+      </c>
+      <c r="K866" s="33" t="s">
+        <v>1525</v>
+      </c>
+      <c r="L866" s="32"/>
+      <c r="M866" s="32"/>
+      <c r="N866" s="32"/>
+      <c r="O866" s="32"/>
+      <c r="P866" s="32"/>
+      <c r="Q866" s="32"/>
+      <c r="R866" s="32"/>
+      <c r="S866" s="32"/>
+      <c r="T866" s="32"/>
+      <c r="U866" s="32"/>
+      <c r="V866" s="32"/>
+      <c r="W866" s="32"/>
+      <c r="X866" s="32"/>
+      <c r="Y866" s="32"/>
+      <c r="Z866" s="32"/>
+      <c r="AA866" s="32"/>
+      <c r="AB866" s="32"/>
+      <c r="AC866" s="32"/>
+      <c r="AD866" s="32"/>
+      <c r="AE866" s="32"/>
+      <c r="AF866" s="32"/>
+      <c r="AG866" s="32"/>
+      <c r="AH866" s="32"/>
+      <c r="AI866" s="32"/>
+      <c r="AJ866" s="32"/>
+      <c r="AK866" s="32"/>
     </row>
     <row r="867" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A867" s="7" t="s">
         <v>1553</v>
       </c>
       <c r="B867" s="7" t="s">
-        <v>3102</v>
+        <v>3110</v>
       </c>
       <c r="C867" s="7" t="s">
-        <v>2905</v>
+        <v>3111</v>
       </c>
       <c r="D867" s="7" t="s">
         <v>805</v>
@@ -76270,22 +76282,22 @@
         <v>1567</v>
       </c>
       <c r="F867" s="7" t="s">
-        <v>3103</v>
+        <v>3112</v>
       </c>
       <c r="G867" s="7" t="s">
-        <v>3103</v>
+        <v>3112</v>
       </c>
       <c r="H867" s="7">
-        <v>10868</v>
+        <v>19619</v>
       </c>
       <c r="I867" s="7">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="J867" s="7" t="s">
         <v>1556</v>
       </c>
       <c r="K867" s="7" t="s">
-        <v>675</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="868" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -76293,10 +76305,10 @@
         <v>1553</v>
       </c>
       <c r="B868" s="7" t="s">
-        <v>3099</v>
+        <v>3102</v>
       </c>
       <c r="C868" s="7" t="s">
-        <v>1748</v>
+        <v>2905</v>
       </c>
       <c r="D868" s="7" t="s">
         <v>805</v>
@@ -76305,13 +76317,13 @@
         <v>1567</v>
       </c>
       <c r="F868" s="7" t="s">
-        <v>3100</v>
+        <v>3103</v>
       </c>
       <c r="G868" s="7" t="s">
-        <v>3100</v>
+        <v>3103</v>
       </c>
       <c r="H868" s="7">
-        <v>11169</v>
+        <v>10868</v>
       </c>
       <c r="I868" s="7">
         <v>34</v>
@@ -76328,7 +76340,7 @@
         <v>1553</v>
       </c>
       <c r="B869" s="7" t="s">
-        <v>3104</v>
+        <v>3099</v>
       </c>
       <c r="C869" s="7" t="s">
         <v>1748</v>
@@ -76340,16 +76352,16 @@
         <v>1567</v>
       </c>
       <c r="F869" s="7" t="s">
-        <v>3105</v>
+        <v>3100</v>
       </c>
       <c r="G869" s="7" t="s">
-        <v>3105</v>
+        <v>3100</v>
       </c>
       <c r="H869" s="7">
-        <v>11307</v>
+        <v>11169</v>
       </c>
       <c r="I869" s="7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J869" s="7" t="s">
         <v>1556</v>
@@ -76363,10 +76375,10 @@
         <v>1553</v>
       </c>
       <c r="B870" s="7" t="s">
-        <v>3099</v>
+        <v>3104</v>
       </c>
       <c r="C870" s="7" t="s">
-        <v>2905</v>
+        <v>1748</v>
       </c>
       <c r="D870" s="7" t="s">
         <v>805</v>
@@ -76375,13 +76387,13 @@
         <v>1567</v>
       </c>
       <c r="F870" s="7" t="s">
-        <v>3101</v>
+        <v>3105</v>
       </c>
       <c r="G870" s="7" t="s">
-        <v>3101</v>
+        <v>3105</v>
       </c>
       <c r="H870" s="7">
-        <v>11345</v>
+        <v>11307</v>
       </c>
       <c r="I870" s="7">
         <v>35</v>
@@ -76398,7 +76410,7 @@
         <v>1553</v>
       </c>
       <c r="B871" s="7" t="s">
-        <v>3108</v>
+        <v>3099</v>
       </c>
       <c r="C871" s="7" t="s">
         <v>2905</v>
@@ -76410,16 +76422,16 @@
         <v>1567</v>
       </c>
       <c r="F871" s="7" t="s">
-        <v>3109</v>
+        <v>3101</v>
       </c>
       <c r="G871" s="7" t="s">
-        <v>3109</v>
+        <v>3101</v>
       </c>
       <c r="H871" s="7">
         <v>11345</v>
       </c>
       <c r="I871" s="7">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J871" s="7" t="s">
         <v>1556</v>
@@ -76433,7 +76445,7 @@
         <v>1553</v>
       </c>
       <c r="B872" s="7" t="s">
-        <v>3106</v>
+        <v>3108</v>
       </c>
       <c r="C872" s="7" t="s">
         <v>2905</v>
@@ -76445,13 +76457,13 @@
         <v>1567</v>
       </c>
       <c r="F872" s="7" t="s">
-        <v>3107</v>
+        <v>3109</v>
       </c>
       <c r="G872" s="7" t="s">
-        <v>3107</v>
+        <v>3109</v>
       </c>
       <c r="H872" s="7">
-        <v>11576</v>
+        <v>11345</v>
       </c>
       <c r="I872" s="7">
         <v>42</v>
@@ -76465,13 +76477,13 @@
     </row>
     <row r="873" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A873" s="7" t="s">
-        <v>3113</v>
+        <v>1553</v>
       </c>
       <c r="B873" s="7" t="s">
-        <v>3117</v>
+        <v>3106</v>
       </c>
       <c r="C873" s="7" t="s">
-        <v>1566</v>
+        <v>2905</v>
       </c>
       <c r="D873" s="7" t="s">
         <v>805</v>
@@ -76480,22 +76492,22 @@
         <v>1567</v>
       </c>
       <c r="F873" s="7" t="s">
-        <v>727</v>
+        <v>3107</v>
       </c>
       <c r="G873" s="7" t="s">
-        <v>3118</v>
+        <v>3107</v>
       </c>
       <c r="H873" s="7">
-        <v>12180</v>
+        <v>11576</v>
       </c>
       <c r="I873" s="7">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="J873" s="7" t="s">
-        <v>3116</v>
+        <v>1556</v>
       </c>
       <c r="K873" s="7" t="s">
-        <v>1472</v>
+        <v>675</v>
       </c>
     </row>
     <row r="874" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -76503,7 +76515,7 @@
         <v>3113</v>
       </c>
       <c r="B874" s="7" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
       <c r="C874" s="7" t="s">
         <v>1566</v>
@@ -76518,16 +76530,16 @@
         <v>727</v>
       </c>
       <c r="G874" s="7" t="s">
-        <v>3120</v>
+        <v>3118</v>
       </c>
       <c r="H874" s="7">
-        <v>12760</v>
+        <v>12180</v>
       </c>
       <c r="I874" s="7">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="J874" s="7" t="s">
-        <v>3121</v>
+        <v>3116</v>
       </c>
       <c r="K874" s="7" t="s">
         <v>1472</v>
@@ -76538,7 +76550,7 @@
         <v>3113</v>
       </c>
       <c r="B875" s="7" t="s">
-        <v>3114</v>
+        <v>3119</v>
       </c>
       <c r="C875" s="7" t="s">
         <v>1566</v>
@@ -76553,30 +76565,30 @@
         <v>727</v>
       </c>
       <c r="G875" s="7" t="s">
-        <v>3115</v>
+        <v>3120</v>
       </c>
       <c r="H875" s="7">
-        <v>11600</v>
+        <v>12760</v>
       </c>
       <c r="I875" s="7">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="J875" s="7" t="s">
-        <v>3116</v>
+        <v>3121</v>
       </c>
       <c r="K875" s="7" t="s">
-        <v>1439</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="876" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A876" s="7" t="s">
-        <v>1166</v>
+        <v>3113</v>
       </c>
       <c r="B876" s="7" t="s">
-        <v>3122</v>
+        <v>3114</v>
       </c>
       <c r="C876" s="7" t="s">
-        <v>3123</v>
+        <v>1566</v>
       </c>
       <c r="D876" s="7" t="s">
         <v>805</v>
@@ -76585,22 +76597,22 @@
         <v>1567</v>
       </c>
       <c r="F876" s="7" t="s">
-        <v>3124</v>
+        <v>727</v>
       </c>
       <c r="G876" s="7" t="s">
-        <v>3125</v>
+        <v>3115</v>
       </c>
       <c r="H876" s="7">
-        <v>17530</v>
+        <v>11600</v>
       </c>
       <c r="I876" s="7">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="J876" s="7" t="s">
-        <v>1165</v>
+        <v>3116</v>
       </c>
       <c r="K876" s="7" t="s">
-        <v>1314</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="877" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -76608,10 +76620,10 @@
         <v>1166</v>
       </c>
       <c r="B877" s="7" t="s">
-        <v>3452</v>
+        <v>3122</v>
       </c>
       <c r="C877" s="7" t="s">
-        <v>1566</v>
+        <v>3123</v>
       </c>
       <c r="D877" s="7" t="s">
         <v>805</v>
@@ -76620,22 +76632,22 @@
         <v>1567</v>
       </c>
       <c r="F877" s="7" t="s">
-        <v>3453</v>
+        <v>3124</v>
       </c>
       <c r="G877" s="7" t="s">
-        <v>3454</v>
+        <v>3125</v>
       </c>
       <c r="H877" s="7">
-        <v>8800</v>
+        <v>17530</v>
       </c>
       <c r="I877" s="7">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="J877" s="7" t="s">
         <v>1165</v>
       </c>
       <c r="K877" s="7" t="s">
-        <v>3313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="878" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -76643,10 +76655,10 @@
         <v>1166</v>
       </c>
       <c r="B878" s="7" t="s">
-        <v>3455</v>
+        <v>3452</v>
       </c>
       <c r="C878" s="7" t="s">
-        <v>3456</v>
+        <v>1566</v>
       </c>
       <c r="D878" s="7" t="s">
         <v>805</v>
@@ -76655,16 +76667,16 @@
         <v>1567</v>
       </c>
       <c r="F878" s="7" t="s">
-        <v>3457</v>
+        <v>3453</v>
       </c>
       <c r="G878" s="7" t="s">
-        <v>3459</v>
+        <v>3454</v>
       </c>
       <c r="H878" s="7">
-        <v>8840</v>
+        <v>8800</v>
       </c>
       <c r="I878" s="7">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J878" s="7" t="s">
         <v>1165</v>
@@ -76681,7 +76693,7 @@
         <v>3455</v>
       </c>
       <c r="C879" s="7" t="s">
-        <v>1566</v>
+        <v>3456</v>
       </c>
       <c r="D879" s="7" t="s">
         <v>805</v>
@@ -76690,16 +76702,16 @@
         <v>1567</v>
       </c>
       <c r="F879" s="7" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="G879" s="7" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="H879" s="7">
-        <v>8845</v>
+        <v>8840</v>
       </c>
       <c r="I879" s="7">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J879" s="7" t="s">
         <v>1165</v>
@@ -76713,7 +76725,7 @@
         <v>1166</v>
       </c>
       <c r="B880" s="7" t="s">
-        <v>3452</v>
+        <v>3455</v>
       </c>
       <c r="C880" s="7" t="s">
         <v>1566</v>
@@ -76725,13 +76737,13 @@
         <v>1567</v>
       </c>
       <c r="F880" s="7" t="s">
-        <v>3461</v>
+        <v>3458</v>
       </c>
       <c r="G880" s="7" t="s">
-        <v>3462</v>
+        <v>3460</v>
       </c>
       <c r="H880" s="7">
-        <v>8925</v>
+        <v>8845</v>
       </c>
       <c r="I880" s="7">
         <v>40</v>
@@ -76748,10 +76760,10 @@
         <v>1166</v>
       </c>
       <c r="B881" s="7" t="s">
-        <v>3464</v>
+        <v>3452</v>
       </c>
       <c r="C881" s="7" t="s">
-        <v>3456</v>
+        <v>1566</v>
       </c>
       <c r="D881" s="7" t="s">
         <v>805</v>
@@ -76760,16 +76772,16 @@
         <v>1567</v>
       </c>
       <c r="F881" s="7" t="s">
-        <v>3465</v>
+        <v>3461</v>
       </c>
       <c r="G881" s="7" t="s">
-        <v>3466</v>
+        <v>3462</v>
       </c>
       <c r="H881" s="7">
-        <v>8985</v>
+        <v>8925</v>
       </c>
       <c r="I881" s="7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J881" s="7" t="s">
         <v>1165</v>
@@ -76783,10 +76795,10 @@
         <v>1166</v>
       </c>
       <c r="B882" s="7" t="s">
-        <v>3455</v>
+        <v>3464</v>
       </c>
       <c r="C882" s="7" t="s">
-        <v>1566</v>
+        <v>3456</v>
       </c>
       <c r="D882" s="7" t="s">
         <v>805</v>
@@ -76795,16 +76807,16 @@
         <v>1567</v>
       </c>
       <c r="F882" s="7" t="s">
-        <v>3467</v>
+        <v>3465</v>
       </c>
       <c r="G882" s="7" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="H882" s="7">
-        <v>9010</v>
+        <v>8985</v>
       </c>
       <c r="I882" s="7">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J882" s="7" t="s">
         <v>1165</v>
@@ -76818,7 +76830,7 @@
         <v>1166</v>
       </c>
       <c r="B883" s="7" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="C883" s="7" t="s">
         <v>1566</v>
@@ -76830,16 +76842,16 @@
         <v>1567</v>
       </c>
       <c r="F883" s="7" t="s">
-        <v>3469</v>
+        <v>3467</v>
       </c>
       <c r="G883" s="7" t="s">
-        <v>3471</v>
+        <v>3468</v>
       </c>
       <c r="H883" s="7">
-        <v>9200</v>
+        <v>9010</v>
       </c>
       <c r="I883" s="7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J883" s="7" t="s">
         <v>1165</v>
@@ -76853,7 +76865,7 @@
         <v>1166</v>
       </c>
       <c r="B884" s="7" t="s">
-        <v>3452</v>
+        <v>3463</v>
       </c>
       <c r="C884" s="7" t="s">
         <v>1566</v>
@@ -76865,13 +76877,13 @@
         <v>1567</v>
       </c>
       <c r="F884" s="7" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="G884" s="7" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="H884" s="7">
-        <v>9225</v>
+        <v>9200</v>
       </c>
       <c r="I884" s="7">
         <v>40</v>
@@ -76885,10 +76897,10 @@
     </row>
     <row r="885" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A885" s="7" t="s">
-        <v>45</v>
+        <v>1166</v>
       </c>
       <c r="B885" s="7" t="s">
-        <v>3126</v>
+        <v>3452</v>
       </c>
       <c r="C885" s="7" t="s">
         <v>1566</v>
@@ -76900,22 +76912,22 @@
         <v>1567</v>
       </c>
       <c r="F885" s="7" t="s">
-        <v>676</v>
+        <v>3470</v>
       </c>
       <c r="G885" s="7" t="s">
-        <v>3129</v>
-      </c>
-      <c r="H885" s="38">
-        <v>13970</v>
+        <v>3472</v>
+      </c>
+      <c r="H885" s="7">
+        <v>9225</v>
       </c>
       <c r="I885" s="7">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J885" s="7" t="s">
-        <v>3128</v>
+        <v>1165</v>
       </c>
       <c r="K885" s="7" t="s">
-        <v>1319</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="886" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -76934,17 +76946,17 @@
       <c r="E886" s="7" t="s">
         <v>1567</v>
       </c>
-      <c r="F886" s="42" t="s">
+      <c r="F886" s="7" t="s">
         <v>676</v>
       </c>
       <c r="G886" s="7" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="H886" s="38">
-        <v>14250</v>
+        <v>13970</v>
       </c>
       <c r="I886" s="7">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J886" s="7" t="s">
         <v>3128</v>
@@ -76969,34 +76981,34 @@
       <c r="E887" s="7" t="s">
         <v>1567</v>
       </c>
-      <c r="F887" s="7" t="s">
+      <c r="F887" s="42" t="s">
         <v>676</v>
       </c>
       <c r="G887" s="7" t="s">
-        <v>3127</v>
+        <v>3130</v>
       </c>
       <c r="H887" s="38">
-        <v>10880</v>
+        <v>14250</v>
       </c>
       <c r="I887" s="7">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="J887" s="7" t="s">
         <v>3128</v>
       </c>
       <c r="K887" s="7" t="s">
-        <v>675</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="888" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A888" s="7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B888" s="7" t="s">
-        <v>3419</v>
+        <v>3126</v>
       </c>
       <c r="C888" s="7" t="s">
-        <v>3413</v>
+        <v>1566</v>
       </c>
       <c r="D888" s="7" t="s">
         <v>805</v>
@@ -77004,23 +77016,23 @@
       <c r="E888" s="7" t="s">
         <v>1567</v>
       </c>
-      <c r="F888" s="42" t="s">
+      <c r="F888" s="7" t="s">
         <v>676</v>
       </c>
       <c r="G888" s="7" t="s">
-        <v>3416</v>
+        <v>3127</v>
       </c>
       <c r="H888" s="38">
-        <v>8370</v>
+        <v>10880</v>
       </c>
       <c r="I888" s="7">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="J888" s="7" t="s">
-        <v>3415</v>
+        <v>3128</v>
       </c>
       <c r="K888" s="7" t="s">
-        <v>3313</v>
+        <v>675</v>
       </c>
     </row>
     <row r="889" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -77028,7 +77040,7 @@
         <v>36</v>
       </c>
       <c r="B889" s="7" t="s">
-        <v>3426</v>
+        <v>3419</v>
       </c>
       <c r="C889" s="7" t="s">
         <v>3413</v>
@@ -77040,16 +77052,16 @@
         <v>1567</v>
       </c>
       <c r="F889" s="42" t="s">
-        <v>3427</v>
+        <v>676</v>
       </c>
       <c r="G889" s="7" t="s">
-        <v>3428</v>
+        <v>3416</v>
       </c>
       <c r="H889" s="38">
-        <v>8530</v>
+        <v>8370</v>
       </c>
       <c r="I889" s="7">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J889" s="7" t="s">
         <v>3415</v>
@@ -77063,7 +77075,7 @@
         <v>36</v>
       </c>
       <c r="B890" s="7" t="s">
-        <v>3420</v>
+        <v>3426</v>
       </c>
       <c r="C890" s="7" t="s">
         <v>3413</v>
@@ -77075,16 +77087,16 @@
         <v>1567</v>
       </c>
       <c r="F890" s="42" t="s">
-        <v>676</v>
+        <v>3427</v>
       </c>
       <c r="G890" s="7" t="s">
-        <v>3417</v>
+        <v>3428</v>
       </c>
       <c r="H890" s="38">
-        <v>8590</v>
+        <v>8530</v>
       </c>
       <c r="I890" s="7">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="J890" s="7" t="s">
         <v>3415</v>
@@ -77098,7 +77110,7 @@
         <v>36</v>
       </c>
       <c r="B891" s="7" t="s">
-        <v>3423</v>
+        <v>3420</v>
       </c>
       <c r="C891" s="7" t="s">
         <v>3413</v>
@@ -77113,13 +77125,13 @@
         <v>676</v>
       </c>
       <c r="G891" s="7" t="s">
-        <v>3422</v>
+        <v>3417</v>
       </c>
       <c r="H891" s="38">
-        <v>8750</v>
+        <v>8590</v>
       </c>
       <c r="I891" s="7">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="J891" s="7" t="s">
         <v>3415</v>
@@ -77133,7 +77145,7 @@
         <v>36</v>
       </c>
       <c r="B892" s="7" t="s">
-        <v>3421</v>
+        <v>3423</v>
       </c>
       <c r="C892" s="7" t="s">
         <v>3413</v>
@@ -77148,13 +77160,13 @@
         <v>676</v>
       </c>
       <c r="G892" s="7" t="s">
-        <v>3418</v>
+        <v>3422</v>
       </c>
       <c r="H892" s="38">
-        <v>8995</v>
+        <v>8750</v>
       </c>
       <c r="I892" s="7">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="J892" s="7" t="s">
         <v>3415</v>
@@ -77168,7 +77180,7 @@
         <v>36</v>
       </c>
       <c r="B893" s="7" t="s">
-        <v>3424</v>
+        <v>3421</v>
       </c>
       <c r="C893" s="7" t="s">
         <v>3413</v>
@@ -77183,13 +77195,13 @@
         <v>676</v>
       </c>
       <c r="G893" s="7" t="s">
-        <v>3425</v>
+        <v>3418</v>
       </c>
       <c r="H893" s="38">
-        <v>9150</v>
+        <v>8995</v>
       </c>
       <c r="I893" s="7">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="J893" s="7" t="s">
         <v>3415</v>
@@ -77203,7 +77215,7 @@
         <v>36</v>
       </c>
       <c r="B894" s="7" t="s">
-        <v>3412</v>
+        <v>3424</v>
       </c>
       <c r="C894" s="7" t="s">
         <v>3413</v>
@@ -77218,30 +77230,30 @@
         <v>676</v>
       </c>
       <c r="G894" s="7" t="s">
-        <v>3414</v>
+        <v>3425</v>
       </c>
       <c r="H894" s="38">
-        <v>7800</v>
+        <v>9150</v>
       </c>
       <c r="I894" s="7">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="J894" s="7" t="s">
         <v>3415</v>
       </c>
       <c r="K894" s="7" t="s">
-        <v>3338</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="895" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A895" s="7" t="s">
-        <v>3654</v>
+        <v>36</v>
       </c>
       <c r="B895" s="7" t="s">
-        <v>3657</v>
+        <v>3412</v>
       </c>
       <c r="C895" s="7" t="s">
-        <v>3678</v>
+        <v>3413</v>
       </c>
       <c r="D895" s="7" t="s">
         <v>805</v>
@@ -77249,23 +77261,23 @@
       <c r="E895" s="7" t="s">
         <v>1567</v>
       </c>
-      <c r="F895" s="7" t="s">
-        <v>3660</v>
-      </c>
-      <c r="G895" s="38" t="s">
-        <v>3670</v>
-      </c>
-      <c r="H895" s="7">
-        <v>9041</v>
+      <c r="F895" s="42" t="s">
+        <v>676</v>
+      </c>
+      <c r="G895" s="7" t="s">
+        <v>3414</v>
+      </c>
+      <c r="H895" s="38">
+        <v>7800</v>
       </c>
       <c r="I895" s="7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J895" s="7" t="s">
-        <v>3616</v>
+        <v>3415</v>
       </c>
       <c r="K895" s="7" t="s">
-        <v>675</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="896" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -77276,7 +77288,7 @@
         <v>3657</v>
       </c>
       <c r="C896" s="7" t="s">
-        <v>3653</v>
+        <v>3678</v>
       </c>
       <c r="D896" s="7" t="s">
         <v>805</v>
@@ -77285,16 +77297,16 @@
         <v>1567</v>
       </c>
       <c r="F896" s="7" t="s">
-        <v>3659</v>
+        <v>3660</v>
       </c>
       <c r="G896" s="38" t="s">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="H896" s="7">
-        <v>9118</v>
+        <v>9041</v>
       </c>
       <c r="I896" s="7">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J896" s="7" t="s">
         <v>3616</v>
@@ -77311,7 +77323,7 @@
         <v>3657</v>
       </c>
       <c r="C897" s="7" t="s">
-        <v>1566</v>
+        <v>3653</v>
       </c>
       <c r="D897" s="7" t="s">
         <v>805</v>
@@ -77320,16 +77332,16 @@
         <v>1567</v>
       </c>
       <c r="F897" s="7" t="s">
-        <v>3664</v>
+        <v>3659</v>
       </c>
       <c r="G897" s="38" t="s">
-        <v>3674</v>
+        <v>3669</v>
       </c>
       <c r="H897" s="7">
-        <v>9555</v>
+        <v>9118</v>
       </c>
       <c r="I897" s="7">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J897" s="7" t="s">
         <v>3616</v>
@@ -77346,7 +77358,7 @@
         <v>3657</v>
       </c>
       <c r="C898" s="7" t="s">
-        <v>3679</v>
+        <v>1566</v>
       </c>
       <c r="D898" s="7" t="s">
         <v>805</v>
@@ -77355,16 +77367,16 @@
         <v>1567</v>
       </c>
       <c r="F898" s="7" t="s">
-        <v>3663</v>
+        <v>3664</v>
       </c>
       <c r="G898" s="38" t="s">
-        <v>3673</v>
+        <v>3674</v>
       </c>
       <c r="H898" s="7">
-        <v>9650</v>
+        <v>9555</v>
       </c>
       <c r="I898" s="7">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J898" s="7" t="s">
         <v>3616</v>
@@ -77381,7 +77393,7 @@
         <v>3657</v>
       </c>
       <c r="C899" s="7" t="s">
-        <v>3678</v>
+        <v>3679</v>
       </c>
       <c r="D899" s="7" t="s">
         <v>805</v>
@@ -77390,16 +77402,16 @@
         <v>1567</v>
       </c>
       <c r="F899" s="7" t="s">
-        <v>3665</v>
+        <v>3663</v>
       </c>
       <c r="G899" s="38" t="s">
-        <v>3675</v>
+        <v>3673</v>
       </c>
       <c r="H899" s="7">
-        <v>9685</v>
+        <v>9650</v>
       </c>
       <c r="I899" s="7">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="J899" s="7" t="s">
         <v>3616</v>
@@ -77416,7 +77428,7 @@
         <v>3657</v>
       </c>
       <c r="C900" s="7" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="D900" s="7" t="s">
         <v>805</v>
@@ -77425,16 +77437,16 @@
         <v>1567</v>
       </c>
       <c r="F900" s="7" t="s">
-        <v>3662</v>
+        <v>3665</v>
       </c>
       <c r="G900" s="38" t="s">
-        <v>3672</v>
+        <v>3675</v>
       </c>
       <c r="H900" s="7">
-        <v>9728</v>
+        <v>9685</v>
       </c>
       <c r="I900" s="7">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="J900" s="7" t="s">
         <v>3616</v>
@@ -77451,7 +77463,7 @@
         <v>3657</v>
       </c>
       <c r="C901" s="7" t="s">
-        <v>1566</v>
+        <v>3679</v>
       </c>
       <c r="D901" s="7" t="s">
         <v>805</v>
@@ -77460,16 +77472,16 @@
         <v>1567</v>
       </c>
       <c r="F901" s="7" t="s">
-        <v>3666</v>
+        <v>3662</v>
       </c>
       <c r="G901" s="38" t="s">
-        <v>3676</v>
+        <v>3672</v>
       </c>
       <c r="H901" s="7">
-        <v>9812</v>
+        <v>9728</v>
       </c>
       <c r="I901" s="7">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="J901" s="7" t="s">
         <v>3616</v>
@@ -77486,7 +77498,7 @@
         <v>3657</v>
       </c>
       <c r="C902" s="7" t="s">
-        <v>3678</v>
+        <v>1566</v>
       </c>
       <c r="D902" s="7" t="s">
         <v>805</v>
@@ -77495,16 +77507,16 @@
         <v>1567</v>
       </c>
       <c r="F902" s="7" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="G902" s="38" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
       <c r="H902" s="7">
-        <v>9845</v>
+        <v>9812</v>
       </c>
       <c r="I902" s="7">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="J902" s="7" t="s">
         <v>3616</v>
@@ -77521,7 +77533,7 @@
         <v>3657</v>
       </c>
       <c r="C903" s="7" t="s">
-        <v>3653</v>
+        <v>3678</v>
       </c>
       <c r="D903" s="7" t="s">
         <v>805</v>
@@ -77530,16 +77542,16 @@
         <v>1567</v>
       </c>
       <c r="F903" s="7" t="s">
-        <v>3658</v>
+        <v>3667</v>
       </c>
       <c r="G903" s="38" t="s">
-        <v>3668</v>
+        <v>3677</v>
       </c>
       <c r="H903" s="7">
-        <v>10013</v>
+        <v>9845</v>
       </c>
       <c r="I903" s="7">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J903" s="7" t="s">
         <v>3616</v>
@@ -77556,7 +77568,7 @@
         <v>3657</v>
       </c>
       <c r="C904" s="7" t="s">
-        <v>3678</v>
+        <v>3653</v>
       </c>
       <c r="D904" s="7" t="s">
         <v>805</v>
@@ -77565,16 +77577,16 @@
         <v>1567</v>
       </c>
       <c r="F904" s="7" t="s">
-        <v>3661</v>
+        <v>3658</v>
       </c>
       <c r="G904" s="38" t="s">
-        <v>3671</v>
+        <v>3668</v>
       </c>
       <c r="H904" s="7">
-        <v>10123</v>
+        <v>10013</v>
       </c>
       <c r="I904" s="7">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="J904" s="7" t="s">
         <v>3616</v>
@@ -77585,13 +77597,13 @@
     </row>
     <row r="905" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A905" s="7" t="s">
-        <v>736</v>
+        <v>3654</v>
       </c>
       <c r="B905" s="7" t="s">
-        <v>3500</v>
+        <v>3657</v>
       </c>
       <c r="C905" s="7" t="s">
-        <v>1566</v>
+        <v>3678</v>
       </c>
       <c r="D905" s="7" t="s">
         <v>805</v>
@@ -77600,22 +77612,22 @@
         <v>1567</v>
       </c>
       <c r="F905" s="7" t="s">
-        <v>676</v>
-      </c>
-      <c r="G905" s="7" t="s">
-        <v>3131</v>
-      </c>
-      <c r="H905" s="38">
-        <v>24350</v>
+        <v>3661</v>
+      </c>
+      <c r="G905" s="38" t="s">
+        <v>3671</v>
+      </c>
+      <c r="H905" s="7">
+        <v>10123</v>
       </c>
       <c r="I905" s="7">
-        <v>420</v>
+        <v>57</v>
       </c>
       <c r="J905" s="7" t="s">
-        <v>810</v>
+        <v>3616</v>
       </c>
       <c r="K905" s="7" t="s">
-        <v>1322</v>
+        <v>675</v>
       </c>
     </row>
     <row r="906" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -77623,34 +77635,34 @@
         <v>736</v>
       </c>
       <c r="B906" s="7" t="s">
-        <v>3555</v>
+        <v>3500</v>
       </c>
       <c r="C906" s="7" t="s">
-        <v>1699</v>
+        <v>1566</v>
       </c>
       <c r="D906" s="7" t="s">
-        <v>744</v>
+        <v>805</v>
       </c>
       <c r="E906" s="7" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F906" s="7" t="s">
-        <v>3556</v>
-      </c>
-      <c r="G906" s="7">
-        <v>10563</v>
+        <v>676</v>
+      </c>
+      <c r="G906" s="7" t="s">
+        <v>3131</v>
       </c>
       <c r="H906" s="38">
-        <v>147</v>
+        <v>24350</v>
       </c>
       <c r="I906" s="7">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="J906" s="7" t="s">
-        <v>3554</v>
+        <v>810</v>
       </c>
       <c r="K906" s="7" t="s">
-        <v>1689</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="907" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -77670,16 +77682,16 @@
         <v>1612</v>
       </c>
       <c r="F907" s="7" t="s">
-        <v>3559</v>
+        <v>3556</v>
       </c>
       <c r="G907" s="7">
-        <v>10814</v>
+        <v>10563</v>
       </c>
       <c r="H907" s="38">
-        <v>3236</v>
+        <v>147</v>
       </c>
       <c r="I907" s="7">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J907" s="7" t="s">
         <v>3554</v>
@@ -77705,16 +77717,16 @@
         <v>1612</v>
       </c>
       <c r="F908" s="7" t="s">
-        <v>3562</v>
+        <v>3559</v>
       </c>
       <c r="G908" s="7">
-        <v>10568</v>
+        <v>10814</v>
       </c>
       <c r="H908" s="38">
-        <v>12347</v>
+        <v>3236</v>
       </c>
       <c r="I908" s="7">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J908" s="7" t="s">
         <v>3554</v>
@@ -77737,19 +77749,19 @@
         <v>744</v>
       </c>
       <c r="E909" s="7" t="s">
-        <v>1600</v>
+        <v>1612</v>
       </c>
       <c r="F909" s="7" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="G909" s="7">
-        <v>10815</v>
+        <v>10568</v>
       </c>
       <c r="H909" s="38">
-        <v>85875</v>
+        <v>12347</v>
       </c>
       <c r="I909" s="7">
-        <v>1240</v>
+        <v>90</v>
       </c>
       <c r="J909" s="7" t="s">
         <v>3554</v>
@@ -77775,16 +77787,16 @@
         <v>1600</v>
       </c>
       <c r="F910" s="7" t="s">
-        <v>3560</v>
+        <v>3563</v>
       </c>
       <c r="G910" s="7">
-        <v>10567</v>
+        <v>10815</v>
       </c>
       <c r="H910" s="38">
-        <v>97806</v>
+        <v>85875</v>
       </c>
       <c r="I910" s="7">
-        <v>1010</v>
+        <v>1240</v>
       </c>
       <c r="J910" s="7" t="s">
         <v>3554</v>
@@ -77810,16 +77822,16 @@
         <v>1600</v>
       </c>
       <c r="F911" s="7" t="s">
-        <v>3564</v>
+        <v>3560</v>
       </c>
       <c r="G911" s="7">
-        <v>10816</v>
+        <v>10567</v>
       </c>
       <c r="H911" s="38">
-        <v>103484</v>
+        <v>97806</v>
       </c>
       <c r="I911" s="7">
-        <v>1560</v>
+        <v>1010</v>
       </c>
       <c r="J911" s="7" t="s">
         <v>3554</v>
@@ -77845,16 +77857,16 @@
         <v>1600</v>
       </c>
       <c r="F912" s="7" t="s">
-        <v>3561</v>
+        <v>3564</v>
       </c>
       <c r="G912" s="7">
-        <v>10813</v>
+        <v>10816</v>
       </c>
       <c r="H912" s="38">
-        <v>116237</v>
+        <v>103484</v>
       </c>
       <c r="I912" s="7">
-        <v>1340</v>
+        <v>1560</v>
       </c>
       <c r="J912" s="7" t="s">
         <v>3554</v>
@@ -77880,16 +77892,16 @@
         <v>1600</v>
       </c>
       <c r="F913" s="7" t="s">
-        <v>3557</v>
+        <v>3561</v>
       </c>
       <c r="G913" s="7">
-        <v>10564</v>
+        <v>10813</v>
       </c>
       <c r="H913" s="38">
-        <v>130054</v>
+        <v>116237</v>
       </c>
       <c r="I913" s="7">
-        <v>1100</v>
+        <v>1340</v>
       </c>
       <c r="J913" s="7" t="s">
         <v>3554</v>
@@ -77915,16 +77927,16 @@
         <v>1600</v>
       </c>
       <c r="F914" s="7" t="s">
-        <v>3565</v>
+        <v>3557</v>
       </c>
       <c r="G914" s="7">
-        <v>10569</v>
+        <v>10564</v>
       </c>
       <c r="H914" s="38">
-        <v>227180</v>
+        <v>130054</v>
       </c>
       <c r="I914" s="7">
-        <v>5080</v>
+        <v>1100</v>
       </c>
       <c r="J914" s="7" t="s">
         <v>3554</v>
@@ -77950,16 +77962,16 @@
         <v>1600</v>
       </c>
       <c r="F915" s="7" t="s">
-        <v>3568</v>
+        <v>3565</v>
       </c>
       <c r="G915" s="7">
-        <v>10571</v>
+        <v>10569</v>
       </c>
       <c r="H915" s="38">
-        <v>248278</v>
+        <v>227180</v>
       </c>
       <c r="I915" s="7">
-        <v>8060</v>
+        <v>5080</v>
       </c>
       <c r="J915" s="7" t="s">
         <v>3554</v>
@@ -77985,16 +77997,16 @@
         <v>1600</v>
       </c>
       <c r="F916" s="7" t="s">
-        <v>3567</v>
+        <v>3568</v>
       </c>
       <c r="G916" s="7">
-        <v>10570</v>
+        <v>10571</v>
       </c>
       <c r="H916" s="38">
-        <v>249652</v>
+        <v>248278</v>
       </c>
       <c r="I916" s="7">
-        <v>10380</v>
+        <v>8060</v>
       </c>
       <c r="J916" s="7" t="s">
         <v>3554</v>
@@ -78020,16 +78032,16 @@
         <v>1600</v>
       </c>
       <c r="F917" s="7" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="G917" s="7">
-        <v>10572</v>
+        <v>10570</v>
       </c>
       <c r="H917" s="38">
-        <v>262321</v>
+        <v>249652</v>
       </c>
       <c r="I917" s="7">
-        <v>10670</v>
+        <v>10380</v>
       </c>
       <c r="J917" s="7" t="s">
         <v>3554</v>
@@ -78055,16 +78067,16 @@
         <v>1600</v>
       </c>
       <c r="F918" s="7" t="s">
-        <v>3566</v>
+        <v>3568</v>
       </c>
       <c r="G918" s="7">
-        <v>10817</v>
+        <v>10572</v>
       </c>
       <c r="H918" s="38">
-        <v>269293</v>
+        <v>262321</v>
       </c>
       <c r="I918" s="7">
-        <v>14850</v>
+        <v>10670</v>
       </c>
       <c r="J918" s="7" t="s">
         <v>3554</v>
@@ -78090,16 +78102,16 @@
         <v>1600</v>
       </c>
       <c r="F919" s="7" t="s">
-        <v>3558</v>
+        <v>3566</v>
       </c>
       <c r="G919" s="7">
-        <v>10566</v>
+        <v>10817</v>
       </c>
       <c r="H919" s="38">
-        <v>317291</v>
+        <v>269293</v>
       </c>
       <c r="I919" s="7">
-        <v>12690</v>
+        <v>14850</v>
       </c>
       <c r="J919" s="7" t="s">
         <v>3554</v>
@@ -78113,7 +78125,7 @@
         <v>736</v>
       </c>
       <c r="B920" s="7" t="s">
-        <v>3502</v>
+        <v>3555</v>
       </c>
       <c r="C920" s="7" t="s">
         <v>1699</v>
@@ -78122,25 +78134,25 @@
         <v>744</v>
       </c>
       <c r="E920" s="7" t="s">
-        <v>1612</v>
+        <v>1600</v>
       </c>
       <c r="F920" s="7" t="s">
-        <v>3522</v>
-      </c>
-      <c r="G920" s="7" t="s">
-        <v>3522</v>
+        <v>3558</v>
+      </c>
+      <c r="G920" s="7">
+        <v>10566</v>
       </c>
       <c r="H920" s="38">
-        <v>1567</v>
+        <v>317291</v>
       </c>
       <c r="I920" s="7">
-        <v>165</v>
+        <v>12690</v>
       </c>
       <c r="J920" s="7" t="s">
-        <v>3499</v>
+        <v>3554</v>
       </c>
       <c r="K920" s="7" t="s">
-        <v>3338</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="921" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -78151,7 +78163,7 @@
         <v>3502</v>
       </c>
       <c r="C921" s="7" t="s">
-        <v>3550</v>
+        <v>1699</v>
       </c>
       <c r="D921" s="7" t="s">
         <v>744</v>
@@ -78160,16 +78172,16 @@
         <v>1612</v>
       </c>
       <c r="F921" s="7" t="s">
-        <v>3540</v>
+        <v>3522</v>
       </c>
       <c r="G921" s="7" t="s">
-        <v>3540</v>
+        <v>3522</v>
       </c>
       <c r="H921" s="38">
-        <v>1971</v>
+        <v>1567</v>
       </c>
       <c r="I921" s="7">
-        <v>439</v>
+        <v>165</v>
       </c>
       <c r="J921" s="7" t="s">
         <v>3499</v>
@@ -78186,7 +78198,7 @@
         <v>3502</v>
       </c>
       <c r="C922" s="7" t="s">
-        <v>1699</v>
+        <v>3550</v>
       </c>
       <c r="D922" s="7" t="s">
         <v>744</v>
@@ -78195,16 +78207,16 @@
         <v>1612</v>
       </c>
       <c r="F922" s="7" t="s">
-        <v>3507</v>
+        <v>3540</v>
       </c>
       <c r="G922" s="7" t="s">
-        <v>3507</v>
+        <v>3540</v>
       </c>
       <c r="H922" s="38">
-        <v>2475</v>
+        <v>1971</v>
       </c>
       <c r="I922" s="7">
-        <v>126</v>
+        <v>439</v>
       </c>
       <c r="J922" s="7" t="s">
         <v>3499</v>
@@ -78221,7 +78233,7 @@
         <v>3502</v>
       </c>
       <c r="C923" s="7" t="s">
-        <v>3550</v>
+        <v>1699</v>
       </c>
       <c r="D923" s="7" t="s">
         <v>744</v>
@@ -78230,16 +78242,16 @@
         <v>1612</v>
       </c>
       <c r="F923" s="7" t="s">
-        <v>3546</v>
+        <v>3507</v>
       </c>
       <c r="G923" s="7" t="s">
-        <v>3546</v>
+        <v>3507</v>
       </c>
       <c r="H923" s="38">
-        <v>2925</v>
+        <v>2475</v>
       </c>
       <c r="I923" s="7">
-        <v>279</v>
+        <v>126</v>
       </c>
       <c r="J923" s="7" t="s">
         <v>3499</v>
@@ -78256,7 +78268,7 @@
         <v>3502</v>
       </c>
       <c r="C924" s="7" t="s">
-        <v>1699</v>
+        <v>3550</v>
       </c>
       <c r="D924" s="7" t="s">
         <v>744</v>
@@ -78265,16 +78277,16 @@
         <v>1612</v>
       </c>
       <c r="F924" s="7" t="s">
-        <v>3503</v>
+        <v>3546</v>
       </c>
       <c r="G924" s="7" t="s">
-        <v>3503</v>
+        <v>3546</v>
       </c>
       <c r="H924" s="38">
-        <v>3060</v>
+        <v>2925</v>
       </c>
       <c r="I924" s="7">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="J924" s="7" t="s">
         <v>3499</v>
@@ -78300,16 +78312,16 @@
         <v>1612</v>
       </c>
       <c r="F925" s="7" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="G925" s="7" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="H925" s="38">
-        <v>3480</v>
+        <v>3060</v>
       </c>
       <c r="I925" s="7">
-        <v>600</v>
+        <v>263</v>
       </c>
       <c r="J925" s="7" t="s">
         <v>3499</v>
@@ -78335,16 +78347,16 @@
         <v>1612</v>
       </c>
       <c r="F926" s="7" t="s">
-        <v>3539</v>
+        <v>3504</v>
       </c>
       <c r="G926" s="7" t="s">
-        <v>3539</v>
+        <v>3504</v>
       </c>
       <c r="H926" s="38">
-        <v>3661</v>
+        <v>3480</v>
       </c>
       <c r="I926" s="7">
-        <v>52</v>
+        <v>600</v>
       </c>
       <c r="J926" s="7" t="s">
         <v>3499</v>
@@ -78370,16 +78382,16 @@
         <v>1612</v>
       </c>
       <c r="F927" s="7" t="s">
-        <v>3523</v>
+        <v>3539</v>
       </c>
       <c r="G927" s="7" t="s">
-        <v>3523</v>
+        <v>3539</v>
       </c>
       <c r="H927" s="38">
-        <v>3698</v>
+        <v>3661</v>
       </c>
       <c r="I927" s="7">
-        <v>176</v>
+        <v>52</v>
       </c>
       <c r="J927" s="7" t="s">
         <v>3499</v>
@@ -78405,16 +78417,16 @@
         <v>1612</v>
       </c>
       <c r="F928" s="7" t="s">
-        <v>3514</v>
+        <v>3523</v>
       </c>
       <c r="G928" s="7" t="s">
-        <v>3514</v>
+        <v>3523</v>
       </c>
       <c r="H928" s="38">
-        <v>4101</v>
+        <v>3698</v>
       </c>
       <c r="I928" s="7">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="J928" s="7" t="s">
         <v>3499</v>
@@ -78440,16 +78452,16 @@
         <v>1612</v>
       </c>
       <c r="F929" s="7" t="s">
-        <v>3508</v>
+        <v>3514</v>
       </c>
       <c r="G929" s="7" t="s">
-        <v>3508</v>
+        <v>3514</v>
       </c>
       <c r="H929" s="38">
-        <v>4389</v>
+        <v>4101</v>
       </c>
       <c r="I929" s="7">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="J929" s="7" t="s">
         <v>3499</v>
@@ -78475,16 +78487,16 @@
         <v>1612</v>
       </c>
       <c r="F930" s="7" t="s">
-        <v>3552</v>
+        <v>3508</v>
       </c>
       <c r="G930" s="7" t="s">
-        <v>3552</v>
+        <v>3508</v>
       </c>
       <c r="H930" s="38">
-        <v>4581</v>
+        <v>4389</v>
       </c>
       <c r="I930" s="7">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="J930" s="7" t="s">
         <v>3499</v>
@@ -78510,16 +78522,16 @@
         <v>1612</v>
       </c>
       <c r="F931" s="7" t="s">
-        <v>3532</v>
+        <v>3552</v>
       </c>
       <c r="G931" s="7" t="s">
-        <v>3532</v>
+        <v>3552</v>
       </c>
       <c r="H931" s="38">
-        <v>5414</v>
+        <v>4581</v>
       </c>
       <c r="I931" s="7">
-        <v>393</v>
+        <v>183</v>
       </c>
       <c r="J931" s="7" t="s">
         <v>3499</v>
@@ -78545,16 +78557,16 @@
         <v>1612</v>
       </c>
       <c r="F932" s="7" t="s">
-        <v>3513</v>
+        <v>3532</v>
       </c>
       <c r="G932" s="7" t="s">
-        <v>3513</v>
+        <v>3532</v>
       </c>
       <c r="H932" s="38">
-        <v>5699</v>
+        <v>5414</v>
       </c>
       <c r="I932" s="7">
-        <v>751</v>
+        <v>393</v>
       </c>
       <c r="J932" s="7" t="s">
         <v>3499</v>
@@ -78580,16 +78592,16 @@
         <v>1612</v>
       </c>
       <c r="F933" s="7" t="s">
-        <v>3511</v>
+        <v>3513</v>
       </c>
       <c r="G933" s="7" t="s">
-        <v>3511</v>
+        <v>3513</v>
       </c>
       <c r="H933" s="38">
-        <v>5845</v>
+        <v>5699</v>
       </c>
       <c r="I933" s="7">
-        <v>122</v>
+        <v>751</v>
       </c>
       <c r="J933" s="7" t="s">
         <v>3499</v>
@@ -78615,16 +78627,16 @@
         <v>1612</v>
       </c>
       <c r="F934" s="7" t="s">
-        <v>3533</v>
+        <v>3511</v>
       </c>
       <c r="G934" s="7" t="s">
-        <v>3533</v>
+        <v>3511</v>
       </c>
       <c r="H934" s="38">
-        <v>6061</v>
+        <v>5845</v>
       </c>
       <c r="I934" s="7">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="J934" s="7" t="s">
         <v>3499</v>
@@ -78650,16 +78662,16 @@
         <v>1612</v>
       </c>
       <c r="F935" s="7" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="G935" s="7" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="H935" s="38">
-        <v>6116</v>
+        <v>6061</v>
       </c>
       <c r="I935" s="7">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J935" s="7" t="s">
         <v>3499</v>
@@ -78685,16 +78697,16 @@
         <v>1612</v>
       </c>
       <c r="F936" s="7" t="s">
-        <v>3524</v>
+        <v>3537</v>
       </c>
       <c r="G936" s="7" t="s">
-        <v>3524</v>
+        <v>3537</v>
       </c>
       <c r="H936" s="38">
-        <v>6756</v>
+        <v>6116</v>
       </c>
       <c r="I936" s="7">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J936" s="7" t="s">
         <v>3499</v>
@@ -78720,16 +78732,16 @@
         <v>1612</v>
       </c>
       <c r="F937" s="7" t="s">
-        <v>3529</v>
+        <v>3524</v>
       </c>
       <c r="G937" s="7" t="s">
-        <v>3529</v>
+        <v>3524</v>
       </c>
       <c r="H937" s="38">
-        <v>7218</v>
+        <v>6756</v>
       </c>
       <c r="I937" s="7">
-        <v>108</v>
+        <v>165</v>
       </c>
       <c r="J937" s="7" t="s">
         <v>3499</v>
@@ -78755,16 +78767,16 @@
         <v>1612</v>
       </c>
       <c r="F938" s="7" t="s">
-        <v>3542</v>
+        <v>3529</v>
       </c>
       <c r="G938" s="7" t="s">
-        <v>3542</v>
+        <v>3529</v>
       </c>
       <c r="H938" s="38">
-        <v>7405</v>
+        <v>7218</v>
       </c>
       <c r="I938" s="7">
-        <v>246</v>
+        <v>108</v>
       </c>
       <c r="J938" s="7" t="s">
         <v>3499</v>
@@ -78790,16 +78802,16 @@
         <v>1612</v>
       </c>
       <c r="F939" s="7" t="s">
-        <v>3534</v>
+        <v>3542</v>
       </c>
       <c r="G939" s="7" t="s">
-        <v>3534</v>
+        <v>3542</v>
       </c>
       <c r="H939" s="38">
-        <v>7662</v>
+        <v>7405</v>
       </c>
       <c r="I939" s="7">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="J939" s="7" t="s">
         <v>3499</v>
@@ -78825,16 +78837,16 @@
         <v>1612</v>
       </c>
       <c r="F940" s="7" t="s">
-        <v>3538</v>
+        <v>3534</v>
       </c>
       <c r="G940" s="7" t="s">
-        <v>3538</v>
+        <v>3534</v>
       </c>
       <c r="H940" s="38">
-        <v>7743</v>
+        <v>7662</v>
       </c>
       <c r="I940" s="7">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="J940" s="7" t="s">
         <v>3499</v>
@@ -78860,16 +78872,16 @@
         <v>1612</v>
       </c>
       <c r="F941" s="7" t="s">
-        <v>3551</v>
+        <v>3538</v>
       </c>
       <c r="G941" s="7" t="s">
-        <v>3551</v>
+        <v>3538</v>
       </c>
       <c r="H941" s="38">
-        <v>7884</v>
+        <v>7743</v>
       </c>
       <c r="I941" s="7">
-        <v>306</v>
+        <v>153</v>
       </c>
       <c r="J941" s="7" t="s">
         <v>3499</v>
@@ -78895,16 +78907,16 @@
         <v>1612</v>
       </c>
       <c r="F942" s="7" t="s">
-        <v>3536</v>
+        <v>3551</v>
       </c>
       <c r="G942" s="7" t="s">
-        <v>3536</v>
+        <v>3551</v>
       </c>
       <c r="H942" s="38">
-        <v>8209</v>
+        <v>7884</v>
       </c>
       <c r="I942" s="7">
-        <v>152</v>
+        <v>306</v>
       </c>
       <c r="J942" s="7" t="s">
         <v>3499</v>
@@ -78927,19 +78939,19 @@
         <v>744</v>
       </c>
       <c r="E943" s="7" t="s">
-        <v>1600</v>
+        <v>1612</v>
       </c>
       <c r="F943" s="7" t="s">
-        <v>3509</v>
+        <v>3536</v>
       </c>
       <c r="G943" s="7" t="s">
-        <v>3509</v>
+        <v>3536</v>
       </c>
       <c r="H943" s="38">
-        <v>9091</v>
+        <v>8209</v>
       </c>
       <c r="I943" s="7">
-        <v>257</v>
+        <v>152</v>
       </c>
       <c r="J943" s="7" t="s">
         <v>3499</v>
@@ -78965,16 +78977,16 @@
         <v>1600</v>
       </c>
       <c r="F944" s="7" t="s">
-        <v>3506</v>
+        <v>3509</v>
       </c>
       <c r="G944" s="7" t="s">
-        <v>3506</v>
+        <v>3509</v>
       </c>
       <c r="H944" s="38">
-        <v>10111</v>
+        <v>9091</v>
       </c>
       <c r="I944" s="7">
-        <v>845</v>
+        <v>257</v>
       </c>
       <c r="J944" s="7" t="s">
         <v>3499</v>
@@ -78997,19 +79009,19 @@
         <v>744</v>
       </c>
       <c r="E945" s="7" t="s">
-        <v>1612</v>
+        <v>1600</v>
       </c>
       <c r="F945" s="7" t="s">
-        <v>3544</v>
+        <v>3506</v>
       </c>
       <c r="G945" s="7" t="s">
-        <v>3544</v>
+        <v>3506</v>
       </c>
       <c r="H945" s="38">
-        <v>10336</v>
+        <v>10111</v>
       </c>
       <c r="I945" s="7">
-        <v>646</v>
+        <v>845</v>
       </c>
       <c r="J945" s="7" t="s">
         <v>3499</v>
@@ -79032,19 +79044,19 @@
         <v>744</v>
       </c>
       <c r="E946" s="7" t="s">
-        <v>1600</v>
+        <v>1612</v>
       </c>
       <c r="F946" s="7" t="s">
-        <v>3505</v>
+        <v>3544</v>
       </c>
       <c r="G946" s="7" t="s">
-        <v>3505</v>
+        <v>3544</v>
       </c>
       <c r="H946" s="38">
-        <v>10575</v>
+        <v>10336</v>
       </c>
       <c r="I946" s="7">
-        <v>587</v>
+        <v>646</v>
       </c>
       <c r="J946" s="7" t="s">
         <v>3499</v>
@@ -79067,19 +79079,19 @@
         <v>744</v>
       </c>
       <c r="E947" s="7" t="s">
-        <v>1612</v>
+        <v>1600</v>
       </c>
       <c r="F947" s="7" t="s">
-        <v>3545</v>
+        <v>3505</v>
       </c>
       <c r="G947" s="7" t="s">
-        <v>3545</v>
+        <v>3505</v>
       </c>
       <c r="H947" s="38">
-        <v>10897</v>
+        <v>10575</v>
       </c>
       <c r="I947" s="7">
-        <v>7197</v>
+        <v>587</v>
       </c>
       <c r="J947" s="7" t="s">
         <v>3499</v>
@@ -79102,19 +79114,19 @@
         <v>744</v>
       </c>
       <c r="E948" s="7" t="s">
-        <v>1600</v>
+        <v>1612</v>
       </c>
       <c r="F948" s="7" t="s">
-        <v>3516</v>
+        <v>3545</v>
       </c>
       <c r="G948" s="7" t="s">
-        <v>3516</v>
+        <v>3545</v>
       </c>
       <c r="H948" s="38">
-        <v>21533</v>
+        <v>10897</v>
       </c>
       <c r="I948" s="7">
-        <v>237</v>
+        <v>7197</v>
       </c>
       <c r="J948" s="7" t="s">
         <v>3499</v>
@@ -79140,16 +79152,16 @@
         <v>1600</v>
       </c>
       <c r="F949" s="7" t="s">
-        <v>3525</v>
+        <v>3516</v>
       </c>
       <c r="G949" s="7" t="s">
-        <v>3525</v>
+        <v>3516</v>
       </c>
       <c r="H949" s="38">
-        <v>23354</v>
+        <v>21533</v>
       </c>
       <c r="I949" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J949" s="7" t="s">
         <v>3499</v>
@@ -79175,16 +79187,16 @@
         <v>1600</v>
       </c>
       <c r="F950" s="7" t="s">
-        <v>3517</v>
+        <v>3525</v>
       </c>
       <c r="G950" s="7" t="s">
-        <v>3517</v>
+        <v>3525</v>
       </c>
       <c r="H950" s="38">
-        <v>46449</v>
+        <v>23354</v>
       </c>
       <c r="I950" s="7">
-        <v>641</v>
+        <v>234</v>
       </c>
       <c r="J950" s="7" t="s">
         <v>3499</v>
@@ -79210,16 +79222,16 @@
         <v>1600</v>
       </c>
       <c r="F951" s="7" t="s">
-        <v>3512</v>
+        <v>3517</v>
       </c>
       <c r="G951" s="7" t="s">
-        <v>3512</v>
+        <v>3517</v>
       </c>
       <c r="H951" s="38">
-        <v>49755</v>
+        <v>46449</v>
       </c>
       <c r="I951" s="7">
-        <v>477</v>
+        <v>641</v>
       </c>
       <c r="J951" s="7" t="s">
         <v>3499</v>
@@ -79245,16 +79257,16 @@
         <v>1600</v>
       </c>
       <c r="F952" s="7" t="s">
-        <v>3535</v>
+        <v>3512</v>
       </c>
       <c r="G952" s="7" t="s">
-        <v>3535</v>
+        <v>3512</v>
       </c>
       <c r="H952" s="38">
-        <v>53147</v>
+        <v>49755</v>
       </c>
       <c r="I952" s="7">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="J952" s="7" t="s">
         <v>3499</v>
@@ -79280,16 +79292,16 @@
         <v>1600</v>
       </c>
       <c r="F953" s="7" t="s">
-        <v>3518</v>
+        <v>3535</v>
       </c>
       <c r="G953" s="7" t="s">
-        <v>3518</v>
+        <v>3535</v>
       </c>
       <c r="H953" s="38">
-        <v>65641</v>
+        <v>53147</v>
       </c>
       <c r="I953" s="7">
-        <v>819</v>
+        <v>441</v>
       </c>
       <c r="J953" s="7" t="s">
         <v>3499</v>
@@ -79315,16 +79327,16 @@
         <v>1600</v>
       </c>
       <c r="F954" s="7" t="s">
-        <v>3515</v>
+        <v>3518</v>
       </c>
       <c r="G954" s="7" t="s">
-        <v>3515</v>
+        <v>3518</v>
       </c>
       <c r="H954" s="38">
-        <v>72836</v>
+        <v>65641</v>
       </c>
       <c r="I954" s="7">
-        <v>425</v>
+        <v>819</v>
       </c>
       <c r="J954" s="7" t="s">
         <v>3499</v>
@@ -79350,16 +79362,16 @@
         <v>1600</v>
       </c>
       <c r="F955" s="7" t="s">
-        <v>3519</v>
+        <v>3515</v>
       </c>
       <c r="G955" s="7" t="s">
-        <v>3519</v>
+        <v>3515</v>
       </c>
       <c r="H955" s="38">
-        <v>79498</v>
+        <v>72836</v>
       </c>
       <c r="I955" s="7">
-        <v>1818</v>
+        <v>425</v>
       </c>
       <c r="J955" s="7" t="s">
         <v>3499</v>
@@ -79385,16 +79397,16 @@
         <v>1600</v>
       </c>
       <c r="F956" s="7" t="s">
-        <v>3526</v>
+        <v>3519</v>
       </c>
       <c r="G956" s="7" t="s">
-        <v>3526</v>
+        <v>3519</v>
       </c>
       <c r="H956" s="38">
-        <v>82264</v>
+        <v>79498</v>
       </c>
       <c r="I956" s="7">
-        <v>442</v>
+        <v>1818</v>
       </c>
       <c r="J956" s="7" t="s">
         <v>3499</v>
@@ -79420,16 +79432,16 @@
         <v>1600</v>
       </c>
       <c r="F957" s="7" t="s">
-        <v>3521</v>
+        <v>3526</v>
       </c>
       <c r="G957" s="7" t="s">
-        <v>3521</v>
+        <v>3526</v>
       </c>
       <c r="H957" s="38">
-        <v>95501</v>
+        <v>82264</v>
       </c>
       <c r="I957" s="7">
-        <v>1019</v>
+        <v>442</v>
       </c>
       <c r="J957" s="7" t="s">
         <v>3499</v>
@@ -79455,16 +79467,16 @@
         <v>1600</v>
       </c>
       <c r="F958" s="7" t="s">
-        <v>3520</v>
+        <v>3521</v>
       </c>
       <c r="G958" s="7" t="s">
-        <v>3520</v>
+        <v>3521</v>
       </c>
       <c r="H958" s="38">
-        <v>96445</v>
+        <v>95501</v>
       </c>
       <c r="I958" s="7">
-        <v>1032</v>
+        <v>1019</v>
       </c>
       <c r="J958" s="7" t="s">
         <v>3499</v>
@@ -79490,16 +79502,16 @@
         <v>1600</v>
       </c>
       <c r="F959" s="7" t="s">
-        <v>3510</v>
+        <v>3520</v>
       </c>
       <c r="G959" s="7" t="s">
-        <v>3510</v>
+        <v>3520</v>
       </c>
       <c r="H959" s="38">
-        <v>104481</v>
+        <v>96445</v>
       </c>
       <c r="I959" s="7">
-        <v>2451</v>
+        <v>1032</v>
       </c>
       <c r="J959" s="7" t="s">
         <v>3499</v>
@@ -79525,16 +79537,16 @@
         <v>1600</v>
       </c>
       <c r="F960" s="7" t="s">
-        <v>3543</v>
+        <v>3510</v>
       </c>
       <c r="G960" s="7" t="s">
-        <v>3543</v>
+        <v>3510</v>
       </c>
       <c r="H960" s="38">
-        <v>124252</v>
+        <v>104481</v>
       </c>
       <c r="I960" s="7">
-        <v>1423</v>
+        <v>2451</v>
       </c>
       <c r="J960" s="7" t="s">
         <v>3499</v>
@@ -79560,16 +79572,16 @@
         <v>1600</v>
       </c>
       <c r="F961" s="7" t="s">
-        <v>3531</v>
+        <v>3543</v>
       </c>
       <c r="G961" s="7" t="s">
-        <v>3531</v>
+        <v>3543</v>
       </c>
       <c r="H961" s="38">
-        <v>125175</v>
+        <v>124252</v>
       </c>
       <c r="I961" s="7">
-        <v>971</v>
+        <v>1423</v>
       </c>
       <c r="J961" s="7" t="s">
         <v>3499</v>
@@ -79586,7 +79598,7 @@
         <v>3502</v>
       </c>
       <c r="C962" s="7" t="s">
-        <v>3550</v>
+        <v>1699</v>
       </c>
       <c r="D962" s="7" t="s">
         <v>744</v>
@@ -79595,16 +79607,16 @@
         <v>1600</v>
       </c>
       <c r="F962" s="7" t="s">
-        <v>3547</v>
+        <v>3531</v>
       </c>
       <c r="G962" s="7" t="s">
-        <v>3547</v>
+        <v>3531</v>
       </c>
       <c r="H962" s="38">
-        <v>130724</v>
+        <v>125175</v>
       </c>
       <c r="I962" s="7">
-        <v>1129</v>
+        <v>971</v>
       </c>
       <c r="J962" s="7" t="s">
         <v>3499</v>
@@ -79621,7 +79633,7 @@
         <v>3502</v>
       </c>
       <c r="C963" s="7" t="s">
-        <v>1699</v>
+        <v>3550</v>
       </c>
       <c r="D963" s="7" t="s">
         <v>744</v>
@@ -79630,16 +79642,16 @@
         <v>1600</v>
       </c>
       <c r="F963" s="7" t="s">
-        <v>3530</v>
+        <v>3547</v>
       </c>
       <c r="G963" s="7" t="s">
-        <v>3530</v>
+        <v>3547</v>
       </c>
       <c r="H963" s="38">
-        <v>155067</v>
+        <v>130724</v>
       </c>
       <c r="I963" s="7">
-        <v>1453</v>
+        <v>1129</v>
       </c>
       <c r="J963" s="7" t="s">
         <v>3499</v>
@@ -79665,16 +79677,16 @@
         <v>1600</v>
       </c>
       <c r="F964" s="7" t="s">
-        <v>3527</v>
+        <v>3530</v>
       </c>
       <c r="G964" s="7" t="s">
-        <v>3527</v>
+        <v>3530</v>
       </c>
       <c r="H964" s="38">
-        <v>182719</v>
+        <v>155067</v>
       </c>
       <c r="I964" s="7">
-        <v>1494</v>
+        <v>1453</v>
       </c>
       <c r="J964" s="7" t="s">
         <v>3499</v>
@@ -79691,7 +79703,7 @@
         <v>3502</v>
       </c>
       <c r="C965" s="7" t="s">
-        <v>3550</v>
+        <v>1699</v>
       </c>
       <c r="D965" s="7" t="s">
         <v>744</v>
@@ -79700,16 +79712,16 @@
         <v>1600</v>
       </c>
       <c r="F965" s="7" t="s">
-        <v>3548</v>
+        <v>3527</v>
       </c>
       <c r="G965" s="7" t="s">
-        <v>3548</v>
+        <v>3527</v>
       </c>
       <c r="H965" s="38">
-        <v>233038</v>
+        <v>182719</v>
       </c>
       <c r="I965" s="7">
-        <v>5646</v>
+        <v>1494</v>
       </c>
       <c r="J965" s="7" t="s">
         <v>3499</v>
@@ -79726,7 +79738,7 @@
         <v>3502</v>
       </c>
       <c r="C966" s="7" t="s">
-        <v>1699</v>
+        <v>3550</v>
       </c>
       <c r="D966" s="7" t="s">
         <v>744</v>
@@ -79735,16 +79747,16 @@
         <v>1600</v>
       </c>
       <c r="F966" s="7" t="s">
-        <v>3528</v>
+        <v>3548</v>
       </c>
       <c r="G966" s="7" t="s">
-        <v>3528</v>
+        <v>3548</v>
       </c>
       <c r="H966" s="38">
-        <v>240842</v>
+        <v>233038</v>
       </c>
       <c r="I966" s="7">
-        <v>2518</v>
+        <v>5646</v>
       </c>
       <c r="J966" s="7" t="s">
         <v>3499</v>
@@ -79761,7 +79773,7 @@
         <v>3502</v>
       </c>
       <c r="C967" s="7" t="s">
-        <v>3550</v>
+        <v>1699</v>
       </c>
       <c r="D967" s="7" t="s">
         <v>744</v>
@@ -79770,16 +79782,16 @@
         <v>1600</v>
       </c>
       <c r="F967" s="7" t="s">
-        <v>3549</v>
+        <v>3528</v>
       </c>
       <c r="G967" s="7" t="s">
-        <v>3549</v>
+        <v>3528</v>
       </c>
       <c r="H967" s="38">
-        <v>261593</v>
+        <v>240842</v>
       </c>
       <c r="I967" s="7">
-        <v>4916</v>
+        <v>2518</v>
       </c>
       <c r="J967" s="7" t="s">
         <v>3499</v>
@@ -79805,16 +79817,16 @@
         <v>1600</v>
       </c>
       <c r="F968" s="7" t="s">
-        <v>3541</v>
+        <v>3549</v>
       </c>
       <c r="G968" s="7" t="s">
-        <v>3541</v>
+        <v>3549</v>
       </c>
       <c r="H968" s="38">
-        <v>269199</v>
+        <v>261593</v>
       </c>
       <c r="I968" s="7">
-        <v>7275</v>
+        <v>4916</v>
       </c>
       <c r="J968" s="7" t="s">
         <v>3499</v>
@@ -79825,48 +79837,48 @@
     </row>
     <row r="969" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A969" s="7" t="s">
-        <v>6</v>
+        <v>736</v>
       </c>
       <c r="B969" s="7" t="s">
-        <v>3496</v>
+        <v>3502</v>
       </c>
       <c r="C969" s="7" t="s">
-        <v>1566</v>
+        <v>3550</v>
       </c>
       <c r="D969" s="7" t="s">
-        <v>805</v>
+        <v>744</v>
       </c>
       <c r="E969" s="7" t="s">
-        <v>1567</v>
+        <v>1600</v>
       </c>
       <c r="F969" s="7" t="s">
-        <v>676</v>
+        <v>3541</v>
       </c>
       <c r="G969" s="7" t="s">
-        <v>3497</v>
+        <v>3541</v>
       </c>
       <c r="H969" s="38">
-        <v>8890</v>
+        <v>269199</v>
       </c>
       <c r="I969" s="7">
-        <v>90</v>
+        <v>7275</v>
       </c>
       <c r="J969" s="7" t="s">
-        <v>1753</v>
+        <v>3499</v>
       </c>
       <c r="K969" s="7" t="s">
-        <v>3313</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="970" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A970" s="7" t="s">
-        <v>1341</v>
+        <v>6</v>
       </c>
       <c r="B970" s="7" t="s">
-        <v>3136</v>
+        <v>3496</v>
       </c>
       <c r="C970" s="7" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
       <c r="D970" s="7" t="s">
         <v>805</v>
@@ -79878,19 +79890,19 @@
         <v>676</v>
       </c>
       <c r="G970" s="7" t="s">
-        <v>3138</v>
-      </c>
-      <c r="H970" s="7">
-        <v>14570</v>
+        <v>3497</v>
+      </c>
+      <c r="H970" s="38">
+        <v>8890</v>
       </c>
       <c r="I970" s="7">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="J970" s="7" t="s">
-        <v>1343</v>
+        <v>1753</v>
       </c>
       <c r="K970" s="7" t="s">
-        <v>1313</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="971" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -79898,10 +79910,10 @@
         <v>1341</v>
       </c>
       <c r="B971" s="7" t="s">
-        <v>3139</v>
+        <v>3136</v>
       </c>
       <c r="C971" s="7" t="s">
-        <v>3140</v>
+        <v>1570</v>
       </c>
       <c r="D971" s="7" t="s">
         <v>805</v>
@@ -79913,10 +79925,10 @@
         <v>676</v>
       </c>
       <c r="G971" s="7" t="s">
-        <v>3141</v>
+        <v>3138</v>
       </c>
       <c r="H971" s="7">
-        <v>14600</v>
+        <v>14570</v>
       </c>
       <c r="I971" s="7">
         <v>70</v>
@@ -79933,10 +79945,10 @@
         <v>1341</v>
       </c>
       <c r="B972" s="7" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C972" s="7" t="s">
-        <v>1570</v>
+        <v>3140</v>
       </c>
       <c r="D972" s="7" t="s">
         <v>805</v>
@@ -79948,10 +79960,10 @@
         <v>676</v>
       </c>
       <c r="G972" s="7" t="s">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="H972" s="7">
-        <v>14710</v>
+        <v>14600</v>
       </c>
       <c r="I972" s="7">
         <v>70</v>
@@ -79968,10 +79980,10 @@
         <v>1341</v>
       </c>
       <c r="B973" s="7" t="s">
-        <v>3136</v>
+        <v>3142</v>
       </c>
       <c r="C973" s="7" t="s">
-        <v>2733</v>
+        <v>1570</v>
       </c>
       <c r="D973" s="7" t="s">
         <v>805</v>
@@ -79983,19 +79995,19 @@
         <v>676</v>
       </c>
       <c r="G973" s="7" t="s">
-        <v>3137</v>
+        <v>3143</v>
       </c>
       <c r="H973" s="7">
-        <v>14430</v>
+        <v>14710</v>
       </c>
       <c r="I973" s="7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J973" s="7" t="s">
         <v>1343</v>
       </c>
       <c r="K973" s="7" t="s">
-        <v>1591</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="974" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -80003,10 +80015,10 @@
         <v>1341</v>
       </c>
       <c r="B974" s="7" t="s">
-        <v>3132</v>
+        <v>3136</v>
       </c>
       <c r="C974" s="7" t="s">
-        <v>3133</v>
+        <v>2733</v>
       </c>
       <c r="D974" s="7" t="s">
         <v>805</v>
@@ -80015,57 +80027,57 @@
         <v>1567</v>
       </c>
       <c r="F974" s="7" t="s">
-        <v>3134</v>
+        <v>676</v>
       </c>
       <c r="G974" s="7" t="s">
-        <v>3135</v>
+        <v>3137</v>
       </c>
       <c r="H974" s="7">
-        <v>13930</v>
+        <v>14430</v>
       </c>
       <c r="I974" s="7">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J974" s="7" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="K974" s="7" t="s">
-        <v>1319</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="975" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A975" s="7" t="s">
-        <v>704</v>
+        <v>1341</v>
       </c>
       <c r="B975" s="7" t="s">
-        <v>3144</v>
+        <v>3132</v>
       </c>
       <c r="C975" s="7" t="s">
-        <v>1566</v>
+        <v>3133</v>
       </c>
       <c r="D975" s="7" t="s">
-        <v>1678</v>
+        <v>805</v>
       </c>
       <c r="E975" s="7" t="s">
         <v>1567</v>
       </c>
       <c r="F975" s="7" t="s">
-        <v>676</v>
+        <v>3134</v>
       </c>
       <c r="G975" s="7" t="s">
-        <v>3145</v>
+        <v>3135</v>
       </c>
       <c r="H975" s="7">
-        <v>21650</v>
+        <v>13930</v>
       </c>
       <c r="I975" s="7">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="J975" s="7" t="s">
-        <v>3146</v>
+        <v>1342</v>
       </c>
       <c r="K975" s="7" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="976" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -80073,31 +80085,31 @@
         <v>704</v>
       </c>
       <c r="B976" s="7" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="C976" s="7" t="s">
         <v>1566</v>
       </c>
       <c r="D976" s="7" t="s">
-        <v>805</v>
+        <v>1678</v>
       </c>
       <c r="E976" s="7" t="s">
         <v>1567</v>
       </c>
       <c r="F976" s="7" t="s">
-        <v>3148</v>
+        <v>676</v>
       </c>
       <c r="G976" s="7" t="s">
-        <v>3149</v>
+        <v>3145</v>
       </c>
       <c r="H976" s="7">
-        <v>22120</v>
+        <v>21650</v>
       </c>
       <c r="I976" s="7">
-        <v>150</v>
+        <v>800</v>
       </c>
       <c r="J976" s="7" t="s">
-        <v>3045</v>
+        <v>3146</v>
       </c>
       <c r="K976" s="7" t="s">
         <v>1323</v>
@@ -80105,37 +80117,37 @@
     </row>
     <row r="977" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A977" s="7" t="s">
-        <v>3258</v>
+        <v>704</v>
       </c>
       <c r="B977" s="7" t="s">
-        <v>3182</v>
+        <v>3147</v>
       </c>
       <c r="C977" s="7" t="s">
-        <v>2426</v>
+        <v>1566</v>
       </c>
       <c r="D977" s="7" t="s">
-        <v>744</v>
+        <v>805</v>
       </c>
       <c r="E977" s="7" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F977" s="7" t="s">
-        <v>676</v>
+        <v>3148</v>
       </c>
       <c r="G977" s="7" t="s">
-        <v>3183</v>
-      </c>
-      <c r="H977" s="38">
-        <v>29650</v>
+        <v>3149</v>
+      </c>
+      <c r="H977" s="7">
+        <v>22120</v>
       </c>
       <c r="I977" s="7">
-        <v>550</v>
+        <v>150</v>
       </c>
       <c r="J977" s="7" t="s">
-        <v>855</v>
+        <v>3045</v>
       </c>
       <c r="K977" s="7" t="s">
-        <v>1228</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="978" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -80161,10 +80173,10 @@
         <v>3183</v>
       </c>
       <c r="H978" s="38">
-        <v>30800</v>
-      </c>
-      <c r="I978" s="38">
-        <v>5600</v>
+        <v>29650</v>
+      </c>
+      <c r="I978" s="7">
+        <v>550</v>
       </c>
       <c r="J978" s="7" t="s">
         <v>855</v>
@@ -80178,31 +80190,31 @@
         <v>3258</v>
       </c>
       <c r="B979" s="7" t="s">
-        <v>3180</v>
+        <v>3182</v>
       </c>
       <c r="C979" s="7" t="s">
-        <v>3181</v>
+        <v>2426</v>
       </c>
       <c r="D979" s="7" t="s">
-        <v>805</v>
+        <v>744</v>
       </c>
       <c r="E979" s="7" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F979" s="7" t="s">
         <v>676</v>
       </c>
       <c r="G979" s="7" t="s">
-        <v>3478</v>
+        <v>3183</v>
       </c>
       <c r="H979" s="38">
-        <v>32990</v>
-      </c>
-      <c r="I979" s="7">
-        <v>450</v>
+        <v>30800</v>
+      </c>
+      <c r="I979" s="38">
+        <v>5600</v>
       </c>
       <c r="J979" s="7" t="s">
-        <v>2801</v>
+        <v>855</v>
       </c>
       <c r="K979" s="7" t="s">
         <v>1228</v>
@@ -80213,31 +80225,31 @@
         <v>3258</v>
       </c>
       <c r="B980" s="7" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="C980" s="7" t="s">
-        <v>2426</v>
+        <v>3181</v>
       </c>
       <c r="D980" s="7" t="s">
-        <v>744</v>
+        <v>805</v>
       </c>
       <c r="E980" s="7" t="s">
-        <v>1600</v>
+        <v>1567</v>
       </c>
       <c r="F980" s="7" t="s">
         <v>676</v>
       </c>
       <c r="G980" s="7" t="s">
-        <v>3184</v>
+        <v>3478</v>
       </c>
       <c r="H980" s="38">
-        <v>35540</v>
+        <v>32990</v>
       </c>
       <c r="I980" s="7">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="J980" s="7" t="s">
-        <v>855</v>
+        <v>2801</v>
       </c>
       <c r="K980" s="7" t="s">
         <v>1228</v>
@@ -80266,10 +80278,10 @@
         <v>3184</v>
       </c>
       <c r="H981" s="38">
-        <v>36200</v>
-      </c>
-      <c r="I981" s="38">
-        <v>1500</v>
+        <v>35540</v>
+      </c>
+      <c r="I981" s="7">
+        <v>390</v>
       </c>
       <c r="J981" s="7" t="s">
         <v>855</v>
@@ -80283,34 +80295,34 @@
         <v>3258</v>
       </c>
       <c r="B982" s="7" t="s">
-        <v>3155</v>
+        <v>3182</v>
       </c>
       <c r="C982" s="7" t="s">
-        <v>1566</v>
+        <v>2426</v>
       </c>
       <c r="D982" s="7" t="s">
-        <v>805</v>
+        <v>744</v>
       </c>
       <c r="E982" s="7" t="s">
-        <v>1567</v>
+        <v>1600</v>
       </c>
       <c r="F982" s="7" t="s">
         <v>676</v>
       </c>
       <c r="G982" s="7" t="s">
-        <v>3156</v>
+        <v>3184</v>
       </c>
       <c r="H982" s="38">
-        <v>12180</v>
-      </c>
-      <c r="I982" s="7">
-        <v>110</v>
+        <v>36200</v>
+      </c>
+      <c r="I982" s="38">
+        <v>1500</v>
       </c>
       <c r="J982" s="7" t="s">
-        <v>3152</v>
+        <v>855</v>
       </c>
       <c r="K982" s="7" t="s">
-        <v>1318</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="983" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -80318,7 +80330,7 @@
         <v>3258</v>
       </c>
       <c r="B983" s="7" t="s">
-        <v>3157</v>
+        <v>3155</v>
       </c>
       <c r="C983" s="7" t="s">
         <v>1566</v>
@@ -80333,16 +80345,16 @@
         <v>676</v>
       </c>
       <c r="G983" s="7" t="s">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="H983" s="38">
-        <v>12330</v>
+        <v>12180</v>
       </c>
       <c r="I983" s="7">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="J983" s="7" t="s">
-        <v>3159</v>
+        <v>3152</v>
       </c>
       <c r="K983" s="7" t="s">
         <v>1318</v>
@@ -80353,7 +80365,7 @@
         <v>3258</v>
       </c>
       <c r="B984" s="7" t="s">
-        <v>3160</v>
+        <v>3157</v>
       </c>
       <c r="C984" s="7" t="s">
         <v>1566</v>
@@ -80364,20 +80376,20 @@
       <c r="E984" s="7" t="s">
         <v>1567</v>
       </c>
-      <c r="F984" s="42" t="s">
+      <c r="F984" s="7" t="s">
         <v>676</v>
       </c>
       <c r="G984" s="7" t="s">
-        <v>3161</v>
+        <v>3158</v>
       </c>
       <c r="H984" s="38">
-        <v>12490</v>
+        <v>12330</v>
       </c>
       <c r="I984" s="7">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="J984" s="7" t="s">
-        <v>3152</v>
+        <v>3159</v>
       </c>
       <c r="K984" s="7" t="s">
         <v>1318</v>
@@ -80388,31 +80400,31 @@
         <v>3258</v>
       </c>
       <c r="B985" s="7" t="s">
-        <v>3162</v>
+        <v>3160</v>
       </c>
       <c r="C985" s="7" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
       <c r="D985" s="7" t="s">
-        <v>1678</v>
+        <v>805</v>
       </c>
       <c r="E985" s="7" t="s">
         <v>1567</v>
       </c>
-      <c r="F985" s="7" t="s">
+      <c r="F985" s="42" t="s">
         <v>676</v>
       </c>
       <c r="G985" s="7" t="s">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="H985" s="38">
-        <v>12890</v>
+        <v>12490</v>
       </c>
       <c r="I985" s="7">
-        <v>530</v>
+        <v>110</v>
       </c>
       <c r="J985" s="7" t="s">
-        <v>3164</v>
+        <v>3152</v>
       </c>
       <c r="K985" s="7" t="s">
         <v>1318</v>
@@ -80423,34 +80435,34 @@
         <v>3258</v>
       </c>
       <c r="B986" s="7" t="s">
-        <v>3178</v>
+        <v>3162</v>
       </c>
       <c r="C986" s="7" t="s">
-        <v>1629</v>
+        <v>1570</v>
       </c>
       <c r="D986" s="7" t="s">
-        <v>805</v>
+        <v>1678</v>
       </c>
       <c r="E986" s="7" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F986" s="7" t="s">
         <v>676</v>
       </c>
       <c r="G986" s="7" t="s">
-        <v>3179</v>
+        <v>3163</v>
       </c>
       <c r="H986" s="38">
-        <v>15160</v>
+        <v>12890</v>
       </c>
       <c r="I986" s="7">
-        <v>230</v>
+        <v>530</v>
       </c>
       <c r="J986" s="7" t="s">
-        <v>3152</v>
+        <v>3164</v>
       </c>
       <c r="K986" s="7" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="987" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -80458,34 +80470,34 @@
         <v>3258</v>
       </c>
       <c r="B987" s="7" t="s">
-        <v>3165</v>
+        <v>3178</v>
       </c>
       <c r="C987" s="7" t="s">
-        <v>1566</v>
+        <v>1629</v>
       </c>
       <c r="D987" s="7" t="s">
         <v>805</v>
       </c>
       <c r="E987" s="7" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F987" s="7" t="s">
         <v>676</v>
       </c>
       <c r="G987" s="7" t="s">
-        <v>3166</v>
+        <v>3179</v>
       </c>
       <c r="H987" s="38">
-        <v>13210</v>
+        <v>15160</v>
       </c>
       <c r="I987" s="7">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="J987" s="7" t="s">
         <v>3152</v>
       </c>
       <c r="K987" s="7" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="988" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -80493,7 +80505,7 @@
         <v>3258</v>
       </c>
       <c r="B988" s="7" t="s">
-        <v>3167</v>
+        <v>3165</v>
       </c>
       <c r="C988" s="7" t="s">
         <v>1566</v>
@@ -80508,13 +80520,13 @@
         <v>676</v>
       </c>
       <c r="G988" s="7" t="s">
-        <v>3168</v>
+        <v>3166</v>
       </c>
       <c r="H988" s="38">
-        <v>13320</v>
+        <v>13210</v>
       </c>
       <c r="I988" s="7">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="J988" s="7" t="s">
         <v>3152</v>
@@ -80528,10 +80540,10 @@
         <v>3258</v>
       </c>
       <c r="B989" s="7" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
       <c r="C989" s="7" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
       <c r="D989" s="7" t="s">
         <v>805</v>
@@ -80543,16 +80555,16 @@
         <v>676</v>
       </c>
       <c r="G989" s="7" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="H989" s="38">
-        <v>13520</v>
+        <v>13320</v>
       </c>
       <c r="I989" s="7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J989" s="7" t="s">
-        <v>1635</v>
+        <v>3152</v>
       </c>
       <c r="K989" s="7" t="s">
         <v>1319</v>
@@ -80563,10 +80575,10 @@
         <v>3258</v>
       </c>
       <c r="B990" s="7" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
       <c r="C990" s="7" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="D990" s="7" t="s">
         <v>805</v>
@@ -80578,16 +80590,16 @@
         <v>676</v>
       </c>
       <c r="G990" s="7" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="H990" s="38">
-        <v>13710</v>
+        <v>13520</v>
       </c>
       <c r="I990" s="7">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="J990" s="7" t="s">
-        <v>3152</v>
+        <v>1635</v>
       </c>
       <c r="K990" s="7" t="s">
         <v>1319</v>
@@ -80598,28 +80610,28 @@
         <v>3258</v>
       </c>
       <c r="B991" s="7" t="s">
-        <v>3173</v>
+        <v>3171</v>
       </c>
       <c r="C991" s="7" t="s">
-        <v>1629</v>
+        <v>1566</v>
       </c>
       <c r="D991" s="7" t="s">
         <v>805</v>
       </c>
       <c r="E991" s="7" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="F991" s="7" t="s">
         <v>676</v>
       </c>
       <c r="G991" s="7" t="s">
-        <v>3174</v>
+        <v>3172</v>
       </c>
       <c r="H991" s="38">
-        <v>14230</v>
+        <v>13710</v>
       </c>
       <c r="I991" s="7">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="J991" s="7" t="s">
         <v>3152</v>
@@ -80633,31 +80645,31 @@
         <v>3258</v>
       </c>
       <c r="B992" s="7" t="s">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="C992" s="7" t="s">
-        <v>1566</v>
+        <v>1629</v>
       </c>
       <c r="D992" s="7" t="s">
-        <v>1678</v>
+        <v>805</v>
       </c>
       <c r="E992" s="7" t="s">
-        <v>1567</v>
+        <v>1612</v>
       </c>
       <c r="F992" s="7" t="s">
         <v>676</v>
       </c>
       <c r="G992" s="7" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="H992" s="38">
-        <v>14350</v>
+        <v>14230</v>
       </c>
       <c r="I992" s="7">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="J992" s="7" t="s">
-        <v>3177</v>
+        <v>3152</v>
       </c>
       <c r="K992" s="7" t="s">
         <v>1319</v>
@@ -80668,13 +80680,13 @@
         <v>3258</v>
       </c>
       <c r="B993" s="7" t="s">
-        <v>3150</v>
+        <v>3175</v>
       </c>
       <c r="C993" s="7" t="s">
         <v>1566</v>
       </c>
       <c r="D993" s="7" t="s">
-        <v>805</v>
+        <v>1678</v>
       </c>
       <c r="E993" s="7" t="s">
         <v>1567</v>
@@ -80683,19 +80695,19 @@
         <v>676</v>
       </c>
       <c r="G993" s="7" t="s">
-        <v>3151</v>
+        <v>3176</v>
       </c>
       <c r="H993" s="38">
-        <v>11140</v>
+        <v>14350</v>
       </c>
       <c r="I993" s="7">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="J993" s="7" t="s">
-        <v>3152</v>
+        <v>3177</v>
       </c>
       <c r="K993" s="7" t="s">
-        <v>1439</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="994" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -80703,7 +80715,7 @@
         <v>3258</v>
       </c>
       <c r="B994" s="7" t="s">
-        <v>3153</v>
+        <v>3150</v>
       </c>
       <c r="C994" s="7" t="s">
         <v>1566</v>
@@ -80718,13 +80730,13 @@
         <v>676</v>
       </c>
       <c r="G994" s="7" t="s">
-        <v>3154</v>
+        <v>3151</v>
       </c>
       <c r="H994" s="38">
-        <v>11610</v>
+        <v>11140</v>
       </c>
       <c r="I994" s="7">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J994" s="7" t="s">
         <v>3152</v>
@@ -80738,7 +80750,7 @@
         <v>3258</v>
       </c>
       <c r="B995" s="7" t="s">
-        <v>3484</v>
+        <v>3153</v>
       </c>
       <c r="C995" s="7" t="s">
         <v>1566</v>
@@ -80750,22 +80762,22 @@
         <v>1567</v>
       </c>
       <c r="F995" s="7" t="s">
-        <v>3485</v>
+        <v>676</v>
       </c>
       <c r="G995" s="7" t="s">
-        <v>3486</v>
+        <v>3154</v>
       </c>
       <c r="H995" s="38">
-        <v>7910</v>
-      </c>
-      <c r="I995" s="38">
-        <v>80</v>
+        <v>11610</v>
+      </c>
+      <c r="I995" s="7">
+        <v>50</v>
       </c>
       <c r="J995" s="7" t="s">
         <v>3152</v>
       </c>
       <c r="K995" s="7" t="s">
-        <v>3313</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="996" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -80773,10 +80785,10 @@
         <v>3258</v>
       </c>
       <c r="B996" s="7" t="s">
-        <v>3385</v>
+        <v>3484</v>
       </c>
       <c r="C996" s="7" t="s">
-        <v>3386</v>
+        <v>1566</v>
       </c>
       <c r="D996" s="7" t="s">
         <v>805</v>
@@ -80785,19 +80797,19 @@
         <v>1567</v>
       </c>
       <c r="F996" s="7" t="s">
-        <v>3387</v>
+        <v>3485</v>
       </c>
       <c r="G996" s="7" t="s">
-        <v>3388</v>
+        <v>3486</v>
       </c>
       <c r="H996" s="38">
-        <v>8470</v>
+        <v>7910</v>
       </c>
       <c r="I996" s="38">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J996" s="7" t="s">
-        <v>2801</v>
+        <v>3152</v>
       </c>
       <c r="K996" s="7" t="s">
         <v>3313</v>
@@ -80808,10 +80820,10 @@
         <v>3258</v>
       </c>
       <c r="B997" s="7" t="s">
-        <v>3479</v>
+        <v>3385</v>
       </c>
       <c r="C997" s="7" t="s">
-        <v>1566</v>
+        <v>3386</v>
       </c>
       <c r="D997" s="7" t="s">
         <v>805</v>
@@ -80820,19 +80832,19 @@
         <v>1567</v>
       </c>
       <c r="F997" s="7" t="s">
-        <v>3480</v>
+        <v>3387</v>
       </c>
       <c r="G997" s="7" t="s">
-        <v>3481</v>
+        <v>3388</v>
       </c>
       <c r="H997" s="38">
-        <v>9940</v>
+        <v>8470</v>
       </c>
       <c r="I997" s="38">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="J997" s="7" t="s">
-        <v>3152</v>
+        <v>2801</v>
       </c>
       <c r="K997" s="7" t="s">
         <v>3313</v>
@@ -80843,7 +80855,7 @@
         <v>3258</v>
       </c>
       <c r="B998" s="7" t="s">
-        <v>3487</v>
+        <v>3479</v>
       </c>
       <c r="C998" s="7" t="s">
         <v>1566</v>
@@ -80855,22 +80867,22 @@
         <v>1567</v>
       </c>
       <c r="F998" s="7" t="s">
-        <v>3489</v>
+        <v>3480</v>
       </c>
       <c r="G998" s="7" t="s">
-        <v>3491</v>
+        <v>3481</v>
       </c>
       <c r="H998" s="38">
-        <v>9650</v>
-      </c>
-      <c r="I998" s="7">
-        <v>100</v>
+        <v>9940</v>
+      </c>
+      <c r="I998" s="38">
+        <v>90</v>
       </c>
       <c r="J998" s="7" t="s">
         <v>3152</v>
       </c>
       <c r="K998" s="7" t="s">
-        <v>3476</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="999" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -80878,7 +80890,7 @@
         <v>3258</v>
       </c>
       <c r="B999" s="7" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="C999" s="7" t="s">
         <v>1566</v>
@@ -80890,33 +80902,33 @@
         <v>1567</v>
       </c>
       <c r="F999" s="7" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="G999" s="7" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="H999" s="38">
-        <v>7440</v>
+        <v>9650</v>
       </c>
       <c r="I999" s="7">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J999" s="7" t="s">
         <v>3152</v>
       </c>
       <c r="K999" s="7" t="s">
-        <v>3493</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="1000" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1000" s="7" t="s">
-        <v>26</v>
+        <v>3258</v>
       </c>
       <c r="B1000" s="7" t="s">
-        <v>1344</v>
+        <v>3488</v>
       </c>
       <c r="C1000" s="7" t="s">
-        <v>3214</v>
+        <v>1566</v>
       </c>
       <c r="D1000" s="7" t="s">
         <v>805</v>
@@ -80925,22 +80937,22 @@
         <v>1567</v>
       </c>
       <c r="F1000" s="7" t="s">
-        <v>676</v>
+        <v>3490</v>
       </c>
       <c r="G1000" s="7" t="s">
-        <v>3215</v>
+        <v>3492</v>
       </c>
       <c r="H1000" s="38">
-        <v>30500</v>
+        <v>7440</v>
       </c>
       <c r="I1000" s="7">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="J1000" s="7" t="s">
-        <v>845</v>
+        <v>3152</v>
       </c>
       <c r="K1000" s="7" t="s">
-        <v>1228</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="1001" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -80951,7 +80963,7 @@
         <v>1344</v>
       </c>
       <c r="C1001" s="7" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="D1001" s="7" t="s">
         <v>805</v>
@@ -80963,13 +80975,13 @@
         <v>676</v>
       </c>
       <c r="G1001" s="7" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="H1001" s="38">
-        <v>33230</v>
+        <v>30500</v>
       </c>
       <c r="I1001" s="7">
-        <v>280</v>
+        <v>190</v>
       </c>
       <c r="J1001" s="7" t="s">
         <v>845</v>
@@ -80983,10 +80995,10 @@
         <v>26</v>
       </c>
       <c r="B1002" s="7" t="s">
-        <v>3185</v>
+        <v>1344</v>
       </c>
       <c r="C1002" s="7" t="s">
-        <v>1707</v>
+        <v>3216</v>
       </c>
       <c r="D1002" s="7" t="s">
         <v>805</v>
@@ -80994,23 +81006,23 @@
       <c r="E1002" s="7" t="s">
         <v>1567</v>
       </c>
-      <c r="F1002" s="7">
-        <v>8</v>
+      <c r="F1002" s="7" t="s">
+        <v>676</v>
       </c>
       <c r="G1002" s="7" t="s">
-        <v>3186</v>
+        <v>3217</v>
       </c>
       <c r="H1002" s="38">
-        <v>12960</v>
+        <v>33230</v>
       </c>
       <c r="I1002" s="7">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="J1002" s="7" t="s">
         <v>845</v>
       </c>
       <c r="K1002" s="7" t="s">
-        <v>1318</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="1003" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -81018,10 +81030,10 @@
         <v>26</v>
       </c>
       <c r="B1003" s="7" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="C1003" s="7" t="s">
-        <v>1570</v>
+        <v>1707</v>
       </c>
       <c r="D1003" s="7" t="s">
         <v>805</v>
@@ -81029,23 +81041,23 @@
       <c r="E1003" s="7" t="s">
         <v>1567</v>
       </c>
-      <c r="F1003" s="7" t="s">
-        <v>676</v>
+      <c r="F1003" s="7">
+        <v>8</v>
       </c>
       <c r="G1003" s="7" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="H1003" s="38">
-        <v>13340</v>
+        <v>12960</v>
       </c>
       <c r="I1003" s="7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="J1003" s="7" t="s">
         <v>845</v>
       </c>
       <c r="K1003" s="7" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="1004" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -81053,7 +81065,7 @@
         <v>26</v>
       </c>
       <c r="B1004" s="7" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
       <c r="C1004" s="7" t="s">
         <v>1570</v>
@@ -81068,16 +81080,16 @@
         <v>676</v>
       </c>
       <c r="G1004" s="7" t="s">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="H1004" s="38">
-        <v>13360</v>
+        <v>13340</v>
       </c>
       <c r="I1004" s="7">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="J1004" s="7" t="s">
-        <v>3191</v>
+        <v>845</v>
       </c>
       <c r="K1004" s="7" t="s">
         <v>1319</v>
@@ -81088,10 +81100,10 @@
         <v>26</v>
       </c>
       <c r="B1005" s="7" t="s">
-        <v>3187</v>
+        <v>3189</v>
       </c>
       <c r="C1005" s="7" t="s">
-        <v>3192</v>
+        <v>1570</v>
       </c>
       <c r="D1005" s="7" t="s">
         <v>805</v>
@@ -81103,10 +81115,10 @@
         <v>676</v>
       </c>
       <c r="G1005" s="7" t="s">
-        <v>3193</v>
+        <v>3190</v>
       </c>
       <c r="H1005" s="38">
-        <v>13460</v>
+        <v>13360</v>
       </c>
       <c r="I1005" s="7">
         <v>70</v>
@@ -81126,7 +81138,7 @@
         <v>3187</v>
       </c>
       <c r="C1006" s="7" t="s">
-        <v>1570</v>
+        <v>3192</v>
       </c>
       <c r="D1006" s="7" t="s">
         <v>805</v>
@@ -81138,16 +81150,16 @@
         <v>676</v>
       </c>
       <c r="G1006" s="7" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="H1006" s="38">
-        <v>13480</v>
+        <v>13460</v>
       </c>
       <c r="I1006" s="7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J1006" s="7" t="s">
-        <v>845</v>
+        <v>3191</v>
       </c>
       <c r="K1006" s="7" t="s">
         <v>1319</v>
@@ -81158,7 +81170,7 @@
         <v>26</v>
       </c>
       <c r="B1007" s="7" t="s">
-        <v>3185</v>
+        <v>3187</v>
       </c>
       <c r="C1007" s="7" t="s">
         <v>1570</v>
@@ -81173,16 +81185,16 @@
         <v>676</v>
       </c>
       <c r="G1007" s="7" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="H1007" s="38">
-        <v>13490</v>
+        <v>13480</v>
       </c>
       <c r="I1007" s="7">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J1007" s="7" t="s">
-        <v>3191</v>
+        <v>845</v>
       </c>
       <c r="K1007" s="7" t="s">
         <v>1319</v>
@@ -81193,10 +81205,10 @@
         <v>26</v>
       </c>
       <c r="B1008" s="7" t="s">
-        <v>3196</v>
+        <v>3185</v>
       </c>
       <c r="C1008" s="7" t="s">
-        <v>1707</v>
+        <v>1570</v>
       </c>
       <c r="D1008" s="7" t="s">
         <v>805</v>
@@ -81208,16 +81220,16 @@
         <v>676</v>
       </c>
       <c r="G1008" s="7" t="s">
-        <v>3197</v>
+        <v>3195</v>
       </c>
       <c r="H1008" s="38">
-        <v>13600</v>
+        <v>13490</v>
       </c>
       <c r="I1008" s="7">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="J1008" s="7" t="s">
-        <v>845</v>
+        <v>3191</v>
       </c>
       <c r="K1008" s="7" t="s">
         <v>1319</v>
@@ -81228,10 +81240,10 @@
         <v>26</v>
       </c>
       <c r="B1009" s="7" t="s">
-        <v>3187</v>
+        <v>3196</v>
       </c>
       <c r="C1009" s="7" t="s">
-        <v>3192</v>
+        <v>1707</v>
       </c>
       <c r="D1009" s="7" t="s">
         <v>805</v>
@@ -81243,16 +81255,16 @@
         <v>676</v>
       </c>
       <c r="G1009" s="7" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="H1009" s="38">
-        <v>13610</v>
+        <v>13600</v>
       </c>
       <c r="I1009" s="7">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="J1009" s="7" t="s">
-        <v>3191</v>
+        <v>845</v>
       </c>
       <c r="K1009" s="7" t="s">
         <v>1319</v>
@@ -81278,13 +81290,13 @@
         <v>676</v>
       </c>
       <c r="G1010" s="7" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="H1010" s="38">
-        <v>13640</v>
+        <v>13610</v>
       </c>
       <c r="I1010" s="7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J1010" s="7" t="s">
         <v>3191</v>
@@ -81313,13 +81325,13 @@
         <v>676</v>
       </c>
       <c r="G1011" s="7" t="s">
-        <v>3202</v>
+        <v>3199</v>
       </c>
       <c r="H1011" s="38">
-        <v>13750</v>
+        <v>13640</v>
       </c>
       <c r="I1011" s="7">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J1011" s="7" t="s">
         <v>3191</v>
@@ -81333,10 +81345,10 @@
         <v>26</v>
       </c>
       <c r="B1012" s="7" t="s">
-        <v>1344</v>
+        <v>3187</v>
       </c>
       <c r="C1012" s="7" t="s">
-        <v>1707</v>
+        <v>3192</v>
       </c>
       <c r="D1012" s="7" t="s">
         <v>805</v>
@@ -81348,16 +81360,16 @@
         <v>676</v>
       </c>
       <c r="G1012" s="7" t="s">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="H1012" s="38">
         <v>13750</v>
       </c>
       <c r="I1012" s="7">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="J1012" s="7" t="s">
-        <v>845</v>
+        <v>3191</v>
       </c>
       <c r="K1012" s="7" t="s">
         <v>1319</v>
@@ -81383,13 +81395,13 @@
         <v>676</v>
       </c>
       <c r="G1013" s="7" t="s">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="H1013" s="38">
         <v>13750</v>
       </c>
       <c r="I1013" s="7">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J1013" s="7" t="s">
         <v>845</v>
@@ -81403,7 +81415,7 @@
         <v>26</v>
       </c>
       <c r="B1014" s="7" t="s">
-        <v>3189</v>
+        <v>1344</v>
       </c>
       <c r="C1014" s="7" t="s">
         <v>1707</v>
@@ -81418,13 +81430,13 @@
         <v>676</v>
       </c>
       <c r="G1014" s="7" t="s">
-        <v>3203</v>
+        <v>3200</v>
       </c>
       <c r="H1014" s="38">
-        <v>13780</v>
+        <v>13750</v>
       </c>
       <c r="I1014" s="7">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="J1014" s="7" t="s">
         <v>845</v>
@@ -81438,10 +81450,10 @@
         <v>26</v>
       </c>
       <c r="B1015" s="7" t="s">
-        <v>3196</v>
+        <v>3189</v>
       </c>
       <c r="C1015" s="7" t="s">
-        <v>3204</v>
+        <v>1707</v>
       </c>
       <c r="D1015" s="7" t="s">
         <v>805</v>
@@ -81453,13 +81465,13 @@
         <v>676</v>
       </c>
       <c r="G1015" s="7" t="s">
-        <v>3205</v>
+        <v>3203</v>
       </c>
       <c r="H1015" s="38">
-        <v>13840</v>
+        <v>13780</v>
       </c>
       <c r="I1015" s="7">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="J1015" s="7" t="s">
         <v>845</v>
@@ -81473,10 +81485,10 @@
         <v>26</v>
       </c>
       <c r="B1016" s="7" t="s">
-        <v>3189</v>
+        <v>3196</v>
       </c>
       <c r="C1016" s="7" t="s">
-        <v>3206</v>
+        <v>3204</v>
       </c>
       <c r="D1016" s="7" t="s">
         <v>805</v>
@@ -81488,13 +81500,13 @@
         <v>676</v>
       </c>
       <c r="G1016" s="7" t="s">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="H1016" s="38">
-        <v>13920</v>
+        <v>13840</v>
       </c>
       <c r="I1016" s="7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J1016" s="7" t="s">
         <v>845</v>
@@ -81523,13 +81535,13 @@
         <v>676</v>
       </c>
       <c r="G1017" s="7" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="H1017" s="38">
-        <v>13930</v>
+        <v>13920</v>
       </c>
       <c r="I1017" s="7">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J1017" s="7" t="s">
         <v>845</v>
@@ -81558,13 +81570,13 @@
         <v>676</v>
       </c>
       <c r="G1018" s="7" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="H1018" s="38">
         <v>13930</v>
       </c>
       <c r="I1018" s="7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J1018" s="7" t="s">
         <v>845</v>
@@ -81581,7 +81593,7 @@
         <v>3189</v>
       </c>
       <c r="C1019" s="7" t="s">
-        <v>3210</v>
+        <v>3206</v>
       </c>
       <c r="D1019" s="7" t="s">
         <v>805</v>
@@ -81593,13 +81605,13 @@
         <v>676</v>
       </c>
       <c r="G1019" s="7" t="s">
-        <v>3211</v>
+        <v>3209</v>
       </c>
       <c r="H1019" s="38">
-        <v>14120</v>
+        <v>13930</v>
       </c>
       <c r="I1019" s="7">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J1019" s="7" t="s">
         <v>845</v>
@@ -81613,10 +81625,10 @@
         <v>26</v>
       </c>
       <c r="B1020" s="7" t="s">
-        <v>3212</v>
+        <v>3189</v>
       </c>
       <c r="C1020" s="7" t="s">
-        <v>1570</v>
+        <v>3210</v>
       </c>
       <c r="D1020" s="7" t="s">
         <v>805</v>
@@ -81628,13 +81640,13 @@
         <v>676</v>
       </c>
       <c r="G1020" s="7" t="s">
-        <v>3213</v>
+        <v>3211</v>
       </c>
       <c r="H1020" s="38">
-        <v>14350</v>
+        <v>14120</v>
       </c>
       <c r="I1020" s="7">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="J1020" s="7" t="s">
         <v>845</v>
@@ -81645,13 +81657,13 @@
     </row>
     <row r="1021" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1021" s="7" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B1021" s="7" t="s">
-        <v>3218</v>
+        <v>3212</v>
       </c>
       <c r="C1021" s="7" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="D1021" s="7" t="s">
         <v>805</v>
@@ -81660,33 +81672,33 @@
         <v>1567</v>
       </c>
       <c r="F1021" s="7" t="s">
-        <v>3219</v>
+        <v>676</v>
       </c>
       <c r="G1021" s="7" t="s">
-        <v>3220</v>
-      </c>
-      <c r="H1021" s="7">
-        <v>12750</v>
+        <v>3213</v>
+      </c>
+      <c r="H1021" s="38">
+        <v>14350</v>
       </c>
       <c r="I1021" s="7">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="J1021" s="7" t="s">
-        <v>2621</v>
+        <v>845</v>
       </c>
       <c r="K1021" s="7" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="1022" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1022" s="7" t="s">
-        <v>1345</v>
+        <v>8</v>
       </c>
       <c r="B1022" s="7" t="s">
-        <v>3221</v>
+        <v>3218</v>
       </c>
       <c r="C1022" s="7" t="s">
-        <v>2393</v>
+        <v>1566</v>
       </c>
       <c r="D1022" s="7" t="s">
         <v>805</v>
@@ -81694,23 +81706,23 @@
       <c r="E1022" s="7" t="s">
         <v>1567</v>
       </c>
-      <c r="F1022" s="7">
-        <v>19</v>
+      <c r="F1022" s="7" t="s">
+        <v>3219</v>
       </c>
       <c r="G1022" s="7" t="s">
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="H1022" s="7">
-        <v>26690</v>
+        <v>12750</v>
       </c>
       <c r="I1022" s="7">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="J1022" s="7" t="s">
-        <v>1024</v>
+        <v>2621</v>
       </c>
       <c r="K1022" s="7" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="1023" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -81730,16 +81742,16 @@
         <v>1567</v>
       </c>
       <c r="F1023" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1023" s="7" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="H1023" s="7">
-        <v>27010</v>
+        <v>26690</v>
       </c>
       <c r="I1023" s="7">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="J1023" s="7" t="s">
         <v>1024</v>
@@ -81749,73 +81761,73 @@
       </c>
     </row>
     <row r="1024" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1024" s="33" t="s">
+      <c r="A1024" s="7" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B1024" s="7" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C1024" s="7" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D1024" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="E1024" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F1024" s="7">
+        <v>18</v>
+      </c>
+      <c r="G1024" s="7" t="s">
+        <v>3223</v>
+      </c>
+      <c r="H1024" s="7">
+        <v>27010</v>
+      </c>
+      <c r="I1024" s="7">
+        <v>210</v>
+      </c>
+      <c r="J1024" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K1024" s="7" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1025" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="B1024" s="33" t="s">
+      <c r="B1025" s="33" t="s">
         <v>3232</v>
       </c>
-      <c r="C1024" s="33" t="s">
+      <c r="C1025" s="33" t="s">
         <v>2364</v>
       </c>
-      <c r="D1024" s="33" t="s">
-        <v>805</v>
-      </c>
-      <c r="E1024" s="33" t="s">
+      <c r="D1025" s="33" t="s">
+        <v>805</v>
+      </c>
+      <c r="E1025" s="33" t="s">
         <v>1567</v>
       </c>
-      <c r="F1024" s="33" t="s">
-        <v>727</v>
-      </c>
-      <c r="G1024" s="33" t="s">
+      <c r="F1025" s="33" t="s">
+        <v>727</v>
+      </c>
+      <c r="G1025" s="33" t="s">
         <v>3245</v>
       </c>
-      <c r="H1024" s="33">
+      <c r="H1025" s="33">
         <v>18790</v>
       </c>
-      <c r="I1024" s="33">
+      <c r="I1025" s="33">
         <v>140</v>
       </c>
-      <c r="J1024" s="33" t="s">
+      <c r="J1025" s="33" t="s">
         <v>2621</v>
       </c>
-      <c r="K1024" s="33" t="s">
+      <c r="K1025" s="33" t="s">
         <v>1323</v>
-      </c>
-    </row>
-    <row r="1025" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1025" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1025" s="7" t="s">
-        <v>3232</v>
-      </c>
-      <c r="C1025" s="7" t="s">
-        <v>1707</v>
-      </c>
-      <c r="D1025" s="7" t="s">
-        <v>805</v>
-      </c>
-      <c r="E1025" s="7" t="s">
-        <v>1567</v>
-      </c>
-      <c r="F1025" s="7" t="s">
-        <v>727</v>
-      </c>
-      <c r="G1025" s="7" t="s">
-        <v>3233</v>
-      </c>
-      <c r="H1025" s="7">
-        <v>16100</v>
-      </c>
-      <c r="I1025" s="7">
-        <v>80</v>
-      </c>
-      <c r="J1025" s="7" t="s">
-        <v>2621</v>
-      </c>
-      <c r="K1025" s="7" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="1026" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -81823,7 +81835,7 @@
         <v>103</v>
       </c>
       <c r="B1026" s="7" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
       <c r="C1026" s="7" t="s">
         <v>1707</v>
@@ -81835,16 +81847,16 @@
         <v>1567</v>
       </c>
       <c r="F1026" s="7" t="s">
-        <v>3235</v>
+        <v>727</v>
       </c>
       <c r="G1026" s="7" t="s">
-        <v>676</v>
+        <v>3233</v>
       </c>
       <c r="H1026" s="7">
-        <v>16480</v>
+        <v>16100</v>
       </c>
       <c r="I1026" s="7">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="J1026" s="7" t="s">
         <v>2621</v>
@@ -81858,7 +81870,7 @@
         <v>103</v>
       </c>
       <c r="B1027" s="7" t="s">
-        <v>3232</v>
+        <v>3234</v>
       </c>
       <c r="C1027" s="7" t="s">
         <v>1707</v>
@@ -81870,16 +81882,16 @@
         <v>1567</v>
       </c>
       <c r="F1027" s="7" t="s">
-        <v>727</v>
+        <v>3235</v>
       </c>
       <c r="G1027" s="7" t="s">
-        <v>3236</v>
+        <v>676</v>
       </c>
       <c r="H1027" s="7">
-        <v>16730</v>
+        <v>16480</v>
       </c>
       <c r="I1027" s="7">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="J1027" s="7" t="s">
         <v>2621</v>
@@ -81893,10 +81905,10 @@
         <v>103</v>
       </c>
       <c r="B1028" s="7" t="s">
-        <v>3237</v>
+        <v>3232</v>
       </c>
       <c r="C1028" s="7" t="s">
-        <v>1566</v>
+        <v>1707</v>
       </c>
       <c r="D1028" s="7" t="s">
         <v>805</v>
@@ -81908,13 +81920,13 @@
         <v>727</v>
       </c>
       <c r="G1028" s="7" t="s">
-        <v>3238</v>
+        <v>3236</v>
       </c>
       <c r="H1028" s="7">
-        <v>17460</v>
+        <v>16730</v>
       </c>
       <c r="I1028" s="7">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J1028" s="7" t="s">
         <v>2621</v>
@@ -81928,7 +81940,7 @@
         <v>103</v>
       </c>
       <c r="B1029" s="7" t="s">
-        <v>3239</v>
+        <v>3237</v>
       </c>
       <c r="C1029" s="7" t="s">
         <v>1566</v>
@@ -81943,13 +81955,13 @@
         <v>727</v>
       </c>
       <c r="G1029" s="7" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="H1029" s="7">
-        <v>17680</v>
+        <v>17460</v>
       </c>
       <c r="I1029" s="7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J1029" s="7" t="s">
         <v>2621</v>
@@ -81963,7 +81975,7 @@
         <v>103</v>
       </c>
       <c r="B1030" s="7" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="C1030" s="7" t="s">
         <v>1566</v>
@@ -81978,13 +81990,13 @@
         <v>727</v>
       </c>
       <c r="G1030" s="7" t="s">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="H1030" s="7">
-        <v>18150</v>
+        <v>17680</v>
       </c>
       <c r="I1030" s="7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J1030" s="7" t="s">
         <v>2621</v>
@@ -81998,10 +82010,10 @@
         <v>103</v>
       </c>
       <c r="B1031" s="7" t="s">
-        <v>3232</v>
+        <v>3241</v>
       </c>
       <c r="C1031" s="7" t="s">
-        <v>2364</v>
+        <v>1566</v>
       </c>
       <c r="D1031" s="7" t="s">
         <v>805</v>
@@ -82013,13 +82025,13 @@
         <v>727</v>
       </c>
       <c r="G1031" s="7" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="H1031" s="7">
-        <v>18420</v>
+        <v>18150</v>
       </c>
       <c r="I1031" s="7">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="J1031" s="7" t="s">
         <v>2621</v>
@@ -82048,10 +82060,10 @@
         <v>727</v>
       </c>
       <c r="G1032" s="7" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="H1032" s="7">
-        <v>18470</v>
+        <v>18420</v>
       </c>
       <c r="I1032" s="7">
         <v>130</v>
@@ -82068,10 +82080,10 @@
         <v>103</v>
       </c>
       <c r="B1033" s="7" t="s">
-        <v>3230</v>
+        <v>3232</v>
       </c>
       <c r="C1033" s="7" t="s">
-        <v>1566</v>
+        <v>2364</v>
       </c>
       <c r="D1033" s="7" t="s">
         <v>805</v>
@@ -82083,19 +82095,19 @@
         <v>727</v>
       </c>
       <c r="G1033" s="7" t="s">
-        <v>3231</v>
+        <v>3244</v>
       </c>
       <c r="H1033" s="7">
-        <v>14610</v>
+        <v>18470</v>
       </c>
       <c r="I1033" s="7">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="J1033" s="7" t="s">
         <v>2621</v>
       </c>
       <c r="K1033" s="7" t="s">
-        <v>1387</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="1034" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -82103,7 +82115,7 @@
         <v>103</v>
       </c>
       <c r="B1034" s="7" t="s">
-        <v>3228</v>
+        <v>3230</v>
       </c>
       <c r="C1034" s="7" t="s">
         <v>1566</v>
@@ -82118,10 +82130,10 @@
         <v>727</v>
       </c>
       <c r="G1034" s="7" t="s">
-        <v>3229</v>
+        <v>3231</v>
       </c>
       <c r="H1034" s="7">
-        <v>14350</v>
+        <v>14610</v>
       </c>
       <c r="I1034" s="7">
         <v>90</v>
@@ -82130,18 +82142,18 @@
         <v>2621</v>
       </c>
       <c r="K1034" s="7" t="s">
-        <v>2663</v>
-      </c>
-    </row>
-    <row r="1035" spans="1:37" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1035" s="7" t="s">
         <v>103</v>
       </c>
       <c r="B1035" s="7" t="s">
-        <v>3224</v>
+        <v>3228</v>
       </c>
       <c r="C1035" s="7" t="s">
-        <v>1707</v>
+        <v>1566</v>
       </c>
       <c r="D1035" s="7" t="s">
         <v>805</v>
@@ -82150,51 +82162,85 @@
         <v>1567</v>
       </c>
       <c r="F1035" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="G1035" s="7" t="s">
+        <v>3229</v>
+      </c>
+      <c r="H1035" s="7">
+        <v>14350</v>
+      </c>
+      <c r="I1035" s="7">
+        <v>90</v>
+      </c>
+      <c r="J1035" s="7" t="s">
+        <v>2621</v>
+      </c>
+      <c r="K1035" s="7" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:37" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1036" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1036" s="7" t="s">
+        <v>3224</v>
+      </c>
+      <c r="C1036" s="7" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D1036" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="E1036" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F1036" s="7" t="s">
         <v>3225</v>
       </c>
-      <c r="G1035" s="7" t="s">
+      <c r="G1036" s="7" t="s">
         <v>3226</v>
       </c>
-      <c r="H1035" s="7">
+      <c r="H1036" s="7">
         <v>11970</v>
       </c>
-      <c r="I1035" s="7">
+      <c r="I1036" s="7">
         <v>60</v>
       </c>
-      <c r="J1035" s="7" t="s">
+      <c r="J1036" s="7" t="s">
         <v>3227</v>
       </c>
-      <c r="K1035" s="7" t="s">
+      <c r="K1036" s="7" t="s">
         <v>1439</v>
       </c>
-      <c r="L1035" s="32"/>
-      <c r="M1035" s="32"/>
-      <c r="N1035" s="32"/>
-      <c r="O1035" s="32"/>
-      <c r="P1035" s="32"/>
-      <c r="Q1035" s="32"/>
-      <c r="R1035" s="32"/>
-      <c r="S1035" s="32"/>
-      <c r="T1035" s="32"/>
-      <c r="U1035" s="32"/>
-      <c r="V1035" s="32"/>
-      <c r="W1035" s="32"/>
-      <c r="X1035" s="32"/>
-      <c r="Y1035" s="32"/>
-      <c r="Z1035" s="32"/>
-      <c r="AA1035" s="32"/>
-      <c r="AB1035" s="32"/>
-      <c r="AC1035" s="32"/>
-      <c r="AD1035" s="32"/>
-      <c r="AE1035" s="32"/>
-      <c r="AF1035" s="32"/>
-      <c r="AG1035" s="32"/>
-      <c r="AH1035" s="32"/>
-      <c r="AI1035" s="32"/>
-      <c r="AJ1035" s="32"/>
-      <c r="AK1035" s="32"/>
-    </row>
-    <row r="1036" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="L1036" s="32"/>
+      <c r="M1036" s="32"/>
+      <c r="N1036" s="32"/>
+      <c r="O1036" s="32"/>
+      <c r="P1036" s="32"/>
+      <c r="Q1036" s="32"/>
+      <c r="R1036" s="32"/>
+      <c r="S1036" s="32"/>
+      <c r="T1036" s="32"/>
+      <c r="U1036" s="32"/>
+      <c r="V1036" s="32"/>
+      <c r="W1036" s="32"/>
+      <c r="X1036" s="32"/>
+      <c r="Y1036" s="32"/>
+      <c r="Z1036" s="32"/>
+      <c r="AA1036" s="32"/>
+      <c r="AB1036" s="32"/>
+      <c r="AC1036" s="32"/>
+      <c r="AD1036" s="32"/>
+      <c r="AE1036" s="32"/>
+      <c r="AF1036" s="32"/>
+      <c r="AG1036" s="32"/>
+      <c r="AH1036" s="32"/>
+      <c r="AI1036" s="32"/>
+      <c r="AJ1036" s="32"/>
+      <c r="AK1036" s="32"/>
+    </row>
     <row r="1037" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1038" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1039" spans="1:37" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -82349,14 +82395,15 @@
     <row r="1188" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1189" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1190" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1191" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A1:K1035" xr:uid="{E15FA49C-AA6C-4C9D-BD3F-DDB2E499D207}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K1035">
-      <sortCondition ref="A1:A1035"/>
+  <autoFilter ref="A1:K1036" xr:uid="{E15FA49C-AA6C-4C9D-BD3F-DDB2E499D207}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K1036">
+      <sortCondition ref="A1:A1036"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K1190">
-    <sortCondition ref="A1:A1190"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K1191">
+    <sortCondition ref="A1:A1191"/>
   </sortState>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Table-Data-Base.xlsx
+++ b/data/Table-Data-Base.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inaki\Downloads\Pleistocene_Human_Use_Of_Caves-master\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55321804-3624-45E1-8EE2-5811ADDC3C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC2169D-F0A8-40F3-BDF3-FFDCA7233F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{493D11CC-922E-4265-992F-96F2D38DEEBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Caves" sheetId="2" r:id="rId1"/>
-    <sheet name="Datings" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="Datings" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Caves!$A$1:$Y$503</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datings!$A$1:$K$1036</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Datings!$A$1:$K$1036</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17429" uniqueCount="3796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17466" uniqueCount="3811">
   <si>
     <t>San Antonio</t>
   </si>
@@ -12277,12 +12278,6 @@
     <t>Mask GL3D-009 (Left eye)</t>
   </si>
   <si>
-    <t>43.26851318044371908</t>
-  </si>
-  <si>
-    <t>-1.57166686165771119</t>
-  </si>
-  <si>
     <t>Réseau Martel (Decorated area)</t>
   </si>
   <si>
@@ -13182,6 +13177,57 @@
   </si>
   <si>
     <t>Taçon et al., 2012, p. 139</t>
+  </si>
+  <si>
+    <t>wkt_geom</t>
+  </si>
+  <si>
+    <t>elevation</t>
+  </si>
+  <si>
+    <t>Dating met</t>
+  </si>
+  <si>
+    <t>Reached ap</t>
+  </si>
+  <si>
+    <t>Level of d</t>
+  </si>
+  <si>
+    <t>Discussi��</t>
+  </si>
+  <si>
+    <t>Portable A</t>
+  </si>
+  <si>
+    <t>Structures</t>
+  </si>
+  <si>
+    <t>Lithic Ind</t>
+  </si>
+  <si>
+    <t>Modified b</t>
+  </si>
+  <si>
+    <t>Ochre rema</t>
+  </si>
+  <si>
+    <t>Human Rema</t>
+  </si>
+  <si>
+    <t>Fire Remai</t>
+  </si>
+  <si>
+    <t>Half-shade</t>
+  </si>
+  <si>
+    <t>Point</t>
+  </si>
+  <si>
+    <t>-1.57164900000000007</t>
+  </si>
+  <si>
+    <t>43.26811200000000213</t>
   </si>
 </sst>
 </file>
@@ -13350,7 +13396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13507,6 +13553,15 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14513,25 +14568,25 @@
     </row>
     <row r="11" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>3712</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>3713</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>3714</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="D11" s="11" t="s">
         <v>3715</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>3716</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>3717</v>
       </c>
       <c r="E11" s="8">
         <v>10</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>805</v>
@@ -14540,7 +14595,7 @@
         <v>3313</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K11" s="8">
         <v>130</v>
@@ -16585,7 +16640,7 @@
         <v>1320</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>3780</v>
+        <v>3778</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>356</v>
@@ -16711,7 +16766,7 @@
         <v>1320</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>3780</v>
+        <v>3778</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>356</v>
@@ -18367,34 +18422,34 @@
     </row>
     <row r="73" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
+        <v>3615</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>3611</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>3616</v>
+      </c>
+      <c r="D73" s="11" t="s">
         <v>3617</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>3613</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>3618</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>3619</v>
       </c>
       <c r="E73" s="8">
         <v>10</v>
       </c>
       <c r="F73" s="8" t="s">
+        <v>3612</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>3613</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="J73" s="8" t="s">
         <v>3614</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>3615</v>
-      </c>
-      <c r="H73" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="I73" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="J73" s="8" t="s">
-        <v>3616</v>
       </c>
       <c r="K73" s="8">
         <v>670</v>
@@ -19771,25 +19826,25 @@
     </row>
     <row r="95" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
+        <v>3678</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>3679</v>
+      </c>
+      <c r="C95" s="11" t="s">
         <v>3680</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="D95" s="11" t="s">
         <v>3681</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>3682</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>3683</v>
       </c>
       <c r="E95" s="8">
         <v>10</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="H95" s="8" t="s">
         <v>805</v>
@@ -19798,7 +19853,7 @@
         <v>3338</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K95" s="8">
         <v>1141</v>
@@ -20320,7 +20375,7 @@
         <v>1318</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>3779</v>
+        <v>3777</v>
       </c>
       <c r="K103" s="10" t="s">
         <v>1042</v>
@@ -20335,7 +20390,7 @@
         <v>1367</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>3774</v>
+        <v>3772</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>675</v>
@@ -20354,16 +20409,16 @@
     </row>
     <row r="104" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
+        <v>3603</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>3606</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>3604</v>
+      </c>
+      <c r="D104" s="11" t="s">
         <v>3605</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>3608</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>3606</v>
-      </c>
-      <c r="D104" s="11" t="s">
-        <v>3607</v>
       </c>
       <c r="E104" s="8">
         <v>83</v>
@@ -20375,13 +20430,13 @@
         <v>663</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>3610</v>
+        <v>3608</v>
       </c>
       <c r="I104" s="8" t="s">
         <v>1313</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>3611</v>
+        <v>3609</v>
       </c>
       <c r="K104" s="8">
         <v>20</v>
@@ -20425,16 +20480,16 @@
     </row>
     <row r="105" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
+        <v>3603</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>3607</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>3604</v>
+      </c>
+      <c r="D105" s="11" t="s">
         <v>3605</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>3609</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>3606</v>
-      </c>
-      <c r="D105" s="11" t="s">
-        <v>3607</v>
       </c>
       <c r="E105" s="8">
         <v>83</v>
@@ -20452,7 +20507,7 @@
         <v>1323</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>3611</v>
+        <v>3609</v>
       </c>
       <c r="K105" s="8">
         <v>20</v>
@@ -20639,7 +20694,7 @@
         <v>1437</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>3795</v>
+        <v>3793</v>
       </c>
       <c r="K108" s="14">
         <v>15</v>
@@ -30048,25 +30103,25 @@
     </row>
     <row r="258" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="12" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B258" s="12" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C258" s="13" t="s">
-        <v>3626</v>
+        <v>3624</v>
       </c>
       <c r="D258" s="13" t="s">
-        <v>3627</v>
+        <v>3625</v>
       </c>
       <c r="E258" s="12">
         <v>10</v>
       </c>
       <c r="F258" s="12" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="G258" s="12" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="H258" s="12" t="s">
         <v>805</v>
@@ -30075,7 +30130,7 @@
         <v>675</v>
       </c>
       <c r="J258" s="12" t="s">
-        <v>3632</v>
+        <v>3630</v>
       </c>
       <c r="K258" s="12">
         <v>600</v>
@@ -30113,25 +30168,25 @@
     </row>
     <row r="259" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="12" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B259" s="12" t="s">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="C259" s="13" t="s">
-        <v>3626</v>
+        <v>3624</v>
       </c>
       <c r="D259" s="13" t="s">
-        <v>3627</v>
+        <v>3625</v>
       </c>
       <c r="E259" s="12">
         <v>10</v>
       </c>
       <c r="F259" s="12" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="G259" s="12" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="H259" s="12" t="s">
         <v>805</v>
@@ -30140,7 +30195,7 @@
         <v>3313</v>
       </c>
       <c r="J259" s="12" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K259" s="12">
         <v>600</v>
@@ -31283,16 +31338,16 @@
     </row>
     <row r="277" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="12" t="s">
-        <v>3588</v>
+        <v>3586</v>
       </c>
       <c r="B277" s="12" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C277" s="13" t="s">
-        <v>3586</v>
+        <v>3809</v>
       </c>
       <c r="D277" s="13" t="s">
-        <v>3585</v>
+        <v>3810</v>
       </c>
       <c r="E277" s="12">
         <v>193</v>
@@ -31310,7 +31365,7 @@
         <v>1322</v>
       </c>
       <c r="J277" s="12" t="s">
-        <v>3589</v>
+        <v>3587</v>
       </c>
       <c r="K277" s="12">
         <v>450</v>
@@ -34108,34 +34163,34 @@
     </row>
     <row r="322" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="12" t="s">
-        <v>3612</v>
+        <v>3610</v>
       </c>
       <c r="B322" s="12" t="s">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="C322" s="13" t="s">
-        <v>3741</v>
+        <v>3739</v>
       </c>
       <c r="D322" s="13" t="s">
-        <v>3742</v>
+        <v>3740</v>
       </c>
       <c r="E322" s="12">
         <v>10</v>
       </c>
       <c r="F322" s="12" t="s">
+        <v>3612</v>
+      </c>
+      <c r="G322" s="12" t="s">
+        <v>3613</v>
+      </c>
+      <c r="H322" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="I322" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="J322" s="12" t="s">
         <v>3614</v>
-      </c>
-      <c r="G322" s="12" t="s">
-        <v>3615</v>
-      </c>
-      <c r="H322" s="12" t="s">
-        <v>805</v>
-      </c>
-      <c r="I322" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="J322" s="12" t="s">
-        <v>3616</v>
       </c>
       <c r="K322" s="12">
         <v>380</v>
@@ -35179,25 +35234,25 @@
     </row>
     <row r="339" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="8" t="s">
+        <v>3741</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>3742</v>
+      </c>
+      <c r="C339" s="11" t="s">
         <v>3743</v>
       </c>
-      <c r="B339" s="8" t="s">
+      <c r="D339" s="11" t="s">
         <v>3744</v>
       </c>
-      <c r="C339" s="11" t="s">
+      <c r="E339" s="11" t="s">
         <v>3745</v>
       </c>
-      <c r="D339" s="11" t="s">
-        <v>3746</v>
-      </c>
-      <c r="E339" s="11" t="s">
-        <v>3747</v>
-      </c>
       <c r="F339" s="8" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="G339" s="8" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="H339" s="8" t="s">
         <v>805</v>
@@ -35206,7 +35261,7 @@
         <v>3313</v>
       </c>
       <c r="J339" s="8" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K339" s="8">
         <v>210</v>
@@ -35421,25 +35476,25 @@
     </row>
     <row r="343" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="8" t="s">
+        <v>3726</v>
+      </c>
+      <c r="B343" s="8" t="s">
+        <v>3727</v>
+      </c>
+      <c r="C343" s="11" t="s">
         <v>3728</v>
       </c>
-      <c r="B343" s="8" t="s">
+      <c r="D343" s="11" t="s">
         <v>3729</v>
-      </c>
-      <c r="C343" s="11" t="s">
-        <v>3730</v>
-      </c>
-      <c r="D343" s="11" t="s">
-        <v>3731</v>
       </c>
       <c r="E343" s="8">
         <v>10</v>
       </c>
       <c r="F343" s="8" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="G343" s="8" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="H343" s="8" t="s">
         <v>805</v>
@@ -35448,7 +35503,7 @@
         <v>675</v>
       </c>
       <c r="J343" s="8" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K343" s="8">
         <v>368</v>
@@ -37152,25 +37207,25 @@
     </row>
     <row r="370" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="12" t="s">
+        <v>3732</v>
+      </c>
+      <c r="B370" s="12" t="s">
         <v>3734</v>
       </c>
-      <c r="B370" s="12" t="s">
-        <v>3736</v>
-      </c>
       <c r="C370" s="13" t="s">
+        <v>3733</v>
+      </c>
+      <c r="D370" s="13" t="s">
         <v>3735</v>
-      </c>
-      <c r="D370" s="13" t="s">
-        <v>3737</v>
       </c>
       <c r="E370" s="12">
         <v>10</v>
       </c>
       <c r="F370" s="12" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="G370" s="12" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="H370" s="12" t="s">
         <v>805</v>
@@ -37179,7 +37234,7 @@
         <v>3313</v>
       </c>
       <c r="J370" s="12" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K370" s="12">
         <v>369</v>
@@ -40900,19 +40955,19 @@
     </row>
     <row r="430" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="7" t="s">
+        <v>3773</v>
+      </c>
+      <c r="B430" s="7" t="s">
+        <v>3774</v>
+      </c>
+      <c r="C430" s="6" t="s">
         <v>3775</v>
       </c>
-      <c r="B430" s="7" t="s">
+      <c r="D430" s="6" t="s">
         <v>3776</v>
       </c>
-      <c r="C430" s="6" t="s">
-        <v>3777</v>
-      </c>
-      <c r="D430" s="6" t="s">
-        <v>3778</v>
-      </c>
       <c r="E430" s="6" t="s">
-        <v>3785</v>
+        <v>3783</v>
       </c>
       <c r="F430" s="7" t="s">
         <v>725</v>
@@ -40927,7 +40982,7 @@
         <v>1318</v>
       </c>
       <c r="J430" s="7" t="s">
-        <v>3779</v>
+        <v>3777</v>
       </c>
       <c r="K430" s="7">
         <v>7</v>
@@ -40942,7 +40997,7 @@
         <v>1367</v>
       </c>
       <c r="O430" s="7" t="s">
-        <v>3779</v>
+        <v>3777</v>
       </c>
       <c r="P430" s="7" t="s">
         <v>675</v>
@@ -41646,34 +41701,34 @@
     </row>
     <row r="442" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="8" t="s">
+        <v>3652</v>
+      </c>
+      <c r="B442" s="3" t="s">
+        <v>3655</v>
+      </c>
+      <c r="C442" s="11" t="s">
+        <v>3653</v>
+      </c>
+      <c r="D442" s="11" t="s">
         <v>3654</v>
-      </c>
-      <c r="B442" s="3" t="s">
-        <v>3657</v>
-      </c>
-      <c r="C442" s="11" t="s">
-        <v>3655</v>
-      </c>
-      <c r="D442" s="11" t="s">
-        <v>3656</v>
       </c>
       <c r="E442" s="8">
         <v>10</v>
       </c>
       <c r="F442" s="8" t="s">
+        <v>3612</v>
+      </c>
+      <c r="G442" s="8" t="s">
+        <v>3613</v>
+      </c>
+      <c r="H442" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="I442" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="J442" s="8" t="s">
         <v>3614</v>
-      </c>
-      <c r="G442" s="8" t="s">
-        <v>3615</v>
-      </c>
-      <c r="H442" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="I442" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="J442" s="8" t="s">
-        <v>3616</v>
       </c>
       <c r="K442" s="8">
         <v>650</v>
@@ -42758,16 +42813,16 @@
     </row>
     <row r="460" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="7" t="s">
+        <v>3779</v>
+      </c>
+      <c r="B460" s="7" t="s">
+        <v>3780</v>
+      </c>
+      <c r="C460" s="7" t="s">
         <v>3781</v>
       </c>
-      <c r="B460" s="7" t="s">
+      <c r="D460" s="7" t="s">
         <v>3782</v>
-      </c>
-      <c r="C460" s="7" t="s">
-        <v>3783</v>
-      </c>
-      <c r="D460" s="7" t="s">
-        <v>3784</v>
       </c>
       <c r="E460" s="7">
         <v>885</v>
@@ -42779,13 +42834,13 @@
         <v>663</v>
       </c>
       <c r="H460" s="10" t="s">
-        <v>3786</v>
+        <v>3784</v>
       </c>
       <c r="I460" s="10" t="s">
         <v>1226</v>
       </c>
       <c r="J460" s="10" t="s">
-        <v>3787</v>
+        <v>3785</v>
       </c>
       <c r="K460" s="7">
         <v>70</v>
@@ -42800,7 +42855,7 @@
         <v>1252</v>
       </c>
       <c r="O460" s="10" t="s">
-        <v>3788</v>
+        <v>3786</v>
       </c>
       <c r="P460" s="7"/>
       <c r="Q460" s="7"/>
@@ -42825,16 +42880,16 @@
     </row>
     <row r="461" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
+        <v>3779</v>
+      </c>
+      <c r="B461" s="3" t="s">
+        <v>3787</v>
+      </c>
+      <c r="C461" s="3" t="s">
         <v>3781</v>
       </c>
-      <c r="B461" s="3" t="s">
-        <v>3789</v>
-      </c>
-      <c r="C461" s="3" t="s">
-        <v>3783</v>
-      </c>
       <c r="D461" s="3" t="s">
-        <v>3784</v>
+        <v>3782</v>
       </c>
       <c r="E461" s="3">
         <v>885</v>
@@ -42846,13 +42901,13 @@
         <v>663</v>
       </c>
       <c r="H461" s="8" t="s">
-        <v>3786</v>
+        <v>3784</v>
       </c>
       <c r="I461" s="8" t="s">
-        <v>3790</v>
+        <v>3788</v>
       </c>
       <c r="J461" s="8" t="s">
-        <v>3791</v>
+        <v>3789</v>
       </c>
       <c r="K461" s="3">
         <v>20</v>
@@ -43315,34 +43370,34 @@
     </row>
     <row r="469" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="8" t="s">
+        <v>3721</v>
+      </c>
+      <c r="B469" s="8" t="s">
+        <v>3722</v>
+      </c>
+      <c r="C469" s="11" t="s">
         <v>3723</v>
       </c>
-      <c r="B469" s="8" t="s">
+      <c r="D469" s="11" t="s">
         <v>3724</v>
-      </c>
-      <c r="C469" s="11" t="s">
-        <v>3725</v>
-      </c>
-      <c r="D469" s="11" t="s">
-        <v>3726</v>
       </c>
       <c r="E469" s="8">
         <v>10</v>
       </c>
       <c r="F469" s="8" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="G469" s="8" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="H469" s="8" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="I469" s="8" t="s">
         <v>3313</v>
       </c>
       <c r="J469" s="8" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K469" s="8">
         <v>130</v>
@@ -45523,6 +45578,156 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7680950-4FA9-43D4-B93A-6F2F56B6CBD1}">
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="53" t="s">
+        <v>3794</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53" t="s">
+        <v>647</v>
+      </c>
+      <c r="E1" s="53" t="s">
+        <v>646</v>
+      </c>
+      <c r="F1" s="53" t="s">
+        <v>3795</v>
+      </c>
+      <c r="G1" s="53" t="s">
+        <v>650</v>
+      </c>
+      <c r="H1" s="53" t="s">
+        <v>1258</v>
+      </c>
+      <c r="I1" s="53" t="s">
+        <v>3796</v>
+      </c>
+      <c r="J1" s="53" t="s">
+        <v>1225</v>
+      </c>
+      <c r="K1" s="53" t="s">
+        <v>792</v>
+      </c>
+      <c r="L1" s="53" t="s">
+        <v>3797</v>
+      </c>
+      <c r="M1" s="53" t="s">
+        <v>3798</v>
+      </c>
+      <c r="N1" s="53" t="s">
+        <v>1237</v>
+      </c>
+      <c r="O1" s="53" t="s">
+        <v>1250</v>
+      </c>
+      <c r="P1" s="53" t="s">
+        <v>3799</v>
+      </c>
+      <c r="Q1" s="53" t="s">
+        <v>739</v>
+      </c>
+      <c r="R1" s="53" t="s">
+        <v>3800</v>
+      </c>
+      <c r="S1" s="53" t="s">
+        <v>3801</v>
+      </c>
+      <c r="T1" s="53" t="s">
+        <v>3802</v>
+      </c>
+      <c r="U1" s="53" t="s">
+        <v>3803</v>
+      </c>
+      <c r="V1" s="53" t="s">
+        <v>3804</v>
+      </c>
+      <c r="W1" s="53" t="s">
+        <v>3805</v>
+      </c>
+      <c r="X1" s="53" t="s">
+        <v>745</v>
+      </c>
+      <c r="Y1" s="53" t="s">
+        <v>3806</v>
+      </c>
+      <c r="Z1" s="53" t="s">
+        <v>3807</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="53" t="s">
+        <v>3808</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>3809</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>3810</v>
+      </c>
+      <c r="D2" s="54">
+        <v>-1571666861657710</v>
+      </c>
+      <c r="E2" s="54">
+        <v>4326851318044370</v>
+      </c>
+      <c r="F2" s="53">
+        <v>193</v>
+      </c>
+      <c r="G2" s="53" t="s">
+        <v>655</v>
+      </c>
+      <c r="H2" s="53" t="s">
+        <v>663</v>
+      </c>
+      <c r="I2" s="53" t="s">
+        <v>853</v>
+      </c>
+      <c r="J2" s="53" t="s">
+        <v>1322</v>
+      </c>
+      <c r="K2" s="53" t="s">
+        <v>3587</v>
+      </c>
+      <c r="L2" s="53">
+        <v>450</v>
+      </c>
+      <c r="M2" s="53" t="s">
+        <v>1376</v>
+      </c>
+      <c r="N2" s="53" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="53" t="s">
+        <v>727</v>
+      </c>
+      <c r="P2" s="53" t="s">
+        <v>727</v>
+      </c>
+      <c r="Q2" s="53" t="s">
+        <v>675</v>
+      </c>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53" t="s">
+        <v>676</v>
+      </c>
+      <c r="Z2" s="53"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15FA49C-AA6C-4C9D-BD3F-DDB2E499D207}">
   <dimension ref="A1:AK1191"/>
   <sheetFormatPr defaultColWidth="63.33203125" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -46036,10 +46241,10 @@
     </row>
     <row r="15" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
-        <v>3714</v>
+        <v>3712</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>3715</v>
+        <v>3713</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>1566</v>
@@ -46054,7 +46259,7 @@
         <v>676</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>3721</v>
+        <v>3719</v>
       </c>
       <c r="H15" s="33">
         <v>9139</v>
@@ -46063,7 +46268,7 @@
         <v>23</v>
       </c>
       <c r="J15" s="33" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K15" s="33" t="s">
         <v>3313</v>
@@ -46071,10 +46276,10 @@
     </row>
     <row r="16" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="33" t="s">
-        <v>3714</v>
+        <v>3712</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>3715</v>
+        <v>3713</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>1566</v>
@@ -46089,7 +46294,7 @@
         <v>676</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>3719</v>
+        <v>3717</v>
       </c>
       <c r="H16" s="33">
         <v>9180</v>
@@ -46098,7 +46303,7 @@
         <v>60</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K16" s="33" t="s">
         <v>3313</v>
@@ -46106,10 +46311,10 @@
     </row>
     <row r="17" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="33" t="s">
-        <v>3714</v>
+        <v>3712</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>3715</v>
+        <v>3713</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>1566</v>
@@ -46124,7 +46329,7 @@
         <v>676</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>3720</v>
+        <v>3718</v>
       </c>
       <c r="H17" s="33">
         <v>9318</v>
@@ -46133,7 +46338,7 @@
         <v>37</v>
       </c>
       <c r="J17" s="33" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K17" s="33" t="s">
         <v>3313</v>
@@ -46141,10 +46346,10 @@
     </row>
     <row r="18" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="33" t="s">
-        <v>3714</v>
+        <v>3712</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>3715</v>
+        <v>3713</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>1566</v>
@@ -46159,7 +46364,7 @@
         <v>676</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>3722</v>
+        <v>3720</v>
       </c>
       <c r="H18" s="33">
         <v>9524</v>
@@ -46168,7 +46373,7 @@
         <v>84</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K18" s="33" t="s">
         <v>3313</v>
@@ -49679,10 +49884,10 @@
         <v>1552</v>
       </c>
       <c r="B119" s="33" t="s">
-        <v>3590</v>
+        <v>3588</v>
       </c>
       <c r="C119" s="33" t="s">
-        <v>3596</v>
+        <v>3594</v>
       </c>
       <c r="D119" s="33" t="s">
         <v>805</v>
@@ -49691,10 +49896,10 @@
         <v>1567</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>3599</v>
+        <v>3597</v>
       </c>
       <c r="G119" s="33" t="s">
-        <v>3602</v>
+        <v>3600</v>
       </c>
       <c r="H119" s="7">
         <v>10110</v>
@@ -49703,7 +49908,7 @@
         <v>300</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>3603</v>
+        <v>3601</v>
       </c>
       <c r="K119" s="33" t="s">
         <v>675</v>
@@ -49714,10 +49919,10 @@
         <v>1552</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>3590</v>
+        <v>3588</v>
       </c>
       <c r="C120" s="33" t="s">
-        <v>3604</v>
+        <v>3602</v>
       </c>
       <c r="D120" s="33" t="s">
         <v>805</v>
@@ -49726,10 +49931,10 @@
         <v>1567</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>3597</v>
+        <v>3595</v>
       </c>
       <c r="G120" s="33" t="s">
-        <v>3600</v>
+        <v>3598</v>
       </c>
       <c r="H120" s="7">
         <v>10175</v>
@@ -49738,7 +49943,7 @@
         <v>300</v>
       </c>
       <c r="J120" s="7" t="s">
-        <v>3603</v>
+        <v>3601</v>
       </c>
       <c r="K120" s="33" t="s">
         <v>675</v>
@@ -49749,10 +49954,10 @@
         <v>1552</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>3590</v>
+        <v>3588</v>
       </c>
       <c r="C121" s="33" t="s">
-        <v>3596</v>
+        <v>3594</v>
       </c>
       <c r="D121" s="33" t="s">
         <v>805</v>
@@ -49764,7 +49969,7 @@
         <v>676</v>
       </c>
       <c r="G121" s="33" t="s">
-        <v>3591</v>
+        <v>3589</v>
       </c>
       <c r="H121" s="7">
         <v>11180</v>
@@ -49773,7 +49978,7 @@
         <v>120</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>3592</v>
+        <v>3590</v>
       </c>
       <c r="K121" s="33" t="s">
         <v>675</v>
@@ -49784,10 +49989,10 @@
         <v>1552</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>3590</v>
+        <v>3588</v>
       </c>
       <c r="C122" s="33" t="s">
-        <v>3604</v>
+        <v>3602</v>
       </c>
       <c r="D122" s="33" t="s">
         <v>805</v>
@@ -49796,10 +50001,10 @@
         <v>1567</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>3598</v>
+        <v>3596</v>
       </c>
       <c r="G122" s="33" t="s">
-        <v>3601</v>
+        <v>3599</v>
       </c>
       <c r="H122" s="7">
         <v>11710</v>
@@ -49808,7 +50013,7 @@
         <v>295</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>3603</v>
+        <v>3601</v>
       </c>
       <c r="K122" s="33" t="s">
         <v>675</v>
@@ -49819,10 +50024,10 @@
         <v>1552</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>3593</v>
+        <v>3591</v>
       </c>
       <c r="C123" s="33" t="s">
-        <v>3596</v>
+        <v>3594</v>
       </c>
       <c r="D123" s="33" t="s">
         <v>805</v>
@@ -49834,7 +50039,7 @@
         <v>676</v>
       </c>
       <c r="G123" s="33" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
       <c r="H123" s="7">
         <v>9694</v>
@@ -49843,7 +50048,7 @@
         <v>110</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>3595</v>
+        <v>3593</v>
       </c>
       <c r="K123" s="33" t="s">
         <v>3313</v>
@@ -49886,10 +50091,10 @@
     </row>
     <row r="125" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="33" t="s">
-        <v>3617</v>
+        <v>3615</v>
       </c>
       <c r="B125" s="33" t="s">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="C125" s="33" t="s">
         <v>1566</v>
@@ -49901,10 +50106,10 @@
         <v>1567</v>
       </c>
       <c r="F125" s="33" t="s">
+        <v>3621</v>
+      </c>
+      <c r="G125" s="33" t="s">
         <v>3623</v>
-      </c>
-      <c r="G125" s="33" t="s">
-        <v>3625</v>
       </c>
       <c r="H125" s="33">
         <v>9644</v>
@@ -49913,7 +50118,7 @@
         <v>40</v>
       </c>
       <c r="J125" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K125" s="33" t="s">
         <v>675</v>
@@ -49921,10 +50126,10 @@
     </row>
     <row r="126" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="33" t="s">
-        <v>3617</v>
+        <v>3615</v>
       </c>
       <c r="B126" s="33" t="s">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="C126" s="33" t="s">
         <v>1566</v>
@@ -49936,10 +50141,10 @@
         <v>1567</v>
       </c>
       <c r="F126" s="33" t="s">
+        <v>3620</v>
+      </c>
+      <c r="G126" s="33" t="s">
         <v>3622</v>
-      </c>
-      <c r="G126" s="33" t="s">
-        <v>3624</v>
       </c>
       <c r="H126" s="33">
         <v>9850</v>
@@ -49948,7 +50153,7 @@
         <v>41</v>
       </c>
       <c r="J126" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K126" s="33" t="s">
         <v>675</v>
@@ -51319,10 +51524,10 @@
     </row>
     <row r="166" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B166" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C166" s="33" t="s">
         <v>1566</v>
@@ -51334,7 +51539,7 @@
         <v>1567</v>
       </c>
       <c r="F166" s="33" t="s">
-        <v>3706</v>
+        <v>3704</v>
       </c>
       <c r="G166" s="33" t="s">
         <v>676</v>
@@ -51346,7 +51551,7 @@
         <v>27</v>
       </c>
       <c r="J166" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K166" s="33" t="s">
         <v>3338</v>
@@ -51354,10 +51559,10 @@
     </row>
     <row r="167" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B167" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C167" s="33" t="s">
         <v>1566</v>
@@ -51369,7 +51574,7 @@
         <v>1567</v>
       </c>
       <c r="F167" s="33" t="s">
-        <v>3712</v>
+        <v>3710</v>
       </c>
       <c r="G167" s="33" t="s">
         <v>676</v>
@@ -51381,7 +51586,7 @@
         <v>27</v>
       </c>
       <c r="J167" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K167" s="33" t="s">
         <v>3338</v>
@@ -51389,10 +51594,10 @@
     </row>
     <row r="168" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B168" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C168" s="33" t="s">
         <v>1566</v>
@@ -51404,7 +51609,7 @@
         <v>1567</v>
       </c>
       <c r="F168" s="33" t="s">
-        <v>3711</v>
+        <v>3709</v>
       </c>
       <c r="G168" s="33" t="s">
         <v>676</v>
@@ -51416,7 +51621,7 @@
         <v>27</v>
       </c>
       <c r="J168" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K168" s="33" t="s">
         <v>3338</v>
@@ -51424,10 +51629,10 @@
     </row>
     <row r="169" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B169" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C169" s="33" t="s">
         <v>1566</v>
@@ -51439,7 +51644,7 @@
         <v>1567</v>
       </c>
       <c r="F169" s="33" t="s">
-        <v>3702</v>
+        <v>3700</v>
       </c>
       <c r="G169" s="33" t="s">
         <v>676</v>
@@ -51451,7 +51656,7 @@
         <v>26</v>
       </c>
       <c r="J169" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K169" s="33" t="s">
         <v>3338</v>
@@ -51459,10 +51664,10 @@
     </row>
     <row r="170" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B170" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C170" s="33" t="s">
         <v>1566</v>
@@ -51474,7 +51679,7 @@
         <v>1567</v>
       </c>
       <c r="F170" s="33" t="s">
-        <v>3703</v>
+        <v>3701</v>
       </c>
       <c r="G170" s="33" t="s">
         <v>676</v>
@@ -51486,7 +51691,7 @@
         <v>26</v>
       </c>
       <c r="J170" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K170" s="33" t="s">
         <v>3338</v>
@@ -51494,10 +51699,10 @@
     </row>
     <row r="171" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B171" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C171" s="33" t="s">
         <v>1566</v>
@@ -51509,7 +51714,7 @@
         <v>1567</v>
       </c>
       <c r="F171" s="33" t="s">
-        <v>3713</v>
+        <v>3711</v>
       </c>
       <c r="G171" s="33" t="s">
         <v>676</v>
@@ -51521,7 +51726,7 @@
         <v>30</v>
       </c>
       <c r="J171" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K171" s="33" t="s">
         <v>3338</v>
@@ -51529,10 +51734,10 @@
     </row>
     <row r="172" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B172" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C172" s="33" t="s">
         <v>1566</v>
@@ -51544,7 +51749,7 @@
         <v>1567</v>
       </c>
       <c r="F172" s="33" t="s">
-        <v>3709</v>
+        <v>3707</v>
       </c>
       <c r="G172" s="33" t="s">
         <v>676</v>
@@ -51556,7 +51761,7 @@
         <v>27</v>
       </c>
       <c r="J172" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K172" s="33" t="s">
         <v>3338</v>
@@ -51564,10 +51769,10 @@
     </row>
     <row r="173" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B173" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C173" s="33" t="s">
         <v>1566</v>
@@ -51579,7 +51784,7 @@
         <v>1567</v>
       </c>
       <c r="F173" s="33" t="s">
-        <v>3704</v>
+        <v>3702</v>
       </c>
       <c r="G173" s="33" t="s">
         <v>676</v>
@@ -51591,7 +51796,7 @@
         <v>29</v>
       </c>
       <c r="J173" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K173" s="33" t="s">
         <v>3338</v>
@@ -51599,10 +51804,10 @@
     </row>
     <row r="174" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B174" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C174" s="33" t="s">
         <v>1566</v>
@@ -51614,7 +51819,7 @@
         <v>1567</v>
       </c>
       <c r="F174" s="33" t="s">
-        <v>3707</v>
+        <v>3705</v>
       </c>
       <c r="G174" s="33" t="s">
         <v>676</v>
@@ -51626,7 +51831,7 @@
         <v>29</v>
       </c>
       <c r="J174" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K174" s="33" t="s">
         <v>3338</v>
@@ -51634,10 +51839,10 @@
     </row>
     <row r="175" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B175" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C175" s="33" t="s">
         <v>1566</v>
@@ -51649,7 +51854,7 @@
         <v>1567</v>
       </c>
       <c r="F175" s="33" t="s">
-        <v>3699</v>
+        <v>3697</v>
       </c>
       <c r="G175" s="33" t="s">
         <v>676</v>
@@ -51661,7 +51866,7 @@
         <v>26</v>
       </c>
       <c r="J175" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K175" s="33" t="s">
         <v>3338</v>
@@ -51669,10 +51874,10 @@
     </row>
     <row r="176" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B176" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C176" s="33" t="s">
         <v>1566</v>
@@ -51684,7 +51889,7 @@
         <v>1567</v>
       </c>
       <c r="F176" s="33" t="s">
-        <v>3696</v>
+        <v>3694</v>
       </c>
       <c r="G176" s="33" t="s">
         <v>676</v>
@@ -51696,7 +51901,7 @@
         <v>27</v>
       </c>
       <c r="J176" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K176" s="33" t="s">
         <v>3338</v>
@@ -51704,10 +51909,10 @@
     </row>
     <row r="177" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B177" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C177" s="33" t="s">
         <v>1566</v>
@@ -51719,7 +51924,7 @@
         <v>1567</v>
       </c>
       <c r="F177" s="33" t="s">
-        <v>3700</v>
+        <v>3698</v>
       </c>
       <c r="G177" s="33" t="s">
         <v>676</v>
@@ -51731,7 +51936,7 @@
         <v>28</v>
       </c>
       <c r="J177" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K177" s="33" t="s">
         <v>3338</v>
@@ -51739,10 +51944,10 @@
     </row>
     <row r="178" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B178" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C178" s="33" t="s">
         <v>1566</v>
@@ -51754,7 +51959,7 @@
         <v>1567</v>
       </c>
       <c r="F178" s="33" t="s">
-        <v>3701</v>
+        <v>3699</v>
       </c>
       <c r="G178" s="33" t="s">
         <v>676</v>
@@ -51766,7 +51971,7 @@
         <v>27</v>
       </c>
       <c r="J178" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K178" s="33" t="s">
         <v>3338</v>
@@ -51774,10 +51979,10 @@
     </row>
     <row r="179" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B179" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C179" s="33" t="s">
         <v>1566</v>
@@ -51789,7 +51994,7 @@
         <v>1567</v>
       </c>
       <c r="F179" s="33" t="s">
-        <v>3710</v>
+        <v>3708</v>
       </c>
       <c r="G179" s="33" t="s">
         <v>676</v>
@@ -51801,7 +52006,7 @@
         <v>27</v>
       </c>
       <c r="J179" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K179" s="33" t="s">
         <v>3338</v>
@@ -51809,10 +52014,10 @@
     </row>
     <row r="180" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B180" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C180" s="33" t="s">
         <v>1566</v>
@@ -51824,7 +52029,7 @@
         <v>1567</v>
       </c>
       <c r="F180" s="33" t="s">
-        <v>3698</v>
+        <v>3696</v>
       </c>
       <c r="G180" s="33" t="s">
         <v>676</v>
@@ -51836,7 +52041,7 @@
         <v>28</v>
       </c>
       <c r="J180" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K180" s="33" t="s">
         <v>3338</v>
@@ -51844,10 +52049,10 @@
     </row>
     <row r="181" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B181" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C181" s="33" t="s">
         <v>1566</v>
@@ -51859,7 +52064,7 @@
         <v>1567</v>
       </c>
       <c r="F181" s="33" t="s">
-        <v>3708</v>
+        <v>3706</v>
       </c>
       <c r="G181" s="33" t="s">
         <v>676</v>
@@ -51871,7 +52076,7 @@
         <v>29</v>
       </c>
       <c r="J181" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K181" s="33" t="s">
         <v>3338</v>
@@ -51879,10 +52084,10 @@
     </row>
     <row r="182" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B182" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C182" s="33" t="s">
         <v>1566</v>
@@ -51894,7 +52099,7 @@
         <v>1567</v>
       </c>
       <c r="F182" s="33" t="s">
-        <v>3705</v>
+        <v>3703</v>
       </c>
       <c r="G182" s="33" t="s">
         <v>676</v>
@@ -51906,7 +52111,7 @@
         <v>29</v>
       </c>
       <c r="J182" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K182" s="33" t="s">
         <v>3338</v>
@@ -51914,10 +52119,10 @@
     </row>
     <row r="183" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="33" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="B183" s="33" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="C183" s="33" t="s">
         <v>1566</v>
@@ -51929,7 +52134,7 @@
         <v>1567</v>
       </c>
       <c r="F183" s="33" t="s">
-        <v>3697</v>
+        <v>3695</v>
       </c>
       <c r="G183" s="33" t="s">
         <v>676</v>
@@ -51941,7 +52146,7 @@
         <v>28</v>
       </c>
       <c r="J183" s="33" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="K183" s="33" t="s">
         <v>3338</v>
@@ -67944,13 +68149,13 @@
     </row>
     <row r="636" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B636" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C636" s="33" t="s">
-        <v>3646</v>
+        <v>3644</v>
       </c>
       <c r="D636" s="33" t="s">
         <v>805</v>
@@ -67959,10 +68164,10 @@
         <v>1567</v>
       </c>
       <c r="F636" s="33" t="s">
-        <v>3635</v>
+        <v>3633</v>
       </c>
       <c r="G636" s="33" t="s">
-        <v>3685</v>
+        <v>3683</v>
       </c>
       <c r="H636" s="33">
         <v>9549</v>
@@ -67971,7 +68176,7 @@
         <v>42</v>
       </c>
       <c r="J636" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K636" s="33" t="s">
         <v>675</v>
@@ -67979,13 +68184,13 @@
     </row>
     <row r="637" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B637" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C637" s="33" t="s">
-        <v>3648</v>
+        <v>3646</v>
       </c>
       <c r="D637" s="33" t="s">
         <v>805</v>
@@ -67994,10 +68199,10 @@
         <v>1567</v>
       </c>
       <c r="F637" s="33" t="s">
-        <v>3637</v>
+        <v>3635</v>
       </c>
       <c r="G637" s="33" t="s">
-        <v>3687</v>
+        <v>3685</v>
       </c>
       <c r="H637" s="33">
         <v>9565</v>
@@ -68006,7 +68211,7 @@
         <v>40</v>
       </c>
       <c r="J637" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K637" s="33" t="s">
         <v>675</v>
@@ -68014,13 +68219,13 @@
     </row>
     <row r="638" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B638" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C638" s="33" t="s">
-        <v>3649</v>
+        <v>3647</v>
       </c>
       <c r="D638" s="33" t="s">
         <v>805</v>
@@ -68029,10 +68234,10 @@
         <v>1567</v>
       </c>
       <c r="F638" s="33" t="s">
-        <v>3642</v>
+        <v>3640</v>
       </c>
       <c r="G638" s="33" t="s">
-        <v>3692</v>
+        <v>3690</v>
       </c>
       <c r="H638" s="33">
         <v>9570</v>
@@ -68041,7 +68246,7 @@
         <v>37</v>
       </c>
       <c r="J638" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K638" s="33" t="s">
         <v>675</v>
@@ -68049,13 +68254,13 @@
     </row>
     <row r="639" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B639" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C639" s="33" t="s">
-        <v>3647</v>
+        <v>3645</v>
       </c>
       <c r="D639" s="33" t="s">
         <v>805</v>
@@ -68064,10 +68269,10 @@
         <v>1567</v>
       </c>
       <c r="F639" s="33" t="s">
-        <v>3636</v>
+        <v>3634</v>
       </c>
       <c r="G639" s="33" t="s">
-        <v>3686</v>
+        <v>3684</v>
       </c>
       <c r="H639" s="33">
         <v>9581</v>
@@ -68076,7 +68281,7 @@
         <v>36</v>
       </c>
       <c r="J639" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K639" s="33" t="s">
         <v>675</v>
@@ -68084,13 +68289,13 @@
     </row>
     <row r="640" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B640" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C640" s="33" t="s">
-        <v>3649</v>
+        <v>3647</v>
       </c>
       <c r="D640" s="33" t="s">
         <v>805</v>
@@ -68099,10 +68304,10 @@
         <v>1567</v>
       </c>
       <c r="F640" s="33" t="s">
-        <v>3638</v>
+        <v>3636</v>
       </c>
       <c r="G640" s="33" t="s">
-        <v>3688</v>
+        <v>3686</v>
       </c>
       <c r="H640" s="33">
         <v>9600</v>
@@ -68111,7 +68316,7 @@
         <v>45</v>
       </c>
       <c r="J640" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K640" s="33" t="s">
         <v>675</v>
@@ -68119,13 +68324,13 @@
     </row>
     <row r="641" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A641" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B641" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C641" s="33" t="s">
-        <v>3651</v>
+        <v>3649</v>
       </c>
       <c r="D641" s="33" t="s">
         <v>805</v>
@@ -68134,10 +68339,10 @@
         <v>1567</v>
       </c>
       <c r="F641" s="33" t="s">
-        <v>3643</v>
+        <v>3641</v>
       </c>
       <c r="G641" s="33" t="s">
-        <v>3693</v>
+        <v>3691</v>
       </c>
       <c r="H641" s="33">
         <v>9650</v>
@@ -68146,7 +68351,7 @@
         <v>45</v>
       </c>
       <c r="J641" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K641" s="33" t="s">
         <v>675</v>
@@ -68154,13 +68359,13 @@
     </row>
     <row r="642" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B642" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C642" s="33" t="s">
-        <v>3646</v>
+        <v>3644</v>
       </c>
       <c r="D642" s="33" t="s">
         <v>805</v>
@@ -68169,10 +68374,10 @@
         <v>1567</v>
       </c>
       <c r="F642" s="33" t="s">
-        <v>3641</v>
+        <v>3639</v>
       </c>
       <c r="G642" s="33" t="s">
-        <v>3691</v>
+        <v>3689</v>
       </c>
       <c r="H642" s="33">
         <v>9744</v>
@@ -68181,7 +68386,7 @@
         <v>41</v>
       </c>
       <c r="J642" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K642" s="33" t="s">
         <v>675</v>
@@ -68189,13 +68394,13 @@
     </row>
     <row r="643" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B643" s="33" t="s">
-        <v>3630</v>
+        <v>3628</v>
       </c>
       <c r="C643" s="33" t="s">
-        <v>3628</v>
+        <v>3626</v>
       </c>
       <c r="D643" s="33" t="s">
         <v>805</v>
@@ -68207,7 +68412,7 @@
         <v>8205</v>
       </c>
       <c r="G643" s="33" t="s">
-        <v>3631</v>
+        <v>3629</v>
       </c>
       <c r="H643" s="33">
         <v>10970</v>
@@ -68216,7 +68421,7 @@
         <v>25</v>
       </c>
       <c r="J643" s="33" t="s">
-        <v>3632</v>
+        <v>3630</v>
       </c>
       <c r="K643" s="33" t="s">
         <v>675</v>
@@ -68224,13 +68429,13 @@
     </row>
     <row r="644" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B644" s="33" t="s">
-        <v>3630</v>
+        <v>3628</v>
       </c>
       <c r="C644" s="33" t="s">
-        <v>3628</v>
+        <v>3626</v>
       </c>
       <c r="D644" s="33" t="s">
         <v>805</v>
@@ -68242,7 +68447,7 @@
         <v>8205</v>
       </c>
       <c r="G644" s="33" t="s">
-        <v>3633</v>
+        <v>3631</v>
       </c>
       <c r="H644" s="33">
         <v>10985</v>
@@ -68251,7 +68456,7 @@
         <v>30</v>
       </c>
       <c r="J644" s="33" t="s">
-        <v>3632</v>
+        <v>3630</v>
       </c>
       <c r="K644" s="33" t="s">
         <v>675</v>
@@ -68259,13 +68464,13 @@
     </row>
     <row r="645" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B645" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C645" s="33" t="s">
-        <v>3650</v>
+        <v>3648</v>
       </c>
       <c r="D645" s="33" t="s">
         <v>805</v>
@@ -68274,10 +68479,10 @@
         <v>1567</v>
       </c>
       <c r="F645" s="33" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G645" s="33" t="s">
-        <v>3695</v>
+        <v>3693</v>
       </c>
       <c r="H645" s="33">
         <v>8982</v>
@@ -68286,7 +68491,7 @@
         <v>54</v>
       </c>
       <c r="J645" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K645" s="33" t="s">
         <v>3313</v>
@@ -68294,13 +68499,13 @@
     </row>
     <row r="646" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B646" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C646" s="33" t="s">
-        <v>3652</v>
+        <v>3650</v>
       </c>
       <c r="D646" s="33" t="s">
         <v>805</v>
@@ -68309,10 +68514,10 @@
         <v>1567</v>
       </c>
       <c r="F646" s="33" t="s">
-        <v>3644</v>
+        <v>3642</v>
       </c>
       <c r="G646" s="33" t="s">
-        <v>3694</v>
+        <v>3692</v>
       </c>
       <c r="H646" s="33">
         <v>9277</v>
@@ -68321,7 +68526,7 @@
         <v>46</v>
       </c>
       <c r="J646" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K646" s="33" t="s">
         <v>3313</v>
@@ -68329,13 +68534,13 @@
     </row>
     <row r="647" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B647" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C647" s="33" t="s">
-        <v>3650</v>
+        <v>3648</v>
       </c>
       <c r="D647" s="33" t="s">
         <v>805</v>
@@ -68344,10 +68549,10 @@
         <v>1567</v>
       </c>
       <c r="F647" s="33" t="s">
-        <v>3639</v>
+        <v>3637</v>
       </c>
       <c r="G647" s="33" t="s">
-        <v>3689</v>
+        <v>3687</v>
       </c>
       <c r="H647" s="33">
         <v>9313</v>
@@ -68356,7 +68561,7 @@
         <v>36</v>
       </c>
       <c r="J647" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K647" s="33" t="s">
         <v>3313</v>
@@ -68364,13 +68569,13 @@
     </row>
     <row r="648" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="33" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="B648" s="33" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="C648" s="33" t="s">
-        <v>3649</v>
+        <v>3647</v>
       </c>
       <c r="D648" s="33" t="s">
         <v>805</v>
@@ -68379,10 +68584,10 @@
         <v>1567</v>
       </c>
       <c r="F648" s="33" t="s">
-        <v>3640</v>
+        <v>3638</v>
       </c>
       <c r="G648" s="33" t="s">
-        <v>3690</v>
+        <v>3688</v>
       </c>
       <c r="H648" s="33">
         <v>9478</v>
@@ -68391,7 +68596,7 @@
         <v>39</v>
       </c>
       <c r="J648" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K648" s="33" t="s">
         <v>3313</v>
@@ -71606,10 +71811,10 @@
     </row>
     <row r="737" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A737" s="33" t="s">
-        <v>3612</v>
+        <v>3610</v>
       </c>
       <c r="B737" s="33" t="s">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="C737" s="33" t="s">
         <v>1566</v>
@@ -71621,10 +71826,10 @@
         <v>1567</v>
       </c>
       <c r="F737" s="33" t="s">
-        <v>3620</v>
+        <v>3618</v>
       </c>
       <c r="G737" s="33" t="s">
-        <v>3621</v>
+        <v>3619</v>
       </c>
       <c r="H737" s="33">
         <v>10146</v>
@@ -71633,7 +71838,7 @@
         <v>45</v>
       </c>
       <c r="J737" s="33" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K737" s="33" t="s">
         <v>675</v>
@@ -71644,7 +71849,7 @@
         <v>1266</v>
       </c>
       <c r="B738" s="33" t="s">
-        <v>3792</v>
+        <v>3790</v>
       </c>
       <c r="C738" s="33" t="s">
         <v>1566</v>
@@ -71662,13 +71867,13 @@
         <v>676</v>
       </c>
       <c r="H738" s="33" t="s">
-        <v>3793</v>
+        <v>3791</v>
       </c>
       <c r="I738" s="33" t="s">
         <v>727</v>
       </c>
       <c r="J738" s="33" t="s">
-        <v>3794</v>
+        <v>3792</v>
       </c>
       <c r="K738" s="33" t="s">
         <v>1439</v>
@@ -71921,10 +72126,10 @@
     </row>
     <row r="746" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A746" s="33" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="B746" s="33" t="s">
-        <v>3753</v>
+        <v>3751</v>
       </c>
       <c r="C746" s="33" t="s">
         <v>1566</v>
@@ -71939,7 +72144,7 @@
         <v>727</v>
       </c>
       <c r="G746" s="33" t="s">
-        <v>3762</v>
+        <v>3760</v>
       </c>
       <c r="H746" s="33">
         <v>9646</v>
@@ -71948,7 +72153,7 @@
         <v>45</v>
       </c>
       <c r="J746" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K746" s="33" t="s">
         <v>675</v>
@@ -71956,13 +72161,13 @@
     </row>
     <row r="747" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A747" s="33" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="B747" s="33" t="s">
-        <v>3750</v>
+        <v>3748</v>
       </c>
       <c r="C747" s="33" t="s">
-        <v>3751</v>
+        <v>3749</v>
       </c>
       <c r="D747" s="33" t="s">
         <v>805</v>
@@ -71974,7 +72179,7 @@
         <v>727</v>
       </c>
       <c r="G747" s="33" t="s">
-        <v>3754</v>
+        <v>3752</v>
       </c>
       <c r="H747" s="33">
         <v>8605</v>
@@ -71983,7 +72188,7 @@
         <v>34</v>
       </c>
       <c r="J747" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K747" s="33" t="s">
         <v>3313</v>
@@ -71991,13 +72196,13 @@
     </row>
     <row r="748" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A748" s="33" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="B748" s="33" t="s">
-        <v>3752</v>
+        <v>3750</v>
       </c>
       <c r="C748" s="33" t="s">
-        <v>3751</v>
+        <v>3749</v>
       </c>
       <c r="D748" s="33" t="s">
         <v>805</v>
@@ -72009,7 +72214,7 @@
         <v>727</v>
       </c>
       <c r="G748" s="33" t="s">
-        <v>3755</v>
+        <v>3753</v>
       </c>
       <c r="H748" s="33">
         <v>8749</v>
@@ -72018,7 +72223,7 @@
         <v>44</v>
       </c>
       <c r="J748" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K748" s="33" t="s">
         <v>3313</v>
@@ -72026,10 +72231,10 @@
     </row>
     <row r="749" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A749" s="33" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="B749" s="33" t="s">
-        <v>3753</v>
+        <v>3751</v>
       </c>
       <c r="C749" s="33" t="s">
         <v>1566</v>
@@ -72044,7 +72249,7 @@
         <v>727</v>
       </c>
       <c r="G749" s="33" t="s">
-        <v>3759</v>
+        <v>3757</v>
       </c>
       <c r="H749" s="33">
         <v>8890</v>
@@ -72053,7 +72258,7 @@
         <v>100</v>
       </c>
       <c r="J749" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K749" s="33" t="s">
         <v>3313</v>
@@ -72061,10 +72266,10 @@
     </row>
     <row r="750" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A750" s="33" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="B750" s="33" t="s">
-        <v>3750</v>
+        <v>3748</v>
       </c>
       <c r="C750" s="33" t="s">
         <v>1566</v>
@@ -72079,7 +72284,7 @@
         <v>727</v>
       </c>
       <c r="G750" s="33" t="s">
-        <v>3756</v>
+        <v>3754</v>
       </c>
       <c r="H750" s="33">
         <v>9301</v>
@@ -72088,7 +72293,7 @@
         <v>50</v>
       </c>
       <c r="J750" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K750" s="33" t="s">
         <v>3313</v>
@@ -72096,10 +72301,10 @@
     </row>
     <row r="751" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A751" s="33" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="B751" s="33" t="s">
-        <v>3750</v>
+        <v>3748</v>
       </c>
       <c r="C751" s="33" t="s">
         <v>1566</v>
@@ -72114,7 +72319,7 @@
         <v>727</v>
       </c>
       <c r="G751" s="33" t="s">
-        <v>3757</v>
+        <v>3755</v>
       </c>
       <c r="H751" s="33">
         <v>9375</v>
@@ -72123,7 +72328,7 @@
         <v>45</v>
       </c>
       <c r="J751" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K751" s="33" t="s">
         <v>3313</v>
@@ -72131,10 +72336,10 @@
     </row>
     <row r="752" spans="1:11" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A752" s="33" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="B752" s="33" t="s">
-        <v>3750</v>
+        <v>3748</v>
       </c>
       <c r="C752" s="33" t="s">
         <v>1566</v>
@@ -72149,7 +72354,7 @@
         <v>727</v>
       </c>
       <c r="G752" s="33" t="s">
-        <v>3758</v>
+        <v>3756</v>
       </c>
       <c r="H752" s="33">
         <v>9430</v>
@@ -72158,7 +72363,7 @@
         <v>36</v>
       </c>
       <c r="J752" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K752" s="33" t="s">
         <v>3313</v>
@@ -72166,10 +72371,10 @@
     </row>
     <row r="753" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A753" s="33" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="B753" s="33" t="s">
-        <v>3753</v>
+        <v>3751</v>
       </c>
       <c r="C753" s="33" t="s">
         <v>1566</v>
@@ -72184,7 +72389,7 @@
         <v>727</v>
       </c>
       <c r="G753" s="33" t="s">
-        <v>3761</v>
+        <v>3759</v>
       </c>
       <c r="H753" s="33">
         <v>9588</v>
@@ -72193,7 +72398,7 @@
         <v>55</v>
       </c>
       <c r="J753" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K753" s="33" t="s">
         <v>3313</v>
@@ -72201,10 +72406,10 @@
     </row>
     <row r="754" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A754" s="33" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="B754" s="33" t="s">
-        <v>3753</v>
+        <v>3751</v>
       </c>
       <c r="C754" s="33" t="s">
         <v>1566</v>
@@ -72219,7 +72424,7 @@
         <v>727</v>
       </c>
       <c r="G754" s="33" t="s">
-        <v>3760</v>
+        <v>3758</v>
       </c>
       <c r="H754" s="33">
         <v>9589</v>
@@ -72228,7 +72433,7 @@
         <v>36</v>
       </c>
       <c r="J754" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K754" s="33" t="s">
         <v>3313</v>
@@ -72236,10 +72441,10 @@
     </row>
     <row r="755" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A755" s="33" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="B755" s="33" t="s">
-        <v>3729</v>
+        <v>3727</v>
       </c>
       <c r="C755" s="33" t="s">
         <v>3361</v>
@@ -72254,7 +72459,7 @@
         <v>727</v>
       </c>
       <c r="G755" s="33" t="s">
-        <v>3733</v>
+        <v>3731</v>
       </c>
       <c r="H755" s="33">
         <v>11670</v>
@@ -72263,7 +72468,7 @@
         <v>60</v>
       </c>
       <c r="J755" s="33" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K755" s="33" t="s">
         <v>675</v>
@@ -74910,10 +75115,10 @@
     </row>
     <row r="829" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A829" s="33" t="s">
+        <v>3732</v>
+      </c>
+      <c r="B829" s="33" t="s">
         <v>3734</v>
-      </c>
-      <c r="B829" s="33" t="s">
-        <v>3736</v>
       </c>
       <c r="C829" s="33" t="s">
         <v>1566</v>
@@ -74928,7 +75133,7 @@
         <v>727</v>
       </c>
       <c r="G829" s="33" t="s">
-        <v>3740</v>
+        <v>3738</v>
       </c>
       <c r="H829" s="33">
         <v>7740</v>
@@ -74937,7 +75142,7 @@
         <v>39</v>
       </c>
       <c r="J829" s="33" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K829" s="33" t="s">
         <v>3313</v>
@@ -74945,13 +75150,13 @@
     </row>
     <row r="830" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A830" s="33" t="s">
+        <v>3732</v>
+      </c>
+      <c r="B830" s="33" t="s">
         <v>3734</v>
       </c>
-      <c r="B830" s="33" t="s">
-        <v>3736</v>
-      </c>
       <c r="C830" s="33" t="s">
-        <v>3732</v>
+        <v>3730</v>
       </c>
       <c r="D830" s="33" t="s">
         <v>805</v>
@@ -74963,7 +75168,7 @@
         <v>727</v>
       </c>
       <c r="G830" s="33" t="s">
-        <v>3738</v>
+        <v>3736</v>
       </c>
       <c r="H830" s="33">
         <v>8050</v>
@@ -74972,7 +75177,7 @@
         <v>130</v>
       </c>
       <c r="J830" s="33" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K830" s="33" t="s">
         <v>3313</v>
@@ -74980,10 +75185,10 @@
     </row>
     <row r="831" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A831" s="33" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
       <c r="B831" s="33" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
       <c r="C831" s="33" t="s">
         <v>1566</v>
@@ -74998,7 +75203,7 @@
         <v>727</v>
       </c>
       <c r="G831" s="33" t="s">
-        <v>3763</v>
+        <v>3761</v>
       </c>
       <c r="H831" s="33">
         <v>8737</v>
@@ -75007,7 +75212,7 @@
         <v>30</v>
       </c>
       <c r="J831" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K831" s="33" t="s">
         <v>3313</v>
@@ -75015,10 +75220,10 @@
     </row>
     <row r="832" spans="1:33" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A832" s="33" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
       <c r="B832" s="33" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
       <c r="C832" s="33" t="s">
         <v>1566</v>
@@ -75033,7 +75238,7 @@
         <v>727</v>
       </c>
       <c r="G832" s="33" t="s">
-        <v>3766</v>
+        <v>3764</v>
       </c>
       <c r="H832" s="33">
         <v>8824</v>
@@ -75042,7 +75247,7 @@
         <v>30</v>
       </c>
       <c r="J832" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K832" s="33" t="s">
         <v>3313</v>
@@ -75050,10 +75255,10 @@
     </row>
     <row r="833" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A833" s="33" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
       <c r="B833" s="33" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
       <c r="C833" s="33" t="s">
         <v>1566</v>
@@ -75068,7 +75273,7 @@
         <v>727</v>
       </c>
       <c r="G833" s="33" t="s">
-        <v>3764</v>
+        <v>3762</v>
       </c>
       <c r="H833" s="33">
         <v>8836</v>
@@ -75077,7 +75282,7 @@
         <v>30</v>
       </c>
       <c r="J833" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K833" s="33" t="s">
         <v>3313</v>
@@ -75085,10 +75290,10 @@
     </row>
     <row r="834" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A834" s="33" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
       <c r="B834" s="33" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
       <c r="C834" s="33" t="s">
         <v>1566</v>
@@ -75103,7 +75308,7 @@
         <v>727</v>
       </c>
       <c r="G834" s="33" t="s">
-        <v>3765</v>
+        <v>3763</v>
       </c>
       <c r="H834" s="33">
         <v>8854</v>
@@ -75112,7 +75317,7 @@
         <v>55</v>
       </c>
       <c r="J834" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K834" s="33" t="s">
         <v>3313</v>
@@ -75120,10 +75325,10 @@
     </row>
     <row r="835" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A835" s="33" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
       <c r="B835" s="33" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
       <c r="C835" s="33" t="s">
         <v>1566</v>
@@ -75138,7 +75343,7 @@
         <v>727</v>
       </c>
       <c r="G835" s="33" t="s">
-        <v>3768</v>
+        <v>3766</v>
       </c>
       <c r="H835" s="33">
         <v>8908</v>
@@ -75147,7 +75352,7 @@
         <v>34</v>
       </c>
       <c r="J835" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K835" s="33" t="s">
         <v>3313</v>
@@ -75155,10 +75360,10 @@
     </row>
     <row r="836" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A836" s="33" t="s">
+        <v>3732</v>
+      </c>
+      <c r="B836" s="33" t="s">
         <v>3734</v>
-      </c>
-      <c r="B836" s="33" t="s">
-        <v>3736</v>
       </c>
       <c r="C836" s="33" t="s">
         <v>1566</v>
@@ -75173,7 +75378,7 @@
         <v>727</v>
       </c>
       <c r="G836" s="33" t="s">
-        <v>3739</v>
+        <v>3737</v>
       </c>
       <c r="H836" s="33">
         <v>8941</v>
@@ -75182,7 +75387,7 @@
         <v>39</v>
       </c>
       <c r="J836" s="33" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="K836" s="33" t="s">
         <v>3313</v>
@@ -75190,10 +75395,10 @@
     </row>
     <row r="837" spans="1:36" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A837" s="33" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
       <c r="B837" s="33" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
       <c r="C837" s="33" t="s">
         <v>1566</v>
@@ -75208,7 +75413,7 @@
         <v>727</v>
       </c>
       <c r="G837" s="33" t="s">
-        <v>3767</v>
+        <v>3765</v>
       </c>
       <c r="H837" s="33">
         <v>8963</v>
@@ -75217,7 +75422,7 @@
         <v>35</v>
       </c>
       <c r="J837" s="33" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="K837" s="33" t="s">
         <v>3313</v>
@@ -75278,7 +75483,7 @@
         <v>5</v>
       </c>
       <c r="G839" s="33" t="s">
-        <v>3769</v>
+        <v>3767</v>
       </c>
       <c r="H839" s="33">
         <v>10950</v>
@@ -75314,7 +75519,7 @@
         <v>3054</v>
       </c>
       <c r="G840" s="33" t="s">
-        <v>3770</v>
+        <v>3768</v>
       </c>
       <c r="H840" s="33">
         <v>10980</v>
@@ -75419,7 +75624,7 @@
         <v>4</v>
       </c>
       <c r="G843" s="33" t="s">
-        <v>3771</v>
+        <v>3769</v>
       </c>
       <c r="H843" s="33">
         <v>11130</v>
@@ -75454,7 +75659,7 @@
         <v>2</v>
       </c>
       <c r="G844" s="33" t="s">
-        <v>3772</v>
+        <v>3770</v>
       </c>
       <c r="H844" s="33">
         <v>11470</v>
@@ -75489,7 +75694,7 @@
         <v>3</v>
       </c>
       <c r="G845" s="33" t="s">
-        <v>3773</v>
+        <v>3771</v>
       </c>
       <c r="H845" s="32">
         <v>11540</v>
@@ -77282,13 +77487,13 @@
     </row>
     <row r="896" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A896" s="7" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B896" s="7" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C896" s="7" t="s">
-        <v>3678</v>
+        <v>3676</v>
       </c>
       <c r="D896" s="7" t="s">
         <v>805</v>
@@ -77297,10 +77502,10 @@
         <v>1567</v>
       </c>
       <c r="F896" s="7" t="s">
-        <v>3660</v>
+        <v>3658</v>
       </c>
       <c r="G896" s="38" t="s">
-        <v>3670</v>
+        <v>3668</v>
       </c>
       <c r="H896" s="7">
         <v>9041</v>
@@ -77309,7 +77514,7 @@
         <v>47</v>
       </c>
       <c r="J896" s="7" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K896" s="7" t="s">
         <v>675</v>
@@ -77317,13 +77522,13 @@
     </row>
     <row r="897" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A897" s="7" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B897" s="7" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C897" s="7" t="s">
-        <v>3653</v>
+        <v>3651</v>
       </c>
       <c r="D897" s="7" t="s">
         <v>805</v>
@@ -77332,10 +77537,10 @@
         <v>1567</v>
       </c>
       <c r="F897" s="7" t="s">
-        <v>3659</v>
+        <v>3657</v>
       </c>
       <c r="G897" s="38" t="s">
-        <v>3669</v>
+        <v>3667</v>
       </c>
       <c r="H897" s="7">
         <v>9118</v>
@@ -77344,7 +77549,7 @@
         <v>42</v>
       </c>
       <c r="J897" s="7" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K897" s="7" t="s">
         <v>675</v>
@@ -77352,10 +77557,10 @@
     </row>
     <row r="898" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A898" s="7" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B898" s="7" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C898" s="7" t="s">
         <v>1566</v>
@@ -77367,10 +77572,10 @@
         <v>1567</v>
       </c>
       <c r="F898" s="7" t="s">
-        <v>3664</v>
+        <v>3662</v>
       </c>
       <c r="G898" s="38" t="s">
-        <v>3674</v>
+        <v>3672</v>
       </c>
       <c r="H898" s="7">
         <v>9555</v>
@@ -77379,7 +77584,7 @@
         <v>37</v>
       </c>
       <c r="J898" s="7" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K898" s="7" t="s">
         <v>675</v>
@@ -77387,13 +77592,13 @@
     </row>
     <row r="899" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A899" s="7" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B899" s="7" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C899" s="7" t="s">
-        <v>3679</v>
+        <v>3677</v>
       </c>
       <c r="D899" s="7" t="s">
         <v>805</v>
@@ -77402,10 +77607,10 @@
         <v>1567</v>
       </c>
       <c r="F899" s="7" t="s">
-        <v>3663</v>
+        <v>3661</v>
       </c>
       <c r="G899" s="38" t="s">
-        <v>3673</v>
+        <v>3671</v>
       </c>
       <c r="H899" s="7">
         <v>9650</v>
@@ -77414,7 +77619,7 @@
         <v>43</v>
       </c>
       <c r="J899" s="7" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K899" s="7" t="s">
         <v>675</v>
@@ -77422,13 +77627,13 @@
     </row>
     <row r="900" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A900" s="7" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B900" s="7" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C900" s="7" t="s">
-        <v>3678</v>
+        <v>3676</v>
       </c>
       <c r="D900" s="7" t="s">
         <v>805</v>
@@ -77437,10 +77642,10 @@
         <v>1567</v>
       </c>
       <c r="F900" s="7" t="s">
-        <v>3665</v>
+        <v>3663</v>
       </c>
       <c r="G900" s="38" t="s">
-        <v>3675</v>
+        <v>3673</v>
       </c>
       <c r="H900" s="7">
         <v>9685</v>
@@ -77449,7 +77654,7 @@
         <v>67</v>
       </c>
       <c r="J900" s="7" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K900" s="7" t="s">
         <v>675</v>
@@ -77457,13 +77662,13 @@
     </row>
     <row r="901" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A901" s="7" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B901" s="7" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C901" s="7" t="s">
-        <v>3679</v>
+        <v>3677</v>
       </c>
       <c r="D901" s="7" t="s">
         <v>805</v>
@@ -77472,10 +77677,10 @@
         <v>1567</v>
       </c>
       <c r="F901" s="7" t="s">
-        <v>3662</v>
+        <v>3660</v>
       </c>
       <c r="G901" s="38" t="s">
-        <v>3672</v>
+        <v>3670</v>
       </c>
       <c r="H901" s="7">
         <v>9728</v>
@@ -77484,7 +77689,7 @@
         <v>51</v>
       </c>
       <c r="J901" s="7" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K901" s="7" t="s">
         <v>675</v>
@@ -77492,10 +77697,10 @@
     </row>
     <row r="902" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A902" s="7" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B902" s="7" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C902" s="7" t="s">
         <v>1566</v>
@@ -77507,10 +77712,10 @@
         <v>1567</v>
       </c>
       <c r="F902" s="7" t="s">
-        <v>3666</v>
+        <v>3664</v>
       </c>
       <c r="G902" s="38" t="s">
-        <v>3676</v>
+        <v>3674</v>
       </c>
       <c r="H902" s="7">
         <v>9812</v>
@@ -77519,7 +77724,7 @@
         <v>74</v>
       </c>
       <c r="J902" s="7" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K902" s="7" t="s">
         <v>675</v>
@@ -77527,13 +77732,13 @@
     </row>
     <row r="903" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A903" s="7" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B903" s="7" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C903" s="7" t="s">
-        <v>3678</v>
+        <v>3676</v>
       </c>
       <c r="D903" s="7" t="s">
         <v>805</v>
@@ -77542,10 +77747,10 @@
         <v>1567</v>
       </c>
       <c r="F903" s="7" t="s">
-        <v>3667</v>
+        <v>3665</v>
       </c>
       <c r="G903" s="38" t="s">
-        <v>3677</v>
+        <v>3675</v>
       </c>
       <c r="H903" s="7">
         <v>9845</v>
@@ -77554,7 +77759,7 @@
         <v>55</v>
       </c>
       <c r="J903" s="7" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K903" s="7" t="s">
         <v>675</v>
@@ -77562,13 +77767,13 @@
     </row>
     <row r="904" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A904" s="7" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B904" s="7" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C904" s="7" t="s">
-        <v>3653</v>
+        <v>3651</v>
       </c>
       <c r="D904" s="7" t="s">
         <v>805</v>
@@ -77577,10 +77782,10 @@
         <v>1567</v>
       </c>
       <c r="F904" s="7" t="s">
-        <v>3658</v>
+        <v>3656</v>
       </c>
       <c r="G904" s="38" t="s">
-        <v>3668</v>
+        <v>3666</v>
       </c>
       <c r="H904" s="7">
         <v>10013</v>
@@ -77589,7 +77794,7 @@
         <v>45</v>
       </c>
       <c r="J904" s="7" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K904" s="7" t="s">
         <v>675</v>
@@ -77597,13 +77802,13 @@
     </row>
     <row r="905" spans="1:11" s="2" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A905" s="7" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B905" s="7" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="C905" s="7" t="s">
-        <v>3678</v>
+        <v>3676</v>
       </c>
       <c r="D905" s="7" t="s">
         <v>805</v>
@@ -77612,10 +77817,10 @@
         <v>1567</v>
       </c>
       <c r="F905" s="7" t="s">
-        <v>3661</v>
+        <v>3659</v>
       </c>
       <c r="G905" s="38" t="s">
-        <v>3671</v>
+        <v>3669</v>
       </c>
       <c r="H905" s="7">
         <v>10123</v>
@@ -77624,7 +77829,7 @@
         <v>57</v>
       </c>
       <c r="J905" s="7" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="K905" s="7" t="s">
         <v>675</v>

--- a/data/Table-Data-Base.xlsx
+++ b/data/Table-Data-Base.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inaki\Downloads\Pleistocene_Human_Use_Of_Caves-master\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC2169D-F0A8-40F3-BDF3-FFDCA7233F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C61BD3-8DC5-4849-96FD-140A5201E1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{493D11CC-922E-4265-992F-96F2D38DEEBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Caves" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
-    <sheet name="Datings" sheetId="4" r:id="rId3"/>
+    <sheet name="Datings" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Caves!$A$1:$Y$503</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Datings!$A$1:$K$1036</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Caves!$A$1:$Y$504</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Datings!$A$1:$K$1036</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17466" uniqueCount="3811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17444" uniqueCount="3804">
   <si>
     <t>San Antonio</t>
   </si>
@@ -13179,55 +13178,34 @@
     <t>Taçon et al., 2012, p. 139</t>
   </si>
   <si>
-    <t>wkt_geom</t>
-  </si>
-  <si>
-    <t>elevation</t>
-  </si>
-  <si>
-    <t>Dating met</t>
-  </si>
-  <si>
-    <t>Reached ap</t>
-  </si>
-  <si>
-    <t>Level of d</t>
-  </si>
-  <si>
-    <t>Discussi��</t>
-  </si>
-  <si>
-    <t>Portable A</t>
-  </si>
-  <si>
-    <t>Structures</t>
-  </si>
-  <si>
-    <t>Lithic Ind</t>
-  </si>
-  <si>
-    <t>Modified b</t>
-  </si>
-  <si>
-    <t>Ochre rema</t>
-  </si>
-  <si>
-    <t>Human Rema</t>
-  </si>
-  <si>
-    <t>Fire Remai</t>
-  </si>
-  <si>
-    <t>Half-shade</t>
-  </si>
-  <si>
-    <t>Point</t>
-  </si>
-  <si>
     <t>-1.57164900000000007</t>
   </si>
   <si>
     <t>43.26811200000000213</t>
+  </si>
+  <si>
+    <t>Rece</t>
+  </si>
+  <si>
+    <t>46.83198</t>
+  </si>
+  <si>
+    <t>22.39827</t>
+  </si>
+  <si>
+    <t>II ?</t>
+  </si>
+  <si>
+    <t>Lascu et al., 1996</t>
+  </si>
+  <si>
+    <t>Possible geological explanation / Unknown fire remains</t>
+  </si>
+  <si>
+    <t>Wunn, 2001</t>
+  </si>
+  <si>
+    <t>Final part of the gallery</t>
   </si>
 </sst>
 </file>
@@ -13396,7 +13374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13554,14 +13532,8 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13897,7 +13869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CDA5EAF-A655-4519-9C43-6E6BE0DBE4DA}">
-  <dimension ref="A1:Y503"/>
+  <dimension ref="A1:Y504"/>
   <sheetFormatPr defaultColWidth="35.77734375" defaultRowHeight="17.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45" style="4" bestFit="1" customWidth="1"/>
@@ -31344,10 +31316,10 @@
         <v>3585</v>
       </c>
       <c r="C277" s="13" t="s">
-        <v>3809</v>
+        <v>3794</v>
       </c>
       <c r="D277" s="13" t="s">
-        <v>3810</v>
+        <v>3795</v>
       </c>
       <c r="E277" s="12">
         <v>193</v>
@@ -40215,571 +40187,573 @@
     </row>
     <row r="418" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="7" t="s">
-        <v>787</v>
+        <v>3796</v>
       </c>
       <c r="B418" s="7" t="s">
-        <v>1219</v>
-      </c>
-      <c r="C418" s="44" t="s">
-        <v>759</v>
-      </c>
-      <c r="D418" s="44" t="s">
-        <v>773</v>
+        <v>3803</v>
+      </c>
+      <c r="C418" s="53" t="s">
+        <v>3798</v>
+      </c>
+      <c r="D418" s="53" t="s">
+        <v>3797</v>
       </c>
       <c r="E418" s="7">
-        <v>211</v>
+        <v>560</v>
       </c>
       <c r="F418" s="7" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="G418" s="7" t="s">
-        <v>663</v>
-      </c>
-      <c r="H418" s="7" t="s">
-        <v>1530</v>
-      </c>
-      <c r="I418" s="7" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J418" s="7" t="s">
-        <v>796</v>
+        <v>664</v>
+      </c>
+      <c r="H418" s="10" t="s">
+        <v>842</v>
+      </c>
+      <c r="I418" s="10" t="s">
+        <v>3799</v>
+      </c>
+      <c r="J418" s="10" t="s">
+        <v>3800</v>
       </c>
       <c r="K418" s="7">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="L418" s="7" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="M418" s="7" t="s">
         <v>1238</v>
       </c>
       <c r="N418" s="28" t="s">
-        <v>1367</v>
-      </c>
-      <c r="O418" s="7" t="s">
-        <v>791</v>
+        <v>3801</v>
+      </c>
+      <c r="O418" s="10" t="s">
+        <v>3802</v>
       </c>
       <c r="P418" s="7"/>
       <c r="Q418" s="7"/>
       <c r="R418" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="S418" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="T418" s="7"/>
+      <c r="S418" s="7"/>
+      <c r="T418" s="7" t="s">
+        <v>676</v>
+      </c>
       <c r="U418" s="7"/>
-      <c r="V418" s="7" t="s">
-        <v>675</v>
-      </c>
+      <c r="V418" s="7"/>
       <c r="W418" s="7"/>
-      <c r="X418" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y418" s="7" t="s">
-        <v>675</v>
-      </c>
+      <c r="X418" s="7"/>
+      <c r="Y418" s="7"/>
     </row>
     <row r="419" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="10" t="s">
+      <c r="A419" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="B419" s="7" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C419" s="44" t="s">
+        <v>759</v>
+      </c>
+      <c r="D419" s="44" t="s">
+        <v>773</v>
+      </c>
+      <c r="E419" s="7">
+        <v>211</v>
+      </c>
+      <c r="F419" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="G419" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="H419" s="7" t="s">
+        <v>1530</v>
+      </c>
+      <c r="I419" s="7" t="s">
+        <v>1227</v>
+      </c>
+      <c r="J419" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="K419" s="7">
+        <v>17</v>
+      </c>
+      <c r="L419" s="7" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M419" s="7" t="s">
+        <v>1238</v>
+      </c>
+      <c r="N419" s="28" t="s">
+        <v>1367</v>
+      </c>
+      <c r="O419" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="P419" s="7"/>
+      <c r="Q419" s="7"/>
+      <c r="R419" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="S419" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="T419" s="7"/>
+      <c r="U419" s="7"/>
+      <c r="V419" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="W419" s="7"/>
+      <c r="X419" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y419" s="7" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="420" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A420" s="10" t="s">
         <v>1450</v>
       </c>
-      <c r="B419" s="10" t="s">
+      <c r="B420" s="10" t="s">
         <v>1357</v>
       </c>
-      <c r="C419" s="45" t="s">
+      <c r="C420" s="45" t="s">
         <v>788</v>
       </c>
-      <c r="D419" s="45" t="s">
+      <c r="D420" s="45" t="s">
         <v>789</v>
       </c>
-      <c r="E419" s="10">
+      <c r="E420" s="10">
         <v>870</v>
       </c>
-      <c r="F419" s="10" t="s">
+      <c r="F420" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="G419" s="10" t="s">
+      <c r="G420" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H419" s="10" t="s">
+      <c r="H420" s="10" t="s">
         <v>1073</v>
       </c>
-      <c r="I419" s="10" t="s">
+      <c r="I420" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="J419" s="10" t="s">
+      <c r="J420" s="10" t="s">
         <v>1075</v>
       </c>
-      <c r="K419" s="10">
+      <c r="K420" s="10">
         <v>350</v>
       </c>
-      <c r="L419" s="10" t="s">
+      <c r="L420" s="10" t="s">
         <v>1377</v>
       </c>
-      <c r="M419" s="10" t="s">
+      <c r="M420" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N419" s="26" t="s">
+      <c r="N420" s="26" t="s">
         <v>1074</v>
       </c>
-      <c r="O419" s="10" t="s">
+      <c r="O420" s="10" t="s">
         <v>1076</v>
       </c>
-      <c r="P419" s="10" t="s">
+      <c r="P420" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="Q419" s="10"/>
-      <c r="R419" s="10"/>
-      <c r="S419" s="10"/>
-      <c r="T419" s="10"/>
-      <c r="U419" s="10"/>
-      <c r="V419" s="10"/>
-      <c r="W419" s="10"/>
-      <c r="X419" s="10"/>
-      <c r="Y419" s="10"/>
-    </row>
-    <row r="420" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="8" t="s">
+      <c r="Q420" s="10"/>
+      <c r="R420" s="10"/>
+      <c r="S420" s="10"/>
+      <c r="T420" s="10"/>
+      <c r="U420" s="10"/>
+      <c r="V420" s="10"/>
+      <c r="W420" s="10"/>
+      <c r="X420" s="10"/>
+      <c r="Y420" s="10"/>
+    </row>
+    <row r="421" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A421" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B420" s="8" t="s">
+      <c r="B421" s="8" t="s">
         <v>1357</v>
       </c>
-      <c r="C420" s="11" t="s">
+      <c r="C421" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="D420" s="11" t="s">
+      <c r="D421" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="E420" s="8">
+      <c r="E421" s="8">
         <v>42</v>
       </c>
-      <c r="F420" s="8" t="s">
+      <c r="F421" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="G420" s="8" t="s">
+      <c r="G421" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="H420" s="8" t="s">
+      <c r="H421" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="I420" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="J420" s="8" t="s">
+      <c r="I421" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="J421" s="8" t="s">
         <v>1167</v>
       </c>
-      <c r="K420" s="8">
+      <c r="K421" s="8">
         <v>35</v>
       </c>
-      <c r="L420" s="8" t="s">
+      <c r="L421" s="8" t="s">
         <v>1376</v>
       </c>
-      <c r="M420" s="8" t="s">
+      <c r="M421" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="N420" s="24" t="s">
+      <c r="N421" s="24" t="s">
         <v>1168</v>
       </c>
-      <c r="O420" s="8" t="s">
+      <c r="O421" s="8" t="s">
         <v>1167</v>
       </c>
-      <c r="P420" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q420" s="8"/>
-      <c r="R420" s="8"/>
-      <c r="S420" s="8"/>
-      <c r="T420" s="8"/>
-      <c r="U420" s="8"/>
-      <c r="V420" s="8"/>
-      <c r="W420" s="8"/>
-      <c r="X420" s="8"/>
-      <c r="Y420" s="8"/>
-    </row>
-    <row r="421" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="7" t="s">
+      <c r="P421" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q421" s="8"/>
+      <c r="R421" s="8"/>
+      <c r="S421" s="8"/>
+      <c r="T421" s="8"/>
+      <c r="U421" s="8"/>
+      <c r="V421" s="8"/>
+      <c r="W421" s="8"/>
+      <c r="X421" s="8"/>
+      <c r="Y421" s="8"/>
+    </row>
+    <row r="422" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A422" s="7" t="s">
         <v>1220</v>
       </c>
-      <c r="B421" s="7" t="s">
+      <c r="B422" s="7" t="s">
         <v>1221</v>
       </c>
-      <c r="C421" s="6" t="s">
+      <c r="C422" s="6" t="s">
         <v>770</v>
       </c>
-      <c r="D421" s="6" t="s">
+      <c r="D422" s="6" t="s">
         <v>784</v>
       </c>
-      <c r="E421" s="6" t="s">
+      <c r="E422" s="6" t="s">
         <v>843</v>
       </c>
-      <c r="F421" s="7" t="s">
+      <c r="F422" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="G421" s="7" t="s">
+      <c r="G422" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="H421" s="7" t="s">
+      <c r="H422" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="I421" s="7" t="s">
+      <c r="I422" s="7" t="s">
         <v>1227</v>
       </c>
-      <c r="J421" s="7" t="s">
+      <c r="J422" s="7" t="s">
         <v>844</v>
       </c>
-      <c r="K421" s="7">
+      <c r="K422" s="7">
         <v>50</v>
       </c>
-      <c r="L421" s="7" t="s">
+      <c r="L422" s="7" t="s">
         <v>1377</v>
       </c>
-      <c r="M421" s="7" t="s">
+      <c r="M422" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="N421" s="28" t="s">
+      <c r="N422" s="28" t="s">
         <v>1367</v>
       </c>
-      <c r="O421" s="7" t="s">
+      <c r="O422" s="7" t="s">
         <v>844</v>
       </c>
-      <c r="P421" s="7"/>
-      <c r="Q421" s="7"/>
-      <c r="R421" s="7"/>
-      <c r="S421" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="T421" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="U421" s="7"/>
-      <c r="V421" s="7"/>
-      <c r="W421" s="7"/>
-      <c r="X421" s="7"/>
-      <c r="Y421" s="7" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="422" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="12" t="s">
-        <v>1451</v>
-      </c>
-      <c r="B422" s="12" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C422" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="D422" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="E422" s="12">
-        <v>850</v>
-      </c>
-      <c r="F422" s="12" t="s">
-        <v>651</v>
-      </c>
-      <c r="G422" s="12" t="s">
-        <v>663</v>
-      </c>
-      <c r="H422" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="I422" s="12" t="s">
-        <v>1374</v>
-      </c>
-      <c r="J422" s="12" t="s">
-        <v>942</v>
-      </c>
-      <c r="K422" s="12">
-        <v>40</v>
-      </c>
-      <c r="L422" s="12" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M422" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N422" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O422" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P422" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q422" s="12"/>
-      <c r="R422" s="12"/>
-      <c r="S422" s="12"/>
-      <c r="T422" s="12"/>
-      <c r="U422" s="12"/>
-      <c r="V422" s="12"/>
-      <c r="W422" s="12"/>
-      <c r="X422" s="12"/>
-      <c r="Y422" s="12"/>
+      <c r="P422" s="7"/>
+      <c r="Q422" s="7"/>
+      <c r="R422" s="7"/>
+      <c r="S422" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="T422" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="U422" s="7"/>
+      <c r="V422" s="7"/>
+      <c r="W422" s="7"/>
+      <c r="X422" s="7"/>
+      <c r="Y422" s="7" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="423" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="8" t="s">
+      <c r="A423" s="12" t="s">
         <v>1451</v>
       </c>
       <c r="B423" s="12" t="s">
         <v>1346</v>
       </c>
-      <c r="C423" s="8" t="s">
+      <c r="C423" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D423" s="8" t="s">
+      <c r="D423" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="E423" s="8">
+      <c r="E423" s="12">
         <v>850</v>
       </c>
-      <c r="F423" s="8" t="s">
+      <c r="F423" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="G423" s="8" t="s">
+      <c r="G423" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H423" s="8" t="s">
+      <c r="H423" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="I423" s="8" t="s">
-        <v>1364</v>
-      </c>
-      <c r="J423" s="8" t="s">
-        <v>1077</v>
-      </c>
-      <c r="K423" s="8">
+      <c r="I423" s="12" t="s">
+        <v>1374</v>
+      </c>
+      <c r="J423" s="12" t="s">
+        <v>942</v>
+      </c>
+      <c r="K423" s="12">
         <v>40</v>
       </c>
-      <c r="L423" s="8" t="s">
+      <c r="L423" s="12" t="s">
         <v>1377</v>
       </c>
-      <c r="M423" s="8" t="s">
+      <c r="M423" s="12" t="s">
         <v>1236</v>
       </c>
-      <c r="N423" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O423" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P423" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q423" s="8"/>
-      <c r="R423" s="8"/>
-      <c r="S423" s="8"/>
-      <c r="T423" s="8"/>
-      <c r="U423" s="8"/>
-      <c r="V423" s="8"/>
-      <c r="W423" s="8"/>
-      <c r="X423" s="8"/>
-      <c r="Y423" s="8"/>
+      <c r="N423" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O423" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P423" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q423" s="12"/>
+      <c r="R423" s="12"/>
+      <c r="S423" s="12"/>
+      <c r="T423" s="12"/>
+      <c r="U423" s="12"/>
+      <c r="V423" s="12"/>
+      <c r="W423" s="12"/>
+      <c r="X423" s="12"/>
+      <c r="Y423" s="12"/>
     </row>
     <row r="424" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="8" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B424" s="8" t="s">
-        <v>1533</v>
-      </c>
-      <c r="C424" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D424" s="11" t="s">
-        <v>443</v>
+        <v>1451</v>
+      </c>
+      <c r="B424" s="12" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C424" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D424" s="8" t="s">
+        <v>487</v>
       </c>
       <c r="E424" s="8">
-        <v>652</v>
+        <v>850</v>
       </c>
       <c r="F424" s="8" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G424" s="8" t="s">
         <v>663</v>
       </c>
       <c r="H424" s="8" t="s">
-        <v>878</v>
+        <v>853</v>
       </c>
       <c r="I424" s="8" t="s">
-        <v>1026</v>
+        <v>1364</v>
       </c>
       <c r="J424" s="8" t="s">
-        <v>1170</v>
-      </c>
-      <c r="K424" s="8" t="s">
-        <v>1169</v>
+        <v>1077</v>
+      </c>
+      <c r="K424" s="8">
+        <v>40</v>
       </c>
       <c r="L424" s="8" t="s">
-        <v>1531</v>
+        <v>1377</v>
       </c>
       <c r="M424" s="8" t="s">
         <v>1236</v>
       </c>
       <c r="N424" s="24" t="s">
-        <v>1532</v>
+        <v>727</v>
       </c>
       <c r="O424" s="8" t="s">
-        <v>1171</v>
+        <v>727</v>
       </c>
       <c r="P424" s="8" t="s">
         <v>675</v>
       </c>
       <c r="Q424" s="8"/>
-      <c r="R424" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="R424" s="8"/>
       <c r="S424" s="8"/>
       <c r="T424" s="8"/>
       <c r="U424" s="8"/>
       <c r="V424" s="8"/>
-      <c r="W424" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="X424" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="W424" s="8"/>
+      <c r="X424" s="8"/>
       <c r="Y424" s="8"/>
     </row>
     <row r="425" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="3" t="s">
+      <c r="A425" s="8" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B425" s="8" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C425" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D425" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="E425" s="8">
+        <v>652</v>
+      </c>
+      <c r="F425" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="G425" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H425" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="I425" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="J425" s="8" t="s">
+        <v>1170</v>
+      </c>
+      <c r="K425" s="8" t="s">
+        <v>1169</v>
+      </c>
+      <c r="L425" s="8" t="s">
+        <v>1531</v>
+      </c>
+      <c r="M425" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N425" s="24" t="s">
+        <v>1532</v>
+      </c>
+      <c r="O425" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="P425" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q425" s="8"/>
+      <c r="R425" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="S425" s="8"/>
+      <c r="T425" s="8"/>
+      <c r="U425" s="8"/>
+      <c r="V425" s="8"/>
+      <c r="W425" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="X425" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y425" s="8"/>
+    </row>
+    <row r="426" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A426" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="B425" s="3" t="s">
+      <c r="B426" s="3" t="s">
         <v>1357</v>
       </c>
-      <c r="C425" s="3" t="s">
+      <c r="C426" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D425" s="3" t="s">
+      <c r="D426" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="E425" s="3">
+      <c r="E426" s="3">
         <v>94</v>
       </c>
-      <c r="F425" s="3" t="s">
+      <c r="F426" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="G425" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="H425" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="I425" s="8" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J425" s="8" t="s">
-        <v>883</v>
-      </c>
-      <c r="K425" s="3">
-        <v>105</v>
-      </c>
-      <c r="L425" s="3" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M425" s="3" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N425" s="29" t="s">
-        <v>727</v>
-      </c>
-      <c r="O425" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P425" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q425" s="3"/>
-      <c r="R425" s="3"/>
-      <c r="S425" s="3"/>
-      <c r="T425" s="3"/>
-      <c r="U425" s="3"/>
-      <c r="V425" s="3"/>
-      <c r="W425" s="3"/>
-      <c r="X425" s="3"/>
-      <c r="Y425" s="3"/>
-    </row>
-    <row r="426" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="B426" s="8" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C426" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="D426" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="E426" s="8">
-        <v>102</v>
-      </c>
-      <c r="F426" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="G426" s="8" t="s">
+      <c r="G426" s="3" t="s">
         <v>663</v>
       </c>
       <c r="H426" s="8" t="s">
         <v>853</v>
       </c>
       <c r="I426" s="8" t="s">
-        <v>1313</v>
+        <v>1372</v>
       </c>
       <c r="J426" s="8" t="s">
-        <v>1182</v>
-      </c>
-      <c r="K426" s="8">
-        <v>20</v>
-      </c>
-      <c r="L426" s="8" t="s">
+        <v>883</v>
+      </c>
+      <c r="K426" s="3">
+        <v>105</v>
+      </c>
+      <c r="L426" s="3" t="s">
         <v>1377</v>
       </c>
-      <c r="M426" s="8" t="s">
+      <c r="M426" s="3" t="s">
         <v>1236</v>
       </c>
-      <c r="N426" s="24" t="s">
+      <c r="N426" s="29" t="s">
         <v>727</v>
       </c>
       <c r="O426" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="P426" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q426" s="8"/>
-      <c r="R426" s="8"/>
-      <c r="S426" s="8"/>
-      <c r="T426" s="8"/>
-      <c r="U426" s="8"/>
-      <c r="V426" s="8"/>
-      <c r="W426" s="8"/>
-      <c r="X426" s="8"/>
-      <c r="Y426" s="8"/>
+      <c r="P426" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q426" s="3"/>
+      <c r="R426" s="3"/>
+      <c r="S426" s="3"/>
+      <c r="T426" s="3"/>
+      <c r="U426" s="3"/>
+      <c r="V426" s="3"/>
+      <c r="W426" s="3"/>
+      <c r="X426" s="3"/>
+      <c r="Y426" s="3"/>
     </row>
     <row r="427" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="8" t="s">
-        <v>1452</v>
+        <v>706</v>
       </c>
       <c r="B427" s="8" t="s">
         <v>1357</v>
       </c>
-      <c r="C427" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="D427" s="11" t="s">
-        <v>489</v>
+      <c r="C427" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="D427" s="8" t="s">
+        <v>613</v>
       </c>
       <c r="E427" s="8">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="F427" s="8" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G427" s="8" t="s">
         <v>663</v>
@@ -40788,13 +40762,13 @@
         <v>853</v>
       </c>
       <c r="I427" s="8" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="J427" s="8" t="s">
-        <v>1078</v>
+        <v>1182</v>
       </c>
       <c r="K427" s="8">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="L427" s="8" t="s">
         <v>1377</v>
@@ -40805,7 +40779,7 @@
       <c r="N427" s="24" t="s">
         <v>727</v>
       </c>
-      <c r="O427" s="24" t="s">
+      <c r="O427" s="8" t="s">
         <v>727</v>
       </c>
       <c r="P427" s="8" t="s">
@@ -40813,12 +40787,8 @@
       </c>
       <c r="Q427" s="8"/>
       <c r="R427" s="8"/>
-      <c r="S427" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="T427" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="S427" s="8"/>
+      <c r="T427" s="8"/>
       <c r="U427" s="8"/>
       <c r="V427" s="8"/>
       <c r="W427" s="8"/>
@@ -40827,19 +40797,19 @@
     </row>
     <row r="428" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B428" s="8" t="s">
-        <v>1454</v>
-      </c>
-      <c r="C428" s="8" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D428" s="8" t="s">
-        <v>1081</v>
+        <v>1357</v>
+      </c>
+      <c r="C428" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D428" s="11" t="s">
+        <v>489</v>
       </c>
       <c r="E428" s="8">
-        <v>249</v>
+        <v>160</v>
       </c>
       <c r="F428" s="8" t="s">
         <v>651</v>
@@ -40851,13 +40821,13 @@
         <v>853</v>
       </c>
       <c r="I428" s="8" t="s">
-        <v>1348</v>
+        <v>1314</v>
       </c>
       <c r="J428" s="8" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="K428" s="8">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="L428" s="8" t="s">
         <v>1377</v>
@@ -40868,7 +40838,7 @@
       <c r="N428" s="24" t="s">
         <v>727</v>
       </c>
-      <c r="O428" s="8" t="s">
+      <c r="O428" s="24" t="s">
         <v>727</v>
       </c>
       <c r="P428" s="8" t="s">
@@ -40876,7 +40846,9 @@
       </c>
       <c r="Q428" s="8"/>
       <c r="R428" s="8"/>
-      <c r="S428" s="8"/>
+      <c r="S428" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="T428" s="8" t="s">
         <v>675</v>
       </c>
@@ -40887,449 +40859,445 @@
       <c r="Y428" s="8"/>
     </row>
     <row r="429" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="7" t="s">
-        <v>1222</v>
-      </c>
-      <c r="B429" s="7" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C429" s="6" t="s">
-        <v>762</v>
-      </c>
-      <c r="D429" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="E429" s="6" t="s">
-        <v>818</v>
-      </c>
-      <c r="F429" s="7" t="s">
-        <v>820</v>
-      </c>
-      <c r="G429" s="7" t="s">
-        <v>821</v>
-      </c>
-      <c r="H429" s="7" t="s">
-        <v>819</v>
-      </c>
-      <c r="I429" s="7">
-        <v>0</v>
-      </c>
-      <c r="J429" s="7" t="s">
-        <v>822</v>
-      </c>
-      <c r="K429" s="7">
-        <v>60</v>
-      </c>
-      <c r="L429" s="7" t="s">
-        <v>1378</v>
-      </c>
-      <c r="M429" s="7" t="s">
-        <v>1238</v>
-      </c>
-      <c r="N429" s="28" t="s">
-        <v>1262</v>
-      </c>
-      <c r="O429" s="7" t="s">
-        <v>1261</v>
-      </c>
-      <c r="P429" s="7" t="s">
-        <v>676</v>
-      </c>
-      <c r="Q429" s="7"/>
-      <c r="R429" s="7"/>
-      <c r="S429" s="7" t="s">
-        <v>676</v>
-      </c>
-      <c r="T429" s="7" t="s">
-        <v>676</v>
-      </c>
-      <c r="U429" s="7"/>
-      <c r="V429" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="W429" s="7"/>
-      <c r="X429" s="7" t="s">
-        <v>676</v>
-      </c>
-      <c r="Y429" s="7"/>
+      <c r="A429" s="8" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B429" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C429" s="8" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D429" s="8" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E429" s="8">
+        <v>249</v>
+      </c>
+      <c r="F429" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="G429" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H429" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="I429" s="8" t="s">
+        <v>1348</v>
+      </c>
+      <c r="J429" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K429" s="8">
+        <v>81</v>
+      </c>
+      <c r="L429" s="8" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M429" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N429" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O429" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P429" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q429" s="8"/>
+      <c r="R429" s="8"/>
+      <c r="S429" s="8"/>
+      <c r="T429" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U429" s="8"/>
+      <c r="V429" s="8"/>
+      <c r="W429" s="8"/>
+      <c r="X429" s="8"/>
+      <c r="Y429" s="8"/>
     </row>
     <row r="430" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="7" t="s">
-        <v>3773</v>
+        <v>1222</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>3774</v>
+        <v>1534</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>3775</v>
+        <v>762</v>
       </c>
       <c r="D430" s="6" t="s">
-        <v>3776</v>
+        <v>776</v>
       </c>
       <c r="E430" s="6" t="s">
-        <v>3783</v>
+        <v>818</v>
       </c>
       <c r="F430" s="7" t="s">
-        <v>725</v>
+        <v>820</v>
       </c>
       <c r="G430" s="7" t="s">
-        <v>726</v>
+        <v>821</v>
       </c>
       <c r="H430" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="I430" s="7" t="s">
-        <v>1318</v>
+        <v>819</v>
+      </c>
+      <c r="I430" s="7">
+        <v>0</v>
       </c>
       <c r="J430" s="7" t="s">
-        <v>3777</v>
+        <v>822</v>
       </c>
       <c r="K430" s="7">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="L430" s="7" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="M430" s="7" t="s">
         <v>1238</v>
       </c>
       <c r="N430" s="28" t="s">
-        <v>1367</v>
+        <v>1262</v>
       </c>
       <c r="O430" s="7" t="s">
-        <v>3777</v>
+        <v>1261</v>
       </c>
       <c r="P430" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q430" s="7" t="s">
-        <v>675</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="Q430" s="7"/>
       <c r="R430" s="7"/>
       <c r="S430" s="7" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="T430" s="7" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U430" s="7"/>
-      <c r="V430" s="7"/>
+      <c r="V430" s="7" t="s">
+        <v>675</v>
+      </c>
       <c r="W430" s="7"/>
       <c r="X430" s="7" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Y430" s="7"/>
     </row>
     <row r="431" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A431" s="12" t="s">
+      <c r="A431" s="7" t="s">
+        <v>3773</v>
+      </c>
+      <c r="B431" s="7" t="s">
+        <v>3774</v>
+      </c>
+      <c r="C431" s="6" t="s">
+        <v>3775</v>
+      </c>
+      <c r="D431" s="6" t="s">
+        <v>3776</v>
+      </c>
+      <c r="E431" s="6" t="s">
+        <v>3783</v>
+      </c>
+      <c r="F431" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="G431" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="H431" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="I431" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J431" s="7" t="s">
+        <v>3777</v>
+      </c>
+      <c r="K431" s="7">
+        <v>7</v>
+      </c>
+      <c r="L431" s="7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="M431" s="7" t="s">
+        <v>1238</v>
+      </c>
+      <c r="N431" s="28" t="s">
+        <v>1367</v>
+      </c>
+      <c r="O431" s="7" t="s">
+        <v>3777</v>
+      </c>
+      <c r="P431" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q431" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="R431" s="7"/>
+      <c r="S431" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="T431" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="U431" s="7"/>
+      <c r="V431" s="7"/>
+      <c r="W431" s="7"/>
+      <c r="X431" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y431" s="7"/>
+    </row>
+    <row r="432" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A432" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B431" s="12" t="s">
+      <c r="B432" s="12" t="s">
         <v>1346</v>
       </c>
-      <c r="C431" s="12" t="s">
+      <c r="C432" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="D431" s="12" t="s">
+      <c r="D432" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="E431" s="12">
+      <c r="E432" s="12">
         <v>145</v>
       </c>
-      <c r="F431" s="12" t="s">
+      <c r="F432" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="G431" s="12" t="s">
+      <c r="G432" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H431" s="12" t="s">
+      <c r="H432" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="I431" s="12" t="s">
+      <c r="I432" s="12" t="s">
         <v>1322</v>
       </c>
-      <c r="J431" s="12" t="s">
+      <c r="J432" s="12" t="s">
         <v>1011</v>
       </c>
-      <c r="K431" s="12">
+      <c r="K432" s="12">
         <v>130</v>
       </c>
-      <c r="L431" s="12" t="s">
+      <c r="L432" s="12" t="s">
         <v>1377</v>
       </c>
-      <c r="M431" s="12" t="s">
+      <c r="M432" s="12" t="s">
         <v>1236</v>
       </c>
-      <c r="N431" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O431" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P431" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q431" s="12"/>
-      <c r="R431" s="12"/>
-      <c r="S431" s="12"/>
-      <c r="T431" s="12"/>
-      <c r="U431" s="12"/>
-      <c r="V431" s="12"/>
-      <c r="W431" s="12"/>
-      <c r="X431" s="12"/>
-      <c r="Y431" s="12"/>
-    </row>
-    <row r="432" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A432" s="7" t="s">
+      <c r="N432" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O432" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P432" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q432" s="12"/>
+      <c r="R432" s="12"/>
+      <c r="S432" s="12"/>
+      <c r="T432" s="12"/>
+      <c r="U432" s="12"/>
+      <c r="V432" s="12"/>
+      <c r="W432" s="12"/>
+      <c r="X432" s="12"/>
+      <c r="Y432" s="12"/>
+    </row>
+    <row r="433" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A433" s="7" t="s">
         <v>1484</v>
       </c>
-      <c r="B432" s="7" t="s">
+      <c r="B433" s="7" t="s">
         <v>1211</v>
       </c>
-      <c r="C432" s="6" t="s">
+      <c r="C433" s="6" t="s">
         <v>760</v>
       </c>
-      <c r="D432" s="6" t="s">
+      <c r="D433" s="6" t="s">
         <v>774</v>
       </c>
-      <c r="E432" s="6" t="s">
+      <c r="E433" s="6" t="s">
         <v>812</v>
       </c>
-      <c r="F432" s="7" t="s">
+      <c r="F433" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="G432" s="7" t="s">
+      <c r="G433" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="H432" s="7" t="s">
+      <c r="H433" s="7" t="s">
         <v>813</v>
       </c>
-      <c r="I432" s="7" t="s">
+      <c r="I433" s="7" t="s">
         <v>1227</v>
       </c>
-      <c r="J432" s="7" t="s">
+      <c r="J433" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="K432" s="7">
+      <c r="K433" s="7">
         <v>17</v>
       </c>
-      <c r="L432" s="7" t="s">
+      <c r="L433" s="7" t="s">
         <v>1380</v>
       </c>
-      <c r="M432" s="7" t="s">
+      <c r="M433" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="N432" s="28" t="s">
+      <c r="N433" s="28" t="s">
         <v>1367</v>
       </c>
-      <c r="O432" s="7" t="s">
+      <c r="O433" s="7" t="s">
         <v>815</v>
       </c>
-      <c r="P432" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q432" s="7" t="s">
+      <c r="P433" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q433" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="R432" s="7"/>
-      <c r="S432" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="T432" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="U432" s="7"/>
-      <c r="V432" s="7"/>
-      <c r="W432" s="7"/>
-      <c r="X432" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y432" s="7" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="433" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A433" s="8" t="s">
+      <c r="R433" s="7"/>
+      <c r="S433" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="T433" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="U433" s="7"/>
+      <c r="V433" s="7"/>
+      <c r="W433" s="7"/>
+      <c r="X433" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y433" s="7" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="434" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A434" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B433" s="8" t="s">
+      <c r="B434" s="8" t="s">
         <v>1357</v>
       </c>
-      <c r="C433" s="8" t="s">
+      <c r="C434" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="D433" s="8" t="s">
+      <c r="D434" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="E433" s="8">
+      <c r="E434" s="8">
         <v>151</v>
       </c>
-      <c r="F433" s="8" t="s">
+      <c r="F434" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="G433" s="8" t="s">
+      <c r="G434" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="H433" s="8" t="s">
+      <c r="H434" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="I433" s="8" t="s">
+      <c r="I434" s="8" t="s">
         <v>1314</v>
       </c>
-      <c r="J433" s="8" t="s">
+      <c r="J434" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="K433" s="8">
+      <c r="K434" s="8">
         <v>40</v>
       </c>
-      <c r="L433" s="8" t="s">
+      <c r="L434" s="8" t="s">
         <v>1380</v>
       </c>
-      <c r="M433" s="8" t="s">
+      <c r="M434" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="N433" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O433" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P433" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q433" s="8"/>
-      <c r="R433" s="8"/>
-      <c r="S433" s="8"/>
-      <c r="T433" s="8"/>
-      <c r="U433" s="8"/>
-      <c r="V433" s="8"/>
-      <c r="W433" s="8"/>
-      <c r="X433" s="8"/>
-      <c r="Y433" s="8"/>
-    </row>
-    <row r="434" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A434" s="10" t="s">
+      <c r="N434" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O434" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P434" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q434" s="8"/>
+      <c r="R434" s="8"/>
+      <c r="S434" s="8"/>
+      <c r="T434" s="8"/>
+      <c r="U434" s="8"/>
+      <c r="V434" s="8"/>
+      <c r="W434" s="8"/>
+      <c r="X434" s="8"/>
+      <c r="Y434" s="8"/>
+    </row>
+    <row r="435" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A435" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B434" s="10" t="s">
+      <c r="B435" s="10" t="s">
         <v>1357</v>
       </c>
-      <c r="C434" s="9" t="s">
+      <c r="C435" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="D434" s="9" t="s">
+      <c r="D435" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="E434" s="9">
+      <c r="E435" s="9">
         <v>106</v>
       </c>
-      <c r="F434" s="10" t="s">
+      <c r="F435" s="10" t="s">
         <v>662</v>
       </c>
-      <c r="G434" s="10" t="s">
+      <c r="G435" s="10" t="s">
         <v>664</v>
       </c>
-      <c r="H434" s="10" t="s">
+      <c r="H435" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="I434" s="10" t="s">
+      <c r="I435" s="10" t="s">
         <v>1535</v>
       </c>
-      <c r="J434" s="10" t="s">
+      <c r="J435" s="10" t="s">
         <v>865</v>
       </c>
-      <c r="K434" s="10">
+      <c r="K435" s="10">
         <v>46</v>
       </c>
-      <c r="L434" s="10" t="s">
+      <c r="L435" s="10" t="s">
         <v>1380</v>
       </c>
-      <c r="M434" s="10" t="s">
+      <c r="M435" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N434" s="26" t="s">
+      <c r="N435" s="26" t="s">
         <v>866</v>
       </c>
-      <c r="O434" s="10" t="s">
+      <c r="O435" s="10" t="s">
         <v>865</v>
       </c>
-      <c r="P434" s="10" t="s">
+      <c r="P435" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="Q434" s="10"/>
-      <c r="R434" s="10"/>
-      <c r="S434" s="10"/>
-      <c r="T434" s="10"/>
-      <c r="U434" s="10"/>
-      <c r="V434" s="10"/>
-      <c r="W434" s="10"/>
-      <c r="X434" s="10"/>
-      <c r="Y434" s="10"/>
-    </row>
-    <row r="435" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A435" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B435" s="8" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C435" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D435" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="E435" s="11">
-        <v>106</v>
-      </c>
-      <c r="F435" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="G435" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="H435" s="8" t="s">
-        <v>878</v>
-      </c>
-      <c r="I435" s="8" t="s">
-        <v>1319</v>
-      </c>
-      <c r="J435" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="K435" s="8">
-        <v>46</v>
-      </c>
-      <c r="L435" s="8" t="s">
-        <v>1380</v>
-      </c>
-      <c r="M435" s="8" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N435" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O435" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P435" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q435" s="8"/>
-      <c r="R435" s="8"/>
-      <c r="S435" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="T435" s="8"/>
-      <c r="U435" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="V435" s="8"/>
-      <c r="W435" s="8"/>
-      <c r="X435" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y435" s="8"/>
+      <c r="Q435" s="10"/>
+      <c r="R435" s="10"/>
+      <c r="S435" s="10"/>
+      <c r="T435" s="10"/>
+      <c r="U435" s="10"/>
+      <c r="V435" s="10"/>
+      <c r="W435" s="10"/>
+      <c r="X435" s="10"/>
+      <c r="Y435" s="10"/>
     </row>
     <row r="436" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="8" t="s">
@@ -41357,7 +41325,7 @@
         <v>878</v>
       </c>
       <c r="I436" s="8" t="s">
-        <v>675</v>
+        <v>1319</v>
       </c>
       <c r="J436" s="8" t="s">
         <v>865</v>
@@ -41378,7 +41346,7 @@
         <v>727</v>
       </c>
       <c r="P436" s="8" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="Q436" s="8"/>
       <c r="R436" s="8"/>
@@ -41397,102 +41365,108 @@
       <c r="Y436" s="8"/>
     </row>
     <row r="437" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A437" s="3" t="s">
+      <c r="A437" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B437" s="8" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C437" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D437" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="E437" s="11">
+        <v>106</v>
+      </c>
+      <c r="F437" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="G437" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="H437" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="I437" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="J437" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="K437" s="8">
+        <v>46</v>
+      </c>
+      <c r="L437" s="8" t="s">
+        <v>1380</v>
+      </c>
+      <c r="M437" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N437" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O437" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P437" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="Q437" s="8"/>
+      <c r="R437" s="8"/>
+      <c r="S437" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="T437" s="8"/>
+      <c r="U437" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="V437" s="8"/>
+      <c r="W437" s="8"/>
+      <c r="X437" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y437" s="8"/>
+    </row>
+    <row r="438" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A438" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B437" s="3" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C437" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D437" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="E437" s="3">
-        <v>346</v>
-      </c>
-      <c r="F437" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="G437" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="H437" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="I437" s="8" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J437" s="8" t="s">
-        <v>875</v>
-      </c>
-      <c r="K437" s="3">
-        <v>95</v>
-      </c>
-      <c r="L437" s="3" t="s">
-        <v>1376</v>
-      </c>
-      <c r="M437" s="3" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N437" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O437" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P437" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q437" s="3"/>
-      <c r="R437" s="3"/>
-      <c r="S437" s="3"/>
-      <c r="T437" s="3"/>
-      <c r="U437" s="3"/>
-      <c r="V437" s="3"/>
-      <c r="W437" s="3"/>
-      <c r="X437" s="3"/>
-      <c r="Y437" s="3"/>
-    </row>
-    <row r="438" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A438" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>1357</v>
       </c>
-      <c r="C438" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="D438" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="E438" s="8">
-        <v>225</v>
-      </c>
-      <c r="F438" s="8" t="s">
+      <c r="C438" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D438" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="E438" s="3">
+        <v>346</v>
+      </c>
+      <c r="F438" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="G438" s="8" t="s">
+      <c r="G438" s="3" t="s">
         <v>663</v>
       </c>
       <c r="H438" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="I438" s="12" t="s">
-        <v>1364</v>
+      <c r="I438" s="8" t="s">
+        <v>1372</v>
       </c>
       <c r="J438" s="8" t="s">
-        <v>908</v>
-      </c>
-      <c r="K438" s="8">
-        <v>1200</v>
-      </c>
-      <c r="L438" s="8" t="s">
-        <v>1379</v>
-      </c>
-      <c r="M438" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="K438" s="3">
+        <v>95</v>
+      </c>
+      <c r="L438" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M438" s="3" t="s">
         <v>1236</v>
       </c>
       <c r="N438" s="24" t="s">
@@ -41501,25 +41475,25 @@
       <c r="O438" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="P438" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q438" s="8"/>
-      <c r="R438" s="8"/>
-      <c r="S438" s="8"/>
-      <c r="T438" s="8"/>
-      <c r="U438" s="8"/>
-      <c r="V438" s="8"/>
-      <c r="W438" s="8"/>
-      <c r="X438" s="8"/>
-      <c r="Y438" s="8"/>
+      <c r="P438" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q438" s="3"/>
+      <c r="R438" s="3"/>
+      <c r="S438" s="3"/>
+      <c r="T438" s="3"/>
+      <c r="U438" s="3"/>
+      <c r="V438" s="3"/>
+      <c r="W438" s="3"/>
+      <c r="X438" s="3"/>
+      <c r="Y438" s="3"/>
     </row>
     <row r="439" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="8" t="s">
         <v>36</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>3429</v>
+        <v>1357</v>
       </c>
       <c r="C439" s="11" t="s">
         <v>202</v>
@@ -41537,19 +41511,19 @@
         <v>663</v>
       </c>
       <c r="H439" s="8" t="s">
-        <v>805</v>
+        <v>853</v>
       </c>
       <c r="I439" s="12" t="s">
-        <v>3313</v>
+        <v>1364</v>
       </c>
       <c r="J439" s="8" t="s">
-        <v>3415</v>
+        <v>908</v>
       </c>
       <c r="K439" s="8">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="L439" s="8" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="M439" s="8" t="s">
         <v>1236</v>
@@ -41561,20 +41535,16 @@
         <v>727</v>
       </c>
       <c r="P439" s="8" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="Q439" s="8"/>
       <c r="R439" s="8"/>
-      <c r="S439" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="S439" s="8"/>
       <c r="T439" s="8"/>
       <c r="U439" s="8"/>
       <c r="V439" s="8"/>
       <c r="W439" s="8"/>
-      <c r="X439" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="X439" s="8"/>
       <c r="Y439" s="8"/>
     </row>
     <row r="440" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -41603,7 +41573,7 @@
         <v>805</v>
       </c>
       <c r="I440" s="12" t="s">
-        <v>3338</v>
+        <v>3313</v>
       </c>
       <c r="J440" s="8" t="s">
         <v>3415</v>
@@ -41642,19 +41612,19 @@
     </row>
     <row r="441" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="8" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C441" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="D441" s="8" t="s">
-        <v>622</v>
+        <v>3429</v>
+      </c>
+      <c r="C441" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D441" s="11" t="s">
+        <v>454</v>
       </c>
       <c r="E441" s="8">
-        <v>580</v>
+        <v>225</v>
       </c>
       <c r="F441" s="8" t="s">
         <v>655</v>
@@ -41663,19 +41633,19 @@
         <v>663</v>
       </c>
       <c r="H441" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="I441" s="8" t="s">
-        <v>1319</v>
+        <v>805</v>
+      </c>
+      <c r="I441" s="12" t="s">
+        <v>3338</v>
       </c>
       <c r="J441" s="8" t="s">
-        <v>1183</v>
+        <v>3415</v>
       </c>
       <c r="K441" s="8">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="L441" s="8" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="M441" s="8" t="s">
         <v>1236</v>
@@ -41687,51 +41657,55 @@
         <v>727</v>
       </c>
       <c r="P441" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Q441" s="8"/>
       <c r="R441" s="8"/>
-      <c r="S441" s="8"/>
+      <c r="S441" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="T441" s="8"/>
       <c r="U441" s="8"/>
       <c r="V441" s="8"/>
       <c r="W441" s="8"/>
-      <c r="X441" s="8"/>
+      <c r="X441" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="Y441" s="8"/>
     </row>
     <row r="442" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="8" t="s">
-        <v>3652</v>
+        <v>127</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>3655</v>
-      </c>
-      <c r="C442" s="11" t="s">
-        <v>3653</v>
-      </c>
-      <c r="D442" s="11" t="s">
-        <v>3654</v>
+        <v>1357</v>
+      </c>
+      <c r="C442" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D442" s="8" t="s">
+        <v>622</v>
       </c>
       <c r="E442" s="8">
-        <v>10</v>
+        <v>580</v>
       </c>
       <c r="F442" s="8" t="s">
-        <v>3612</v>
+        <v>655</v>
       </c>
       <c r="G442" s="8" t="s">
-        <v>3613</v>
+        <v>663</v>
       </c>
       <c r="H442" s="8" t="s">
-        <v>805</v>
+        <v>853</v>
       </c>
       <c r="I442" s="8" t="s">
-        <v>675</v>
+        <v>1319</v>
       </c>
       <c r="J442" s="8" t="s">
-        <v>3614</v>
+        <v>1183</v>
       </c>
       <c r="K442" s="8">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="L442" s="8" t="s">
         <v>1376</v>
@@ -41742,59 +41716,55 @@
       <c r="N442" s="24" t="s">
         <v>727</v>
       </c>
-      <c r="O442" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="P442" s="8"/>
+      <c r="O442" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P442" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="Q442" s="8"/>
-      <c r="R442" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="R442" s="8"/>
       <c r="S442" s="8"/>
       <c r="T442" s="8"/>
-      <c r="U442" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="U442" s="8"/>
       <c r="V442" s="8"/>
       <c r="W442" s="8"/>
-      <c r="X442" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="X442" s="8"/>
       <c r="Y442" s="8"/>
     </row>
     <row r="443" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="8" t="s">
-        <v>58</v>
+        <v>3652</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>1357</v>
+        <v>3655</v>
       </c>
       <c r="C443" s="11" t="s">
-        <v>241</v>
+        <v>3653</v>
       </c>
       <c r="D443" s="11" t="s">
-        <v>493</v>
+        <v>3654</v>
       </c>
       <c r="E443" s="8">
-        <v>450</v>
+        <v>10</v>
       </c>
       <c r="F443" s="8" t="s">
-        <v>655</v>
+        <v>3612</v>
       </c>
       <c r="G443" s="8" t="s">
-        <v>663</v>
+        <v>3613</v>
       </c>
       <c r="H443" s="8" t="s">
-        <v>853</v>
+        <v>805</v>
       </c>
       <c r="I443" s="8" t="s">
-        <v>1319</v>
+        <v>675</v>
       </c>
       <c r="J443" s="8" t="s">
-        <v>864</v>
+        <v>3614</v>
       </c>
       <c r="K443" s="8">
-        <v>35</v>
+        <v>650</v>
       </c>
       <c r="L443" s="8" t="s">
         <v>1376</v>
@@ -41805,14 +41775,14 @@
       <c r="N443" s="24" t="s">
         <v>727</v>
       </c>
-      <c r="O443" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P443" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="O443" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="P443" s="8"/>
       <c r="Q443" s="8"/>
-      <c r="R443" s="8"/>
+      <c r="R443" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="S443" s="8"/>
       <c r="T443" s="8"/>
       <c r="U443" s="8" t="s">
@@ -41820,69 +41790,71 @@
       </c>
       <c r="V443" s="8"/>
       <c r="W443" s="8"/>
-      <c r="X443" s="8"/>
+      <c r="X443" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="Y443" s="8"/>
     </row>
     <row r="444" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A444" s="14" t="s">
-        <v>723</v>
-      </c>
-      <c r="B444" s="14" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C444" s="15" t="s">
-        <v>376</v>
-      </c>
-      <c r="D444" s="15" t="s">
-        <v>628</v>
-      </c>
-      <c r="E444" s="14">
-        <v>94</v>
-      </c>
-      <c r="F444" s="14" t="s">
+      <c r="A444" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B444" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C444" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D444" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="E444" s="8">
+        <v>450</v>
+      </c>
+      <c r="F444" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="G444" s="14" t="s">
+      <c r="G444" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="H444" s="14" t="s">
+      <c r="H444" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="I444" s="14" t="s">
-        <v>1323</v>
-      </c>
-      <c r="J444" s="14" t="s">
-        <v>1012</v>
-      </c>
-      <c r="K444" s="14">
-        <v>10</v>
-      </c>
-      <c r="L444" s="14" t="s">
-        <v>1380</v>
-      </c>
-      <c r="M444" s="14" t="s">
-        <v>1238</v>
-      </c>
-      <c r="N444" s="27" t="s">
-        <v>1367</v>
-      </c>
-      <c r="O444" s="14" t="s">
-        <v>727</v>
-      </c>
-      <c r="P444" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q444" s="14"/>
-      <c r="R444" s="14"/>
-      <c r="S444" s="14"/>
-      <c r="T444" s="14"/>
-      <c r="U444" s="14"/>
-      <c r="V444" s="14"/>
-      <c r="W444" s="14"/>
-      <c r="X444" s="14"/>
-      <c r="Y444" s="14" t="s">
-        <v>675</v>
-      </c>
+      <c r="I444" s="8" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J444" s="8" t="s">
+        <v>864</v>
+      </c>
+      <c r="K444" s="8">
+        <v>35</v>
+      </c>
+      <c r="L444" s="8" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M444" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N444" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O444" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P444" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q444" s="8"/>
+      <c r="R444" s="8"/>
+      <c r="S444" s="8"/>
+      <c r="T444" s="8"/>
+      <c r="U444" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="V444" s="8"/>
+      <c r="W444" s="8"/>
+      <c r="X444" s="8"/>
+      <c r="Y444" s="8"/>
     </row>
     <row r="445" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="14" t="s">
@@ -41910,7 +41882,7 @@
         <v>853</v>
       </c>
       <c r="I445" s="14" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
       <c r="J445" s="14" t="s">
         <v>1012</v>
@@ -41927,7 +41899,7 @@
       <c r="N445" s="27" t="s">
         <v>1367</v>
       </c>
-      <c r="O445" s="27" t="s">
+      <c r="O445" s="14" t="s">
         <v>727</v>
       </c>
       <c r="P445" s="14" t="s">
@@ -41946,599 +41918,599 @@
       </c>
     </row>
     <row r="446" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A446" s="8" t="s">
+      <c r="A446" s="14" t="s">
+        <v>723</v>
+      </c>
+      <c r="B446" s="14" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C446" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="D446" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="E446" s="14">
+        <v>94</v>
+      </c>
+      <c r="F446" s="14" t="s">
+        <v>655</v>
+      </c>
+      <c r="G446" s="14" t="s">
+        <v>663</v>
+      </c>
+      <c r="H446" s="14" t="s">
+        <v>853</v>
+      </c>
+      <c r="I446" s="14" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J446" s="14" t="s">
+        <v>1012</v>
+      </c>
+      <c r="K446" s="14">
+        <v>10</v>
+      </c>
+      <c r="L446" s="14" t="s">
+        <v>1380</v>
+      </c>
+      <c r="M446" s="14" t="s">
+        <v>1238</v>
+      </c>
+      <c r="N446" s="27" t="s">
+        <v>1367</v>
+      </c>
+      <c r="O446" s="27" t="s">
+        <v>727</v>
+      </c>
+      <c r="P446" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q446" s="14"/>
+      <c r="R446" s="14"/>
+      <c r="S446" s="14"/>
+      <c r="T446" s="14"/>
+      <c r="U446" s="14"/>
+      <c r="V446" s="14"/>
+      <c r="W446" s="14"/>
+      <c r="X446" s="14"/>
+      <c r="Y446" s="14" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="447" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A447" s="8" t="s">
         <v>1146</v>
       </c>
-      <c r="B446" s="8" t="s">
+      <c r="B447" s="8" t="s">
         <v>1357</v>
       </c>
-      <c r="C446" s="8" t="s">
+      <c r="C447" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="D446" s="8" t="s">
+      <c r="D447" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="E446" s="8">
+      <c r="E447" s="8">
         <v>135</v>
       </c>
-      <c r="F446" s="8" t="s">
+      <c r="F447" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="G446" s="8" t="s">
+      <c r="G447" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="H446" s="8" t="s">
+      <c r="H447" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="I446" s="12" t="s">
+      <c r="I447" s="12" t="s">
         <v>1364</v>
       </c>
-      <c r="J446" s="8" t="s">
+      <c r="J447" s="8" t="s">
         <v>959</v>
       </c>
-      <c r="K446" s="8">
+      <c r="K447" s="8">
         <v>60</v>
       </c>
-      <c r="L446" s="8" t="s">
+      <c r="L447" s="8" t="s">
         <v>1376</v>
       </c>
-      <c r="M446" s="8" t="s">
+      <c r="M447" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="N446" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O446" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="P446" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q446" s="8"/>
-      <c r="R446" s="8"/>
-      <c r="S446" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="T446" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="U446" s="8"/>
-      <c r="V446" s="8"/>
-      <c r="W446" s="8"/>
-      <c r="X446" s="8"/>
-      <c r="Y446" s="8"/>
-    </row>
-    <row r="447" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A447" s="7" t="s">
+      <c r="N447" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O447" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="P447" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q447" s="8"/>
+      <c r="R447" s="8"/>
+      <c r="S447" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="T447" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U447" s="8"/>
+      <c r="V447" s="8"/>
+      <c r="W447" s="8"/>
+      <c r="X447" s="8"/>
+      <c r="Y447" s="8"/>
+    </row>
+    <row r="448" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A448" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="B447" s="7" t="s">
+      <c r="B448" s="7" t="s">
         <v>3501</v>
       </c>
-      <c r="C447" s="7" t="s">
+      <c r="C448" s="7" t="s">
         <v>737</v>
       </c>
-      <c r="D447" s="7" t="s">
+      <c r="D448" s="7" t="s">
         <v>738</v>
       </c>
-      <c r="E447" s="7">
+      <c r="E448" s="7">
         <v>99</v>
       </c>
-      <c r="F447" s="7" t="s">
+      <c r="F448" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="G447" s="7" t="s">
+      <c r="G448" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="H447" s="7" t="s">
+      <c r="H448" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="I447" s="7" t="s">
+      <c r="I448" s="7" t="s">
         <v>1227</v>
       </c>
-      <c r="J447" s="7" t="s">
+      <c r="J448" s="7" t="s">
         <v>810</v>
       </c>
-      <c r="K447" s="7">
+      <c r="K448" s="7">
         <v>500</v>
       </c>
-      <c r="L447" s="7" t="s">
+      <c r="L448" s="7" t="s">
         <v>1377</v>
       </c>
-      <c r="M447" s="7" t="s">
+      <c r="M448" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="N447" s="28" t="s">
+      <c r="N448" s="28" t="s">
         <v>1551</v>
       </c>
-      <c r="O447" s="28" t="s">
-        <v>727</v>
-      </c>
-      <c r="P447" s="7"/>
-      <c r="Q447" s="7"/>
-      <c r="R447" s="7"/>
-      <c r="S447" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="T447" s="7" t="s">
+      <c r="O448" s="28" t="s">
+        <v>727</v>
+      </c>
+      <c r="P448" s="7"/>
+      <c r="Q448" s="7"/>
+      <c r="R448" s="7"/>
+      <c r="S448" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="T448" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="U447" s="7"/>
-      <c r="V447" s="7"/>
-      <c r="W447" s="7"/>
-      <c r="X447" s="7"/>
-      <c r="Y447" s="7"/>
-    </row>
-    <row r="448" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A448" s="12" t="s">
+      <c r="U448" s="7"/>
+      <c r="V448" s="7"/>
+      <c r="W448" s="7"/>
+      <c r="X448" s="7"/>
+      <c r="Y448" s="7"/>
+    </row>
+    <row r="449" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A449" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="B448" s="12" t="s">
+      <c r="B449" s="12" t="s">
         <v>3500</v>
       </c>
-      <c r="C448" s="12" t="s">
+      <c r="C449" s="12" t="s">
         <v>737</v>
       </c>
-      <c r="D448" s="12" t="s">
+      <c r="D449" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="E448" s="12">
+      <c r="E449" s="12">
         <v>99</v>
       </c>
-      <c r="F448" s="12" t="s">
+      <c r="F449" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="G448" s="12" t="s">
+      <c r="G449" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H448" s="12" t="s">
-        <v>805</v>
-      </c>
-      <c r="I448" s="12" t="s">
+      <c r="H449" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="I449" s="12" t="s">
         <v>1322</v>
       </c>
-      <c r="J448" s="12" t="s">
+      <c r="J449" s="12" t="s">
         <v>810</v>
       </c>
-      <c r="K448" s="12">
+      <c r="K449" s="12">
         <v>500</v>
       </c>
-      <c r="L448" s="12" t="s">
+      <c r="L449" s="12" t="s">
         <v>1377</v>
       </c>
-      <c r="M448" s="12" t="s">
+      <c r="M449" s="12" t="s">
         <v>1236</v>
       </c>
-      <c r="N448" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O448" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="P448" s="12" t="s">
+      <c r="N449" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O449" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="P449" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="Q448" s="12"/>
-      <c r="R448" s="12"/>
-      <c r="S448" s="12" t="s">
+      <c r="Q449" s="12"/>
+      <c r="R449" s="12"/>
+      <c r="S449" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="T448" s="12" t="s">
+      <c r="T449" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="U448" s="12" t="s">
+      <c r="U449" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="V448" s="12"/>
-      <c r="W448" s="12"/>
-      <c r="X448" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y448" s="12"/>
-    </row>
-    <row r="449" spans="1:25" s="21" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A449" s="50" t="s">
+      <c r="V449" s="12"/>
+      <c r="W449" s="12"/>
+      <c r="X449" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y449" s="12"/>
+    </row>
+    <row r="450" spans="1:25" s="21" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A450" s="50" t="s">
         <v>736</v>
       </c>
-      <c r="B449" s="50" t="s">
+      <c r="B450" s="50" t="s">
         <v>3498</v>
       </c>
-      <c r="C449" s="50" t="s">
+      <c r="C450" s="50" t="s">
         <v>737</v>
       </c>
-      <c r="D449" s="50" t="s">
+      <c r="D450" s="50" t="s">
         <v>738</v>
       </c>
-      <c r="E449" s="50">
+      <c r="E450" s="50">
         <v>99</v>
       </c>
-      <c r="F449" s="50" t="s">
+      <c r="F450" s="50" t="s">
         <v>655</v>
       </c>
-      <c r="G449" s="50" t="s">
+      <c r="G450" s="50" t="s">
         <v>663</v>
       </c>
-      <c r="H449" s="50" t="s">
+      <c r="H450" s="50" t="s">
         <v>744</v>
       </c>
-      <c r="I449" s="50" t="s">
+      <c r="I450" s="50" t="s">
         <v>3553</v>
       </c>
-      <c r="J449" s="50" t="s">
+      <c r="J450" s="50" t="s">
         <v>3554</v>
       </c>
-      <c r="K449" s="50">
+      <c r="K450" s="50">
         <v>2200</v>
       </c>
-      <c r="L449" s="50" t="s">
+      <c r="L450" s="50" t="s">
         <v>1378</v>
       </c>
-      <c r="M449" s="7" t="s">
+      <c r="M450" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="N449" s="51" t="s">
+      <c r="N450" s="51" t="s">
         <v>1509</v>
       </c>
-      <c r="O449" s="51" t="s">
+      <c r="O450" s="51" t="s">
         <v>3554</v>
       </c>
-      <c r="P449" s="50"/>
-      <c r="Q449" s="50"/>
-      <c r="R449" s="50" t="s">
-        <v>675</v>
-      </c>
-      <c r="S449" s="50"/>
-      <c r="T449" s="50"/>
-      <c r="U449" s="50"/>
-      <c r="V449" s="50"/>
-      <c r="W449" s="50" t="s">
+      <c r="P450" s="50"/>
+      <c r="Q450" s="50"/>
+      <c r="R450" s="50" t="s">
+        <v>675</v>
+      </c>
+      <c r="S450" s="50"/>
+      <c r="T450" s="50"/>
+      <c r="U450" s="50"/>
+      <c r="V450" s="50"/>
+      <c r="W450" s="50" t="s">
         <v>676</v>
       </c>
-      <c r="X449" s="50" t="s">
+      <c r="X450" s="50" t="s">
         <v>676</v>
       </c>
-      <c r="Y449" s="50"/>
-    </row>
-    <row r="450" spans="1:25" s="21" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A450" s="19" t="s">
+      <c r="Y450" s="50"/>
+    </row>
+    <row r="451" spans="1:25" s="21" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A451" s="19" t="s">
         <v>736</v>
       </c>
-      <c r="B450" s="19" t="s">
+      <c r="B451" s="19" t="s">
         <v>3498</v>
       </c>
-      <c r="C450" s="19" t="s">
+      <c r="C451" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="D450" s="19" t="s">
+      <c r="D451" s="19" t="s">
         <v>738</v>
       </c>
-      <c r="E450" s="19">
+      <c r="E451" s="19">
         <v>99</v>
       </c>
-      <c r="F450" s="19" t="s">
+      <c r="F451" s="19" t="s">
         <v>655</v>
       </c>
-      <c r="G450" s="19" t="s">
+      <c r="G451" s="19" t="s">
         <v>663</v>
       </c>
-      <c r="H450" s="19" t="s">
+      <c r="H451" s="19" t="s">
         <v>744</v>
       </c>
-      <c r="I450" s="19" t="s">
+      <c r="I451" s="19" t="s">
         <v>3338</v>
       </c>
-      <c r="J450" s="19" t="s">
+      <c r="J451" s="19" t="s">
         <v>3499</v>
       </c>
-      <c r="K450" s="19">
+      <c r="K451" s="19">
         <v>2200</v>
       </c>
-      <c r="L450" s="19" t="s">
+      <c r="L451" s="19" t="s">
         <v>1378</v>
       </c>
-      <c r="M450" s="19" t="s">
+      <c r="M451" s="19" t="s">
         <v>1236</v>
       </c>
-      <c r="N450" s="49" t="s">
-        <v>727</v>
-      </c>
-      <c r="O450" s="49" t="s">
-        <v>727</v>
-      </c>
-      <c r="P450" s="19"/>
-      <c r="Q450" s="19"/>
-      <c r="R450" s="19" t="s">
-        <v>675</v>
-      </c>
-      <c r="S450" s="19"/>
-      <c r="T450" s="19"/>
-      <c r="U450" s="19"/>
-      <c r="V450" s="19"/>
-      <c r="W450" s="19" t="s">
+      <c r="N451" s="49" t="s">
+        <v>727</v>
+      </c>
+      <c r="O451" s="49" t="s">
+        <v>727</v>
+      </c>
+      <c r="P451" s="19"/>
+      <c r="Q451" s="19"/>
+      <c r="R451" s="19" t="s">
+        <v>675</v>
+      </c>
+      <c r="S451" s="19"/>
+      <c r="T451" s="19"/>
+      <c r="U451" s="19"/>
+      <c r="V451" s="19"/>
+      <c r="W451" s="19" t="s">
         <v>676</v>
       </c>
-      <c r="X450" s="19" t="s">
+      <c r="X451" s="19" t="s">
         <v>676</v>
       </c>
-      <c r="Y450" s="19"/>
-    </row>
-    <row r="451" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A451" s="12" t="s">
+      <c r="Y451" s="19"/>
+    </row>
+    <row r="452" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A452" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B451" s="12" t="s">
+      <c r="B452" s="12" t="s">
         <v>1346</v>
       </c>
-      <c r="C451" s="12" t="s">
+      <c r="C452" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="D451" s="12" t="s">
+      <c r="D452" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="E451" s="12">
+      <c r="E452" s="12">
         <v>450</v>
       </c>
-      <c r="F451" s="12" t="s">
+      <c r="F452" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="G451" s="12" t="s">
+      <c r="G452" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H451" s="12" t="s">
+      <c r="H452" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="I451" s="12" t="s">
+      <c r="I452" s="12" t="s">
         <v>1322</v>
       </c>
-      <c r="J451" s="12" t="s">
+      <c r="J452" s="12" t="s">
         <v>1013</v>
       </c>
-      <c r="K451" s="12">
+      <c r="K452" s="12">
         <v>165</v>
       </c>
-      <c r="L451" s="12" t="s">
+      <c r="L452" s="12" t="s">
         <v>1377</v>
       </c>
-      <c r="M451" s="12" t="s">
+      <c r="M452" s="12" t="s">
         <v>1236</v>
       </c>
-      <c r="N451" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O451" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P451" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q451" s="12"/>
-      <c r="R451" s="12"/>
-      <c r="S451" s="12"/>
-      <c r="T451" s="12" t="s">
+      <c r="N452" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O452" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P452" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q452" s="12"/>
+      <c r="R452" s="12"/>
+      <c r="S452" s="12"/>
+      <c r="T452" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="U451" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="V451" s="12"/>
-      <c r="W451" s="12"/>
-      <c r="X451" s="12" t="s">
+      <c r="U452" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="V452" s="12"/>
+      <c r="W452" s="12"/>
+      <c r="X452" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="Y451" s="12"/>
-    </row>
-    <row r="452" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A452" s="10" t="s">
+      <c r="Y452" s="12"/>
+    </row>
+    <row r="453" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A453" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B452" s="10" t="s">
+      <c r="B453" s="10" t="s">
         <v>1357</v>
       </c>
-      <c r="C452" s="9" t="s">
+      <c r="C453" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D452" s="9" t="s">
+      <c r="D453" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="E452" s="10">
+      <c r="E453" s="10">
         <v>61</v>
       </c>
-      <c r="F452" s="10" t="s">
+      <c r="F453" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="G452" s="10" t="s">
+      <c r="G453" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H452" s="10" t="s">
+      <c r="H453" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="I452" s="10" t="s">
+      <c r="I453" s="10" t="s">
         <v>1348</v>
       </c>
-      <c r="J452" s="10" t="s">
+      <c r="J453" s="10" t="s">
         <v>1184</v>
       </c>
-      <c r="K452" s="10">
+      <c r="K453" s="10">
         <v>100</v>
       </c>
-      <c r="L452" s="10" t="s">
+      <c r="L453" s="10" t="s">
         <v>1377</v>
       </c>
-      <c r="M452" s="10" t="s">
+      <c r="M453" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N452" s="26" t="s">
+      <c r="N453" s="26" t="s">
         <v>1185</v>
       </c>
-      <c r="O452" s="10" t="s">
-        <v>727</v>
-      </c>
-      <c r="P452" s="10" t="s">
+      <c r="O453" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="P453" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="Q452" s="10"/>
-      <c r="R452" s="10"/>
-      <c r="S452" s="10"/>
-      <c r="T452" s="10"/>
-      <c r="U452" s="10"/>
-      <c r="V452" s="10"/>
-      <c r="W452" s="10"/>
-      <c r="X452" s="10"/>
-      <c r="Y452" s="10"/>
-    </row>
-    <row r="453" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="14" t="s">
+      <c r="Q453" s="10"/>
+      <c r="R453" s="10"/>
+      <c r="S453" s="10"/>
+      <c r="T453" s="10"/>
+      <c r="U453" s="10"/>
+      <c r="V453" s="10"/>
+      <c r="W453" s="10"/>
+      <c r="X453" s="10"/>
+      <c r="Y453" s="10"/>
+    </row>
+    <row r="454" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A454" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B453" s="14" t="s">
+      <c r="B454" s="14" t="s">
         <v>1357</v>
       </c>
-      <c r="C453" s="15" t="s">
+      <c r="C454" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="D453" s="15" t="s">
+      <c r="D454" s="15" t="s">
         <v>609</v>
       </c>
-      <c r="E453" s="14">
+      <c r="E454" s="14">
         <v>287</v>
       </c>
-      <c r="F453" s="14" t="s">
+      <c r="F454" s="14" t="s">
         <v>686</v>
       </c>
-      <c r="G453" s="14" t="s">
+      <c r="G454" s="14" t="s">
         <v>664</v>
       </c>
-      <c r="H453" s="14" t="s">
+      <c r="H454" s="14" t="s">
         <v>853</v>
       </c>
-      <c r="I453" s="10" t="s">
+      <c r="I454" s="10" t="s">
         <v>1434</v>
       </c>
-      <c r="J453" s="14" t="s">
+      <c r="J454" s="14" t="s">
         <v>1187</v>
       </c>
-      <c r="K453" s="14">
+      <c r="K454" s="14">
         <v>30</v>
       </c>
-      <c r="L453" s="14" t="s">
+      <c r="L454" s="14" t="s">
         <v>1377</v>
       </c>
-      <c r="M453" s="14" t="s">
+      <c r="M454" s="14" t="s">
         <v>1238</v>
       </c>
-      <c r="N453" s="27" t="s">
+      <c r="N454" s="27" t="s">
         <v>1186</v>
       </c>
-      <c r="O453" s="10" t="s">
-        <v>727</v>
-      </c>
-      <c r="P453" s="14" t="s">
+      <c r="O454" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="P454" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="Q453" s="14"/>
-      <c r="R453" s="14"/>
-      <c r="S453" s="14"/>
-      <c r="T453" s="14"/>
-      <c r="U453" s="14"/>
-      <c r="V453" s="14"/>
-      <c r="W453" s="14"/>
-      <c r="X453" s="14"/>
-      <c r="Y453" s="14"/>
-    </row>
-    <row r="454" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A454" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B454" s="12" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C454" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D454" s="16" t="s">
-        <v>491</v>
-      </c>
-      <c r="E454" s="16">
-        <v>20</v>
-      </c>
-      <c r="F454" s="16" t="s">
-        <v>651</v>
-      </c>
-      <c r="G454" s="16" t="s">
-        <v>663</v>
-      </c>
-      <c r="H454" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="I454" s="12" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J454" s="12" t="s">
-        <v>1014</v>
-      </c>
-      <c r="K454" s="12">
-        <v>175</v>
-      </c>
-      <c r="L454" s="12" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M454" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N454" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O454" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P454" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q454" s="12"/>
-      <c r="R454" s="12" t="s">
-        <v>676</v>
-      </c>
-      <c r="S454" s="12"/>
-      <c r="T454" s="12"/>
-      <c r="U454" s="12"/>
-      <c r="V454" s="12"/>
-      <c r="W454" s="12"/>
-      <c r="X454" s="12"/>
-      <c r="Y454" s="12"/>
+      <c r="Q454" s="14"/>
+      <c r="R454" s="14"/>
+      <c r="S454" s="14"/>
+      <c r="T454" s="14"/>
+      <c r="U454" s="14"/>
+      <c r="V454" s="14"/>
+      <c r="W454" s="14"/>
+      <c r="X454" s="14"/>
+      <c r="Y454" s="14"/>
     </row>
     <row r="455" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="12" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="B455" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="C455" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="D455" s="13" t="s">
-        <v>557</v>
-      </c>
-      <c r="E455" s="13">
-        <v>70</v>
-      </c>
-      <c r="F455" s="12" t="s">
+      <c r="C455" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D455" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="E455" s="16">
+        <v>20</v>
+      </c>
+      <c r="F455" s="16" t="s">
         <v>651</v>
       </c>
-      <c r="G455" s="12" t="s">
+      <c r="G455" s="16" t="s">
         <v>663</v>
       </c>
       <c r="H455" s="12" t="s">
         <v>853</v>
       </c>
       <c r="I455" s="12" t="s">
-        <v>1536</v>
+        <v>1372</v>
       </c>
       <c r="J455" s="12" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="K455" s="12">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="L455" s="12" t="s">
         <v>1377</v>
@@ -42547,16 +42519,18 @@
         <v>1236</v>
       </c>
       <c r="N455" s="25" t="s">
-        <v>1189</v>
+        <v>727</v>
       </c>
       <c r="O455" s="12" t="s">
-        <v>1015</v>
+        <v>727</v>
       </c>
       <c r="P455" s="12" t="s">
         <v>675</v>
       </c>
       <c r="Q455" s="12"/>
-      <c r="R455" s="12"/>
+      <c r="R455" s="12" t="s">
+        <v>676</v>
+      </c>
       <c r="S455" s="12"/>
       <c r="T455" s="12"/>
       <c r="U455" s="12"/>
@@ -42567,19 +42541,19 @@
     </row>
     <row r="456" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="12" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="B456" s="12" t="s">
         <v>1357</v>
       </c>
       <c r="C456" s="13" t="s">
-        <v>164</v>
+        <v>305</v>
       </c>
       <c r="D456" s="13" t="s">
-        <v>416</v>
-      </c>
-      <c r="E456" s="12">
-        <v>150</v>
+        <v>557</v>
+      </c>
+      <c r="E456" s="13">
+        <v>70</v>
       </c>
       <c r="F456" s="12" t="s">
         <v>651</v>
@@ -42591,25 +42565,25 @@
         <v>853</v>
       </c>
       <c r="I456" s="12" t="s">
-        <v>1433</v>
+        <v>1536</v>
       </c>
       <c r="J456" s="12" t="s">
-        <v>1190</v>
+        <v>1016</v>
       </c>
       <c r="K456" s="12">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L456" s="12" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="M456" s="12" t="s">
         <v>1236</v>
       </c>
       <c r="N456" s="25" t="s">
-        <v>727</v>
+        <v>1189</v>
       </c>
       <c r="O456" s="12" t="s">
-        <v>727</v>
+        <v>1015</v>
       </c>
       <c r="P456" s="12" t="s">
         <v>675</v>
@@ -42617,37 +42591,31 @@
       <c r="Q456" s="12"/>
       <c r="R456" s="12"/>
       <c r="S456" s="12"/>
-      <c r="T456" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="U456" s="12" t="s">
-        <v>676</v>
-      </c>
+      <c r="T456" s="12"/>
+      <c r="U456" s="12"/>
       <c r="V456" s="12"/>
       <c r="W456" s="12"/>
-      <c r="X456" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="X456" s="12"/>
       <c r="Y456" s="12"/>
     </row>
     <row r="457" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="12" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B457" s="12" t="s">
         <v>1357</v>
       </c>
       <c r="C457" s="13" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="D457" s="13" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="E457" s="12">
-        <v>295</v>
+        <v>150</v>
       </c>
       <c r="F457" s="12" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G457" s="12" t="s">
         <v>663</v>
@@ -42655,17 +42623,17 @@
       <c r="H457" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="I457" s="8" t="s">
-        <v>1319</v>
+      <c r="I457" s="12" t="s">
+        <v>1433</v>
       </c>
       <c r="J457" s="12" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K457" s="12">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="L457" s="12" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="M457" s="12" t="s">
         <v>1236</v>
@@ -42681,343 +42649,345 @@
       </c>
       <c r="Q457" s="12"/>
       <c r="R457" s="12"/>
-      <c r="S457" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="T457" s="12"/>
-      <c r="U457" s="12"/>
+      <c r="S457" s="12"/>
+      <c r="T457" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="U457" s="12" t="s">
+        <v>676</v>
+      </c>
       <c r="V457" s="12"/>
       <c r="W457" s="12"/>
       <c r="X457" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="Y457" s="12"/>
     </row>
     <row r="458" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A458" s="8" t="s">
-        <v>131</v>
+      <c r="A458" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="B458" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="C458" s="8" t="s">
+      <c r="C458" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="D458" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="E458" s="12">
+        <v>295</v>
+      </c>
+      <c r="F458" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="G458" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="H458" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="I458" s="8" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J458" s="12" t="s">
+        <v>1191</v>
+      </c>
+      <c r="K458" s="12">
+        <v>30</v>
+      </c>
+      <c r="L458" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M458" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N458" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O458" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P458" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q458" s="12"/>
+      <c r="R458" s="12"/>
+      <c r="S458" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="T458" s="12"/>
+      <c r="U458" s="12"/>
+      <c r="V458" s="12"/>
+      <c r="W458" s="12"/>
+      <c r="X458" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="Y458" s="12"/>
+    </row>
+    <row r="459" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A459" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B459" s="12" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C459" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="D458" s="8" t="s">
+      <c r="D459" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="E458" s="8">
+      <c r="E459" s="8">
         <v>364</v>
       </c>
-      <c r="F458" s="8" t="s">
+      <c r="F459" s="8" t="s">
         <v>724</v>
       </c>
-      <c r="G458" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="H458" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="I458" s="8" t="s">
-        <v>1364</v>
-      </c>
-      <c r="J458" s="8" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K458" s="8">
-        <v>120</v>
-      </c>
-      <c r="L458" s="8" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M458" s="8" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N458" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O458" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P458" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q458" s="8"/>
-      <c r="R458" s="8"/>
-      <c r="S458" s="8"/>
-      <c r="T458" s="8"/>
-      <c r="U458" s="8"/>
-      <c r="V458" s="8"/>
-      <c r="W458" s="8"/>
-      <c r="X458" s="8"/>
-      <c r="Y458" s="8"/>
-    </row>
-    <row r="459" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A459" s="3" t="s">
-        <v>1455</v>
-      </c>
-      <c r="B459" s="3" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C459" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D459" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="E459" s="3">
-        <v>170</v>
-      </c>
-      <c r="F459" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="G459" s="3" t="s">
+      <c r="G459" s="8" t="s">
         <v>663</v>
       </c>
       <c r="H459" s="8" t="s">
         <v>853</v>
       </c>
       <c r="I459" s="8" t="s">
+        <v>1364</v>
+      </c>
+      <c r="J459" s="8" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K459" s="8">
+        <v>120</v>
+      </c>
+      <c r="L459" s="8" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M459" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N459" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O459" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P459" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q459" s="8"/>
+      <c r="R459" s="8"/>
+      <c r="S459" s="8"/>
+      <c r="T459" s="8"/>
+      <c r="U459" s="8"/>
+      <c r="V459" s="8"/>
+      <c r="W459" s="8"/>
+      <c r="X459" s="8"/>
+      <c r="Y459" s="8"/>
+    </row>
+    <row r="460" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A460" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B460" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D460" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="E460" s="3">
+        <v>170</v>
+      </c>
+      <c r="F460" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="G460" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="H460" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="I460" s="8" t="s">
         <v>1372</v>
       </c>
-      <c r="J459" s="8" t="s">
+      <c r="J460" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="K459" s="3">
+      <c r="K460" s="3">
         <v>400</v>
       </c>
-      <c r="L459" s="3" t="s">
+      <c r="L460" s="3" t="s">
         <v>1376</v>
       </c>
-      <c r="M459" s="3" t="s">
+      <c r="M460" s="3" t="s">
         <v>1236</v>
       </c>
-      <c r="N459" s="29" t="s">
-        <v>727</v>
-      </c>
-      <c r="O459" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P459" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q459" s="3"/>
-      <c r="R459" s="3"/>
-      <c r="S459" s="3"/>
-      <c r="T459" s="3"/>
-      <c r="U459" s="3"/>
-      <c r="V459" s="3"/>
-      <c r="W459" s="3"/>
-      <c r="X459" s="3"/>
-      <c r="Y459" s="3"/>
-    </row>
-    <row r="460" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A460" s="7" t="s">
+      <c r="N460" s="29" t="s">
+        <v>727</v>
+      </c>
+      <c r="O460" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P460" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q460" s="3"/>
+      <c r="R460" s="3"/>
+      <c r="S460" s="3"/>
+      <c r="T460" s="3"/>
+      <c r="U460" s="3"/>
+      <c r="V460" s="3"/>
+      <c r="W460" s="3"/>
+      <c r="X460" s="3"/>
+      <c r="Y460" s="3"/>
+    </row>
+    <row r="461" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A461" s="7" t="s">
         <v>3779</v>
       </c>
-      <c r="B460" s="7" t="s">
+      <c r="B461" s="7" t="s">
         <v>3780</v>
       </c>
-      <c r="C460" s="7" t="s">
+      <c r="C461" s="7" t="s">
         <v>3781</v>
       </c>
-      <c r="D460" s="7" t="s">
+      <c r="D461" s="7" t="s">
         <v>3782</v>
       </c>
-      <c r="E460" s="7">
+      <c r="E461" s="7">
         <v>885</v>
       </c>
-      <c r="F460" s="7" t="s">
+      <c r="F461" s="7" t="s">
         <v>651</v>
       </c>
-      <c r="G460" s="7" t="s">
+      <c r="G461" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="H460" s="10" t="s">
+      <c r="H461" s="10" t="s">
         <v>3784</v>
       </c>
-      <c r="I460" s="10" t="s">
+      <c r="I461" s="10" t="s">
         <v>1226</v>
       </c>
-      <c r="J460" s="10" t="s">
+      <c r="J461" s="10" t="s">
         <v>3785</v>
       </c>
-      <c r="K460" s="7">
+      <c r="K461" s="7">
         <v>70</v>
       </c>
-      <c r="L460" s="7" t="s">
+      <c r="L461" s="7" t="s">
         <v>1377</v>
       </c>
-      <c r="M460" s="7" t="s">
+      <c r="M461" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="N460" s="28" t="s">
+      <c r="N461" s="28" t="s">
         <v>1252</v>
       </c>
-      <c r="O460" s="10" t="s">
+      <c r="O461" s="10" t="s">
         <v>3786</v>
       </c>
-      <c r="P460" s="7"/>
-      <c r="Q460" s="7"/>
-      <c r="R460" s="7"/>
-      <c r="S460" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="T460" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="U460" s="7"/>
-      <c r="V460" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="W460" s="7"/>
-      <c r="X460" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y460" s="7" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="461" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A461" s="3" t="s">
+      <c r="P461" s="7"/>
+      <c r="Q461" s="7"/>
+      <c r="R461" s="7"/>
+      <c r="S461" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="T461" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="U461" s="7"/>
+      <c r="V461" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="W461" s="7"/>
+      <c r="X461" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y461" s="7" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="462" spans="1:25" s="1" customFormat="1" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A462" s="3" t="s">
         <v>3779</v>
       </c>
-      <c r="B461" s="3" t="s">
+      <c r="B462" s="3" t="s">
         <v>3787</v>
       </c>
-      <c r="C461" s="3" t="s">
+      <c r="C462" s="3" t="s">
         <v>3781</v>
       </c>
-      <c r="D461" s="3" t="s">
+      <c r="D462" s="3" t="s">
         <v>3782</v>
       </c>
-      <c r="E461" s="3">
+      <c r="E462" s="3">
         <v>885</v>
       </c>
-      <c r="F461" s="3" t="s">
+      <c r="F462" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="G461" s="3" t="s">
+      <c r="G462" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="H461" s="8" t="s">
+      <c r="H462" s="8" t="s">
         <v>3784</v>
       </c>
-      <c r="I461" s="8" t="s">
+      <c r="I462" s="8" t="s">
         <v>3788</v>
       </c>
-      <c r="J461" s="8" t="s">
+      <c r="J462" s="8" t="s">
         <v>3789</v>
       </c>
-      <c r="K461" s="3">
+      <c r="K462" s="3">
         <v>20</v>
       </c>
-      <c r="L461" s="3" t="s">
+      <c r="L462" s="3" t="s">
         <v>1377</v>
       </c>
-      <c r="M461" s="3" t="s">
+      <c r="M462" s="3" t="s">
         <v>1236</v>
       </c>
-      <c r="N461" s="29" t="s">
-        <v>727</v>
-      </c>
-      <c r="O461" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P461" s="3" t="s">
+      <c r="N462" s="29" t="s">
+        <v>727</v>
+      </c>
+      <c r="O462" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P462" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="Q461" s="3"/>
-      <c r="R461" s="3"/>
-      <c r="S461" s="3"/>
-      <c r="T461" s="3"/>
-      <c r="U461" s="3"/>
-      <c r="V461" s="3"/>
-      <c r="W461" s="3"/>
-      <c r="X461" s="3"/>
-      <c r="Y461" s="3"/>
-    </row>
-    <row r="462" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A462" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B462" s="12" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C462" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D462" s="11" t="s">
-        <v>430</v>
-      </c>
-      <c r="E462" s="8">
-        <v>795</v>
-      </c>
-      <c r="F462" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="G462" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="H462" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="I462" s="8" t="s">
-        <v>1319</v>
-      </c>
-      <c r="J462" s="12" t="s">
-        <v>1191</v>
-      </c>
-      <c r="K462" s="8">
-        <v>60</v>
-      </c>
-      <c r="L462" s="8" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M462" s="8" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N462" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O462" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P462" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q462" s="8"/>
-      <c r="R462" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="S462" s="8"/>
-      <c r="T462" s="8"/>
-      <c r="U462" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="V462" s="8"/>
-      <c r="W462" s="8"/>
-      <c r="X462" s="8"/>
-      <c r="Y462" s="8"/>
+      <c r="Q462" s="3"/>
+      <c r="R462" s="3"/>
+      <c r="S462" s="3"/>
+      <c r="T462" s="3"/>
+      <c r="U462" s="3"/>
+      <c r="V462" s="3"/>
+      <c r="W462" s="3"/>
+      <c r="X462" s="3"/>
+      <c r="Y462" s="3"/>
     </row>
     <row r="463" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="8" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="B463" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="C463" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="D463" s="8" t="s">
-        <v>549</v>
+      <c r="C463" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D463" s="11" t="s">
+        <v>430</v>
       </c>
       <c r="E463" s="8">
-        <v>185</v>
+        <v>795</v>
       </c>
       <c r="F463" s="8" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G463" s="8" t="s">
         <v>663</v>
@@ -43026,16 +42996,16 @@
         <v>853</v>
       </c>
       <c r="I463" s="8" t="s">
-        <v>1314</v>
-      </c>
-      <c r="J463" s="8" t="s">
-        <v>1192</v>
+        <v>1319</v>
+      </c>
+      <c r="J463" s="12" t="s">
+        <v>1191</v>
       </c>
       <c r="K463" s="8">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L463" s="8" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="M463" s="8" t="s">
         <v>1236</v>
@@ -43050,7 +43020,9 @@
         <v>675</v>
       </c>
       <c r="Q463" s="8"/>
-      <c r="R463" s="8"/>
+      <c r="R463" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="S463" s="8"/>
       <c r="T463" s="8"/>
       <c r="U463" s="8" t="s">
@@ -43063,19 +43035,19 @@
     </row>
     <row r="464" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="8" t="s">
-        <v>1539</v>
-      </c>
-      <c r="B464" s="8" t="s">
-        <v>1346</v>
+        <v>82</v>
+      </c>
+      <c r="B464" s="12" t="s">
+        <v>1357</v>
       </c>
       <c r="C464" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D464" s="8" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E464" s="8">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="F464" s="8" t="s">
         <v>651</v>
@@ -43087,16 +43059,16 @@
         <v>853</v>
       </c>
       <c r="I464" s="8" t="s">
-        <v>1522</v>
+        <v>1314</v>
       </c>
       <c r="J464" s="8" t="s">
-        <v>1154</v>
+        <v>1192</v>
       </c>
       <c r="K464" s="8">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L464" s="8" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="M464" s="8" t="s">
         <v>1236</v>
@@ -43104,7 +43076,7 @@
       <c r="N464" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="O464" s="25" t="s">
+      <c r="O464" s="12" t="s">
         <v>727</v>
       </c>
       <c r="P464" s="8" t="s">
@@ -43114,293 +43086,287 @@
       <c r="R464" s="8"/>
       <c r="S464" s="8"/>
       <c r="T464" s="8"/>
-      <c r="U464" s="8"/>
+      <c r="U464" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="V464" s="8"/>
       <c r="W464" s="8"/>
       <c r="X464" s="8"/>
       <c r="Y464" s="8"/>
     </row>
     <row r="465" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A465" s="10" t="s">
+      <c r="A465" s="8" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B465" s="8" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C465" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D465" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="E465" s="8">
+        <v>209</v>
+      </c>
+      <c r="F465" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="G465" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H465" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="I465" s="8" t="s">
+        <v>1522</v>
+      </c>
+      <c r="J465" s="8" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K465" s="8">
+        <v>100</v>
+      </c>
+      <c r="L465" s="8" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M465" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N465" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O465" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="P465" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q465" s="8"/>
+      <c r="R465" s="8"/>
+      <c r="S465" s="8"/>
+      <c r="T465" s="8"/>
+      <c r="U465" s="8"/>
+      <c r="V465" s="8"/>
+      <c r="W465" s="8"/>
+      <c r="X465" s="8"/>
+      <c r="Y465" s="8"/>
+    </row>
+    <row r="466" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A466" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B465" s="14" t="s">
+      <c r="B466" s="14" t="s">
         <v>1357</v>
       </c>
-      <c r="C465" s="10" t="s">
+      <c r="C466" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D465" s="10" t="s">
+      <c r="D466" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="E465" s="10">
+      <c r="E466" s="10">
         <v>219</v>
       </c>
-      <c r="F465" s="10" t="s">
+      <c r="F466" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="G465" s="10" t="s">
+      <c r="G466" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H465" s="10" t="s">
+      <c r="H466" s="10" t="s">
         <v>878</v>
       </c>
-      <c r="I465" s="10" t="s">
+      <c r="I466" s="10" t="s">
         <v>1472</v>
       </c>
-      <c r="J465" s="10" t="s">
+      <c r="J466" s="10" t="s">
         <v>1154</v>
       </c>
-      <c r="K465" s="10">
+      <c r="K466" s="10">
         <v>130</v>
       </c>
-      <c r="L465" s="10" t="s">
+      <c r="L466" s="10" t="s">
         <v>1379</v>
       </c>
-      <c r="M465" s="10" t="s">
+      <c r="M466" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N465" s="27" t="s">
+      <c r="N466" s="27" t="s">
         <v>1537</v>
       </c>
-      <c r="O465" s="27" t="s">
-        <v>727</v>
-      </c>
-      <c r="P465" s="10" t="s">
+      <c r="O466" s="27" t="s">
+        <v>727</v>
+      </c>
+      <c r="P466" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="Q465" s="10"/>
-      <c r="R465" s="10"/>
-      <c r="S465" s="10"/>
-      <c r="T465" s="10"/>
-      <c r="U465" s="10"/>
-      <c r="V465" s="10"/>
-      <c r="W465" s="10"/>
-      <c r="X465" s="10"/>
-      <c r="Y465" s="10"/>
-    </row>
-    <row r="466" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A466" s="8" t="s">
+      <c r="Q466" s="10"/>
+      <c r="R466" s="10"/>
+      <c r="S466" s="10"/>
+      <c r="T466" s="10"/>
+      <c r="U466" s="10"/>
+      <c r="V466" s="10"/>
+      <c r="W466" s="10"/>
+      <c r="X466" s="10"/>
+      <c r="Y466" s="10"/>
+    </row>
+    <row r="467" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A467" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B466" s="12" t="s">
+      <c r="B467" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="C466" s="8" t="s">
+      <c r="C467" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D466" s="8" t="s">
+      <c r="D467" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="E466" s="8">
+      <c r="E467" s="8">
         <v>219</v>
       </c>
-      <c r="F466" s="8" t="s">
+      <c r="F467" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="G466" s="8" t="s">
+      <c r="G467" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="H466" s="8" t="s">
+      <c r="H467" s="8" t="s">
         <v>878</v>
       </c>
-      <c r="I466" s="8" t="s">
+      <c r="I467" s="8" t="s">
         <v>3313</v>
       </c>
-      <c r="J466" s="8" t="s">
+      <c r="J467" s="8" t="s">
         <v>1154</v>
       </c>
-      <c r="K466" s="8">
+      <c r="K467" s="8">
         <v>130</v>
       </c>
-      <c r="L466" s="8" t="s">
+      <c r="L467" s="8" t="s">
         <v>1379</v>
       </c>
-      <c r="M466" s="8" t="s">
+      <c r="M467" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="N466" s="25" t="s">
+      <c r="N467" s="25" t="s">
         <v>1537</v>
       </c>
-      <c r="O466" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="P466" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q466" s="8"/>
-      <c r="R466" s="8"/>
-      <c r="S466" s="8"/>
-      <c r="T466" s="8"/>
-      <c r="U466" s="8"/>
-      <c r="V466" s="8"/>
-      <c r="W466" s="8"/>
-      <c r="X466" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y466" s="8"/>
-    </row>
-    <row r="467" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A467" s="10" t="s">
+      <c r="O467" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="P467" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q467" s="8"/>
+      <c r="R467" s="8"/>
+      <c r="S467" s="8"/>
+      <c r="T467" s="8"/>
+      <c r="U467" s="8"/>
+      <c r="V467" s="8"/>
+      <c r="W467" s="8"/>
+      <c r="X467" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y467" s="8"/>
+    </row>
+    <row r="468" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A468" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B467" s="14" t="s">
+      <c r="B468" s="14" t="s">
         <v>1357</v>
       </c>
-      <c r="C467" s="10" t="s">
+      <c r="C468" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="D467" s="10" t="s">
+      <c r="D468" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="E467" s="10">
+      <c r="E468" s="10">
         <v>126</v>
       </c>
-      <c r="F467" s="10" t="s">
+      <c r="F468" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="G467" s="10" t="s">
+      <c r="G468" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H467" s="10" t="s">
+      <c r="H468" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="I467" s="10" t="s">
+      <c r="I468" s="10" t="s">
         <v>1314</v>
       </c>
-      <c r="J467" s="10" t="s">
+      <c r="J468" s="10" t="s">
         <v>1050</v>
       </c>
-      <c r="K467" s="10">
+      <c r="K468" s="10">
         <v>20</v>
       </c>
-      <c r="L467" s="10" t="s">
+      <c r="L468" s="10" t="s">
         <v>1377</v>
       </c>
-      <c r="M467" s="10" t="s">
+      <c r="M468" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N467" s="26" t="s">
+      <c r="N468" s="26" t="s">
         <v>1367</v>
       </c>
-      <c r="O467" s="26" t="s">
-        <v>727</v>
-      </c>
-      <c r="P467" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q467" s="10"/>
-      <c r="R467" s="10"/>
-      <c r="S467" s="10"/>
-      <c r="T467" s="10"/>
-      <c r="U467" s="10"/>
-      <c r="V467" s="10"/>
-      <c r="W467" s="10"/>
-      <c r="X467" s="10"/>
-      <c r="Y467" s="10" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="468" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B468" s="8" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C468" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="D468" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="E468" s="8">
-        <v>70</v>
-      </c>
-      <c r="F468" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="G468" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="H468" s="8" t="s">
-        <v>1193</v>
-      </c>
-      <c r="I468" s="8" t="s">
-        <v>1318</v>
-      </c>
-      <c r="J468" s="8" t="s">
-        <v>1194</v>
-      </c>
-      <c r="K468" s="8">
-        <v>20</v>
-      </c>
-      <c r="L468" s="8" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M468" s="8" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N468" s="24" t="s">
-        <v>1195</v>
-      </c>
-      <c r="O468" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="P468" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q468" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="R468" s="8"/>
-      <c r="S468" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="T468" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="U468" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="V468" s="8"/>
-      <c r="W468" s="8"/>
-      <c r="X468" s="8"/>
-      <c r="Y468" s="8"/>
+      <c r="O468" s="26" t="s">
+        <v>727</v>
+      </c>
+      <c r="P468" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q468" s="10"/>
+      <c r="R468" s="10"/>
+      <c r="S468" s="10"/>
+      <c r="T468" s="10"/>
+      <c r="U468" s="10"/>
+      <c r="V468" s="10"/>
+      <c r="W468" s="10"/>
+      <c r="X468" s="10"/>
+      <c r="Y468" s="10" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="469" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="8" t="s">
-        <v>3721</v>
+        <v>5</v>
       </c>
       <c r="B469" s="8" t="s">
-        <v>3722</v>
-      </c>
-      <c r="C469" s="11" t="s">
-        <v>3723</v>
-      </c>
-      <c r="D469" s="11" t="s">
-        <v>3724</v>
+        <v>1357</v>
+      </c>
+      <c r="C469" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D469" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="E469" s="8">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="F469" s="8" t="s">
-        <v>3612</v>
+        <v>651</v>
       </c>
       <c r="G469" s="8" t="s">
-        <v>3613</v>
+        <v>663</v>
       </c>
       <c r="H469" s="8" t="s">
-        <v>3725</v>
+        <v>1193</v>
       </c>
       <c r="I469" s="8" t="s">
-        <v>3313</v>
+        <v>1318</v>
       </c>
       <c r="J469" s="8" t="s">
-        <v>3716</v>
+        <v>1194</v>
       </c>
       <c r="K469" s="8">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="L469" s="8" t="s">
         <v>1377</v>
@@ -43409,13 +43375,17 @@
         <v>1236</v>
       </c>
       <c r="N469" s="24" t="s">
-        <v>727</v>
+        <v>1195</v>
       </c>
       <c r="O469" s="24" t="s">
         <v>727</v>
       </c>
-      <c r="P469" s="8"/>
-      <c r="Q469" s="8"/>
+      <c r="P469" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q469" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="R469" s="8"/>
       <c r="S469" s="8" t="s">
         <v>675</v>
@@ -43423,47 +43393,47 @@
       <c r="T469" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="U469" s="8"/>
+      <c r="U469" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="V469" s="8"/>
       <c r="W469" s="8"/>
-      <c r="X469" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="X469" s="8"/>
       <c r="Y469" s="8"/>
     </row>
     <row r="470" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="8" t="s">
-        <v>1341</v>
+        <v>3721</v>
       </c>
       <c r="B470" s="8" t="s">
-        <v>1540</v>
+        <v>3722</v>
       </c>
       <c r="C470" s="11" t="s">
-        <v>179</v>
+        <v>3723</v>
       </c>
       <c r="D470" s="11" t="s">
-        <v>431</v>
+        <v>3724</v>
       </c>
       <c r="E470" s="8">
-        <v>512</v>
+        <v>10</v>
       </c>
       <c r="F470" s="8" t="s">
-        <v>655</v>
+        <v>3612</v>
       </c>
       <c r="G470" s="8" t="s">
-        <v>663</v>
+        <v>3613</v>
       </c>
       <c r="H470" s="8" t="s">
-        <v>801</v>
+        <v>3725</v>
       </c>
       <c r="I470" s="8" t="s">
-        <v>1313</v>
+        <v>3313</v>
       </c>
       <c r="J470" s="8" t="s">
-        <v>1142</v>
+        <v>3716</v>
       </c>
       <c r="K470" s="8">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="L470" s="8" t="s">
         <v>1377</v>
@@ -43472,14 +43442,12 @@
         <v>1236</v>
       </c>
       <c r="N470" s="24" t="s">
-        <v>1538</v>
+        <v>727</v>
       </c>
       <c r="O470" s="24" t="s">
-        <v>1342</v>
-      </c>
-      <c r="P470" s="8" t="s">
-        <v>676</v>
-      </c>
+        <v>727</v>
+      </c>
+      <c r="P470" s="8"/>
       <c r="Q470" s="8"/>
       <c r="R470" s="8"/>
       <c r="S470" s="8" t="s">
@@ -43491,17 +43459,17 @@
       <c r="U470" s="8"/>
       <c r="V470" s="8"/>
       <c r="W470" s="8"/>
-      <c r="X470" s="8"/>
-      <c r="Y470" s="8" t="s">
-        <v>676</v>
-      </c>
+      <c r="X470" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y470" s="8"/>
     </row>
     <row r="471" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="8" t="s">
         <v>1341</v>
       </c>
       <c r="B471" s="8" t="s">
-        <v>1346</v>
+        <v>1540</v>
       </c>
       <c r="C471" s="11" t="s">
         <v>179</v>
@@ -43519,13 +43487,13 @@
         <v>663</v>
       </c>
       <c r="H471" s="8" t="s">
-        <v>853</v>
+        <v>801</v>
       </c>
       <c r="I471" s="8" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="J471" s="8" t="s">
-        <v>1343</v>
+        <v>1142</v>
       </c>
       <c r="K471" s="8">
         <v>20</v>
@@ -43537,13 +43505,13 @@
         <v>1236</v>
       </c>
       <c r="N471" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O471" s="8" t="s">
-        <v>727</v>
+        <v>1538</v>
+      </c>
+      <c r="O471" s="24" t="s">
+        <v>1342</v>
       </c>
       <c r="P471" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Q471" s="8"/>
       <c r="R471" s="8"/>
@@ -43562,266 +43530,268 @@
       </c>
     </row>
     <row r="472" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="12" t="s">
+      <c r="A472" s="8" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B472" s="8" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C472" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D472" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="E472" s="8">
+        <v>512</v>
+      </c>
+      <c r="F472" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="G472" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H472" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="I472" s="8" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J472" s="8" t="s">
+        <v>1343</v>
+      </c>
+      <c r="K472" s="8">
+        <v>20</v>
+      </c>
+      <c r="L472" s="8" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M472" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N472" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O472" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P472" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q472" s="8"/>
+      <c r="R472" s="8"/>
+      <c r="S472" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="T472" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U472" s="8"/>
+      <c r="V472" s="8"/>
+      <c r="W472" s="8"/>
+      <c r="X472" s="8"/>
+      <c r="Y472" s="8" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="473" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A473" s="12" t="s">
         <v>687</v>
       </c>
-      <c r="B472" s="12" t="s">
+      <c r="B473" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="C472" s="13" t="s">
+      <c r="C473" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="D472" s="13" t="s">
+      <c r="D473" s="13" t="s">
         <v>689</v>
       </c>
-      <c r="E472" s="12">
+      <c r="E473" s="12">
         <v>49</v>
       </c>
-      <c r="F472" s="12" t="s">
+      <c r="F473" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="G472" s="12" t="s">
+      <c r="G473" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H472" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="I472" s="12" t="s">
-        <v>1536</v>
-      </c>
-      <c r="J472" s="12" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K472" s="12">
-        <v>70</v>
-      </c>
-      <c r="L472" s="12" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M472" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N472" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O472" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P472" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q472" s="12"/>
-      <c r="R472" s="12"/>
-      <c r="S472" s="12"/>
-      <c r="T472" s="12"/>
-      <c r="U472" s="12"/>
-      <c r="V472" s="12"/>
-      <c r="W472" s="12"/>
-      <c r="X472" s="12"/>
-      <c r="Y472" s="12"/>
-    </row>
-    <row r="473" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A473" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B473" s="8" t="s">
-        <v>1541</v>
-      </c>
-      <c r="C473" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="D473" s="11" t="s">
-        <v>642</v>
-      </c>
-      <c r="E473" s="8">
-        <v>47</v>
-      </c>
-      <c r="F473" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="G473" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="H473" s="8" t="s">
+      <c r="H473" s="12" t="s">
         <v>853</v>
       </c>
       <c r="I473" s="12" t="s">
         <v>1536</v>
       </c>
-      <c r="J473" s="8" t="s">
+      <c r="J473" s="12" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K473" s="12">
+        <v>70</v>
+      </c>
+      <c r="L473" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M473" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N473" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O473" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P473" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q473" s="12"/>
+      <c r="R473" s="12"/>
+      <c r="S473" s="12"/>
+      <c r="T473" s="12"/>
+      <c r="U473" s="12"/>
+      <c r="V473" s="12"/>
+      <c r="W473" s="12"/>
+      <c r="X473" s="12"/>
+      <c r="Y473" s="12"/>
+    </row>
+    <row r="474" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A474" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B474" s="8" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C474" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="D474" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="E474" s="8">
+        <v>47</v>
+      </c>
+      <c r="F474" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="G474" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H474" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="I474" s="12" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J474" s="8" t="s">
         <v>1188</v>
       </c>
-      <c r="K473" s="8">
+      <c r="K474" s="8">
         <v>120</v>
       </c>
-      <c r="L473" s="8" t="s">
+      <c r="L474" s="8" t="s">
         <v>1376</v>
       </c>
-      <c r="M473" s="8" t="s">
+      <c r="M474" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="N473" s="24" t="s">
+      <c r="N474" s="24" t="s">
         <v>1196</v>
       </c>
-      <c r="O473" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P473" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q473" s="8"/>
-      <c r="R473" s="8"/>
-      <c r="S473" s="8"/>
-      <c r="T473" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="U473" s="8"/>
-      <c r="V473" s="8"/>
-      <c r="W473" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="X473" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y473" s="8"/>
-    </row>
-    <row r="474" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A474" s="10" t="s">
+      <c r="O474" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P474" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q474" s="8"/>
+      <c r="R474" s="8"/>
+      <c r="S474" s="8"/>
+      <c r="T474" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U474" s="8"/>
+      <c r="V474" s="8"/>
+      <c r="W474" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="X474" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y474" s="8"/>
+    </row>
+    <row r="475" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A475" s="10" t="s">
         <v>1456</v>
       </c>
-      <c r="B474" s="10" t="s">
+      <c r="B475" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="C474" s="9" t="s">
+      <c r="C475" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D474" s="9" t="s">
+      <c r="D475" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="E474" s="10">
+      <c r="E475" s="10">
         <v>320</v>
       </c>
-      <c r="F474" s="10" t="s">
+      <c r="F475" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="G474" s="10" t="s">
+      <c r="G475" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H474" s="10" t="s">
+      <c r="H475" s="10" t="s">
         <v>1082</v>
       </c>
-      <c r="I474" s="10" t="s">
+      <c r="I475" s="10" t="s">
         <v>1439</v>
       </c>
-      <c r="J474" s="10" t="s">
+      <c r="J475" s="10" t="s">
         <v>1083</v>
       </c>
-      <c r="K474" s="10">
+      <c r="K475" s="10">
         <v>20</v>
       </c>
-      <c r="L474" s="10" t="s">
+      <c r="L475" s="10" t="s">
         <v>1377</v>
       </c>
-      <c r="M474" s="10" t="s">
+      <c r="M475" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N474" s="26" t="s">
+      <c r="N475" s="26" t="s">
         <v>1084</v>
       </c>
-      <c r="O474" s="10" t="s">
+      <c r="O475" s="10" t="s">
         <v>1085</v>
       </c>
-      <c r="P474" s="10" t="s">
+      <c r="P475" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="Q474" s="10"/>
-      <c r="R474" s="10"/>
-      <c r="S474" s="10"/>
-      <c r="T474" s="10"/>
-      <c r="U474" s="10"/>
-      <c r="V474" s="10"/>
-      <c r="W474" s="10"/>
-      <c r="X474" s="10"/>
-      <c r="Y474" s="10"/>
-    </row>
-    <row r="475" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A475" s="12" t="s">
-        <v>704</v>
-      </c>
-      <c r="B475" s="12" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C475" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="D475" s="13" t="s">
-        <v>601</v>
-      </c>
-      <c r="E475" s="12">
-        <v>165</v>
-      </c>
-      <c r="F475" s="12" t="s">
-        <v>655</v>
-      </c>
-      <c r="G475" s="12" t="s">
-        <v>663</v>
-      </c>
-      <c r="H475" s="12" t="s">
-        <v>878</v>
-      </c>
-      <c r="I475" s="12" t="s">
-        <v>1323</v>
-      </c>
-      <c r="J475" s="12" t="s">
-        <v>1003</v>
-      </c>
-      <c r="K475" s="12">
-        <v>30</v>
-      </c>
-      <c r="L475" s="12" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M475" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N475" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O475" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P475" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q475" s="12"/>
-      <c r="R475" s="12"/>
-      <c r="S475" s="12"/>
-      <c r="T475" s="12"/>
-      <c r="U475" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="V475" s="12"/>
-      <c r="W475" s="12"/>
-      <c r="X475" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y475" s="12"/>
+      <c r="Q475" s="10"/>
+      <c r="R475" s="10"/>
+      <c r="S475" s="10"/>
+      <c r="T475" s="10"/>
+      <c r="U475" s="10"/>
+      <c r="V475" s="10"/>
+      <c r="W475" s="10"/>
+      <c r="X475" s="10"/>
+      <c r="Y475" s="10"/>
     </row>
     <row r="476" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="12" t="s">
-        <v>24</v>
+        <v>704</v>
       </c>
       <c r="B476" s="12" t="s">
-        <v>1542</v>
-      </c>
-      <c r="C476" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D476" s="12" t="s">
-        <v>434</v>
+        <v>1357</v>
+      </c>
+      <c r="C476" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="D476" s="13" t="s">
+        <v>601</v>
       </c>
       <c r="E476" s="12">
-        <v>530</v>
+        <v>165</v>
       </c>
       <c r="F476" s="12" t="s">
         <v>655</v>
@@ -43830,16 +43800,16 @@
         <v>663</v>
       </c>
       <c r="H476" s="12" t="s">
-        <v>853</v>
+        <v>878</v>
       </c>
       <c r="I476" s="12" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="J476" s="12" t="s">
-        <v>1018</v>
+        <v>1003</v>
       </c>
       <c r="K476" s="12">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="L476" s="12" t="s">
         <v>1377</v>
@@ -43860,10 +43830,14 @@
       <c r="R476" s="12"/>
       <c r="S476" s="12"/>
       <c r="T476" s="12"/>
-      <c r="U476" s="12"/>
+      <c r="U476" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="V476" s="12"/>
       <c r="W476" s="12"/>
-      <c r="X476" s="12"/>
+      <c r="X476" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="Y476" s="12"/>
     </row>
     <row r="477" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -43871,7 +43845,7 @@
         <v>24</v>
       </c>
       <c r="B477" s="12" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="C477" s="12" t="s">
         <v>182</v>
@@ -43891,14 +43865,14 @@
       <c r="H477" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="I477" s="8" t="s">
-        <v>1319</v>
+      <c r="I477" s="12" t="s">
+        <v>1322</v>
       </c>
       <c r="J477" s="12" t="s">
         <v>1018</v>
       </c>
       <c r="K477" s="12">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="L477" s="12" t="s">
         <v>1377</v>
@@ -43927,37 +43901,37 @@
     </row>
     <row r="478" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="12" t="s">
-        <v>3258</v>
+        <v>24</v>
       </c>
       <c r="B478" s="12" t="s">
-        <v>1545</v>
-      </c>
-      <c r="C478" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D478" s="13" t="s">
-        <v>395</v>
+        <v>1543</v>
+      </c>
+      <c r="C478" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D478" s="12" t="s">
+        <v>434</v>
       </c>
       <c r="E478" s="12">
-        <v>45</v>
+        <v>530</v>
       </c>
       <c r="F478" s="12" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G478" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H478" s="8" t="s">
-        <v>1132</v>
-      </c>
-      <c r="I478" s="12" t="s">
-        <v>1318</v>
+      <c r="H478" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="I478" s="8" t="s">
+        <v>1319</v>
       </c>
       <c r="J478" s="12" t="s">
-        <v>1197</v>
+        <v>1018</v>
       </c>
       <c r="K478" s="12">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="L478" s="12" t="s">
         <v>1377</v>
@@ -43968,32 +43942,20 @@
       <c r="N478" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="O478" s="25" t="s">
+      <c r="O478" s="12" t="s">
         <v>727</v>
       </c>
       <c r="P478" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="Q478" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="R478" s="12" t="s">
-        <v>676</v>
-      </c>
-      <c r="S478" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="T478" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="U478" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="Q478" s="12"/>
+      <c r="R478" s="12"/>
+      <c r="S478" s="12"/>
+      <c r="T478" s="12"/>
+      <c r="U478" s="12"/>
       <c r="V478" s="12"/>
       <c r="W478" s="12"/>
-      <c r="X478" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="X478" s="12"/>
       <c r="Y478" s="12"/>
     </row>
     <row r="479" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -44001,7 +43963,7 @@
         <v>3258</v>
       </c>
       <c r="B479" s="12" t="s">
-        <v>1347</v>
+        <v>1545</v>
       </c>
       <c r="C479" s="13" t="s">
         <v>143</v>
@@ -44019,19 +43981,19 @@
         <v>663</v>
       </c>
       <c r="H479" s="8" t="s">
-        <v>853</v>
+        <v>1132</v>
       </c>
       <c r="I479" s="12" t="s">
-        <v>1374</v>
+        <v>1318</v>
       </c>
       <c r="J479" s="12" t="s">
         <v>1197</v>
       </c>
       <c r="K479" s="12">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="L479" s="12" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="M479" s="12" t="s">
         <v>1236</v>
@@ -44045,17 +44007,25 @@
       <c r="P479" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="Q479" s="12"/>
+      <c r="Q479" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="R479" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="S479" s="12"/>
-      <c r="T479" s="12"/>
-      <c r="U479" s="12"/>
+      <c r="S479" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="T479" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="U479" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="V479" s="12"/>
       <c r="W479" s="12"/>
       <c r="X479" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="Y479" s="12"/>
     </row>
@@ -44082,16 +44052,16 @@
         <v>663</v>
       </c>
       <c r="H480" s="8" t="s">
-        <v>878</v>
+        <v>853</v>
       </c>
       <c r="I480" s="12" t="s">
-        <v>1313</v>
+        <v>1374</v>
       </c>
       <c r="J480" s="12" t="s">
         <v>1197</v>
       </c>
       <c r="K480" s="12">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="L480" s="12" t="s">
         <v>1376</v>
@@ -44112,15 +44082,9 @@
       <c r="R480" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="S480" s="12" t="s">
-        <v>676</v>
-      </c>
-      <c r="T480" s="12" t="s">
-        <v>676</v>
-      </c>
-      <c r="U480" s="12" t="s">
-        <v>676</v>
-      </c>
+      <c r="S480" s="12"/>
+      <c r="T480" s="12"/>
+      <c r="U480" s="12"/>
       <c r="V480" s="12"/>
       <c r="W480" s="12"/>
       <c r="X480" s="12" t="s">
@@ -44151,10 +44115,10 @@
         <v>663</v>
       </c>
       <c r="H481" s="8" t="s">
-        <v>1132</v>
+        <v>878</v>
       </c>
       <c r="I481" s="12" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="J481" s="12" t="s">
         <v>1197</v>
@@ -44171,31 +44135,29 @@
       <c r="N481" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="O481" s="12" t="s">
+      <c r="O481" s="25" t="s">
         <v>727</v>
       </c>
       <c r="P481" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="Q481" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="Q481" s="12"/>
       <c r="R481" s="12" t="s">
         <v>676</v>
       </c>
       <c r="S481" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="T481" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U481" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="V481" s="12"/>
       <c r="W481" s="12"/>
       <c r="X481" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Y481" s="12"/>
     </row>
@@ -44204,7 +44166,7 @@
         <v>3258</v>
       </c>
       <c r="B482" s="12" t="s">
-        <v>1544</v>
+        <v>1347</v>
       </c>
       <c r="C482" s="13" t="s">
         <v>143</v>
@@ -44221,20 +44183,20 @@
       <c r="G482" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H482" s="12" t="s">
-        <v>934</v>
+      <c r="H482" s="8" t="s">
+        <v>1132</v>
       </c>
       <c r="I482" s="12" t="s">
-        <v>1228</v>
+        <v>1319</v>
       </c>
       <c r="J482" s="12" t="s">
-        <v>855</v>
+        <v>1197</v>
       </c>
       <c r="K482" s="12">
         <v>540</v>
       </c>
       <c r="L482" s="12" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="M482" s="12" t="s">
         <v>1236</v>
@@ -44248,18 +44210,26 @@
       <c r="P482" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="Q482" s="12"/>
+      <c r="Q482" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="R482" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="S482" s="12"/>
+      <c r="S482" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="T482" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="U482" s="12"/>
+      <c r="U482" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="V482" s="12"/>
       <c r="W482" s="12"/>
-      <c r="X482" s="12"/>
+      <c r="X482" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="Y482" s="12"/>
     </row>
     <row r="483" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -44267,7 +44237,7 @@
         <v>3258</v>
       </c>
       <c r="B483" s="12" t="s">
-        <v>3482</v>
+        <v>1544</v>
       </c>
       <c r="C483" s="13" t="s">
         <v>143</v>
@@ -44285,19 +44255,19 @@
         <v>663</v>
       </c>
       <c r="H483" s="12" t="s">
-        <v>1500</v>
+        <v>934</v>
       </c>
       <c r="I483" s="12" t="s">
-        <v>3313</v>
+        <v>1228</v>
       </c>
       <c r="J483" s="12" t="s">
-        <v>3483</v>
+        <v>855</v>
       </c>
       <c r="K483" s="12">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="L483" s="12" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="M483" s="12" t="s">
         <v>1236</v>
@@ -44312,155 +44282,159 @@
         <v>675</v>
       </c>
       <c r="Q483" s="12"/>
-      <c r="R483" s="12"/>
+      <c r="R483" s="12" t="s">
+        <v>676</v>
+      </c>
       <c r="S483" s="12"/>
-      <c r="T483" s="12"/>
-      <c r="U483" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="V483" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="T483" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="U483" s="12"/>
+      <c r="V483" s="12"/>
       <c r="W483" s="12"/>
       <c r="X483" s="12"/>
       <c r="Y483" s="12"/>
     </row>
     <row r="484" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A484" s="14" t="s">
+      <c r="A484" s="12" t="s">
         <v>3258</v>
       </c>
-      <c r="B484" s="14" t="s">
+      <c r="B484" s="12" t="s">
+        <v>3482</v>
+      </c>
+      <c r="C484" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D484" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="E484" s="12">
+        <v>45</v>
+      </c>
+      <c r="F484" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="G484" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="H484" s="12" t="s">
+        <v>1500</v>
+      </c>
+      <c r="I484" s="12" t="s">
+        <v>3313</v>
+      </c>
+      <c r="J484" s="12" t="s">
+        <v>3483</v>
+      </c>
+      <c r="K484" s="12">
+        <v>120</v>
+      </c>
+      <c r="L484" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M484" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N484" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O484" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P484" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q484" s="12"/>
+      <c r="R484" s="12"/>
+      <c r="S484" s="12"/>
+      <c r="T484" s="12"/>
+      <c r="U484" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="V484" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="W484" s="12"/>
+      <c r="X484" s="12"/>
+      <c r="Y484" s="12"/>
+    </row>
+    <row r="485" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A485" s="14" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B485" s="14" t="s">
         <v>3494</v>
       </c>
-      <c r="C484" s="15" t="s">
+      <c r="C485" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="D484" s="15" t="s">
+      <c r="D485" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="E484" s="14">
+      <c r="E485" s="14">
         <v>45</v>
       </c>
-      <c r="F484" s="14" t="s">
+      <c r="F485" s="14" t="s">
         <v>651</v>
       </c>
-      <c r="G484" s="14" t="s">
+      <c r="G485" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="H484" s="14" t="s">
-        <v>805</v>
-      </c>
-      <c r="I484" s="14" t="s">
+      <c r="H485" s="14" t="s">
+        <v>805</v>
+      </c>
+      <c r="I485" s="14" t="s">
         <v>3338</v>
       </c>
-      <c r="J484" s="14" t="s">
+      <c r="J485" s="14" t="s">
         <v>3483</v>
       </c>
-      <c r="K484" s="14">
+      <c r="K485" s="14">
         <v>120</v>
       </c>
-      <c r="L484" s="14" t="s">
+      <c r="L485" s="14" t="s">
         <v>1377</v>
       </c>
-      <c r="M484" s="14" t="s">
+      <c r="M485" s="14" t="s">
         <v>1238</v>
       </c>
-      <c r="N484" s="27" t="s">
+      <c r="N485" s="27" t="s">
         <v>1265</v>
       </c>
-      <c r="O484" s="14" t="s">
+      <c r="O485" s="14" t="s">
         <v>3483</v>
       </c>
-      <c r="P484" s="14" t="s">
+      <c r="P485" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="Q484" s="14"/>
-      <c r="R484" s="14"/>
-      <c r="S484" s="14"/>
-      <c r="T484" s="14"/>
-      <c r="U484" s="14"/>
-      <c r="V484" s="14"/>
-      <c r="W484" s="14"/>
-      <c r="X484" s="14"/>
-      <c r="Y484" s="14"/>
-    </row>
-    <row r="485" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A485" s="12" t="s">
-        <v>1458</v>
-      </c>
-      <c r="B485" s="12" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C485" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="D485" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="E485" s="12">
-        <v>500</v>
-      </c>
-      <c r="F485" s="12" t="s">
-        <v>651</v>
-      </c>
-      <c r="G485" s="12" t="s">
-        <v>663</v>
-      </c>
-      <c r="H485" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="I485" s="12" t="s">
-        <v>1374</v>
-      </c>
-      <c r="J485" s="12" t="s">
-        <v>945</v>
-      </c>
-      <c r="K485" s="12" t="s">
-        <v>944</v>
-      </c>
-      <c r="L485" s="12" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M485" s="12" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N485" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O485" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P485" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q485" s="12"/>
-      <c r="R485" s="12"/>
-      <c r="S485" s="12"/>
-      <c r="T485" s="12"/>
-      <c r="U485" s="12"/>
-      <c r="V485" s="12"/>
-      <c r="W485" s="12"/>
-      <c r="X485" s="12"/>
-      <c r="Y485" s="12"/>
+      <c r="Q485" s="14"/>
+      <c r="R485" s="14"/>
+      <c r="S485" s="14"/>
+      <c r="T485" s="14"/>
+      <c r="U485" s="14"/>
+      <c r="V485" s="14"/>
+      <c r="W485" s="14"/>
+      <c r="X485" s="14"/>
+      <c r="Y485" s="14"/>
     </row>
     <row r="486" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="12" t="s">
-        <v>109</v>
+        <v>1458</v>
       </c>
       <c r="B486" s="12" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C486" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="D486" s="13" t="s">
-        <v>592</v>
+        <v>1346</v>
+      </c>
+      <c r="C486" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="D486" s="12" t="s">
+        <v>468</v>
       </c>
       <c r="E486" s="12">
-        <v>255</v>
+        <v>500</v>
       </c>
       <c r="F486" s="12" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G486" s="12" t="s">
         <v>663</v>
@@ -44472,13 +44446,13 @@
         <v>1374</v>
       </c>
       <c r="J486" s="12" t="s">
-        <v>1019</v>
-      </c>
-      <c r="K486" s="12">
-        <v>90</v>
+        <v>945</v>
+      </c>
+      <c r="K486" s="12" t="s">
+        <v>944</v>
       </c>
       <c r="L486" s="12" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="M486" s="12" t="s">
         <v>1236</v>
@@ -44493,9 +44467,7 @@
         <v>675</v>
       </c>
       <c r="Q486" s="12"/>
-      <c r="R486" s="12" t="s">
-        <v>675</v>
-      </c>
+      <c r="R486" s="12"/>
       <c r="S486" s="12"/>
       <c r="T486" s="12"/>
       <c r="U486" s="12"/>
@@ -44506,22 +44478,22 @@
     </row>
     <row r="487" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="12" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="B487" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="C487" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="D487" s="12" t="s">
-        <v>528</v>
+      <c r="C487" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="D487" s="13" t="s">
+        <v>592</v>
       </c>
       <c r="E487" s="12">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F487" s="12" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G487" s="12" t="s">
         <v>663</v>
@@ -44530,13 +44502,13 @@
         <v>853</v>
       </c>
       <c r="I487" s="12" t="s">
-        <v>1384</v>
+        <v>1374</v>
       </c>
       <c r="J487" s="12" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="K487" s="12">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="L487" s="12" t="s">
         <v>1376</v>
@@ -44554,7 +44526,9 @@
         <v>675</v>
       </c>
       <c r="Q487" s="12"/>
-      <c r="R487" s="12"/>
+      <c r="R487" s="12" t="s">
+        <v>675</v>
+      </c>
       <c r="S487" s="12"/>
       <c r="T487" s="12"/>
       <c r="U487" s="12"/>
@@ -44564,144 +44538,140 @@
       <c r="Y487" s="12"/>
     </row>
     <row r="488" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A488" s="10" t="s">
+      <c r="A488" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B488" s="12" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C488" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D488" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="E488" s="12">
+        <v>50</v>
+      </c>
+      <c r="F488" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="G488" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="H488" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="I488" s="12" t="s">
+        <v>1384</v>
+      </c>
+      <c r="J488" s="12" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K488" s="12">
+        <v>18</v>
+      </c>
+      <c r="L488" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M488" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N488" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O488" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P488" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q488" s="12"/>
+      <c r="R488" s="12"/>
+      <c r="S488" s="12"/>
+      <c r="T488" s="12"/>
+      <c r="U488" s="12"/>
+      <c r="V488" s="12"/>
+      <c r="W488" s="12"/>
+      <c r="X488" s="12"/>
+      <c r="Y488" s="12"/>
+    </row>
+    <row r="489" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A489" s="10" t="s">
         <v>1224</v>
       </c>
-      <c r="B488" s="10" t="s">
+      <c r="B489" s="10" t="s">
         <v>1223</v>
       </c>
-      <c r="C488" s="9" t="s">
+      <c r="C489" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D488" s="9" t="s">
+      <c r="D489" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="E488" s="9" t="s">
+      <c r="E489" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="F488" s="10" t="s">
+      <c r="F489" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="G488" s="10" t="s">
+      <c r="G489" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H488" s="10" t="s">
+      <c r="H489" s="10" t="s">
         <v>798</v>
       </c>
-      <c r="I488" s="10" t="s">
+      <c r="I489" s="10" t="s">
         <v>1227</v>
       </c>
-      <c r="J488" s="10" t="s">
+      <c r="J489" s="10" t="s">
         <v>845</v>
       </c>
-      <c r="K488" s="10">
+      <c r="K489" s="10">
         <v>410</v>
       </c>
-      <c r="L488" s="10" t="s">
+      <c r="L489" s="10" t="s">
         <v>1379</v>
       </c>
-      <c r="M488" s="10" t="s">
+      <c r="M489" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N488" s="28" t="s">
+      <c r="N489" s="28" t="s">
         <v>1263</v>
       </c>
-      <c r="O488" s="10" t="s">
+      <c r="O489" s="10" t="s">
         <v>845</v>
       </c>
-      <c r="P488" s="10"/>
-      <c r="Q488" s="10"/>
-      <c r="R488" s="10"/>
-      <c r="S488" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="T488" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="U488" s="10"/>
-      <c r="V488" s="10"/>
-      <c r="W488" s="10"/>
-      <c r="X488" s="10"/>
-      <c r="Y488" s="10"/>
-    </row>
-    <row r="489" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A489" s="8" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B489" s="8" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C489" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D489" s="11" t="s">
-        <v>436</v>
-      </c>
-      <c r="E489" s="11" t="s">
-        <v>869</v>
-      </c>
-      <c r="F489" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="G489" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="H489" s="8" t="s">
-        <v>801</v>
-      </c>
-      <c r="I489" s="8" t="s">
-        <v>1228</v>
-      </c>
-      <c r="J489" s="8" t="s">
-        <v>845</v>
-      </c>
-      <c r="K489" s="8">
-        <v>410</v>
-      </c>
-      <c r="L489" s="8" t="s">
-        <v>1376</v>
-      </c>
-      <c r="M489" s="8" t="s">
-        <v>1236</v>
-      </c>
-      <c r="N489" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O489" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P489" s="8"/>
-      <c r="Q489" s="8"/>
-      <c r="R489" s="8"/>
-      <c r="S489" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="T489" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="U489" s="8"/>
-      <c r="V489" s="8"/>
-      <c r="W489" s="8"/>
-      <c r="X489" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="Y489" s="8"/>
+      <c r="P489" s="10"/>
+      <c r="Q489" s="10"/>
+      <c r="R489" s="10"/>
+      <c r="S489" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="T489" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="U489" s="10"/>
+      <c r="V489" s="10"/>
+      <c r="W489" s="10"/>
+      <c r="X489" s="10"/>
+      <c r="Y489" s="10"/>
     </row>
     <row r="490" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="8" t="s">
-        <v>26</v>
+        <v>1224</v>
       </c>
       <c r="B490" s="8" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C490" s="8" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C490" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D490" s="8" t="s">
+      <c r="D490" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="E490" s="8">
-        <v>450</v>
+      <c r="E490" s="11" t="s">
+        <v>869</v>
       </c>
       <c r="F490" s="8" t="s">
         <v>655</v>
@@ -44710,19 +44680,19 @@
         <v>663</v>
       </c>
       <c r="H490" s="8" t="s">
-        <v>1132</v>
+        <v>801</v>
       </c>
       <c r="I490" s="8" t="s">
-        <v>1319</v>
+        <v>1228</v>
       </c>
       <c r="J490" s="8" t="s">
         <v>845</v>
       </c>
       <c r="K490" s="8">
-        <v>650</v>
+        <v>410</v>
       </c>
       <c r="L490" s="8" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="M490" s="8" t="s">
         <v>1236</v>
@@ -44733,69 +44703,59 @@
       <c r="O490" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="P490" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q490" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="R490" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="P490" s="8"/>
+      <c r="Q490" s="8"/>
+      <c r="R490" s="8"/>
       <c r="S490" s="8" t="s">
         <v>675</v>
       </c>
       <c r="T490" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="U490" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="U490" s="8"/>
       <c r="V490" s="8"/>
-      <c r="W490" s="8" t="s">
-        <v>675</v>
-      </c>
+      <c r="W490" s="8"/>
       <c r="X490" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Y490" s="8"/>
     </row>
     <row r="491" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="8" t="s">
-        <v>677</v>
+        <v>26</v>
       </c>
       <c r="B491" s="8" t="s">
         <v>1357</v>
       </c>
-      <c r="C491" s="11" t="s">
-        <v>678</v>
-      </c>
-      <c r="D491" s="11" t="s">
-        <v>679</v>
+      <c r="C491" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D491" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="E491" s="8">
-        <v>1070</v>
+        <v>450</v>
       </c>
       <c r="F491" s="8" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G491" s="8" t="s">
         <v>663</v>
       </c>
       <c r="H491" s="8" t="s">
-        <v>853</v>
+        <v>1132</v>
       </c>
       <c r="I491" s="8" t="s">
-        <v>1364</v>
+        <v>1319</v>
       </c>
       <c r="J491" s="8" t="s">
-        <v>942</v>
+        <v>845</v>
       </c>
       <c r="K491" s="8">
-        <v>80</v>
+        <v>650</v>
       </c>
       <c r="L491" s="8" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="M491" s="8" t="s">
         <v>1236</v>
@@ -44809,31 +44769,45 @@
       <c r="P491" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="Q491" s="8"/>
-      <c r="R491" s="8"/>
-      <c r="S491" s="8"/>
-      <c r="T491" s="8"/>
-      <c r="U491" s="8"/>
+      <c r="Q491" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="R491" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="S491" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="T491" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U491" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="V491" s="8"/>
-      <c r="W491" s="8"/>
-      <c r="X491" s="8"/>
+      <c r="W491" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="X491" s="8" t="s">
+        <v>675</v>
+      </c>
       <c r="Y491" s="8"/>
     </row>
     <row r="492" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="8" t="s">
-        <v>8</v>
+        <v>677</v>
       </c>
       <c r="B492" s="8" t="s">
         <v>1357</v>
       </c>
       <c r="C492" s="11" t="s">
-        <v>163</v>
+        <v>678</v>
       </c>
       <c r="D492" s="11" t="s">
-        <v>415</v>
+        <v>679</v>
       </c>
       <c r="E492" s="8">
-        <v>25</v>
+        <v>1070</v>
       </c>
       <c r="F492" s="8" t="s">
         <v>651</v>
@@ -44842,19 +44816,19 @@
         <v>663</v>
       </c>
       <c r="H492" s="8" t="s">
-        <v>878</v>
+        <v>853</v>
       </c>
       <c r="I492" s="8" t="s">
-        <v>1318</v>
+        <v>1364</v>
       </c>
       <c r="J492" s="8" t="s">
-        <v>1198</v>
+        <v>942</v>
       </c>
       <c r="K492" s="8">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L492" s="8" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="M492" s="8" t="s">
         <v>1236</v>
@@ -44879,555 +44853,545 @@
       <c r="Y492" s="8"/>
     </row>
     <row r="493" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A493" s="10" t="s">
+      <c r="A493" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B493" s="8" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C493" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D493" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="E493" s="8">
+        <v>25</v>
+      </c>
+      <c r="F493" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="G493" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H493" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="I493" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J493" s="8" t="s">
+        <v>1198</v>
+      </c>
+      <c r="K493" s="8">
+        <v>40</v>
+      </c>
+      <c r="L493" s="8" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M493" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N493" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O493" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P493" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q493" s="8"/>
+      <c r="R493" s="8"/>
+      <c r="S493" s="8"/>
+      <c r="T493" s="8"/>
+      <c r="U493" s="8"/>
+      <c r="V493" s="8"/>
+      <c r="W493" s="8"/>
+      <c r="X493" s="8"/>
+      <c r="Y493" s="8"/>
+    </row>
+    <row r="494" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A494" s="10" t="s">
         <v>1485</v>
       </c>
-      <c r="B493" s="10" t="s">
+      <c r="B494" s="10" t="s">
         <v>1486</v>
       </c>
-      <c r="C493" s="9" t="s">
+      <c r="C494" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="D493" s="9" t="s">
+      <c r="D494" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="E493" s="10">
+      <c r="E494" s="10">
         <v>595</v>
       </c>
-      <c r="F493" s="10" t="s">
+      <c r="F494" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="G493" s="10" t="s">
+      <c r="G494" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H493" s="10" t="s">
+      <c r="H494" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="I493" s="14" t="s">
+      <c r="I494" s="14" t="s">
         <v>1434</v>
       </c>
-      <c r="J493" s="10" t="s">
+      <c r="J494" s="10" t="s">
         <v>1118</v>
       </c>
-      <c r="K493" s="10">
+      <c r="K494" s="10">
         <v>80</v>
       </c>
-      <c r="L493" s="10" t="s">
+      <c r="L494" s="10" t="s">
         <v>1380</v>
       </c>
-      <c r="M493" s="10" t="s">
+      <c r="M494" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N493" s="27" t="s">
+      <c r="N494" s="27" t="s">
         <v>1265</v>
       </c>
-      <c r="O493" s="10" t="s">
-        <v>727</v>
-      </c>
-      <c r="P493" s="10" t="s">
+      <c r="O494" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="P494" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="Q493" s="10"/>
-      <c r="R493" s="10"/>
-      <c r="S493" s="10"/>
-      <c r="T493" s="10"/>
-      <c r="U493" s="10"/>
-      <c r="V493" s="10"/>
-      <c r="W493" s="10"/>
-      <c r="X493" s="10"/>
-      <c r="Y493" s="10"/>
-    </row>
-    <row r="494" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A494" s="14" t="s">
+      <c r="Q494" s="10"/>
+      <c r="R494" s="10"/>
+      <c r="S494" s="10"/>
+      <c r="T494" s="10"/>
+      <c r="U494" s="10"/>
+      <c r="V494" s="10"/>
+      <c r="W494" s="10"/>
+      <c r="X494" s="10"/>
+      <c r="Y494" s="10"/>
+    </row>
+    <row r="495" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A495" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B494" s="14" t="s">
+      <c r="B495" s="14" t="s">
         <v>1546</v>
       </c>
-      <c r="C494" s="15" t="s">
+      <c r="C495" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="D494" s="15" t="s">
+      <c r="D495" s="15" t="s">
         <v>604</v>
       </c>
-      <c r="E494" s="14">
+      <c r="E495" s="14">
         <v>220</v>
       </c>
-      <c r="F494" s="14" t="s">
+      <c r="F495" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="G494" s="14" t="s">
+      <c r="G495" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="H494" s="14" t="s">
+      <c r="H495" s="14" t="s">
         <v>853</v>
       </c>
-      <c r="I494" s="14" t="s">
+      <c r="I495" s="14" t="s">
         <v>1547</v>
       </c>
-      <c r="J494" s="14" t="s">
+      <c r="J495" s="14" t="s">
         <v>1021</v>
       </c>
-      <c r="K494" s="14">
+      <c r="K495" s="14">
         <v>60</v>
       </c>
-      <c r="L494" s="14" t="s">
+      <c r="L495" s="14" t="s">
         <v>1378</v>
       </c>
-      <c r="M494" s="14" t="s">
+      <c r="M495" s="14" t="s">
         <v>1238</v>
       </c>
-      <c r="N494" s="27" t="s">
+      <c r="N495" s="27" t="s">
         <v>1023</v>
       </c>
-      <c r="O494" s="14" t="s">
+      <c r="O495" s="14" t="s">
         <v>1022</v>
       </c>
-      <c r="P494" s="14" t="s">
+      <c r="P495" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="Q494" s="14"/>
-      <c r="R494" s="14"/>
-      <c r="S494" s="14"/>
-      <c r="T494" s="14"/>
-      <c r="U494" s="14"/>
-      <c r="V494" s="14"/>
-      <c r="W494" s="14"/>
-      <c r="X494" s="14"/>
-      <c r="Y494" s="14"/>
-    </row>
-    <row r="495" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A495" s="8" t="s">
+      <c r="Q495" s="14"/>
+      <c r="R495" s="14"/>
+      <c r="S495" s="14"/>
+      <c r="T495" s="14"/>
+      <c r="U495" s="14"/>
+      <c r="V495" s="14"/>
+      <c r="W495" s="14"/>
+      <c r="X495" s="14"/>
+      <c r="Y495" s="14"/>
+    </row>
+    <row r="496" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A496" s="8" t="s">
         <v>1299</v>
       </c>
-      <c r="B495" s="8" t="s">
+      <c r="B496" s="8" t="s">
         <v>1357</v>
       </c>
-      <c r="C495" s="8" t="s">
+      <c r="C496" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="D495" s="8" t="s">
+      <c r="D496" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="E495" s="8">
+      <c r="E496" s="8">
         <v>144</v>
       </c>
-      <c r="F495" s="8" t="s">
+      <c r="F496" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="G495" s="8" t="s">
+      <c r="G496" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="H495" s="8" t="s">
+      <c r="H496" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="I495" s="8" t="s">
+      <c r="I496" s="8" t="s">
         <v>1364</v>
       </c>
-      <c r="J495" s="8" t="s">
+      <c r="J496" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="K495" s="8">
+      <c r="K496" s="8">
         <v>12</v>
       </c>
-      <c r="L495" s="8" t="s">
+      <c r="L496" s="8" t="s">
         <v>1376</v>
       </c>
-      <c r="M495" s="8" t="s">
+      <c r="M496" s="8" t="s">
         <v>1236</v>
       </c>
-      <c r="N495" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O495" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="P495" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q495" s="8"/>
-      <c r="R495" s="8"/>
-      <c r="S495" s="8"/>
-      <c r="T495" s="8"/>
-      <c r="U495" s="8"/>
-      <c r="V495" s="8"/>
-      <c r="W495" s="8"/>
-      <c r="X495" s="8"/>
-      <c r="Y495" s="8"/>
-    </row>
-    <row r="496" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A496" s="7" t="s">
+      <c r="N496" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O496" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="P496" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q496" s="8"/>
+      <c r="R496" s="8"/>
+      <c r="S496" s="8"/>
+      <c r="T496" s="8"/>
+      <c r="U496" s="8"/>
+      <c r="V496" s="8"/>
+      <c r="W496" s="8"/>
+      <c r="X496" s="8"/>
+      <c r="Y496" s="8"/>
+    </row>
+    <row r="497" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A497" s="7" t="s">
         <v>756</v>
       </c>
-      <c r="B496" s="7" t="s">
+      <c r="B497" s="7" t="s">
         <v>1230</v>
       </c>
-      <c r="C496" s="6" t="s">
+      <c r="C497" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="D496" s="6" t="s">
+      <c r="D497" s="6" t="s">
         <v>782</v>
       </c>
-      <c r="E496" s="6" t="s">
+      <c r="E497" s="6" t="s">
         <v>836</v>
       </c>
-      <c r="F496" s="7" t="s">
+      <c r="F497" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="G496" s="7" t="s">
+      <c r="G497" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="H496" s="7" t="s">
+      <c r="H497" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="I496" s="7" t="s">
+      <c r="I497" s="7" t="s">
         <v>1227</v>
       </c>
-      <c r="J496" s="7" t="s">
+      <c r="J497" s="7" t="s">
         <v>837</v>
       </c>
-      <c r="K496" s="7">
+      <c r="K497" s="7">
         <v>15</v>
       </c>
-      <c r="L496" s="7" t="s">
+      <c r="L497" s="7" t="s">
         <v>1377</v>
       </c>
-      <c r="M496" s="7" t="s">
+      <c r="M497" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="N496" s="28" t="s">
+      <c r="N497" s="28" t="s">
         <v>1367</v>
       </c>
-      <c r="O496" s="7" t="s">
+      <c r="O497" s="7" t="s">
         <v>837</v>
       </c>
-      <c r="P496" s="7"/>
-      <c r="Q496" s="7"/>
-      <c r="R496" s="7"/>
-      <c r="S496" s="7"/>
-      <c r="T496" s="7"/>
-      <c r="U496" s="7"/>
-      <c r="V496" s="7"/>
-      <c r="W496" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="X496" s="7"/>
-      <c r="Y496" s="7"/>
-    </row>
-    <row r="497" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A497" s="14" t="s">
+      <c r="P497" s="7"/>
+      <c r="Q497" s="7"/>
+      <c r="R497" s="7"/>
+      <c r="S497" s="7"/>
+      <c r="T497" s="7"/>
+      <c r="U497" s="7"/>
+      <c r="V497" s="7"/>
+      <c r="W497" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="X497" s="7"/>
+      <c r="Y497" s="7"/>
+    </row>
+    <row r="498" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A498" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B497" s="14" t="s">
+      <c r="B498" s="14" t="s">
         <v>1421</v>
       </c>
-      <c r="C497" s="15" t="s">
+      <c r="C498" s="15" t="s">
         <v>668</v>
       </c>
-      <c r="D497" s="15" t="s">
+      <c r="D498" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="E497" s="14">
+      <c r="E498" s="14">
         <v>74</v>
       </c>
-      <c r="F497" s="14" t="s">
+      <c r="F498" s="14" t="s">
         <v>651</v>
       </c>
-      <c r="G497" s="14" t="s">
+      <c r="G498" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="H497" s="10" t="s">
+      <c r="H498" s="10" t="s">
         <v>1548</v>
       </c>
-      <c r="I497" s="14" t="s">
+      <c r="I498" s="14" t="s">
         <v>1318</v>
       </c>
-      <c r="J497" s="14" t="s">
+      <c r="J498" s="14" t="s">
         <v>1068</v>
       </c>
-      <c r="K497" s="14">
+      <c r="K498" s="14">
         <v>40</v>
       </c>
-      <c r="L497" s="14" t="s">
+      <c r="L498" s="14" t="s">
         <v>1376</v>
       </c>
-      <c r="M497" s="14" t="s">
+      <c r="M498" s="14" t="s">
         <v>1238</v>
       </c>
-      <c r="N497" s="27" t="s">
+      <c r="N498" s="27" t="s">
         <v>1367</v>
       </c>
-      <c r="O497" s="14" t="s">
-        <v>727</v>
-      </c>
-      <c r="P497" s="14"/>
-      <c r="Q497" s="14"/>
-      <c r="R497" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="S497" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="T497" s="14"/>
-      <c r="U497" s="14"/>
-      <c r="V497" s="14"/>
-      <c r="W497" s="14"/>
-      <c r="X497" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y497" s="14" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="498" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A498" s="12" t="s">
+      <c r="O498" s="14" t="s">
+        <v>727</v>
+      </c>
+      <c r="P498" s="14"/>
+      <c r="Q498" s="14"/>
+      <c r="R498" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="S498" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="T498" s="14"/>
+      <c r="U498" s="14"/>
+      <c r="V498" s="14"/>
+      <c r="W498" s="14"/>
+      <c r="X498" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y498" s="14" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="499" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A499" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B498" s="12" t="s">
+      <c r="B499" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="C498" s="13" t="s">
+      <c r="C499" s="13" t="s">
         <v>668</v>
       </c>
-      <c r="D498" s="13" t="s">
+      <c r="D499" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="E498" s="12">
+      <c r="E499" s="12">
         <v>74</v>
       </c>
-      <c r="F498" s="12" t="s">
+      <c r="F499" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="G498" s="12" t="s">
+      <c r="G499" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H498" s="12" t="s">
+      <c r="H499" s="12" t="s">
         <v>853</v>
       </c>
-      <c r="I498" s="12" t="s">
+      <c r="I499" s="12" t="s">
         <v>1374</v>
       </c>
-      <c r="J498" s="12" t="s">
+      <c r="J499" s="12" t="s">
         <v>1068</v>
       </c>
-      <c r="K498" s="12">
+      <c r="K499" s="12">
         <v>100</v>
       </c>
-      <c r="L498" s="12" t="s">
+      <c r="L499" s="12" t="s">
         <v>1376</v>
       </c>
-      <c r="M498" s="12" t="s">
+      <c r="M499" s="12" t="s">
         <v>1236</v>
       </c>
-      <c r="N498" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="O498" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="P498" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q498" s="12"/>
-      <c r="R498" s="12"/>
-      <c r="S498" s="12"/>
-      <c r="T498" s="12"/>
-      <c r="U498" s="12"/>
-      <c r="V498" s="12"/>
-      <c r="W498" s="12"/>
-      <c r="X498" s="12"/>
-      <c r="Y498" s="12"/>
-    </row>
-    <row r="499" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A499" s="10" t="s">
+      <c r="N499" s="25" t="s">
+        <v>727</v>
+      </c>
+      <c r="O499" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="P499" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q499" s="12"/>
+      <c r="R499" s="12"/>
+      <c r="S499" s="12"/>
+      <c r="T499" s="12"/>
+      <c r="U499" s="12"/>
+      <c r="V499" s="12"/>
+      <c r="W499" s="12"/>
+      <c r="X499" s="12"/>
+      <c r="Y499" s="12"/>
+    </row>
+    <row r="500" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A500" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B499" s="10" t="s">
+      <c r="B500" s="10" t="s">
         <v>1357</v>
       </c>
-      <c r="C499" s="10" t="s">
+      <c r="C500" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="D499" s="10" t="s">
+      <c r="D500" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="E499" s="10">
+      <c r="E500" s="10">
         <v>112</v>
       </c>
-      <c r="F499" s="10" t="s">
+      <c r="F500" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="G499" s="10" t="s">
+      <c r="G500" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H499" s="10" t="s">
+      <c r="H500" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="I499" s="10" t="s">
+      <c r="I500" s="10" t="s">
         <v>1318</v>
       </c>
-      <c r="J499" s="10" t="s">
+      <c r="J500" s="10" t="s">
         <v>1050</v>
       </c>
-      <c r="K499" s="10">
+      <c r="K500" s="10">
         <v>15</v>
       </c>
-      <c r="L499" s="10" t="s">
+      <c r="L500" s="10" t="s">
         <v>1376</v>
       </c>
-      <c r="M499" s="10" t="s">
+      <c r="M500" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="N499" s="26" t="s">
+      <c r="N500" s="26" t="s">
         <v>1070</v>
       </c>
-      <c r="O499" s="10" t="s">
+      <c r="O500" s="10" t="s">
         <v>1050</v>
       </c>
-      <c r="P499" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q499" s="10"/>
-      <c r="R499" s="10"/>
-      <c r="S499" s="10"/>
-      <c r="T499" s="10"/>
-      <c r="U499" s="10"/>
-      <c r="V499" s="10"/>
-      <c r="W499" s="10"/>
-      <c r="X499" s="10"/>
-      <c r="Y499" s="10" t="s">
+      <c r="P500" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q500" s="10"/>
+      <c r="R500" s="10"/>
+      <c r="S500" s="10"/>
+      <c r="T500" s="10"/>
+      <c r="U500" s="10"/>
+      <c r="V500" s="10"/>
+      <c r="W500" s="10"/>
+      <c r="X500" s="10"/>
+      <c r="Y500" s="10" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="500" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A500" s="12" t="s">
+    <row r="501" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A501" s="12" t="s">
         <v>1345</v>
       </c>
-      <c r="B500" s="12" t="s">
+      <c r="B501" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="C500" s="12" t="s">
+      <c r="C501" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="D500" s="12" t="s">
+      <c r="D501" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="E500" s="12">
+      <c r="E501" s="12">
         <v>123</v>
       </c>
-      <c r="F500" s="12" t="s">
+      <c r="F501" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="G500" s="12" t="s">
+      <c r="G501" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="H500" s="12" t="s">
+      <c r="H501" s="12" t="s">
         <v>878</v>
       </c>
-      <c r="I500" s="12" t="s">
+      <c r="I501" s="12" t="s">
         <v>1322</v>
       </c>
-      <c r="J500" s="12" t="s">
+      <c r="J501" s="12" t="s">
         <v>1024</v>
       </c>
-      <c r="K500" s="12">
+      <c r="K501" s="12">
         <v>60</v>
       </c>
-      <c r="L500" s="12" t="s">
+      <c r="L501" s="12" t="s">
         <v>1376</v>
       </c>
-      <c r="M500" s="12" t="s">
+      <c r="M501" s="12" t="s">
         <v>1236</v>
       </c>
-      <c r="N500" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="O500" s="24" t="s">
-        <v>727</v>
-      </c>
-      <c r="P500" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q500" s="12"/>
-      <c r="R500" s="12"/>
-      <c r="S500" s="12"/>
-      <c r="T500" s="12"/>
-      <c r="U500" s="12"/>
-      <c r="V500" s="12" t="s">
-        <v>675</v>
-      </c>
-      <c r="W500" s="12"/>
-      <c r="X500" s="12"/>
-      <c r="Y500" s="12"/>
-    </row>
-    <row r="501" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A501" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B501" s="8" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C501" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="D501" s="8" t="s">
-        <v>584</v>
-      </c>
-      <c r="E501" s="8">
-        <v>171</v>
-      </c>
-      <c r="F501" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="G501" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="H501" s="8" t="s">
-        <v>878</v>
-      </c>
-      <c r="I501" s="8" t="s">
-        <v>1323</v>
-      </c>
-      <c r="J501" s="8" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K501" s="8">
-        <v>125</v>
-      </c>
-      <c r="L501" s="8" t="s">
-        <v>1376</v>
-      </c>
-      <c r="M501" s="8" t="s">
-        <v>1236</v>
-      </c>
       <c r="N501" s="24" t="s">
         <v>727</v>
       </c>
       <c r="O501" s="24" t="s">
         <v>727</v>
       </c>
-      <c r="P501" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q501" s="8"/>
-      <c r="R501" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="S501" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="T501" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="U501" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="V501" s="8"/>
-      <c r="W501" s="8"/>
-      <c r="X501" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="Y501" s="8"/>
+      <c r="P501" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q501" s="12"/>
+      <c r="R501" s="12"/>
+      <c r="S501" s="12"/>
+      <c r="T501" s="12"/>
+      <c r="U501" s="12"/>
+      <c r="V501" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="W501" s="12"/>
+      <c r="X501" s="12"/>
+      <c r="Y501" s="12"/>
     </row>
     <row r="502" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="8" t="s">
@@ -45455,7 +45419,7 @@
         <v>878</v>
       </c>
       <c r="I502" s="8" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
       <c r="J502" s="8" t="s">
         <v>1071</v>
@@ -45480,97 +45444,166 @@
       </c>
       <c r="Q502" s="8"/>
       <c r="R502" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="S502" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="T502" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U502" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="V502" s="8"/>
       <c r="W502" s="8"/>
       <c r="X502" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Y502" s="8"/>
     </row>
     <row r="503" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A503" s="7" t="s">
+      <c r="A503" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B503" s="8" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C503" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="D503" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="E503" s="8">
+        <v>171</v>
+      </c>
+      <c r="F503" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="G503" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="H503" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="I503" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J503" s="8" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K503" s="8">
+        <v>125</v>
+      </c>
+      <c r="L503" s="8" t="s">
+        <v>1376</v>
+      </c>
+      <c r="M503" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N503" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="O503" s="24" t="s">
+        <v>727</v>
+      </c>
+      <c r="P503" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q503" s="8"/>
+      <c r="R503" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="S503" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="T503" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="U503" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="V503" s="8"/>
+      <c r="W503" s="8"/>
+      <c r="X503" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y503" s="8"/>
+    </row>
+    <row r="504" spans="1:25" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A504" s="7" t="s">
         <v>1232</v>
       </c>
-      <c r="B503" s="7" t="s">
+      <c r="B504" s="7" t="s">
         <v>1231</v>
       </c>
-      <c r="C503" s="6" t="s">
+      <c r="C504" s="6" t="s">
         <v>1176</v>
       </c>
-      <c r="D503" s="6" t="s">
+      <c r="D504" s="6" t="s">
         <v>1178</v>
       </c>
-      <c r="E503" s="6" t="s">
+      <c r="E504" s="6" t="s">
         <v>1180</v>
       </c>
-      <c r="F503" s="7" t="s">
+      <c r="F504" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="G503" s="7" t="s">
+      <c r="G504" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="H503" s="7" t="s">
+      <c r="H504" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="I503" s="7">
+      <c r="I504" s="7">
         <v>0</v>
       </c>
-      <c r="J503" s="7" t="s">
+      <c r="J504" s="7" t="s">
         <v>1173</v>
       </c>
-      <c r="K503" s="7">
+      <c r="K504" s="7">
         <v>140</v>
       </c>
-      <c r="L503" s="7" t="s">
+      <c r="L504" s="7" t="s">
         <v>1377</v>
       </c>
-      <c r="M503" s="7" t="s">
+      <c r="M504" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="N503" s="28" t="s">
+      <c r="N504" s="28" t="s">
         <v>1481</v>
       </c>
-      <c r="O503" s="7" t="s">
+      <c r="O504" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="P503" s="7"/>
-      <c r="Q503" s="7" t="s">
+      <c r="P504" s="7"/>
+      <c r="Q504" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="R503" s="7"/>
-      <c r="S503" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="T503" s="7"/>
-      <c r="U503" s="7"/>
-      <c r="V503" s="7"/>
-      <c r="W503" s="7"/>
-      <c r="X503" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="Y503" s="7" t="s">
+      <c r="R504" s="7"/>
+      <c r="S504" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="T504" s="7"/>
+      <c r="U504" s="7"/>
+      <c r="V504" s="7"/>
+      <c r="W504" s="7"/>
+      <c r="X504" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="Y504" s="7" t="s">
         <v>675</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y503" xr:uid="{8CDA5EAF-A655-4519-9C43-6E6BE0DBE4DA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y503">
-      <sortCondition ref="A1:A503"/>
+  <autoFilter ref="A1:Y504" xr:uid="{8CDA5EAF-A655-4519-9C43-6E6BE0DBE4DA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y504">
+      <sortCondition ref="A1:A504"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y503">
-    <sortCondition ref="A93:A503"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y504">
+    <sortCondition ref="A93:A504"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -45578,156 +45611,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7680950-4FA9-43D4-B93A-6F2F56B6CBD1}">
-  <dimension ref="A1:Z2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>3794</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53" t="s">
-        <v>647</v>
-      </c>
-      <c r="E1" s="53" t="s">
-        <v>646</v>
-      </c>
-      <c r="F1" s="53" t="s">
-        <v>3795</v>
-      </c>
-      <c r="G1" s="53" t="s">
-        <v>650</v>
-      </c>
-      <c r="H1" s="53" t="s">
-        <v>1258</v>
-      </c>
-      <c r="I1" s="53" t="s">
-        <v>3796</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>1225</v>
-      </c>
-      <c r="K1" s="53" t="s">
-        <v>792</v>
-      </c>
-      <c r="L1" s="53" t="s">
-        <v>3797</v>
-      </c>
-      <c r="M1" s="53" t="s">
-        <v>3798</v>
-      </c>
-      <c r="N1" s="53" t="s">
-        <v>1237</v>
-      </c>
-      <c r="O1" s="53" t="s">
-        <v>1250</v>
-      </c>
-      <c r="P1" s="53" t="s">
-        <v>3799</v>
-      </c>
-      <c r="Q1" s="53" t="s">
-        <v>739</v>
-      </c>
-      <c r="R1" s="53" t="s">
-        <v>3800</v>
-      </c>
-      <c r="S1" s="53" t="s">
-        <v>3801</v>
-      </c>
-      <c r="T1" s="53" t="s">
-        <v>3802</v>
-      </c>
-      <c r="U1" s="53" t="s">
-        <v>3803</v>
-      </c>
-      <c r="V1" s="53" t="s">
-        <v>3804</v>
-      </c>
-      <c r="W1" s="53" t="s">
-        <v>3805</v>
-      </c>
-      <c r="X1" s="53" t="s">
-        <v>745</v>
-      </c>
-      <c r="Y1" s="53" t="s">
-        <v>3806</v>
-      </c>
-      <c r="Z1" s="53" t="s">
-        <v>3807</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="53" t="s">
-        <v>3808</v>
-      </c>
-      <c r="B2" s="55" t="s">
-        <v>3809</v>
-      </c>
-      <c r="C2" s="55" t="s">
-        <v>3810</v>
-      </c>
-      <c r="D2" s="54">
-        <v>-1571666861657710</v>
-      </c>
-      <c r="E2" s="54">
-        <v>4326851318044370</v>
-      </c>
-      <c r="F2" s="53">
-        <v>193</v>
-      </c>
-      <c r="G2" s="53" t="s">
-        <v>655</v>
-      </c>
-      <c r="H2" s="53" t="s">
-        <v>663</v>
-      </c>
-      <c r="I2" s="53" t="s">
-        <v>853</v>
-      </c>
-      <c r="J2" s="53" t="s">
-        <v>1322</v>
-      </c>
-      <c r="K2" s="53" t="s">
-        <v>3587</v>
-      </c>
-      <c r="L2" s="53">
-        <v>450</v>
-      </c>
-      <c r="M2" s="53" t="s">
-        <v>1376</v>
-      </c>
-      <c r="N2" s="53" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="53" t="s">
-        <v>727</v>
-      </c>
-      <c r="P2" s="53" t="s">
-        <v>727</v>
-      </c>
-      <c r="Q2" s="53" t="s">
-        <v>675</v>
-      </c>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53" t="s">
-        <v>676</v>
-      </c>
-      <c r="Z2" s="53"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15FA49C-AA6C-4C9D-BD3F-DDB2E499D207}">
   <dimension ref="A1:AK1191"/>
   <sheetFormatPr defaultColWidth="63.33203125" defaultRowHeight="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
